--- a/Data_Table/스테이지 테이블.xlsx
+++ b/Data_Table/스테이지 테이블.xlsx
@@ -7,11 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Boss" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Boss_Line" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Atk_Type" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Situation_Type" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column_Desc" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stage" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Boss" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Boss_Line" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Atk_Type" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Situation_Type" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column_Desc" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,6 +426,1006 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>층</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>방 수</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>적정 전투력</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>물건 체력 배율</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>치즈 배율</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>계단 벽 배율</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>일반 벽 배율</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>추가 제한시간</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>메모</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>floor</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>rooms</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>pow_need</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>item_hp</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>cheese</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>wall_stairs</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>wall_normal</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>time_add</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="1" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>552</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>762</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>1050</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>1450</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1" t="inlineStr">
+        <is>
+          <t>보스 층</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>2760</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>11.39</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>3810</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>17.09</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="1" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>5260</v>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>25.63</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>7260</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>38.44</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1" t="inlineStr">
+        <is>
+          <t>보스 층</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>25.05</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>57.67</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>13800</v>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>34.57</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="1" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>19100</v>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="1" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>26300</v>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>65.83</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>195</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>36300</v>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>90.84999999999999</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>292</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="1" t="inlineStr">
+        <is>
+          <t>보스 층</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>50100</v>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>125</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>438</v>
+      </c>
+      <c r="F19" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="G19" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="1" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>69200</v>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>173</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>657</v>
+      </c>
+      <c r="F20" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="G20" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="1" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>95500</v>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>239</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>985</v>
+      </c>
+      <c r="F21" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="G21" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="1" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>132000</v>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>329</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>1480</v>
+      </c>
+      <c r="F22" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="G22" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="1" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>182000</v>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>455</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>2220</v>
+      </c>
+      <c r="F23" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="G23" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="1" t="inlineStr">
+        <is>
+          <t>보스 층</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>251000</v>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>627</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>3330</v>
+      </c>
+      <c r="F24" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="G24" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="1" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C25" s="1" t="n">
+        <v>346000</v>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>866</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>4990</v>
+      </c>
+      <c r="F25" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="G25" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H25" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="1" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C26" s="1" t="n">
+        <v>478000</v>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>1190</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>7480</v>
+      </c>
+      <c r="F26" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="G26" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="1" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>660000</v>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>1650</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>11200</v>
+      </c>
+      <c r="F27" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="G27" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H27" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="1" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>910000</v>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>2280</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>16800</v>
+      </c>
+      <c r="F28" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="G28" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="1" t="inlineStr">
+        <is>
+          <t>보스 층</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C29" s="1" t="n">
+        <v>1260000</v>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>3140</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>25300</v>
+      </c>
+      <c r="F29" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="G29" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="1" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C30" s="1" t="n">
+        <v>1730000</v>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>4330</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>37900</v>
+      </c>
+      <c r="F30" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="G30" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="1" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C31" s="1" t="n">
+        <v>2390000</v>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>5980</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>56800</v>
+      </c>
+      <c r="F31" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="G31" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="1" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C32" s="1" t="n">
+        <v>3300000</v>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>8250</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>85200</v>
+      </c>
+      <c r="F32" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="G32" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H32" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="1" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="C33" s="1" t="n">
+        <v>4560000</v>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>11400</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>128000</v>
+      </c>
+      <c r="F33" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="G33" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H33" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="1" t="inlineStr">
+        <is>
+          <t>보스 층</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -757,7 +1758,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1023,7 +2024,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1081,108 +2082,6 @@
       <c r="B4" s="1" t="inlineStr">
         <is>
           <t>0.5초 웅크림(화난 얼굴·덜덜) → 가장 가까운 쥐 쪽으로 높이 점프 → 착지: 공격 반경 안 쥐 기절(공격 기절 초)·데굴, 물건 날아감, 쿠웅!</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>상황</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>정의</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>situation</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>desc</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>계단 방이 열려 전투 시작할 때 (배너 부제 · 말풍선)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>Attack</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>공격 직전</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Hit</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>쥐에게 맞을 때 가끔</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>Down</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>쓰러질 때</t>
         </is>
       </c>
     </row>
@@ -1201,6 +2100,108 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>상황</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>정의</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>situation</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Intro</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>계단 방이 열려 전투 시작할 때 (배너 부제 · 말풍선)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>공격 직전</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>쥐에게 맞을 때 가끔</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>쓰러질 때</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -1288,6 +2289,78 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>pow_need</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>Stage: 적정 전투력(찍찍!!) = 무리 공격력 합. 모자라면 벽 피해 = (전투력÷적정)^지수 (계단 방 1.5 · 일반 0.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>item_hp</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>Stage: 물건·사람·고양이 체력 = 기본(12 × 물건 체력 배율) × 이 값 × 3.6^(방 거리 × 0.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>cheese</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>Stage: 물건·사람·고양이·보스 치즈 = 기본(3 × 치즈 배율) × 이 값 × 1.8^(방 거리 × 0.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>wall_stairs / wall_normal</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>Stage: 벽 체력 = 적정 전투력 × 이 값 (일반 벽은 × (1 + 0.25 × 시작 방 거리))</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>time_add</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>Stage: 층 제한시간에 더하는 초 (기본 190 + 35 × 방 수 + 보스 층 90)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Stage 생성</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>Tools/gen_stage_table.py 로 생성 (곡선 숫자를 바꾸고 다시 실행)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data_Table/스테이지 테이블.xlsx
+++ b/Data_Table/스테이지 테이블.xlsx
@@ -1426,25 +1426,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="60" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="60" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1465,65 +1466,70 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>리그</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>등장 층</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>공격 타입</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>두 번째 공격</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>두 번째 공격 확률</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>테마 색</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>크기 배율</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>충돌 반경 배율</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>체력 (적정 전투력 × 초)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>치즈 배율</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>걷기 속도</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>공격 간격 최소</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>공격 간격 최대</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>공격 반경</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>공격 기절 (초)</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
@@ -1547,65 +1553,70 @@
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
+          <t>rig</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
           <t>floor</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>atk_type</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>atk2_type</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>atk2_chance</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>color</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>scale</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>radius_mul</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t>hp_pow_sec</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>cheese_mul</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="N2" s="1" t="inlineStr">
         <is>
           <t>move_speed</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="O2" s="1" t="inlineStr">
         <is>
           <t>atk_cd_min</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="P2" s="1" t="inlineStr">
         <is>
           <t>atk_cd_max</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t>atk_radius</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t>atk_stun</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
+      <c r="Q2" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1629,65 +1640,70 @@
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>enum</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="J3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="H3" s="1" t="inlineStr">
+      <c r="K3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="L3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
+      <c r="M3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="K3" s="1" t="inlineStr">
+      <c r="N3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="L3" s="1" t="inlineStr">
+      <c r="O3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="M3" s="1" t="inlineStr">
+      <c r="P3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="N3" s="1" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="O3" s="1" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="P3" s="1" t="inlineStr">
+      <c r="Q3" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1707,49 +1723,391 @@
           <t>boss_chief</t>
         </is>
       </c>
-      <c r="D4" s="1" t="n">
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="E4" s="1" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>Stomp</t>
         </is>
       </c>
-      <c r="F4" s="1" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
         <is>
           <t>#8fb3c7</t>
         </is>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="J4" s="1" t="n">
         <v>2.8</v>
       </c>
-      <c r="H4" s="1" t="n">
+      <c r="K4" s="1" t="n">
         <v>2.8</v>
       </c>
-      <c r="I4" s="1" t="n">
+      <c r="L4" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="J4" s="1" t="n">
+      <c r="M4" s="1" t="n">
         <v>300</v>
       </c>
-      <c r="K4" s="1" t="n">
+      <c r="N4" s="1" t="n">
         <v>95</v>
       </c>
-      <c r="L4" s="1" t="n">
+      <c r="O4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="M4" s="1" t="n">
+      <c r="P4" s="1" t="n">
         <v>4.5</v>
       </c>
-      <c r="N4" s="1" t="n">
+      <c r="Q4" s="1" t="inlineStr">
+        <is>
+          <t>5층 보스. 쥐 무리 쪽으로 쿵쿵 걸어와 점프 내려찍기</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>95002</v>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>광기의 수석 연구원</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>boss_mad</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>Flask</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t>#9dd5a8</t>
+        </is>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L5" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="M5" s="1" t="n">
         <v>300</v>
       </c>
-      <c r="O4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="P4" s="1" t="inlineStr">
-        <is>
-          <t>5층 보스. 쥐 무리 쪽으로 쿵쿵 걸어와 점프 내려찍기 (반경 안 쥐 기절·데굴, 물건 날아감)</t>
+      <c r="N5" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="O5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="P5" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q5" s="1" t="inlineStr">
+        <is>
+          <t>10층 보스. 초록 약품 플라스크를 3개씩 던짐 (떨어진 곳 쥐 기절)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>95003</v>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>연구소장</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>boss_director</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>Swing</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>#d9786a</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="O6" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="P6" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q6" s="1" t="inlineStr">
+        <is>
+          <t>15층 보스. 주먹 휘두르기로 주변 쥐를 날림, 두 번에 한 번 경비원 호출</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>95004</v>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>실험체 제로 (거대 메인쿤)</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>gym</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>Cat</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>Pounce</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>Hairball</t>
+        </is>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
+        <is>
+          <t>#e39a5a</t>
+        </is>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q7" s="1" t="inlineStr">
+        <is>
+          <t>20층 보스. 거대 고양이: 덮치기 · 헤어볼 투척</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>95005</v>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>대마법사 마녀 고양이</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>fire</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>Cat</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>Fireball</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>Pounce</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I8" s="1" t="inlineStr">
+        <is>
+          <t>#cdb4db</t>
+        </is>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="N8" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="O8" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q8" s="1" t="inlineStr">
+        <is>
+          <t>25층 보스. 불덩이 5개 · 덮치기</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>95006</v>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>우주 고양이 사령관</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>space</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>Cat</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="inlineStr">
+        <is>
+          <t>Pounce</t>
+        </is>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I9" s="1" t="inlineStr">
+        <is>
+          <t>#a9d3dc</t>
+        </is>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="N9" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="O9" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q9" s="1" t="inlineStr">
+        <is>
+          <t>30층 보스. 무중력 파동 (주변 쥐가 떠올랐다 떨어지며 기절) · 덮치기. 30층 뒤로는 5층 보스부터 다시 반복</t>
         </is>
       </c>
     </row>
@@ -1764,7 +2122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2016,6 +2374,798 @@
       <c r="D13" s="1" t="inlineStr">
         <is>
           <t>으아아아~!</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>96011</v>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>95002</v>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>Intro</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>내 실험체들이 탈출해?!</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>96012</v>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>95002</v>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>실험체는 실험실로!</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>96013</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>95002</v>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>이거나 먹어라!</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>96014</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>95002</v>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>내 연구가!</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>96015</v>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>95002</v>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>으윽, 시약이!</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>96016</v>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>95002</v>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>감히!</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>96017</v>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>95002</v>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>내 논문이이이~!</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>96018</v>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>95002</v>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t>실험 실패다아~!</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>96019</v>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>95003</v>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>Intro</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="inlineStr">
+        <is>
+          <t>예산 삭감이다!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>96020</v>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>95003</v>
+      </c>
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="inlineStr">
+        <is>
+          <t>예산 삭감!</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>96021</v>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>95003</v>
+      </c>
+      <c r="C24" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="inlineStr">
+        <is>
+          <t>해고다!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>96023</v>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>95003</v>
+      </c>
+      <c r="C25" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="inlineStr">
+        <is>
+          <t>내 양복이!</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>96024</v>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>95003</v>
+      </c>
+      <c r="C26" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="inlineStr">
+        <is>
+          <t>이건 감사 대상이야!</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>96025</v>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>95003</v>
+      </c>
+      <c r="C27" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="inlineStr">
+        <is>
+          <t>아얏!</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>96026</v>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>95003</v>
+      </c>
+      <c r="C28" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="inlineStr">
+        <is>
+          <t>퇴직금은?!</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>96027</v>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>95003</v>
+      </c>
+      <c r="C29" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="inlineStr">
+        <is>
+          <t>기억해 두겠다아아~!</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>96028</v>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>95004</v>
+      </c>
+      <c r="C30" s="1" t="inlineStr">
+        <is>
+          <t>Intro</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="inlineStr">
+        <is>
+          <t>냐아아아옹!!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>96029</v>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>95004</v>
+      </c>
+      <c r="C31" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="inlineStr">
+        <is>
+          <t>냐아앙!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>96030</v>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>95004</v>
+      </c>
+      <c r="C32" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="inlineStr">
+        <is>
+          <t>크르르…</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>96031</v>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>95004</v>
+      </c>
+      <c r="C33" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="inlineStr">
+        <is>
+          <t>캑… 캑캑…</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>96032</v>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>95004</v>
+      </c>
+      <c r="C34" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="inlineStr">
+        <is>
+          <t>우웨엑(헤어볼)!</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>96033</v>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>95004</v>
+      </c>
+      <c r="C35" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="inlineStr">
+        <is>
+          <t>캬악!</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>96034</v>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>95004</v>
+      </c>
+      <c r="C36" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="inlineStr">
+        <is>
+          <t>냐앙?!</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>96035</v>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>95004</v>
+      </c>
+      <c r="C37" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D37" s="1" t="inlineStr">
+        <is>
+          <t>하악!</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>96036</v>
+      </c>
+      <c r="B38" s="1" t="n">
+        <v>95004</v>
+      </c>
+      <c r="C38" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="inlineStr">
+        <is>
+          <t>냐아아아~!</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>96037</v>
+      </c>
+      <c r="B39" s="1" t="n">
+        <v>95004</v>
+      </c>
+      <c r="C39" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D39" s="1" t="inlineStr">
+        <is>
+          <t>냐옹…(기절)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>96038</v>
+      </c>
+      <c r="B40" s="1" t="n">
+        <v>95005</v>
+      </c>
+      <c r="C40" s="1" t="inlineStr">
+        <is>
+          <t>Intro</t>
+        </is>
+      </c>
+      <c r="D40" s="1" t="inlineStr">
+        <is>
+          <t>냐브라카다브라!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>96039</v>
+      </c>
+      <c r="B41" s="1" t="n">
+        <v>95005</v>
+      </c>
+      <c r="C41" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D41" s="1" t="inlineStr">
+        <is>
+          <t>냐브라카다브라!</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>96040</v>
+      </c>
+      <c r="B42" s="1" t="n">
+        <v>95005</v>
+      </c>
+      <c r="C42" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D42" s="1" t="inlineStr">
+        <is>
+          <t>불타라 냥!</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>96041</v>
+      </c>
+      <c r="B43" s="1" t="n">
+        <v>95005</v>
+      </c>
+      <c r="C43" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D43" s="1" t="inlineStr">
+        <is>
+          <t>냐아앙!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>96042</v>
+      </c>
+      <c r="B44" s="1" t="n">
+        <v>95005</v>
+      </c>
+      <c r="C44" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D44" s="1" t="inlineStr">
+        <is>
+          <t>내 모자가!</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>96043</v>
+      </c>
+      <c r="B45" s="1" t="n">
+        <v>95005</v>
+      </c>
+      <c r="C45" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="inlineStr">
+        <is>
+          <t>캬악!</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>96044</v>
+      </c>
+      <c r="B46" s="1" t="n">
+        <v>95005</v>
+      </c>
+      <c r="C46" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D46" s="1" t="inlineStr">
+        <is>
+          <t>주문이 꼬였다냥!</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>96045</v>
+      </c>
+      <c r="B47" s="1" t="n">
+        <v>95005</v>
+      </c>
+      <c r="C47" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D47" s="1" t="inlineStr">
+        <is>
+          <t>마법이 풀렸다냐아~!</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>96046</v>
+      </c>
+      <c r="B48" s="1" t="n">
+        <v>95005</v>
+      </c>
+      <c r="C48" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D48" s="1" t="inlineStr">
+        <is>
+          <t>냐아아아~!</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>96047</v>
+      </c>
+      <c r="B49" s="1" t="n">
+        <v>95006</v>
+      </c>
+      <c r="C49" s="1" t="inlineStr">
+        <is>
+          <t>Intro</t>
+        </is>
+      </c>
+      <c r="D49" s="1" t="inlineStr">
+        <is>
+          <t>이 연구소는 우주 냥국이 접수한다!</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>96048</v>
+      </c>
+      <c r="B50" s="1" t="n">
+        <v>95006</v>
+      </c>
+      <c r="C50" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D50" s="1" t="inlineStr">
+        <is>
+          <t>중력 해제 냥!</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>96049</v>
+      </c>
+      <c r="B51" s="1" t="n">
+        <v>95006</v>
+      </c>
+      <c r="C51" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D51" s="1" t="inlineStr">
+        <is>
+          <t>둥실둥실 냥~</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>96050</v>
+      </c>
+      <c r="B52" s="1" t="n">
+        <v>95006</v>
+      </c>
+      <c r="C52" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D52" s="1" t="inlineStr">
+        <is>
+          <t>냐아앙!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>96051</v>
+      </c>
+      <c r="B53" s="1" t="n">
+        <v>95006</v>
+      </c>
+      <c r="C53" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D53" s="1" t="inlineStr">
+        <is>
+          <t>헬멧에 금이!</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>96052</v>
+      </c>
+      <c r="B54" s="1" t="n">
+        <v>95006</v>
+      </c>
+      <c r="C54" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D54" s="1" t="inlineStr">
+        <is>
+          <t>캬악!</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>96053</v>
+      </c>
+      <c r="B55" s="1" t="n">
+        <v>95006</v>
+      </c>
+      <c r="C55" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D55" s="1" t="inlineStr">
+        <is>
+          <t>지구 쥐 주제에!</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>96054</v>
+      </c>
+      <c r="B56" s="1" t="n">
+        <v>95006</v>
+      </c>
+      <c r="C56" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D56" s="1" t="inlineStr">
+        <is>
+          <t>우주로 돌아간다냐아~!</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>96055</v>
+      </c>
+      <c r="B57" s="1" t="n">
+        <v>95006</v>
+      </c>
+      <c r="C57" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D57" s="1" t="inlineStr">
+        <is>
+          <t>냐아아아~!</t>
         </is>
       </c>
     </row>
@@ -2030,11 +3180,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2048,6 +3203,31 @@
           <t>정의</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>반경</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>기절 (초)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>개수</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>웅크림 (초)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>공격 길이 (초)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -2060,6 +3240,31 @@
           <t>desc</t>
         </is>
       </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>radius</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>stun</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>windup</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>dur</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -2072,17 +3277,246 @@
           <t>-</t>
         </is>
       </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>없음 (두 번째 공격 없음)</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
           <t>Stomp</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>0.5초 웅크림(화난 얼굴·덜덜) → 가장 가까운 쥐 쪽으로 높이 점프 → 착지: 공격 반경 안 쥐 기절(공격 기절 초)·데굴, 물건 날아감, 쿠웅!</t>
-        </is>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>웅크림(화난 얼굴·덜덜) → 가장 가까운 쥐 쪽으로 높이 점프 → 착지: 반경 안 쥐 기절·데굴, 물건 날아감, 쿠웅!</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Pounce</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>고양이: 웅크렸다가 쥐 떼 한가운데로 덮치기 (Stomp 보다 낮고 빠른 점프), 착지 판정은 Stomp 와 같음</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>280</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Flask</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>덜덜 → 화면 속 쥐 쪽으로 플라스크를 개수만큼 0.22초 간격으로 던짐. 떨어진 곳 반경 안 쥐 기절 + 초록 얼룩</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Hairball</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>Flask 와 같음, 헤어볼 (털뭉치 팝업)</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Fireball</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>Flask 와 같음, 불덩이</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Swing</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>주먹 휘두르기: 반경 안 쥐 기절·날림. 두 번에 한 번 경비원(개수)명 호출</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>280</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>무중력 파동: 반경 안 쥐가 둥실 떠올랐다 떨어지며 기절, 물건도 떠오름</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>360</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>
@@ -2198,7 +3632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2361,6 +3795,42 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>rig</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>Boss: Human = 사람 리그 (사람 그림 모음 code_id) · Cat = 고양이 리그 (고양이 그림 모음 code_id, 크기 = 고양이 몸길이 × scale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>atk2_type / atk2_chance</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>Boss: 공격할 때 이 확률로 두 번째 공격 (None = 없음). 공격 수치는 Atk_Type 시트</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>보스 반복</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>보스 층(5층마다)에 floor 가 같은 보스. 표에 없는 보스 층은 5층 보스부터 순서대로 반복</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data_Table/스테이지 테이블.xlsx
+++ b/Data_Table/스테이지 테이블.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -598,10 +598,10 @@
         <v>1</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>3</v>
+        <v>46.88</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>1.2</v>
+        <v>46.88</v>
       </c>
       <c r="H4" s="1" t="n">
         <v>0</v>
@@ -625,10 +625,10 @@
         <v>1.5</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>3.6</v>
+        <v>37.21</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>1.2</v>
+        <v>37.21</v>
       </c>
       <c r="H5" s="1" t="n">
         <v>0</v>
@@ -652,10 +652,10 @@
         <v>2.25</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>4.2</v>
+        <v>39.26</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>1.2</v>
+        <v>39.26</v>
       </c>
       <c r="H6" s="1" t="n">
         <v>0</v>
@@ -679,10 +679,10 @@
         <v>3.38</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>4.8</v>
+        <v>21.45</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>1.2</v>
+        <v>10.73</v>
       </c>
       <c r="H7" s="1" t="n">
         <v>0</v>
@@ -706,10 +706,10 @@
         <v>5.06</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>5.4</v>
+        <v>4.51</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>1.2</v>
+        <v>2.26</v>
       </c>
       <c r="H8" s="1" t="n">
         <v>0</v>
@@ -737,10 +737,10 @@
         <v>7.59</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>6</v>
+        <v>9.15</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>1.2</v>
+        <v>3.05</v>
       </c>
       <c r="H9" s="1" t="n">
         <v>0</v>
@@ -764,10 +764,10 @@
         <v>11.39</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>6.6</v>
+        <v>8.82</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>1.2</v>
+        <v>2.94</v>
       </c>
       <c r="H10" s="1" t="n">
         <v>0</v>
@@ -791,10 +791,10 @@
         <v>17.09</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>7.2</v>
+        <v>4.54</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="H11" s="1" t="n">
         <v>0</v>
@@ -818,10 +818,10 @@
         <v>25.63</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>7.8</v>
+        <v>7.64</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>1.2</v>
+        <v>3.82</v>
       </c>
       <c r="H12" s="1" t="n">
         <v>0</v>
@@ -845,10 +845,10 @@
         <v>38.44</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>8.4</v>
+        <v>7.32</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>1.2</v>
+        <v>2.44</v>
       </c>
       <c r="H13" s="1" t="n">
         <v>0</v>
@@ -876,10 +876,10 @@
         <v>57.67</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>9</v>
+        <v>1.27</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="H14" s="1" t="n">
         <v>0</v>
@@ -903,10 +903,10 @@
         <v>86.5</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>9.6</v>
+        <v>3.73</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>1.2</v>
+        <v>1.86</v>
       </c>
       <c r="H15" s="1" t="n">
         <v>0</v>
@@ -930,10 +930,10 @@
         <v>130</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>10</v>
+        <v>7.56</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>1.2</v>
+        <v>1.89</v>
       </c>
       <c r="H16" s="1" t="n">
         <v>0</v>
@@ -957,10 +957,10 @@
         <v>195</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>10</v>
+        <v>7.29</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>1.2</v>
+        <v>2.43</v>
       </c>
       <c r="H17" s="1" t="n">
         <v>0</v>
@@ -984,10 +984,10 @@
         <v>292</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>10</v>
+        <v>3.09</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="H18" s="1" t="n">
         <v>0</v>
@@ -1015,10 +1015,10 @@
         <v>438</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>10</v>
+        <v>35.77</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>1.2</v>
+        <v>35.77</v>
       </c>
       <c r="H19" s="1" t="n">
         <v>0</v>
@@ -1042,10 +1042,10 @@
         <v>657</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>10</v>
+        <v>3.67</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="H20" s="1" t="n">
         <v>0</v>
@@ -1069,10 +1069,10 @@
         <v>985</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>10</v>
+        <v>6.73</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>1.2</v>
+        <v>1.68</v>
       </c>
       <c r="H21" s="1" t="n">
         <v>0</v>
@@ -1096,10 +1096,10 @@
         <v>1480</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>10</v>
+        <v>9.57</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>1.2</v>
+        <v>3.19</v>
       </c>
       <c r="H22" s="1" t="n">
         <v>0</v>
@@ -1123,10 +1123,10 @@
         <v>2220</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>10</v>
+        <v>13.36</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>1.2</v>
+        <v>4.45</v>
       </c>
       <c r="H23" s="1" t="n">
         <v>0</v>
@@ -1154,10 +1154,10 @@
         <v>3330</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>10</v>
+        <v>5.12</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="H24" s="1" t="n">
         <v>0</v>
@@ -1181,10 +1181,10 @@
         <v>4990</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>10</v>
+        <v>26.83</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>1.2</v>
+        <v>8.94</v>
       </c>
       <c r="H25" s="1" t="n">
         <v>0</v>
@@ -1208,10 +1208,10 @@
         <v>7480</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>10</v>
+        <v>9.93</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>1.2</v>
+        <v>3.31</v>
       </c>
       <c r="H26" s="1" t="n">
         <v>0</v>
@@ -1235,10 +1235,10 @@
         <v>11200</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>10</v>
+        <v>21.01</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>1.2</v>
+        <v>7</v>
       </c>
       <c r="H27" s="1" t="n">
         <v>0</v>
@@ -1262,10 +1262,10 @@
         <v>16800</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>10</v>
+        <v>6.95</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>1.2</v>
+        <v>1.74</v>
       </c>
       <c r="H28" s="1" t="n">
         <v>0</v>
@@ -1293,10 +1293,10 @@
         <v>25300</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>10</v>
+        <v>7.94</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="H29" s="1" t="n">
         <v>0</v>
@@ -1320,10 +1320,10 @@
         <v>37900</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>10</v>
+        <v>7.94</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>1.2</v>
+        <v>2.65</v>
       </c>
       <c r="H30" s="1" t="n">
         <v>0</v>
@@ -1347,10 +1347,10 @@
         <v>56800</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>10</v>
+        <v>7.94</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="H31" s="1" t="n">
         <v>0</v>
@@ -1374,10 +1374,10 @@
         <v>85200</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>10</v>
+        <v>7.94</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>1.2</v>
+        <v>2.65</v>
       </c>
       <c r="H32" s="1" t="n">
         <v>0</v>
@@ -1401,15 +1401,571 @@
         <v>128000</v>
       </c>
       <c r="F33" s="1" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="G33" s="1" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="H33" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="1" t="inlineStr">
+        <is>
+          <t>보스 층</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C34" s="1" t="n">
+        <v>6290000</v>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>15700</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>192000</v>
+      </c>
+      <c r="F34" s="1" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="G34" s="1" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="H34" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="1" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>8680000</v>
+      </c>
+      <c r="D35" s="1" t="n">
+        <v>21700</v>
+      </c>
+      <c r="E35" s="1" t="n">
+        <v>288000</v>
+      </c>
+      <c r="F35" s="1" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="G35" s="1" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H35" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="1" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="D36" s="1" t="n">
+        <v>29900</v>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>431000</v>
+      </c>
+      <c r="F36" s="1" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="G36" s="1" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H36" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="1" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>16500000</v>
+      </c>
+      <c r="D37" s="1" t="n">
+        <v>41300</v>
+      </c>
+      <c r="E37" s="1" t="n">
+        <v>647000</v>
+      </c>
+      <c r="F37" s="1" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="G37" s="1" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="H37" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="1" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B38" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="G33" s="1" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H33" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="1" t="inlineStr">
+      <c r="C38" s="1" t="n">
+        <v>22800000</v>
+      </c>
+      <c r="D38" s="1" t="n">
+        <v>57000</v>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>971000</v>
+      </c>
+      <c r="F38" s="1" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="G38" s="1" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="H38" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="1" t="inlineStr">
+        <is>
+          <t>보스 층</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B39" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C39" s="1" t="n">
+        <v>31500000</v>
+      </c>
+      <c r="D39" s="1" t="n">
+        <v>78700</v>
+      </c>
+      <c r="E39" s="1" t="n">
+        <v>1460000</v>
+      </c>
+      <c r="F39" s="1" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="G39" s="1" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="H39" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="1" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B40" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C40" s="1" t="n">
+        <v>43400000</v>
+      </c>
+      <c r="D40" s="1" t="n">
+        <v>109000</v>
+      </c>
+      <c r="E40" s="1" t="n">
+        <v>2180000</v>
+      </c>
+      <c r="F40" s="1" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="G40" s="1" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H40" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="1" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B41" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C41" s="1" t="n">
+        <v>59900000</v>
+      </c>
+      <c r="D41" s="1" t="n">
+        <v>150000</v>
+      </c>
+      <c r="E41" s="1" t="n">
+        <v>3280000</v>
+      </c>
+      <c r="F41" s="1" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="G41" s="1" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="H41" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="1" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="B42" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C42" s="1" t="n">
+        <v>82700000</v>
+      </c>
+      <c r="D42" s="1" t="n">
+        <v>207000</v>
+      </c>
+      <c r="E42" s="1" t="n">
+        <v>4910000</v>
+      </c>
+      <c r="F42" s="1" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="G42" s="1" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="H42" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="1" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B43" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="C43" s="1" t="n">
+        <v>114000000</v>
+      </c>
+      <c r="D43" s="1" t="n">
+        <v>285000</v>
+      </c>
+      <c r="E43" s="1" t="n">
+        <v>7370000</v>
+      </c>
+      <c r="F43" s="1" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="G43" s="1" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="H43" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="1" t="inlineStr">
+        <is>
+          <t>보스 층</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="B44" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C44" s="1" t="n">
+        <v>157000000</v>
+      </c>
+      <c r="D44" s="1" t="n">
+        <v>394000</v>
+      </c>
+      <c r="E44" s="1" t="n">
+        <v>11100000</v>
+      </c>
+      <c r="F44" s="1" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="G44" s="1" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="H44" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="1" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="B45" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C45" s="1" t="n">
+        <v>217000000</v>
+      </c>
+      <c r="D45" s="1" t="n">
+        <v>543000</v>
+      </c>
+      <c r="E45" s="1" t="n">
+        <v>16600000</v>
+      </c>
+      <c r="F45" s="1" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="G45" s="1" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="H45" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="1" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="B46" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C46" s="1" t="n">
+        <v>300000000</v>
+      </c>
+      <c r="D46" s="1" t="n">
+        <v>750000</v>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>24900000</v>
+      </c>
+      <c r="F46" s="1" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="G46" s="1" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="H46" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="1" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="B47" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C47" s="1" t="n">
+        <v>414000000</v>
+      </c>
+      <c r="D47" s="1" t="n">
+        <v>1030000</v>
+      </c>
+      <c r="E47" s="1" t="n">
+        <v>37300000</v>
+      </c>
+      <c r="F47" s="1" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="G47" s="1" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="H47" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="1" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="B48" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="C48" s="1" t="n">
+        <v>571000000</v>
+      </c>
+      <c r="D48" s="1" t="n">
+        <v>1430000</v>
+      </c>
+      <c r="E48" s="1" t="n">
+        <v>56000000</v>
+      </c>
+      <c r="F48" s="1" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="G48" s="1" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H48" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="1" t="inlineStr">
+        <is>
+          <t>보스 층</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="B49" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C49" s="1" t="n">
+        <v>788000000</v>
+      </c>
+      <c r="D49" s="1" t="n">
+        <v>1970000</v>
+      </c>
+      <c r="E49" s="1" t="n">
+        <v>84000000</v>
+      </c>
+      <c r="F49" s="1" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="G49" s="1" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="H49" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="1" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>47</v>
+      </c>
+      <c r="B50" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C50" s="1" t="n">
+        <v>1090000000</v>
+      </c>
+      <c r="D50" s="1" t="n">
+        <v>2720000</v>
+      </c>
+      <c r="E50" s="1" t="n">
+        <v>126000000</v>
+      </c>
+      <c r="F50" s="1" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="G50" s="1" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="H50" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="1" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B51" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C51" s="1" t="n">
+        <v>1500000000</v>
+      </c>
+      <c r="D51" s="1" t="n">
+        <v>3750000</v>
+      </c>
+      <c r="E51" s="1" t="n">
+        <v>189000000</v>
+      </c>
+      <c r="F51" s="1" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="G51" s="1" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="H51" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="1" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>49</v>
+      </c>
+      <c r="B52" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C52" s="1" t="n">
+        <v>2070000000</v>
+      </c>
+      <c r="D52" s="1" t="n">
+        <v>5180000</v>
+      </c>
+      <c r="E52" s="1" t="n">
+        <v>283000000</v>
+      </c>
+      <c r="F52" s="1" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="G52" s="1" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="H52" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="1" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="B53" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="C53" s="1" t="n">
+        <v>2860000000</v>
+      </c>
+      <c r="D53" s="1" t="n">
+        <v>7150000</v>
+      </c>
+      <c r="E53" s="1" t="n">
+        <v>425000000</v>
+      </c>
+      <c r="F53" s="1" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="G53" s="1" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="H53" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="1" t="inlineStr">
         <is>
           <t>보스 층</t>
         </is>
@@ -1756,7 +2312,7 @@
         <v>2.8</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="M4" s="1" t="n">
         <v>300</v>
@@ -1823,7 +2379,7 @@
         <v>2.8</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="M5" s="1" t="n">
         <v>300</v>
@@ -1957,7 +2513,7 @@
         <v>3.4</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="M7" s="1" t="n">
         <v>300</v>
@@ -2024,7 +2580,7 @@
         <v>3.4</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="M8" s="1" t="n">
         <v>300</v>
@@ -2091,7 +2647,7 @@
         <v>3.4</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="M9" s="1" t="n">
         <v>300</v>

--- a/Data_Table/스테이지 테이블.xlsx
+++ b/Data_Table/스테이지 테이블.xlsx
@@ -598,10 +598,10 @@
         <v>1</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>46.88</v>
+        <v>52.33</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>46.88</v>
+        <v>52.33</v>
       </c>
       <c r="H4" s="1" t="n">
         <v>0</v>
@@ -625,10 +625,10 @@
         <v>1.5</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>37.21</v>
+        <v>39.76</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>37.21</v>
+        <v>39.76</v>
       </c>
       <c r="H5" s="1" t="n">
         <v>0</v>
@@ -652,10 +652,10 @@
         <v>2.25</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>39.26</v>
+        <v>44.97</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>39.26</v>
+        <v>44.97</v>
       </c>
       <c r="H6" s="1" t="n">
         <v>0</v>
@@ -679,10 +679,10 @@
         <v>3.38</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>21.45</v>
+        <v>25.74</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>10.73</v>
+        <v>12.87</v>
       </c>
       <c r="H7" s="1" t="n">
         <v>0</v>
@@ -706,10 +706,10 @@
         <v>5.06</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>4.51</v>
+        <v>3.72</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>2.26</v>
+        <v>1.86</v>
       </c>
       <c r="H8" s="1" t="n">
         <v>0</v>
@@ -737,10 +737,10 @@
         <v>7.59</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>9.15</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="H9" s="1" t="n">
         <v>0</v>
@@ -764,10 +764,10 @@
         <v>11.39</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>8.82</v>
+        <v>10.9</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>2.94</v>
+        <v>3.63</v>
       </c>
       <c r="H10" s="1" t="n">
         <v>0</v>
@@ -791,10 +791,10 @@
         <v>17.09</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>4.54</v>
+        <v>7.94</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>1.13</v>
+        <v>2.65</v>
       </c>
       <c r="H11" s="1" t="n">
         <v>0</v>
@@ -818,10 +818,10 @@
         <v>25.63</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>7.64</v>
+        <v>7.76</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>3.82</v>
+        <v>3.88</v>
       </c>
       <c r="H12" s="1" t="n">
         <v>0</v>
@@ -845,10 +845,10 @@
         <v>38.44</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>7.32</v>
+        <v>7.94</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>2.44</v>
+        <v>2.65</v>
       </c>
       <c r="H13" s="1" t="n">
         <v>0</v>
@@ -876,10 +876,10 @@
         <v>57.67</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>1.27</v>
+        <v>7.94</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>0.8</v>
+        <v>2.65</v>
       </c>
       <c r="H14" s="1" t="n">
         <v>0</v>
@@ -903,10 +903,10 @@
         <v>86.5</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>3.73</v>
+        <v>3.74</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="H15" s="1" t="n">
         <v>0</v>
@@ -930,10 +930,10 @@
         <v>130</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>7.56</v>
+        <v>7.94</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>1.89</v>
+        <v>2.65</v>
       </c>
       <c r="H16" s="1" t="n">
         <v>0</v>
@@ -957,10 +957,10 @@
         <v>195</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>7.29</v>
+        <v>6.78</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>2.43</v>
+        <v>2.26</v>
       </c>
       <c r="H17" s="1" t="n">
         <v>0</v>
@@ -984,10 +984,10 @@
         <v>292</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>3.09</v>
+        <v>6.88</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>0.8</v>
+        <v>2.29</v>
       </c>
       <c r="H18" s="1" t="n">
         <v>0</v>
@@ -1015,10 +1015,10 @@
         <v>438</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>35.77</v>
+        <v>54.39</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>35.77</v>
+        <v>54.39</v>
       </c>
       <c r="H19" s="1" t="n">
         <v>0</v>
@@ -1042,10 +1042,10 @@
         <v>657</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>3.67</v>
+        <v>7.94</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>0.8</v>
+        <v>2.65</v>
       </c>
       <c r="H20" s="1" t="n">
         <v>0</v>
@@ -1069,10 +1069,10 @@
         <v>985</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>6.73</v>
+        <v>7.94</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>1.68</v>
+        <v>2.65</v>
       </c>
       <c r="H21" s="1" t="n">
         <v>0</v>
@@ -1096,10 +1096,10 @@
         <v>1480</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>9.57</v>
+        <v>14.11</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>3.19</v>
+        <v>4.7</v>
       </c>
       <c r="H22" s="1" t="n">
         <v>0</v>
@@ -1123,10 +1123,10 @@
         <v>2220</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>13.36</v>
+        <v>16.23</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>4.45</v>
+        <v>5.41</v>
       </c>
       <c r="H23" s="1" t="n">
         <v>0</v>
@@ -1154,10 +1154,10 @@
         <v>3330</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>5.12</v>
+        <v>7.94</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>1.02</v>
+        <v>2.65</v>
       </c>
       <c r="H24" s="1" t="n">
         <v>0</v>
@@ -1181,10 +1181,10 @@
         <v>4990</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>26.83</v>
+        <v>43.63</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>8.94</v>
+        <v>14.54</v>
       </c>
       <c r="H25" s="1" t="n">
         <v>0</v>
@@ -1208,10 +1208,10 @@
         <v>7480</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>9.93</v>
+        <v>14.41</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>3.31</v>
+        <v>4.8</v>
       </c>
       <c r="H26" s="1" t="n">
         <v>0</v>
@@ -1235,10 +1235,10 @@
         <v>11200</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>21.01</v>
+        <v>31.02</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>7</v>
+        <v>10.34</v>
       </c>
       <c r="H27" s="1" t="n">
         <v>0</v>
@@ -1262,10 +1262,10 @@
         <v>16800</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>6.95</v>
+        <v>6.88</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>1.74</v>
+        <v>2.29</v>
       </c>
       <c r="H28" s="1" t="n">
         <v>0</v>
@@ -1296,7 +1296,7 @@
         <v>7.94</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>1.13</v>
+        <v>2.65</v>
       </c>
       <c r="H29" s="1" t="n">
         <v>0</v>
@@ -1350,7 +1350,7 @@
         <v>7.94</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>1.32</v>
+        <v>2.65</v>
       </c>
       <c r="H31" s="1" t="n">
         <v>0</v>
@@ -1404,7 +1404,7 @@
         <v>6.88</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>0.86</v>
+        <v>2.29</v>
       </c>
       <c r="H33" s="1" t="n">
         <v>0</v>
@@ -1462,7 +1462,7 @@
         <v>7.94</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>1.59</v>
+        <v>2.65</v>
       </c>
       <c r="H35" s="1" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
         <v>7.94</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>1.59</v>
+        <v>2.65</v>
       </c>
       <c r="H36" s="1" t="n">
         <v>0</v>
@@ -1601,7 +1601,7 @@
         <v>7.94</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>1.59</v>
+        <v>2.65</v>
       </c>
       <c r="H40" s="1" t="n">
         <v>0</v>
@@ -1740,7 +1740,7 @@
         <v>7.94</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>1.99</v>
+        <v>2.65</v>
       </c>
       <c r="H45" s="1" t="n">
         <v>0</v>
@@ -1821,7 +1821,7 @@
         <v>6.88</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>1.72</v>
+        <v>2.29</v>
       </c>
       <c r="H48" s="1" t="n">
         <v>0</v>
@@ -1852,7 +1852,7 @@
         <v>7.94</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>1.99</v>
+        <v>2.65</v>
       </c>
       <c r="H49" s="1" t="n">
         <v>0</v>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>gym</t>
+          <t>boss_zero</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>fire</t>
+          <t>boss_witch</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>space</t>
+          <t>boss_commander</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">

--- a/Data_Table/스테이지 테이블.xlsx
+++ b/Data_Table/스테이지 테이블.xlsx
@@ -706,10 +706,10 @@
         <v>5.06</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>3.72</v>
+        <v>3.07</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>1.86</v>
+        <v>1.53</v>
       </c>
       <c r="H8" s="1" t="n">
         <v>0</v>
@@ -818,10 +818,10 @@
         <v>25.63</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>7.76</v>
+        <v>4.85</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>3.88</v>
+        <v>2.43</v>
       </c>
       <c r="H12" s="1" t="n">
         <v>0</v>
@@ -876,10 +876,10 @@
         <v>57.67</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>7.94</v>
+        <v>3.1</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>2.65</v>
+        <v>1.03</v>
       </c>
       <c r="H14" s="1" t="n">
         <v>0</v>
@@ -903,10 +903,10 @@
         <v>86.5</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>3.74</v>
+        <v>7.85</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>1.87</v>
+        <v>3.92</v>
       </c>
       <c r="H15" s="1" t="n">
         <v>0</v>
@@ -930,10 +930,10 @@
         <v>130</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>7.94</v>
+        <v>10.35</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>2.65</v>
+        <v>3.45</v>
       </c>
       <c r="H16" s="1" t="n">
         <v>0</v>
@@ -957,10 +957,10 @@
         <v>195</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>6.78</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>2.26</v>
+        <v>3.18</v>
       </c>
       <c r="H17" s="1" t="n">
         <v>0</v>
@@ -984,10 +984,10 @@
         <v>292</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>6.88</v>
+        <v>2.69</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>2.29</v>
+        <v>0.9</v>
       </c>
       <c r="H18" s="1" t="n">
         <v>0</v>
@@ -1015,10 +1015,10 @@
         <v>438</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>54.39</v>
+        <v>76.36</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>54.39</v>
+        <v>76.36</v>
       </c>
       <c r="H19" s="1" t="n">
         <v>0</v>
@@ -1042,10 +1042,10 @@
         <v>657</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>7.94</v>
+        <v>4.86</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>2.65</v>
+        <v>1.62</v>
       </c>
       <c r="H20" s="1" t="n">
         <v>0</v>
@@ -1069,10 +1069,10 @@
         <v>985</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>7.94</v>
+        <v>11.83</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>2.65</v>
+        <v>3.94</v>
       </c>
       <c r="H21" s="1" t="n">
         <v>0</v>
@@ -1154,10 +1154,10 @@
         <v>3330</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>7.94</v>
+        <v>18.6</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>2.65</v>
+        <v>6.2</v>
       </c>
       <c r="H24" s="1" t="n">
         <v>0</v>
@@ -1208,10 +1208,10 @@
         <v>7480</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>14.41</v>
+        <v>18.47</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>4.8</v>
+        <v>6.16</v>
       </c>
       <c r="H26" s="1" t="n">
         <v>0</v>
@@ -1262,10 +1262,10 @@
         <v>16800</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>6.88</v>
+        <v>17.21</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>2.29</v>
+        <v>5.74</v>
       </c>
       <c r="H28" s="1" t="n">
         <v>0</v>
@@ -2312,7 +2312,7 @@
         <v>2.8</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>20</v>
+        <v>33.4</v>
       </c>
       <c r="M4" s="1" t="n">
         <v>300</v>
@@ -2379,7 +2379,7 @@
         <v>2.8</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="M5" s="1" t="n">
         <v>300</v>
@@ -2446,7 +2446,7 @@
         <v>2.8</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>40</v>
+        <v>70.7</v>
       </c>
       <c r="M6" s="1" t="n">
         <v>300</v>
@@ -2513,7 +2513,7 @@
         <v>3.4</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>36</v>
+        <v>47.3</v>
       </c>
       <c r="M7" s="1" t="n">
         <v>300</v>
@@ -2580,7 +2580,7 @@
         <v>3.4</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>36</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="M8" s="1" t="n">
         <v>300</v>

--- a/Data_Table/스테이지 테이블.xlsx
+++ b/Data_Table/스테이지 테이블.xlsx
@@ -876,10 +876,10 @@
         <v>57.67</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>3.1</v>
+        <v>1.48</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>1.03</v>
+        <v>0.8</v>
       </c>
       <c r="H14" s="1" t="n">
         <v>0</v>
@@ -903,10 +903,10 @@
         <v>86.5</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>7.85</v>
+        <v>6.11</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>3.92</v>
+        <v>3.05</v>
       </c>
       <c r="H15" s="1" t="n">
         <v>0</v>
@@ -930,10 +930,10 @@
         <v>130</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>10.35</v>
+        <v>16.68</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>3.45</v>
+        <v>5.56</v>
       </c>
       <c r="H16" s="1" t="n">
         <v>0</v>
@@ -984,10 +984,10 @@
         <v>292</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>2.69</v>
+        <v>1.84</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H18" s="1" t="n">
         <v>0</v>
@@ -1262,10 +1262,10 @@
         <v>16800</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>17.21</v>
+        <v>22.35</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>5.74</v>
+        <v>7.45</v>
       </c>
       <c r="H28" s="1" t="n">
         <v>0</v>
@@ -2513,7 +2513,7 @@
         <v>3.4</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>47.3</v>
+        <v>56.1</v>
       </c>
       <c r="M7" s="1" t="n">
         <v>300</v>
@@ -2580,7 +2580,7 @@
         <v>3.4</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>71.59999999999999</v>
+        <v>53.9</v>
       </c>
       <c r="M8" s="1" t="n">
         <v>300</v>

--- a/Data_Table/스테이지 테이블.xlsx
+++ b/Data_Table/스테이지 테이블.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -436,8 +436,9 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -478,10 +479,15 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>경로 벽 합</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>추가 제한시간</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
@@ -525,10 +531,15 @@
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
+          <t>wall_path</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
           <t>time_add</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -576,6 +587,11 @@
         </is>
       </c>
       <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -604,9 +620,12 @@
         <v>52.33</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="1" t="inlineStr"/>
+        <v>85.44</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="1" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -631,9 +650,12 @@
         <v>39.76</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="1" t="inlineStr"/>
+        <v>79.53</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -658,9 +680,12 @@
         <v>44.97</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="1" t="inlineStr"/>
+        <v>81.2</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -685,9 +710,12 @@
         <v>12.87</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="1" t="inlineStr"/>
+        <v>51.49</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -712,9 +740,12 @@
         <v>1.53</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="1" t="inlineStr">
+        <v>18.26</v>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1" t="inlineStr">
         <is>
           <t>보스 층</t>
         </is>
@@ -743,9 +774,12 @@
         <v>2.9</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="1" t="inlineStr"/>
+        <v>17.42</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -770,9 +804,12 @@
         <v>3.63</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="1" t="inlineStr"/>
+        <v>15.52</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -797,9 +834,12 @@
         <v>2.65</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="1" t="inlineStr"/>
+        <v>18.32</v>
+      </c>
+      <c r="I11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -824,9 +864,12 @@
         <v>2.43</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="1" t="inlineStr"/>
+        <v>15.88</v>
+      </c>
+      <c r="I12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -851,9 +894,12 @@
         <v>2.65</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="1" t="inlineStr">
+        <v>10.59</v>
+      </c>
+      <c r="I13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1" t="inlineStr">
         <is>
           <t>보스 층</t>
         </is>
@@ -882,9 +928,12 @@
         <v>0.8</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="1" t="inlineStr"/>
+        <v>12.22</v>
+      </c>
+      <c r="I14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -909,9 +958,12 @@
         <v>3.05</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="1" t="inlineStr"/>
+        <v>18.32</v>
+      </c>
+      <c r="I15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -936,9 +988,12 @@
         <v>5.56</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="1" t="inlineStr"/>
+        <v>12.22</v>
+      </c>
+      <c r="I16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -963,9 +1018,12 @@
         <v>3.18</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="1" t="inlineStr"/>
+        <v>19.09</v>
+      </c>
+      <c r="I17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -990,9 +1048,12 @@
         <v>0.8</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="1" t="inlineStr">
+        <v>16.54</v>
+      </c>
+      <c r="I18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="1" t="inlineStr">
         <is>
           <t>보스 층</t>
         </is>
@@ -1021,9 +1082,12 @@
         <v>76.36</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="1" t="inlineStr"/>
+        <v>19.09</v>
+      </c>
+      <c r="I19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="1" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -1048,9 +1112,12 @@
         <v>1.62</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="1" t="inlineStr"/>
+        <v>23.67</v>
+      </c>
+      <c r="I20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="1" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -1075,9 +1142,12 @@
         <v>3.94</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="1" t="inlineStr"/>
+        <v>28.21</v>
+      </c>
+      <c r="I21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="1" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -1102,9 +1172,12 @@
         <v>4.7</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="1" t="inlineStr"/>
+        <v>28.21</v>
+      </c>
+      <c r="I22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="1" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -1129,9 +1202,12 @@
         <v>5.41</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="1" t="inlineStr">
+        <v>32.24</v>
+      </c>
+      <c r="I23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="1" t="inlineStr">
         <is>
           <t>보스 층</t>
         </is>
@@ -1160,9 +1236,12 @@
         <v>6.2</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="1" t="inlineStr"/>
+        <v>37.2</v>
+      </c>
+      <c r="I24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="1" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -1187,9 +1266,12 @@
         <v>14.54</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="1" t="inlineStr"/>
+        <v>37.46</v>
+      </c>
+      <c r="I25" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="1" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -1214,9 +1296,12 @@
         <v>6.16</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="1" t="inlineStr"/>
+        <v>51.57</v>
+      </c>
+      <c r="I26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="1" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -1241,9 +1326,12 @@
         <v>10.34</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="1" t="inlineStr"/>
+        <v>51.57</v>
+      </c>
+      <c r="I27" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="1" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -1268,9 +1356,12 @@
         <v>7.45</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" s="1" t="inlineStr">
+        <v>44.69</v>
+      </c>
+      <c r="I28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="1" t="inlineStr">
         <is>
           <t>보스 층</t>
         </is>
@@ -1299,9 +1390,12 @@
         <v>2.65</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="1" t="inlineStr"/>
+        <v>51.57</v>
+      </c>
+      <c r="I29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="1" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -1326,9 +1420,12 @@
         <v>2.65</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="1" t="inlineStr"/>
+        <v>51.57</v>
+      </c>
+      <c r="I30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="1" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -1353,9 +1450,12 @@
         <v>2.65</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="1" t="inlineStr"/>
+        <v>15.88</v>
+      </c>
+      <c r="I31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="1" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -1380,9 +1480,12 @@
         <v>2.65</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="1" t="inlineStr"/>
+        <v>15.88</v>
+      </c>
+      <c r="I32" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="1" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -1407,9 +1510,12 @@
         <v>2.29</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="1" t="inlineStr">
+        <v>13.76</v>
+      </c>
+      <c r="I33" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="1" t="inlineStr">
         <is>
           <t>보스 층</t>
         </is>
@@ -1438,9 +1544,12 @@
         <v>3.97</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="1" t="inlineStr"/>
+        <v>15.88</v>
+      </c>
+      <c r="I34" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="1" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -1465,9 +1574,12 @@
         <v>2.65</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="1" t="inlineStr"/>
+        <v>15.88</v>
+      </c>
+      <c r="I35" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="1" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -1492,9 +1604,12 @@
         <v>2.65</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="1" t="inlineStr"/>
+        <v>15.88</v>
+      </c>
+      <c r="I36" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="1" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -1519,9 +1634,12 @@
         <v>3.97</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" s="1" t="inlineStr"/>
+        <v>15.88</v>
+      </c>
+      <c r="I37" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="1" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -1546,9 +1664,12 @@
         <v>2.29</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="1" t="inlineStr">
+        <v>13.76</v>
+      </c>
+      <c r="I38" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="1" t="inlineStr">
         <is>
           <t>보스 층</t>
         </is>
@@ -1577,9 +1698,12 @@
         <v>2.65</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="1" t="inlineStr"/>
+        <v>15.88</v>
+      </c>
+      <c r="I39" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="1" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -1604,9 +1728,12 @@
         <v>2.65</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="1" t="inlineStr"/>
+        <v>15.88</v>
+      </c>
+      <c r="I40" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="1" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -1631,9 +1758,12 @@
         <v>2.65</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="1" t="inlineStr"/>
+        <v>15.88</v>
+      </c>
+      <c r="I41" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="1" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -1658,9 +1788,12 @@
         <v>3.97</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" s="1" t="inlineStr"/>
+        <v>15.88</v>
+      </c>
+      <c r="I42" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="1" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -1685,9 +1818,12 @@
         <v>2.29</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="1" t="inlineStr">
+        <v>13.76</v>
+      </c>
+      <c r="I43" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="1" t="inlineStr">
         <is>
           <t>보스 층</t>
         </is>
@@ -1716,9 +1852,12 @@
         <v>2.65</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" s="1" t="inlineStr"/>
+        <v>15.88</v>
+      </c>
+      <c r="I44" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="1" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -1743,9 +1882,12 @@
         <v>2.65</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="1" t="inlineStr"/>
+        <v>15.88</v>
+      </c>
+      <c r="I45" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="1" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -1770,9 +1912,12 @@
         <v>3.97</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" s="1" t="inlineStr"/>
+        <v>15.88</v>
+      </c>
+      <c r="I46" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="1" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -1797,9 +1942,12 @@
         <v>2.65</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" s="1" t="inlineStr"/>
+        <v>15.88</v>
+      </c>
+      <c r="I47" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="1" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -1824,9 +1972,12 @@
         <v>2.29</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="1" t="inlineStr">
+        <v>13.76</v>
+      </c>
+      <c r="I48" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="1" t="inlineStr">
         <is>
           <t>보스 층</t>
         </is>
@@ -1855,9 +2006,12 @@
         <v>2.65</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" s="1" t="inlineStr"/>
+        <v>15.88</v>
+      </c>
+      <c r="I49" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="1" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -1882,9 +2036,12 @@
         <v>2.65</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" s="1" t="inlineStr"/>
+        <v>15.88</v>
+      </c>
+      <c r="I50" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="1" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -1909,9 +2066,12 @@
         <v>3.97</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="1" t="inlineStr"/>
+        <v>15.88</v>
+      </c>
+      <c r="I51" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="1" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -1936,9 +2096,12 @@
         <v>3.97</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" s="1" t="inlineStr"/>
+        <v>15.88</v>
+      </c>
+      <c r="I52" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="1" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -1963,9 +2126,12 @@
         <v>2.29</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="1" t="inlineStr">
+        <v>13.76</v>
+      </c>
+      <c r="I53" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="1" t="inlineStr">
         <is>
           <t>보스 층</t>
         </is>
@@ -4188,7 +4354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4387,6 +4553,18 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>wall_path</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>Stage: 계단까지 최단 경로 벽 배율 합 목표. 판마다 지형이 랜덤이라 게임(StageManager)이 계단 거리 d 로 나눔: 일반 = max(0.8, 합×0.5÷(d-1)), 계단 = 나머지. 0 이면 wall_stairs·wall_normal 사용</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data_Table/스테이지 테이블.xlsx
+++ b/Data_Table/스테이지 테이블.xlsx
@@ -2148,7 +2148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:T9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2253,6 +2253,21 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>필살 패턴 1 (체력 70%)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>필살 패턴 2 (체력 35%)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>그 뒤 필살 확률</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>설명</t>
         </is>
       </c>
@@ -2340,6 +2355,21 @@
       </c>
       <c r="Q2" s="1" t="inlineStr">
         <is>
+          <t>special1_type</t>
+        </is>
+      </c>
+      <c r="R2" s="1" t="inlineStr">
+        <is>
+          <t>special2_type</t>
+        </is>
+      </c>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>special_chance</t>
+        </is>
+      </c>
+      <c r="T2" s="1" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
@@ -2426,6 +2456,21 @@
         </is>
       </c>
       <c r="Q3" s="1" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="R3" s="1" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="S3" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="T3" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2494,6 +2539,19 @@
       </c>
       <c r="Q4" s="1" t="inlineStr">
         <is>
+          <t>Mega_Stomp</t>
+        </is>
+      </c>
+      <c r="R4" s="1" t="inlineStr">
+        <is>
+          <t>Cone_Rain</t>
+        </is>
+      </c>
+      <c r="S4" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T4" s="1" t="inlineStr">
+        <is>
           <t>5층 보스. 쥐 무리 쪽으로 쿵쿵 걸어와 점프 내려찍기</t>
         </is>
       </c>
@@ -2561,6 +2619,19 @@
       </c>
       <c r="Q5" s="1" t="inlineStr">
         <is>
+          <t>Potion_Party</t>
+        </is>
+      </c>
+      <c r="R5" s="1" t="inlineStr">
+        <is>
+          <t>Self_Experiment</t>
+        </is>
+      </c>
+      <c r="S5" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T5" s="1" t="inlineStr">
+        <is>
           <t>10층 보스. 초록 약품 플라스크를 3개씩 던짐 (떨어진 곳 쥐 기절)</t>
         </is>
       </c>
@@ -2628,6 +2699,19 @@
       </c>
       <c r="Q6" s="1" t="inlineStr">
         <is>
+          <t>Paper_Storm</t>
+        </is>
+      </c>
+      <c r="R6" s="1" t="inlineStr">
+        <is>
+          <t>Board_Meeting</t>
+        </is>
+      </c>
+      <c r="S6" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T6" s="1" t="inlineStr">
+        <is>
           <t>15층 보스. 주먹 휘두르기로 주변 쥐를 날림, 두 번에 한 번 경비원 호출</t>
         </is>
       </c>
@@ -2695,6 +2779,19 @@
       </c>
       <c r="Q7" s="1" t="inlineStr">
         <is>
+          <t>Zoomies</t>
+        </is>
+      </c>
+      <c r="R7" s="1" t="inlineStr">
+        <is>
+          <t>Box_Fit</t>
+        </is>
+      </c>
+      <c r="S7" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T7" s="1" t="inlineStr">
+        <is>
           <t>20층 보스. 거대 고양이: 덮치기 · 헤어볼 투척</t>
         </is>
       </c>
@@ -2762,6 +2859,19 @@
       </c>
       <c r="Q8" s="1" t="inlineStr">
         <is>
+          <t>Meteor_Shower</t>
+        </is>
+      </c>
+      <c r="R8" s="1" t="inlineStr">
+        <is>
+          <t>Frog_Curse</t>
+        </is>
+      </c>
+      <c r="S8" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T8" s="1" t="inlineStr">
+        <is>
           <t>25층 보스. 불덩이 5개 · 덮치기</t>
         </is>
       </c>
@@ -2828,6 +2938,19 @@
         <v>4.5</v>
       </c>
       <c r="Q9" s="1" t="inlineStr">
+        <is>
+          <t>Orbital_Laser</t>
+        </is>
+      </c>
+      <c r="R9" s="1" t="inlineStr">
+        <is>
+          <t>Black_Hole</t>
+        </is>
+      </c>
+      <c r="S9" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T9" s="1" t="inlineStr">
         <is>
           <t>30층 보스. 무중력 파동 (주변 쥐가 떠올랐다 떨어지며 기절) · 덮치기. 30층 뒤로는 5층 보스부터 다시 반복</t>
         </is>
@@ -2844,7 +2967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3888,6 +4011,330 @@
       <c r="D57" s="1" t="inlineStr">
         <is>
           <t>냐아아아~!</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>96056</v>
+      </c>
+      <c r="B58" s="1" t="n">
+        <v>95001</v>
+      </c>
+      <c r="C58" s="1" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D58" s="1" t="inlineStr">
+        <is>
+          <t>비상! 비상!! 전원 출동!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>96057</v>
+      </c>
+      <c r="B59" s="1" t="n">
+        <v>95001</v>
+      </c>
+      <c r="C59" s="1" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D59" s="1" t="inlineStr">
+        <is>
+          <t>호루라기 삐이이익!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>96058</v>
+      </c>
+      <c r="B60" s="1" t="n">
+        <v>95001</v>
+      </c>
+      <c r="C60" s="1" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D60" s="1" t="inlineStr">
+        <is>
+          <t>경비 30년의 내공을 보여주마!</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>96059</v>
+      </c>
+      <c r="B61" s="1" t="n">
+        <v>95002</v>
+      </c>
+      <c r="C61" s="1" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D61" s="1" t="inlineStr">
+        <is>
+          <t>실험은 폭발이다아아!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>96060</v>
+      </c>
+      <c r="B62" s="1" t="n">
+        <v>95002</v>
+      </c>
+      <c r="C62" s="1" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D62" s="1" t="inlineStr">
+        <is>
+          <t>이번엔 이걸 섞어볼까~?</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>96061</v>
+      </c>
+      <c r="B63" s="1" t="n">
+        <v>95002</v>
+      </c>
+      <c r="C63" s="1" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D63" s="1" t="inlineStr">
+        <is>
+          <t>내 몸으로 직접 실험한다!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>96062</v>
+      </c>
+      <c r="B64" s="1" t="n">
+        <v>95003</v>
+      </c>
+      <c r="C64" s="1" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D64" s="1" t="inlineStr">
+        <is>
+          <t>결재 올려!! 전부 다!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>96063</v>
+      </c>
+      <c r="B65" s="1" t="n">
+        <v>95003</v>
+      </c>
+      <c r="C65" s="1" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D65" s="1" t="inlineStr">
+        <is>
+          <t>이사회 소집이다!!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>96064</v>
+      </c>
+      <c r="B66" s="1" t="n">
+        <v>95003</v>
+      </c>
+      <c r="C66" s="1" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D66" s="1" t="inlineStr">
+        <is>
+          <t>예산은 너희들 몫이 아니다!</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>96065</v>
+      </c>
+      <c r="B67" s="1" t="n">
+        <v>95004</v>
+      </c>
+      <c r="C67" s="1" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D67" s="1" t="inlineStr">
+        <is>
+          <t>냐아아아아앙!!!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>96066</v>
+      </c>
+      <c r="B68" s="1" t="n">
+        <v>95004</v>
+      </c>
+      <c r="C68" s="1" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D68" s="1" t="inlineStr">
+        <is>
+          <t>(우다다다다다)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>96067</v>
+      </c>
+      <c r="B69" s="1" t="n">
+        <v>95004</v>
+      </c>
+      <c r="C69" s="1" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D69" s="1" t="inlineStr">
+        <is>
+          <t>상자다… 상자다…!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>96068</v>
+      </c>
+      <c r="B70" s="1" t="n">
+        <v>95005</v>
+      </c>
+      <c r="C70" s="1" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D70" s="1" t="inlineStr">
+        <is>
+          <t>하늘이여 무너져라냥!</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>96069</v>
+      </c>
+      <c r="B71" s="1" t="n">
+        <v>95005</v>
+      </c>
+      <c r="C71" s="1" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D71" s="1" t="inlineStr">
+        <is>
+          <t>개굴개굴해져라~!</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>96070</v>
+      </c>
+      <c r="B72" s="1" t="n">
+        <v>95005</v>
+      </c>
+      <c r="C72" s="1" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D72" s="1" t="inlineStr">
+        <is>
+          <t>마법 학교 수석의 힘이다냥!</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>96071</v>
+      </c>
+      <c r="B73" s="1" t="n">
+        <v>95006</v>
+      </c>
+      <c r="C73" s="1" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D73" s="1" t="inlineStr">
+        <is>
+          <t>궤도 포격 허가한다냥!</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>96072</v>
+      </c>
+      <c r="B74" s="1" t="n">
+        <v>95006</v>
+      </c>
+      <c r="C74" s="1" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D74" s="1" t="inlineStr">
+        <is>
+          <t>블랙홀 생성 완료.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>96073</v>
+      </c>
+      <c r="B75" s="1" t="n">
+        <v>95006</v>
+      </c>
+      <c r="C75" s="1" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D75" s="1" t="inlineStr">
+        <is>
+          <t>우주는 넓고 쥐는 작다냥.</t>
         </is>
       </c>
     </row>
@@ -3902,7 +4349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3950,6 +4397,11 @@
           <t>공격 길이 (초)</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>화면 이름</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -3987,6 +4439,11 @@
           <t>dur</t>
         </is>
       </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>atk_name</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -4024,6 +4481,11 @@
           <t>float</t>
         </is>
       </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -4051,6 +4513,11 @@
       <c r="G4" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -4078,6 +4545,11 @@
       <c r="G5" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t>내려찍기</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -4105,6 +4577,11 @@
       <c r="G6" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t>덮치기</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -4132,6 +4609,11 @@
       <c r="G7" s="1" t="n">
         <v>1.6</v>
       </c>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t>플라스크 투척</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -4159,6 +4641,11 @@
       <c r="G8" s="1" t="n">
         <v>1.6</v>
       </c>
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t>헤어볼</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -4186,6 +4673,11 @@
       <c r="G9" s="1" t="n">
         <v>1.6</v>
       </c>
+      <c r="H9" s="1" t="inlineStr">
+        <is>
+          <t>불덩이</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -4213,6 +4705,11 @@
       <c r="G10" s="1" t="n">
         <v>1.2</v>
       </c>
+      <c r="H10" s="1" t="inlineStr">
+        <is>
+          <t>휘두르기</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -4239,6 +4736,395 @@
       </c>
       <c r="G11" s="1" t="n">
         <v>1.3</v>
+      </c>
+      <c r="H11" s="1" t="inlineStr">
+        <is>
+          <t>무중력 파동</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Mega_Stomp</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>[필살] 쥐 무리 3곳에 차례로 경고 원 → 공중 3단 점프 내려찍기</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>240</v>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1" t="inlineStr">
+        <is>
+          <t>3단 공중 내려찍기</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Cone_Rain</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>[필살] 하늘에서 안전 고깔이 개수만큼 쥐 무리에 떨어짐</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H13" s="1" t="inlineStr">
+        <is>
+          <t>안전 고깔 폭격</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Potion_Party</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>[필살] 제자리에서 빙글 돌며 플라스크를 개수만큼 사방(나선)으로 던짐</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H14" s="1" t="inlineStr">
+        <is>
+          <t>약품 대방출 파티</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Self_Experiment</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>[필살] 약을 마시고 거대화(공격 길이 초 동안) → 빨라지고 개수만큼 주변 충격파</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>230</v>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="H15" s="1" t="inlineStr">
+        <is>
+          <t>자가 실험: 거대화!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Paper_Storm</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>[필살] 결재 서류 더미가 개수만큼 쥐 무리에 떨어짐</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H16" s="1" t="inlineStr">
+        <is>
+          <t>결재 서류 폭탄</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Board_Meeting</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>[필살] 책상 내리치기 충격파(반경) + 경비원 개수만큼 소집</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>380</v>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H17" s="1" t="inlineStr">
+        <is>
+          <t>긴급 이사회 소집</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Zoomies</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>[필살] 방 안을 개수만큼 미친 듯이 질주, 지나간 길(반경)의 쥐 기절</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="H18" s="1" t="inlineStr">
+        <is>
+          <t>새벽 3시 우다다</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Box_Fit</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>[필살] 거대 상자에 쏙 들어감(웅크림 초 동안 무적) → 상자 폭발 충격파(반경)</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="1" t="inlineStr">
+        <is>
+          <t>상자 들어가기</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Meteor_Shower</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>[필살] 운석이 개수만큼 쥐 무리에 떨어짐</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="F20" s="1" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G20" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" s="1" t="inlineStr">
+        <is>
+          <t>운석 소나기</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>Frog_Curse</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>[필살] 반경 안 쥐가 개구리가 됨 (개굴! 기절)</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>340</v>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="1" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="1" t="inlineStr">
+        <is>
+          <t>개구리 저주</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Orbital_Laser</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>[필살] 궤도 레이저가 개수만큼 쥐 무리를 차례로 포격</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="F22" s="1" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G22" s="1" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H22" s="1" t="inlineStr">
+        <is>
+          <t>궤도 레이저 포격</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>Black_Hole</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>[필살] 쥐 무리 한가운데 초거대 블랙홀 → 웅크림 초 동안 빨아들인 뒤 띄워서 기절</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>450</v>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="1" t="inlineStr">
+        <is>
+          <t>초거대 블랙홀</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4252,7 +5138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4340,6 +5226,18 @@
       <c r="B7" s="1" t="inlineStr">
         <is>
           <t>쓰러질 때</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>필살 패턴 쓸 때</t>
         </is>
       </c>
     </row>
@@ -4354,7 +5252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4565,6 +5463,18 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>special1_type · special2_type · special_chance</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>필살 패턴: 체력 70% 아래로 처음 내려가면 1번, 35% 아래면 2번을 바로 씀 (배너 + 대사). 둘 다 쓴 뒤로는 공격할 때마다 special_chance 확률로 둘 중 하나. 수치는 Atk_Type 시트 (화면 이름 atk_name)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data_Table/스테이지 테이블.xlsx
+++ b/Data_Table/스테이지 테이블.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:P53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -434,7 +434,13 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -485,6 +491,36 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>층 유형</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>목표 돌파 (초)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>보스전 목표 (초)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>클리어 연구자료</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>건너뛰기 상한</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>기준 전투력 (지수)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>메모</t>
         </is>
       </c>
@@ -537,6 +573,36 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
+          <t>floor_type</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>target_sec</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>boss_sec</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>skip_cap</t>
+        </is>
+      </c>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>player_pow</t>
+        </is>
+      </c>
+      <c r="P2" s="1" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
@@ -588,6 +654,36 @@
         </is>
       </c>
       <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="O3" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="P3" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -598,7 +694,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>400</v>
@@ -610,18 +706,42 @@
         <v>1</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>52.33</v>
+        <v>83.72</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>52.33</v>
+        <v>1.2</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>85.44</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="I4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="1" t="inlineStr"/>
+      <c r="J4" s="1" t="inlineStr">
+        <is>
+          <t>도입</t>
+        </is>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="L4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="N4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="P4" s="1" t="inlineStr">
+        <is>
+          <t>도입</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -631,57 +751,105 @@
         <v>3</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>552</v>
+        <v>500</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>39.76</v>
+        <v>31.81</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>39.76</v>
+        <v>31.81</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>79.53</v>
+        <v>63.62</v>
       </c>
       <c r="I5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="1" t="inlineStr"/>
+      <c r="J5" s="1" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="L5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="1" t="n">
+        <v>127</v>
+      </c>
+      <c r="P5" s="1" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>762</v>
+        <v>625</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>1.9</v>
+        <v>1.56</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>44.97</v>
+        <v>71.95</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44.97</v>
+        <v>1.2</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>81.2</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="I6" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="1" t="inlineStr"/>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" s="1" t="n">
+        <v>161</v>
+      </c>
+      <c r="P6" s="1" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -691,59 +859,103 @@
         <v>4</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>1050</v>
+        <v>781</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>2.63</v>
+        <v>1.95</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>3.38</v>
+        <v>2.31</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>25.74</v>
+        <v>20.59</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>12.87</v>
+        <v>10.3</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>51.49</v>
+        <v>41.19</v>
       </c>
       <c r="I7" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="1" t="inlineStr"/>
+      <c r="J7" s="1" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>15.62</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>205</v>
+      </c>
+      <c r="P7" s="1" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>1450</v>
+        <v>1410</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>3.63</v>
+        <v>3.52</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>5.06</v>
+        <v>4.81</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>3.07</v>
+        <v>2.55</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>1.53</v>
+        <v>1.27</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>18.26</v>
+        <v>15.17</v>
       </c>
       <c r="I8" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>보스 층</t>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>28.12</v>
+      </c>
+      <c r="N8" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="O8" s="1" t="n">
+        <v>273</v>
+      </c>
+      <c r="P8" s="1" t="inlineStr">
+        <is>
+          <t>보스 층 · 허들</t>
         </is>
       </c>
     </row>
@@ -755,57 +967,105 @@
         <v>5</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>2000</v>
+        <v>1860</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>5</v>
+        <v>4.64</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>7.59</v>
+        <v>6.81</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>8.710000000000001</v>
+        <v>6.97</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>2.9</v>
+        <v>2.32</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>17.42</v>
+        <v>13.94</v>
       </c>
       <c r="I9" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="1" t="inlineStr"/>
+      <c r="J9" s="1" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>37.12</v>
+      </c>
+      <c r="N9" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O9" s="1" t="n">
+        <v>402</v>
+      </c>
+      <c r="P9" s="1" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>2760</v>
+        <v>2450</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>6.91</v>
+        <v>6.13</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>11.39</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>10.9</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>3.63</v>
+        <v>2.91</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>15.52</v>
+        <v>12.41</v>
       </c>
       <c r="I10" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="1" t="inlineStr"/>
+      <c r="J10" s="1" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="L10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>49.01</v>
+      </c>
+      <c r="N10" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O10" s="1" t="n">
+        <v>601</v>
+      </c>
+      <c r="P10" s="1" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -815,89 +1075,157 @@
         <v>6</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>3810</v>
+        <v>3230</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>9.529999999999999</v>
+        <v>8.09</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>17.09</v>
+        <v>13.64</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>7.94</v>
+        <v>6.35</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>2.65</v>
+        <v>2.12</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>18.32</v>
+        <v>14.65</v>
       </c>
       <c r="I11" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="1" t="inlineStr"/>
+      <c r="J11" s="1" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="L11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>64.69</v>
+      </c>
+      <c r="N11" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="O11" s="1" t="n">
+        <v>836</v>
+      </c>
+      <c r="P11" s="1" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
         <v>9</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>5260</v>
+        <v>4270</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>13.15</v>
+        <v>10.67</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>25.63</v>
+        <v>19.29</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>4.85</v>
+        <v>3.88</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>2.43</v>
+        <v>1.94</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>15.88</v>
+        <v>12.71</v>
       </c>
       <c r="I12" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="1" t="inlineStr"/>
+      <c r="J12" s="1" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="K12" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="L12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1" t="n">
+        <v>85.39</v>
+      </c>
+      <c r="N12" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="O12" s="1" t="n">
+        <v>1120</v>
+      </c>
+      <c r="P12" s="1" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
         <v>10</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>7260</v>
+        <v>5640</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>18.15</v>
+        <v>14.09</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>38.44</v>
+        <v>27.3</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>7.94</v>
+        <v>4.4</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>2.65</v>
+        <v>1.47</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>10.59</v>
+        <v>5.86</v>
       </c>
       <c r="I13" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="1" t="inlineStr">
         <is>
-          <t>보스 층</t>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="K13" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="L13" s="1" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>113</v>
+      </c>
+      <c r="N13" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="O13" s="1" t="n">
+        <v>1500</v>
+      </c>
+      <c r="P13" s="1" t="inlineStr">
+        <is>
+          <t>보스 층 · 보통</t>
         </is>
       </c>
     </row>
@@ -906,30 +1234,54 @@
         <v>11</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>10000</v>
+        <v>7440</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>25.05</v>
+        <v>18.6</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>57.67</v>
+        <v>38.62</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>1.48</v>
+        <v>0.8</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>0.8</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>12.22</v>
+        <v>9.77</v>
       </c>
       <c r="I14" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="1" t="inlineStr"/>
+      <c r="J14" s="1" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="K14" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="L14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="1" t="n">
+        <v>149</v>
+      </c>
+      <c r="N14" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="O14" s="1" t="n">
+        <v>2010</v>
+      </c>
+      <c r="P14" s="1" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -939,57 +1291,105 @@
         <v>8</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>13800</v>
+        <v>9820</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>34.57</v>
+        <v>24.55</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>86.5</v>
+        <v>54.64</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>6.11</v>
+        <v>4.89</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>3.05</v>
+        <v>2.44</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>18.32</v>
+        <v>14.65</v>
       </c>
       <c r="I15" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="1" t="inlineStr"/>
+      <c r="J15" s="1" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="K15" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="L15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="1" t="n">
+        <v>196</v>
+      </c>
+      <c r="N15" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="O15" s="1" t="n">
+        <v>2690</v>
+      </c>
+      <c r="P15" s="1" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
         <v>13</v>
       </c>
       <c r="B16" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>19100</v>
+        <v>13000</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>47.7</v>
+        <v>32.4</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>130</v>
+        <v>77.31</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>16.68</v>
+        <v>13.35</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>5.56</v>
+        <v>4.45</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>12.22</v>
+        <v>9.77</v>
       </c>
       <c r="I16" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="1" t="inlineStr"/>
+      <c r="J16" s="1" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="K16" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="L16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="N16" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="O16" s="1" t="n">
+        <v>3610</v>
+      </c>
+      <c r="P16" s="1" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -999,59 +1399,103 @@
         <v>9</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>26300</v>
+        <v>17100</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>65.83</v>
+        <v>42.77</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>195</v>
+        <v>109</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>9.539999999999999</v>
+        <v>7.64</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>3.18</v>
+        <v>2.55</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>19.09</v>
+        <v>15.27</v>
       </c>
       <c r="I17" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="1" t="inlineStr"/>
+      <c r="J17" s="1" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="K17" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="L17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="1" t="n">
+        <v>342</v>
+      </c>
+      <c r="N17" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="O17" s="1" t="n">
+        <v>4840</v>
+      </c>
+      <c r="P17" s="1" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
         <v>15</v>
       </c>
       <c r="B18" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>36300</v>
+        <v>22600</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>90.84999999999999</v>
+        <v>56.46</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>292</v>
+        <v>155</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>1.84</v>
+        <v>0.8</v>
       </c>
       <c r="G18" s="1" t="n">
         <v>0.8</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>16.54</v>
+        <v>9.16</v>
       </c>
       <c r="I18" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="1" t="inlineStr">
         <is>
-          <t>보스 층</t>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="K18" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="L18" s="1" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="M18" s="1" t="n">
+        <v>452</v>
+      </c>
+      <c r="N18" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="O18" s="1" t="n">
+        <v>6480</v>
+      </c>
+      <c r="P18" s="1" t="inlineStr">
+        <is>
+          <t>보스 층 · 보통</t>
         </is>
       </c>
     </row>
@@ -1063,27 +1507,51 @@
         <v>9</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>50100</v>
+        <v>39500</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>125</v>
+        <v>98.81</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>438</v>
+        <v>312</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>76.36</v>
+        <v>91.63</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>76.36</v>
+        <v>91.63</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>19.09</v>
+        <v>22.91</v>
       </c>
       <c r="I19" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="1" t="inlineStr"/>
+      <c r="J19" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K19" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="1" t="n">
+        <v>790</v>
+      </c>
+      <c r="N19" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="O19" s="1" t="n">
+        <v>9340</v>
+      </c>
+      <c r="P19" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -1093,13 +1561,13 @@
         <v>9</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>69200</v>
+        <v>67200</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>657</v>
+        <v>605</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>4.86</v>
@@ -1113,7 +1581,31 @@
       <c r="I20" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="1" t="inlineStr"/>
+      <c r="J20" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="K20" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="L20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="1" t="n">
+        <v>1340</v>
+      </c>
+      <c r="N20" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="O20" s="1" t="n">
+        <v>14900</v>
+      </c>
+      <c r="P20" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -1123,27 +1615,51 @@
         <v>9</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>95500</v>
+        <v>141000</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>239</v>
+        <v>353</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>985</v>
+        <v>1530</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>11.83</v>
+        <v>14.2</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>3.94</v>
+        <v>4.73</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>28.21</v>
+        <v>33.85</v>
       </c>
       <c r="I21" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="1" t="inlineStr"/>
+      <c r="J21" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K21" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="1" t="n">
+        <v>2820</v>
+      </c>
+      <c r="N21" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="O21" s="1" t="n">
+        <v>24900</v>
+      </c>
+      <c r="P21" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -1153,13 +1669,13 @@
         <v>9</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>132000</v>
+        <v>310000</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>329</v>
+        <v>776</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>1480</v>
+        <v>4100</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>14.11</v>
@@ -1173,39 +1689,83 @@
       <c r="I22" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J22" s="1" t="inlineStr"/>
+      <c r="J22" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="K22" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="L22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="1" t="n">
+        <v>6210</v>
+      </c>
+      <c r="N22" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="O22" s="1" t="n">
+        <v>43700</v>
+      </c>
+      <c r="P22" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
         <v>20</v>
       </c>
       <c r="B23" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>182000</v>
+        <v>745000</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>455</v>
+        <v>1860</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>2220</v>
+        <v>12200</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>16.23</v>
+        <v>13.49</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>5.41</v>
+        <v>4.5</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>32.24</v>
+        <v>26.78</v>
       </c>
       <c r="I23" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="1" t="inlineStr">
         <is>
-          <t>보스 층</t>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K23" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L23" s="1" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="M23" s="1" t="n">
+        <v>14900</v>
+      </c>
+      <c r="N23" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O23" s="1" t="n">
+        <v>81000</v>
+      </c>
+      <c r="P23" s="1" t="inlineStr">
+        <is>
+          <t>보스 층 · 허들</t>
         </is>
       </c>
     </row>
@@ -1217,27 +1777,51 @@
         <v>9</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>251000</v>
+        <v>1300000</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>627</v>
+        <v>3260</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>3330</v>
+        <v>24600</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>18.6</v>
+        <v>22.32</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>6.2</v>
+        <v>7.44</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>37.2</v>
+        <v>44.63</v>
       </c>
       <c r="I24" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J24" s="1" t="inlineStr"/>
+      <c r="J24" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K24" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="1" t="n">
+        <v>26100</v>
+      </c>
+      <c r="N24" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O24" s="1" t="n">
+        <v>150000</v>
+      </c>
+      <c r="P24" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -1247,13 +1831,13 @@
         <v>9</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>346000</v>
+        <v>2220000</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>866</v>
+        <v>5540</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>4990</v>
+        <v>47800</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>43.63</v>
@@ -1267,7 +1851,31 @@
       <c r="I25" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J25" s="1" t="inlineStr"/>
+      <c r="J25" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="K25" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="L25" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="1" t="n">
+        <v>44300</v>
+      </c>
+      <c r="N25" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O25" s="1" t="n">
+        <v>277000</v>
+      </c>
+      <c r="P25" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -1277,27 +1885,51 @@
         <v>9</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>478000</v>
+        <v>4650000</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>1190</v>
+        <v>11600</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>7480</v>
+        <v>121000</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>18.47</v>
+        <v>22.16</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>6.16</v>
+        <v>7.39</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>51.57</v>
+        <v>61.88</v>
       </c>
       <c r="I26" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J26" s="1" t="inlineStr"/>
+      <c r="J26" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K26" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="1" t="n">
+        <v>93100</v>
+      </c>
+      <c r="N26" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O26" s="1" t="n">
+        <v>513000</v>
+      </c>
+      <c r="P26" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -1307,13 +1939,13 @@
         <v>9</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>660000</v>
+        <v>10200000</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>1650</v>
+        <v>25600</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>11200</v>
+        <v>324000</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>31.02</v>
@@ -1327,39 +1959,83 @@
       <c r="I27" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J27" s="1" t="inlineStr"/>
+      <c r="J27" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="K27" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="L27" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="1" t="n">
+        <v>205000</v>
+      </c>
+      <c r="N27" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O27" s="1" t="n">
+        <v>949000</v>
+      </c>
+      <c r="P27" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
         <v>25</v>
       </c>
       <c r="B28" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>910000</v>
+        <v>24600000</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>2280</v>
+        <v>61400</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>16800</v>
+        <v>967000</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>22.35</v>
+        <v>18.56</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>7.45</v>
+        <v>6.19</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>44.69</v>
+        <v>37.13</v>
       </c>
       <c r="I28" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="1" t="inlineStr">
         <is>
-          <t>보스 층</t>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K28" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L28" s="1" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="M28" s="1" t="n">
+        <v>491000</v>
+      </c>
+      <c r="N28" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O28" s="1" t="n">
+        <v>1760000</v>
+      </c>
+      <c r="P28" s="1" t="inlineStr">
+        <is>
+          <t>보스 층 · 허들</t>
         </is>
       </c>
     </row>
@@ -1371,27 +2047,51 @@
         <v>9</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>1260000</v>
+        <v>43000000</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>3140</v>
+        <v>108000</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>25300</v>
+        <v>1950000</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>7.94</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>2.65</v>
+        <v>3.18</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>51.57</v>
+        <v>61.88</v>
       </c>
       <c r="I29" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J29" s="1" t="inlineStr"/>
+      <c r="J29" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K29" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="1" t="n">
+        <v>860000</v>
+      </c>
+      <c r="N29" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O29" s="1" t="n">
+        <v>3250000</v>
+      </c>
+      <c r="P29" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -1401,13 +2101,13 @@
         <v>9</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>1730000</v>
+        <v>73100000</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>4330</v>
+        <v>183000</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>37900</v>
+        <v>3780000</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>7.94</v>
@@ -1421,7 +2121,31 @@
       <c r="I30" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J30" s="1" t="inlineStr"/>
+      <c r="J30" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="K30" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="L30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="1" t="n">
+        <v>1460000</v>
+      </c>
+      <c r="N30" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O30" s="1" t="n">
+        <v>6010000</v>
+      </c>
+      <c r="P30" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -1431,27 +2155,51 @@
         <v>9</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>2390000</v>
+        <v>154000000</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>5980</v>
+        <v>384000</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>56800</v>
+        <v>9550000</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>7.94</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>2.65</v>
+        <v>3.18</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>15.88</v>
+        <v>19.06</v>
       </c>
       <c r="I31" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J31" s="1" t="inlineStr"/>
+      <c r="J31" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K31" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="1" t="n">
+        <v>3070000</v>
+      </c>
+      <c r="N31" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O31" s="1" t="n">
+        <v>11100000</v>
+      </c>
+      <c r="P31" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -1461,13 +2209,13 @@
         <v>9</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>3300000</v>
+        <v>338000000</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>8250</v>
+        <v>844000</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>85200</v>
+        <v>25600000</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>7.94</v>
@@ -1481,39 +2229,83 @@
       <c r="I32" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J32" s="1" t="inlineStr"/>
+      <c r="J32" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="K32" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="L32" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="1" t="n">
+        <v>6760000</v>
+      </c>
+      <c r="N32" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O32" s="1" t="n">
+        <v>20600000</v>
+      </c>
+      <c r="P32" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
         <v>30</v>
       </c>
       <c r="B33" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>4560000</v>
+        <v>811000000</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>11400</v>
+        <v>2030000</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>128000</v>
+        <v>76500000</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>6.88</v>
+        <v>5.72</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>2.29</v>
+        <v>1.91</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>13.76</v>
+        <v>11.44</v>
       </c>
       <c r="I33" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="1" t="inlineStr">
         <is>
-          <t>보스 층</t>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K33" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L33" s="1" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="M33" s="1" t="n">
+        <v>16200000</v>
+      </c>
+      <c r="N33" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O33" s="1" t="n">
+        <v>38100000</v>
+      </c>
+      <c r="P33" s="1" t="inlineStr">
+        <is>
+          <t>보스 층 · 허들</t>
         </is>
       </c>
     </row>
@@ -1525,27 +2317,51 @@
         <v>9</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>6290000</v>
+        <v>1420000000</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>15700</v>
+        <v>3550000</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>192000</v>
+        <v>154000000</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>7.94</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>3.97</v>
+        <v>4.76</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>15.88</v>
+        <v>19.06</v>
       </c>
       <c r="I34" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J34" s="1" t="inlineStr"/>
+      <c r="J34" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K34" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L34" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="1" t="n">
+        <v>28400000</v>
+      </c>
+      <c r="N34" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O34" s="1" t="n">
+        <v>70400000</v>
+      </c>
+      <c r="P34" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -1555,13 +2371,13 @@
         <v>9</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>8680000</v>
+        <v>2410000000</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>21700</v>
+        <v>6030000</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>288000</v>
+        <v>299000000</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>7.94</v>
@@ -1575,7 +2391,31 @@
       <c r="I35" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J35" s="1" t="inlineStr"/>
+      <c r="J35" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="K35" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="L35" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="1" t="n">
+        <v>48200000</v>
+      </c>
+      <c r="N35" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O35" s="1" t="n">
+        <v>130000000</v>
+      </c>
+      <c r="P35" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -1585,27 +2425,51 @@
         <v>9</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>12000000</v>
+        <v>5060000000</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>29900</v>
+        <v>12700000</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>431000</v>
+        <v>755000000</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>7.94</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>2.65</v>
+        <v>3.18</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>15.88</v>
+        <v>19.06</v>
       </c>
       <c r="I36" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J36" s="1" t="inlineStr"/>
+      <c r="J36" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K36" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L36" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="1" t="n">
+        <v>101000000</v>
+      </c>
+      <c r="N36" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O36" s="1" t="n">
+        <v>241000000</v>
+      </c>
+      <c r="P36" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -1615,13 +2479,13 @@
         <v>9</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>16500000</v>
+        <v>11100000000</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>41300</v>
+        <v>27900000</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>647000</v>
+        <v>2020000000</v>
       </c>
       <c r="F37" s="1" t="n">
         <v>7.94</v>
@@ -1635,39 +2499,83 @@
       <c r="I37" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J37" s="1" t="inlineStr"/>
+      <c r="J37" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="K37" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="L37" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="1" t="n">
+        <v>223000000</v>
+      </c>
+      <c r="N37" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O37" s="1" t="n">
+        <v>446000000</v>
+      </c>
+      <c r="P37" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
         <v>35</v>
       </c>
       <c r="B38" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>22800000</v>
+        <v>26700000000</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>57000</v>
+        <v>66900000</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>971000</v>
+        <v>6040000000</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>6.88</v>
+        <v>5.72</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>2.29</v>
+        <v>1.91</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>13.76</v>
+        <v>11.44</v>
       </c>
       <c r="I38" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J38" s="1" t="inlineStr">
         <is>
-          <t>보스 층</t>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K38" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L38" s="1" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="M38" s="1" t="n">
+        <v>535000000</v>
+      </c>
+      <c r="N38" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O38" s="1" t="n">
+        <v>825000000</v>
+      </c>
+      <c r="P38" s="1" t="inlineStr">
+        <is>
+          <t>보스 층 · 허들</t>
         </is>
       </c>
     </row>
@@ -1679,27 +2587,51 @@
         <v>9</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>31500000</v>
+        <v>46800000000</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>78700</v>
+        <v>117000000</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>1460000</v>
+        <v>12200000000</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>7.94</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>2.65</v>
+        <v>3.18</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>15.88</v>
+        <v>19.06</v>
       </c>
       <c r="I39" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J39" s="1" t="inlineStr"/>
+      <c r="J39" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K39" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L39" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="1" t="n">
+        <v>936000000</v>
+      </c>
+      <c r="N39" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O39" s="1" t="n">
+        <v>1530000000</v>
+      </c>
+      <c r="P39" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -1709,13 +2641,13 @@
         <v>9</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>43400000</v>
+        <v>79600000000</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>109000</v>
+        <v>199000000</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>2180000</v>
+        <v>23600000000</v>
       </c>
       <c r="F40" s="1" t="n">
         <v>7.94</v>
@@ -1729,7 +2661,31 @@
       <c r="I40" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J40" s="1" t="inlineStr"/>
+      <c r="J40" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="K40" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="L40" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="1" t="n">
+        <v>1590000000</v>
+      </c>
+      <c r="N40" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O40" s="1" t="n">
+        <v>2820000000</v>
+      </c>
+      <c r="P40" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -1739,27 +2695,51 @@
         <v>9</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>59900000</v>
+        <v>167000000000</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>150000</v>
+        <v>418000000</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>3280000</v>
+        <v>59700000000</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>7.94</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>2.65</v>
+        <v>3.18</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>15.88</v>
+        <v>19.06</v>
       </c>
       <c r="I41" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J41" s="1" t="inlineStr"/>
+      <c r="J41" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K41" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L41" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="1" t="n">
+        <v>3340000000</v>
+      </c>
+      <c r="N41" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O41" s="1" t="n">
+        <v>5220000000</v>
+      </c>
+      <c r="P41" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -1769,13 +2749,13 @@
         <v>9</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>82700000</v>
+        <v>368000000000</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>207000</v>
+        <v>919000000</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>4910000</v>
+        <v>160000000000</v>
       </c>
       <c r="F42" s="1" t="n">
         <v>7.94</v>
@@ -1789,39 +2769,83 @@
       <c r="I42" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J42" s="1" t="inlineStr"/>
+      <c r="J42" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="K42" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="L42" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="1" t="n">
+        <v>7350000000</v>
+      </c>
+      <c r="N42" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O42" s="1" t="n">
+        <v>9660000000</v>
+      </c>
+      <c r="P42" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
         <v>40</v>
       </c>
       <c r="B43" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>114000000</v>
+        <v>882000000000</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>285000</v>
+        <v>2210000000</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>7370000</v>
+        <v>478000000000</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>6.88</v>
+        <v>5.72</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>2.29</v>
+        <v>2.86</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>13.76</v>
+        <v>11.44</v>
       </c>
       <c r="I43" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J43" s="1" t="inlineStr">
         <is>
-          <t>보스 층</t>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K43" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L43" s="1" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="M43" s="1" t="n">
+        <v>17600000000</v>
+      </c>
+      <c r="N43" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O43" s="1" t="n">
+        <v>17900000000</v>
+      </c>
+      <c r="P43" s="1" t="inlineStr">
+        <is>
+          <t>보스 층 · 허들</t>
         </is>
       </c>
     </row>
@@ -1833,27 +2857,51 @@
         <v>9</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>157000000</v>
+        <v>1540000000000</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>394000</v>
+        <v>3860000000</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>11100000</v>
+        <v>962000000000</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>7.94</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>2.65</v>
+        <v>3.18</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>15.88</v>
+        <v>19.06</v>
       </c>
       <c r="I44" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J44" s="1" t="inlineStr"/>
+      <c r="J44" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K44" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L44" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="1" t="n">
+        <v>30900000000</v>
+      </c>
+      <c r="N44" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O44" s="1" t="n">
+        <v>33100000000</v>
+      </c>
+      <c r="P44" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -1863,13 +2911,13 @@
         <v>9</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>217000000</v>
+        <v>2620000000000</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>543000</v>
+        <v>6560000000</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>16600000</v>
+        <v>1870000000000</v>
       </c>
       <c r="F45" s="1" t="n">
         <v>7.94</v>
@@ -1883,7 +2931,31 @@
       <c r="I45" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J45" s="1" t="inlineStr"/>
+      <c r="J45" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="K45" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="L45" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="1" t="n">
+        <v>52500000000</v>
+      </c>
+      <c r="N45" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O45" s="1" t="n">
+        <v>61200000000</v>
+      </c>
+      <c r="P45" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -1893,27 +2965,51 @@
         <v>9</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>300000000</v>
+        <v>5510000000000</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>750000</v>
+        <v>13800000000</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>24900000</v>
+        <v>4720000000000</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>7.94</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>3.97</v>
+        <v>4.76</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>15.88</v>
+        <v>19.06</v>
       </c>
       <c r="I46" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J46" s="1" t="inlineStr"/>
+      <c r="J46" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K46" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L46" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="1" t="n">
+        <v>110000000000</v>
+      </c>
+      <c r="N46" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O46" s="1" t="n">
+        <v>113000000000</v>
+      </c>
+      <c r="P46" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -1923,13 +3019,13 @@
         <v>9</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>414000000</v>
+        <v>12100000000000</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>1030000</v>
+        <v>30300000000</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>37300000</v>
+        <v>12600000000000</v>
       </c>
       <c r="F47" s="1" t="n">
         <v>7.94</v>
@@ -1943,39 +3039,83 @@
       <c r="I47" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J47" s="1" t="inlineStr"/>
+      <c r="J47" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="K47" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="L47" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="1" t="n">
+        <v>242000000000</v>
+      </c>
+      <c r="N47" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O47" s="1" t="n">
+        <v>209000000000</v>
+      </c>
+      <c r="P47" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
         <v>45</v>
       </c>
       <c r="B48" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>571000000</v>
+        <v>29100000000000</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>1430000</v>
+        <v>72700000000</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>56000000</v>
+        <v>37800000000000</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>6.88</v>
+        <v>5.72</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>2.29</v>
+        <v>1.91</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>13.76</v>
+        <v>11.44</v>
       </c>
       <c r="I48" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="1" t="inlineStr">
         <is>
-          <t>보스 층</t>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K48" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L48" s="1" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="M48" s="1" t="n">
+        <v>582000000000</v>
+      </c>
+      <c r="N48" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O48" s="1" t="n">
+        <v>387000000000</v>
+      </c>
+      <c r="P48" s="1" t="inlineStr">
+        <is>
+          <t>보스 층 · 허들</t>
         </is>
       </c>
     </row>
@@ -1987,27 +3127,51 @@
         <v>9</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>788000000</v>
+        <v>50900000000000</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>1970000</v>
+        <v>127000000000</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>84000000</v>
+        <v>76000000000000</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>7.94</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>2.65</v>
+        <v>3.18</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>15.88</v>
+        <v>19.06</v>
       </c>
       <c r="I49" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J49" s="1" t="inlineStr"/>
+      <c r="J49" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K49" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L49" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="1" t="n">
+        <v>1020000000000</v>
+      </c>
+      <c r="N49" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O49" s="1" t="n">
+        <v>716000000000</v>
+      </c>
+      <c r="P49" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -2017,13 +3181,13 @@
         <v>9</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>1090000000</v>
+        <v>86600000000000</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>2720000</v>
+        <v>216000000000</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>126000000</v>
+        <v>148000000000000</v>
       </c>
       <c r="F50" s="1" t="n">
         <v>7.94</v>
@@ -2037,7 +3201,31 @@
       <c r="I50" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J50" s="1" t="inlineStr"/>
+      <c r="J50" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="K50" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="L50" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="1" t="n">
+        <v>1730000000000</v>
+      </c>
+      <c r="N50" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O50" s="1" t="n">
+        <v>1330000000000</v>
+      </c>
+      <c r="P50" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -2047,27 +3235,51 @@
         <v>9</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>1500000000</v>
+        <v>182000000000000</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>3750000</v>
+        <v>454000000000</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>189000000</v>
+        <v>373000000000000</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>7.94</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>3.97</v>
+        <v>4.76</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>15.88</v>
+        <v>19.06</v>
       </c>
       <c r="I51" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J51" s="1" t="inlineStr"/>
+      <c r="J51" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K51" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L51" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="1" t="n">
+        <v>3640000000000</v>
+      </c>
+      <c r="N51" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O51" s="1" t="n">
+        <v>2450000000000</v>
+      </c>
+      <c r="P51" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -2077,13 +3289,13 @@
         <v>9</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>2070000000</v>
+        <v>400000000000000</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>5180000</v>
+        <v>1000000000000</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>283000000</v>
+        <v>1000000000000000</v>
       </c>
       <c r="F52" s="1" t="n">
         <v>7.94</v>
@@ -2097,39 +3309,83 @@
       <c r="I52" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J52" s="1" t="inlineStr"/>
+      <c r="J52" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="K52" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="L52" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="1" t="n">
+        <v>8000000000000</v>
+      </c>
+      <c r="N52" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O52" s="1" t="n">
+        <v>4540000000000</v>
+      </c>
+      <c r="P52" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
         <v>50</v>
       </c>
       <c r="B53" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>2860000000</v>
+        <v>960000000000000</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>7150000</v>
+        <v>2400000000000</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>425000000</v>
+        <v>2990000000000000</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>6.88</v>
+        <v>5.72</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>2.29</v>
+        <v>2.86</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>13.76</v>
+        <v>11.44</v>
       </c>
       <c r="I53" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J53" s="1" t="inlineStr">
         <is>
-          <t>보스 층</t>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K53" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L53" s="1" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="M53" s="1" t="n">
+        <v>19200000000000</v>
+      </c>
+      <c r="N53" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O53" s="1" t="n">
+        <v>8390000000000</v>
+      </c>
+      <c r="P53" s="1" t="inlineStr">
+        <is>
+          <t>보스 층 · 허들</t>
         </is>
       </c>
     </row>
@@ -2144,7 +3400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2271,6 +3527,66 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>floor_type</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>Stage: 층 유형 (층 별 허들 기획서 Ver02): 도입·쉬움·보통·어려움·허들. 목표 돌파 시간과 적정 찍찍 배율이 유형별</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>target_sec / boss_sec</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>Stage: 적정 찍찍일 때 목표 돌파 초 (제한 180초의 60·75·90%) · 그중 보스전 목표 초 (보스 테이블 hp_pow_sec 로 맞춤)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>Stage: 층 클리어(계단) 연구자료 = 8 × 난이도 지수 (Heist). 뽑기 비용 단위 BR = 최고 도달 층의 이 값</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>skip_cap</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>Stage: 이 층을 최고로 클리어했을 때 고를 수 있는 가장 높은 시작 층 (기획서 26장). 실제 = min(1 + 스테이지 스킵 노드 합, 이 값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>player_pow</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>Stage: 기획서 플레이어 기준 전투력 (1층 = 100 지수). 측정 비교용 (게임은 안 씀)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data_Table/스테이지 테이블.xlsx
+++ b/Data_Table/스테이지 테이블.xlsx
@@ -697,7 +697,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>1</v>

--- a/Data_Table/스테이지 테이블.xlsx
+++ b/Data_Table/스테이지 테이블.xlsx
@@ -1812,7 +1812,7 @@
         <v>26100</v>
       </c>
       <c r="N24" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O24" s="1" t="n">
         <v>150000</v>
@@ -1866,7 +1866,7 @@
         <v>44300</v>
       </c>
       <c r="N25" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O25" s="1" t="n">
         <v>277000</v>
@@ -1920,7 +1920,7 @@
         <v>93100</v>
       </c>
       <c r="N26" s="1" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="O26" s="1" t="n">
         <v>513000</v>
@@ -1974,7 +1974,7 @@
         <v>205000</v>
       </c>
       <c r="N27" s="1" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="O27" s="1" t="n">
         <v>949000</v>
@@ -2028,7 +2028,7 @@
         <v>491000</v>
       </c>
       <c r="N28" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O28" s="1" t="n">
         <v>1760000</v>
@@ -2082,7 +2082,7 @@
         <v>860000</v>
       </c>
       <c r="N29" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O29" s="1" t="n">
         <v>3250000</v>
@@ -2136,7 +2136,7 @@
         <v>1460000</v>
       </c>
       <c r="N30" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O30" s="1" t="n">
         <v>6010000</v>
@@ -2190,7 +2190,7 @@
         <v>3070000</v>
       </c>
       <c r="N31" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O31" s="1" t="n">
         <v>11100000</v>
@@ -2244,7 +2244,7 @@
         <v>6760000</v>
       </c>
       <c r="N32" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O32" s="1" t="n">
         <v>20600000</v>
@@ -2298,7 +2298,7 @@
         <v>16200000</v>
       </c>
       <c r="N33" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O33" s="1" t="n">
         <v>38100000</v>
@@ -2352,7 +2352,7 @@
         <v>28400000</v>
       </c>
       <c r="N34" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O34" s="1" t="n">
         <v>70400000</v>
@@ -2406,7 +2406,7 @@
         <v>48200000</v>
       </c>
       <c r="N35" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O35" s="1" t="n">
         <v>130000000</v>
@@ -2460,7 +2460,7 @@
         <v>101000000</v>
       </c>
       <c r="N36" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O36" s="1" t="n">
         <v>241000000</v>
@@ -2514,7 +2514,7 @@
         <v>223000000</v>
       </c>
       <c r="N37" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O37" s="1" t="n">
         <v>446000000</v>
@@ -2568,7 +2568,7 @@
         <v>535000000</v>
       </c>
       <c r="N38" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O38" s="1" t="n">
         <v>825000000</v>
@@ -2622,7 +2622,7 @@
         <v>936000000</v>
       </c>
       <c r="N39" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O39" s="1" t="n">
         <v>1530000000</v>
@@ -2676,7 +2676,7 @@
         <v>1590000000</v>
       </c>
       <c r="N40" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O40" s="1" t="n">
         <v>2820000000</v>
@@ -2730,7 +2730,7 @@
         <v>3340000000</v>
       </c>
       <c r="N41" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O41" s="1" t="n">
         <v>5220000000</v>
@@ -2784,7 +2784,7 @@
         <v>7350000000</v>
       </c>
       <c r="N42" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O42" s="1" t="n">
         <v>9660000000</v>
@@ -2838,7 +2838,7 @@
         <v>17600000000</v>
       </c>
       <c r="N43" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O43" s="1" t="n">
         <v>17900000000</v>
@@ -2892,7 +2892,7 @@
         <v>30900000000</v>
       </c>
       <c r="N44" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O44" s="1" t="n">
         <v>33100000000</v>
@@ -2946,7 +2946,7 @@
         <v>52500000000</v>
       </c>
       <c r="N45" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O45" s="1" t="n">
         <v>61200000000</v>
@@ -3000,7 +3000,7 @@
         <v>110000000000</v>
       </c>
       <c r="N46" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O46" s="1" t="n">
         <v>113000000000</v>
@@ -3054,7 +3054,7 @@
         <v>242000000000</v>
       </c>
       <c r="N47" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O47" s="1" t="n">
         <v>209000000000</v>
@@ -3108,7 +3108,7 @@
         <v>582000000000</v>
       </c>
       <c r="N48" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O48" s="1" t="n">
         <v>387000000000</v>
@@ -3162,7 +3162,7 @@
         <v>1020000000000</v>
       </c>
       <c r="N49" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O49" s="1" t="n">
         <v>716000000000</v>
@@ -3216,7 +3216,7 @@
         <v>1730000000000</v>
       </c>
       <c r="N50" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O50" s="1" t="n">
         <v>1330000000000</v>
@@ -3270,7 +3270,7 @@
         <v>3640000000000</v>
       </c>
       <c r="N51" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O51" s="1" t="n">
         <v>2450000000000</v>
@@ -3324,7 +3324,7 @@
         <v>8000000000000</v>
       </c>
       <c r="N52" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O52" s="1" t="n">
         <v>4540000000000</v>
@@ -3378,7 +3378,7 @@
         <v>19200000000000</v>
       </c>
       <c r="N53" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O53" s="1" t="n">
         <v>8390000000000</v>

--- a/Data_Table/스테이지 테이블.xlsx
+++ b/Data_Table/스테이지 테이블.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P53"/>
+  <dimension ref="A1:P103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2317,13 +2317,13 @@
         <v>9</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>1420000000</v>
+        <v>908000000</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>3550000</v>
+        <v>2270000</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>154000000</v>
+        <v>88100000</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>9.529999999999999</v>
@@ -2349,13 +2349,13 @@
         <v>0</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>28400000</v>
+        <v>18200000</v>
       </c>
       <c r="N34" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O34" s="1" t="n">
-        <v>70400000</v>
+        <v>42600000</v>
       </c>
       <c r="P34" s="1" t="inlineStr">
         <is>
@@ -2371,13 +2371,13 @@
         <v>9</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>2410000000</v>
+        <v>981000000</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>6030000</v>
+        <v>2450000</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>299000000</v>
+        <v>97000000</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>7.94</v>
@@ -2403,13 +2403,13 @@
         <v>0</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>48200000</v>
+        <v>19600000</v>
       </c>
       <c r="N35" s="1" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="O35" s="1" t="n">
-        <v>130000000</v>
+        <v>46000000</v>
       </c>
       <c r="P35" s="1" t="inlineStr">
         <is>
@@ -2425,13 +2425,13 @@
         <v>9</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>5060000000</v>
+        <v>1120000000</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>12700000</v>
+        <v>2790000</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>755000000</v>
+        <v>114000000</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>9.529999999999999</v>
@@ -2457,13 +2457,13 @@
         <v>0</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>101000000</v>
+        <v>22400000</v>
       </c>
       <c r="N36" s="1" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="O36" s="1" t="n">
-        <v>241000000</v>
+        <v>52500000</v>
       </c>
       <c r="P36" s="1" t="inlineStr">
         <is>
@@ -2479,13 +2479,13 @@
         <v>9</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>11100000000</v>
+        <v>1210000000</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>27900000</v>
+        <v>3020000</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>2020000000</v>
+        <v>126000000</v>
       </c>
       <c r="F37" s="1" t="n">
         <v>7.94</v>
@@ -2511,13 +2511,13 @@
         <v>0</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>223000000</v>
+        <v>24100000</v>
       </c>
       <c r="N37" s="1" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="O37" s="1" t="n">
-        <v>446000000</v>
+        <v>56700000</v>
       </c>
       <c r="P37" s="1" t="inlineStr">
         <is>
@@ -2533,13 +2533,13 @@
         <v>9</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>26700000000</v>
+        <v>1400000000</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>66900000</v>
+        <v>3500000</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>6040000000</v>
+        <v>151000000</v>
       </c>
       <c r="F38" s="1" t="n">
         <v>5.72</v>
@@ -2565,13 +2565,13 @@
         <v>64.8</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>535000000</v>
+        <v>28000000</v>
       </c>
       <c r="N38" s="1" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="O38" s="1" t="n">
-        <v>825000000</v>
+        <v>65700000</v>
       </c>
       <c r="P38" s="1" t="inlineStr">
         <is>
@@ -2587,13 +2587,13 @@
         <v>9</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46800000000</v>
+        <v>1570000000</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>117000000</v>
+        <v>3920000</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>12200000000</v>
+        <v>174000000</v>
       </c>
       <c r="F39" s="1" t="n">
         <v>9.529999999999999</v>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>936000000</v>
+        <v>31400000</v>
       </c>
       <c r="N39" s="1" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="O39" s="1" t="n">
-        <v>1530000000</v>
+        <v>73600000</v>
       </c>
       <c r="P39" s="1" t="inlineStr">
         <is>
@@ -2641,13 +2641,13 @@
         <v>9</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>79600000000</v>
+        <v>1690000000</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>199000000</v>
+        <v>4230000</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>23600000000</v>
+        <v>192000000</v>
       </c>
       <c r="F40" s="1" t="n">
         <v>7.94</v>
@@ -2673,13 +2673,13 @@
         <v>0</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>1590000000</v>
+        <v>33900000</v>
       </c>
       <c r="N40" s="1" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="O40" s="1" t="n">
-        <v>2820000000</v>
+        <v>79500000</v>
       </c>
       <c r="P40" s="1" t="inlineStr">
         <is>
@@ -2695,13 +2695,13 @@
         <v>9</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>167000000000</v>
+        <v>1930000000</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>418000000</v>
+        <v>4830000</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>59700000000</v>
+        <v>226000000</v>
       </c>
       <c r="F41" s="1" t="n">
         <v>9.529999999999999</v>
@@ -2727,13 +2727,13 @@
         <v>0</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>3340000000</v>
+        <v>38600000</v>
       </c>
       <c r="N41" s="1" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="O41" s="1" t="n">
-        <v>5220000000</v>
+        <v>90600000</v>
       </c>
       <c r="P41" s="1" t="inlineStr">
         <is>
@@ -2749,13 +2749,13 @@
         <v>9</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>368000000000</v>
+        <v>2090000000</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>919000000</v>
+        <v>5210000</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>160000000000</v>
+        <v>249000000</v>
       </c>
       <c r="F42" s="1" t="n">
         <v>7.94</v>
@@ -2781,13 +2781,13 @@
         <v>0</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>7350000000</v>
+        <v>41700000</v>
       </c>
       <c r="N42" s="1" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="O42" s="1" t="n">
-        <v>9660000000</v>
+        <v>97900000</v>
       </c>
       <c r="P42" s="1" t="inlineStr">
         <is>
@@ -2803,13 +2803,13 @@
         <v>9</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>882000000000</v>
+        <v>2420000000</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>2210000000</v>
+        <v>6050000</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>478000000000</v>
+        <v>300000000</v>
       </c>
       <c r="F43" s="1" t="n">
         <v>5.72</v>
@@ -2835,13 +2835,13 @@
         <v>64.8</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>17600000000</v>
+        <v>48400000</v>
       </c>
       <c r="N43" s="1" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="O43" s="1" t="n">
-        <v>17900000000</v>
+        <v>114000000</v>
       </c>
       <c r="P43" s="1" t="inlineStr">
         <is>
@@ -2857,13 +2857,13 @@
         <v>9</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>1540000000000</v>
+        <v>2710000000</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>3860000000</v>
+        <v>6770000</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>962000000000</v>
+        <v>346000000</v>
       </c>
       <c r="F44" s="1" t="n">
         <v>9.529999999999999</v>
@@ -2889,13 +2889,13 @@
         <v>0</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>30900000000</v>
+        <v>54200000</v>
       </c>
       <c r="N44" s="1" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="O44" s="1" t="n">
-        <v>33100000000</v>
+        <v>127000000</v>
       </c>
       <c r="P44" s="1" t="inlineStr">
         <is>
@@ -2911,13 +2911,13 @@
         <v>9</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>2620000000000</v>
+        <v>2930000000</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>6560000000</v>
+        <v>7320000</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>1870000000000</v>
+        <v>380000000</v>
       </c>
       <c r="F45" s="1" t="n">
         <v>7.94</v>
@@ -2943,13 +2943,13 @@
         <v>0</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>52500000000</v>
+        <v>58500000</v>
       </c>
       <c r="N45" s="1" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="O45" s="1" t="n">
-        <v>61200000000</v>
+        <v>137000000</v>
       </c>
       <c r="P45" s="1" t="inlineStr">
         <is>
@@ -2965,13 +2965,13 @@
         <v>9</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>5510000000000</v>
+        <v>3340000000</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>13800000000</v>
+        <v>8340000</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>4720000000000</v>
+        <v>448000000</v>
       </c>
       <c r="F46" s="1" t="n">
         <v>9.529999999999999</v>
@@ -2997,13 +2997,13 @@
         <v>0</v>
       </c>
       <c r="M46" s="1" t="n">
-        <v>110000000000</v>
+        <v>66700000</v>
       </c>
       <c r="N46" s="1" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="O46" s="1" t="n">
-        <v>113000000000</v>
+        <v>157000000</v>
       </c>
       <c r="P46" s="1" t="inlineStr">
         <is>
@@ -3019,13 +3019,13 @@
         <v>9</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>12100000000000</v>
+        <v>3600000000</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>30300000000</v>
+        <v>9010000</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>12600000000000</v>
+        <v>493000000</v>
       </c>
       <c r="F47" s="1" t="n">
         <v>7.94</v>
@@ -3051,13 +3051,13 @@
         <v>0</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>242000000000</v>
+        <v>72100000</v>
       </c>
       <c r="N47" s="1" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="O47" s="1" t="n">
-        <v>209000000000</v>
+        <v>169000000</v>
       </c>
       <c r="P47" s="1" t="inlineStr">
         <is>
@@ -3073,13 +3073,13 @@
         <v>9</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>29100000000000</v>
+        <v>4180000000</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>72700000000</v>
+        <v>10400000</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>37800000000000</v>
+        <v>594000000</v>
       </c>
       <c r="F48" s="1" t="n">
         <v>5.72</v>
@@ -3105,13 +3105,13 @@
         <v>64.8</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>582000000000</v>
+        <v>83600000</v>
       </c>
       <c r="N48" s="1" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="O48" s="1" t="n">
-        <v>387000000000</v>
+        <v>196000000</v>
       </c>
       <c r="P48" s="1" t="inlineStr">
         <is>
@@ -3127,13 +3127,13 @@
         <v>9</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>50900000000000</v>
+        <v>4680000000</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>127000000000</v>
+        <v>11700000</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>76000000000000</v>
+        <v>684000000</v>
       </c>
       <c r="F49" s="1" t="n">
         <v>9.529999999999999</v>
@@ -3159,13 +3159,13 @@
         <v>0</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>1020000000000</v>
+        <v>93600000</v>
       </c>
       <c r="N49" s="1" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="O49" s="1" t="n">
-        <v>716000000000</v>
+        <v>220000000</v>
       </c>
       <c r="P49" s="1" t="inlineStr">
         <is>
@@ -3181,13 +3181,13 @@
         <v>9</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>86600000000000</v>
+        <v>5060000000</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>216000000000</v>
+        <v>12600000</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>148000000000000</v>
+        <v>754000000</v>
       </c>
       <c r="F50" s="1" t="n">
         <v>7.94</v>
@@ -3213,13 +3213,13 @@
         <v>0</v>
       </c>
       <c r="M50" s="1" t="n">
-        <v>1730000000000</v>
+        <v>101000000</v>
       </c>
       <c r="N50" s="1" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="O50" s="1" t="n">
-        <v>1330000000000</v>
+        <v>237000000</v>
       </c>
       <c r="P50" s="1" t="inlineStr">
         <is>
@@ -3235,13 +3235,13 @@
         <v>9</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>182000000000000</v>
+        <v>5760000000</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>454000000000</v>
+        <v>14400000</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>373000000000000</v>
+        <v>888000000</v>
       </c>
       <c r="F51" s="1" t="n">
         <v>9.529999999999999</v>
@@ -3267,13 +3267,13 @@
         <v>0</v>
       </c>
       <c r="M51" s="1" t="n">
-        <v>3640000000000</v>
+        <v>115000000</v>
       </c>
       <c r="N51" s="1" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="O51" s="1" t="n">
-        <v>2450000000000</v>
+        <v>271000000</v>
       </c>
       <c r="P51" s="1" t="inlineStr">
         <is>
@@ -3289,13 +3289,13 @@
         <v>9</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>400000000000000</v>
+        <v>6220000000</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>1000000000000</v>
+        <v>15600000</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>1000000000000000</v>
+        <v>977000000</v>
       </c>
       <c r="F52" s="1" t="n">
         <v>7.94</v>
@@ -3321,13 +3321,13 @@
         <v>0</v>
       </c>
       <c r="M52" s="1" t="n">
-        <v>8000000000000</v>
+        <v>124000000</v>
       </c>
       <c r="N52" s="1" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="O52" s="1" t="n">
-        <v>4540000000000</v>
+        <v>292000000</v>
       </c>
       <c r="P52" s="1" t="inlineStr">
         <is>
@@ -3343,13 +3343,13 @@
         <v>9</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>960000000000000</v>
+        <v>7220000000</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>2400000000000</v>
+        <v>18000000</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>2990000000000000</v>
+        <v>1180000000</v>
       </c>
       <c r="F53" s="1" t="n">
         <v>5.72</v>
@@ -3375,15 +3375,2715 @@
         <v>64.8</v>
       </c>
       <c r="M53" s="1" t="n">
-        <v>19200000000000</v>
+        <v>144000000</v>
       </c>
       <c r="N53" s="1" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="O53" s="1" t="n">
-        <v>8390000000000</v>
+        <v>339000000</v>
       </c>
       <c r="P53" s="1" t="inlineStr">
+        <is>
+          <t>보스 층 · 허들</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>51</v>
+      </c>
+      <c r="B54" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C54" s="1" t="n">
+        <v>8090000000</v>
+      </c>
+      <c r="D54" s="1" t="n">
+        <v>20200000</v>
+      </c>
+      <c r="E54" s="1" t="n">
+        <v>1360000000</v>
+      </c>
+      <c r="F54" s="1" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="G54" s="1" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H54" s="1" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="I54" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K54" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L54" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="1" t="n">
+        <v>162000000</v>
+      </c>
+      <c r="N54" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="O54" s="1" t="n">
+        <v>380000000</v>
+      </c>
+      <c r="P54" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B55" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C55" s="1" t="n">
+        <v>8730000000</v>
+      </c>
+      <c r="D55" s="1" t="n">
+        <v>21800000</v>
+      </c>
+      <c r="E55" s="1" t="n">
+        <v>1490000000</v>
+      </c>
+      <c r="F55" s="1" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="G55" s="1" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="H55" s="1" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="I55" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="K55" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="L55" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="1" t="n">
+        <v>175000000</v>
+      </c>
+      <c r="N55" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="O55" s="1" t="n">
+        <v>410000000</v>
+      </c>
+      <c r="P55" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>53</v>
+      </c>
+      <c r="B56" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C56" s="1" t="n">
+        <v>9960000000</v>
+      </c>
+      <c r="D56" s="1" t="n">
+        <v>24900000</v>
+      </c>
+      <c r="E56" s="1" t="n">
+        <v>1760000000</v>
+      </c>
+      <c r="F56" s="1" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="G56" s="1" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H56" s="1" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="I56" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K56" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L56" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="1" t="n">
+        <v>199000000</v>
+      </c>
+      <c r="N56" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="O56" s="1" t="n">
+        <v>467000000</v>
+      </c>
+      <c r="P56" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="B57" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C57" s="1" t="n">
+        <v>10800000000</v>
+      </c>
+      <c r="D57" s="1" t="n">
+        <v>26900000</v>
+      </c>
+      <c r="E57" s="1" t="n">
+        <v>1940000000</v>
+      </c>
+      <c r="F57" s="1" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="G57" s="1" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="H57" s="1" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="I57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="K57" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="L57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" s="1" t="n">
+        <v>215000000</v>
+      </c>
+      <c r="N57" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="O57" s="1" t="n">
+        <v>505000000</v>
+      </c>
+      <c r="P57" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="B58" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C58" s="1" t="n">
+        <v>12500000000</v>
+      </c>
+      <c r="D58" s="1" t="n">
+        <v>31200000</v>
+      </c>
+      <c r="E58" s="1" t="n">
+        <v>2330000000</v>
+      </c>
+      <c r="F58" s="1" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="G58" s="1" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H58" s="1" t="n">
+        <v>11.44</v>
+      </c>
+      <c r="I58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K58" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L58" s="1" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="M58" s="1" t="n">
+        <v>249000000</v>
+      </c>
+      <c r="N58" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="O58" s="1" t="n">
+        <v>585000000</v>
+      </c>
+      <c r="P58" s="1" t="inlineStr">
+        <is>
+          <t>보스 층 · 허들</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="B59" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C59" s="1" t="n">
+        <v>14000000000</v>
+      </c>
+      <c r="D59" s="1" t="n">
+        <v>34900000</v>
+      </c>
+      <c r="E59" s="1" t="n">
+        <v>2680000000</v>
+      </c>
+      <c r="F59" s="1" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="G59" s="1" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="H59" s="1" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="I59" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K59" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L59" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" s="1" t="n">
+        <v>279000000</v>
+      </c>
+      <c r="N59" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="O59" s="1" t="n">
+        <v>656000000</v>
+      </c>
+      <c r="P59" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>57</v>
+      </c>
+      <c r="B60" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C60" s="1" t="n">
+        <v>15100000000</v>
+      </c>
+      <c r="D60" s="1" t="n">
+        <v>37700000</v>
+      </c>
+      <c r="E60" s="1" t="n">
+        <v>2960000000</v>
+      </c>
+      <c r="F60" s="1" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="G60" s="1" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="H60" s="1" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="I60" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="K60" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="L60" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="1" t="n">
+        <v>302000000</v>
+      </c>
+      <c r="N60" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="O60" s="1" t="n">
+        <v>708000000</v>
+      </c>
+      <c r="P60" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>58</v>
+      </c>
+      <c r="B61" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C61" s="1" t="n">
+        <v>17200000000</v>
+      </c>
+      <c r="D61" s="1" t="n">
+        <v>43000000</v>
+      </c>
+      <c r="E61" s="1" t="n">
+        <v>3480000000</v>
+      </c>
+      <c r="F61" s="1" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="G61" s="1" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="H61" s="1" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="I61" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K61" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L61" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" s="1" t="n">
+        <v>344000000</v>
+      </c>
+      <c r="N61" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="O61" s="1" t="n">
+        <v>807000000</v>
+      </c>
+      <c r="P61" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="B62" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C62" s="1" t="n">
+        <v>18600000000</v>
+      </c>
+      <c r="D62" s="1" t="n">
+        <v>46400000</v>
+      </c>
+      <c r="E62" s="1" t="n">
+        <v>3830000000</v>
+      </c>
+      <c r="F62" s="1" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="G62" s="1" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="H62" s="1" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="I62" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="K62" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="L62" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="1" t="n">
+        <v>372000000</v>
+      </c>
+      <c r="N62" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="O62" s="1" t="n">
+        <v>872000000</v>
+      </c>
+      <c r="P62" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="B63" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C63" s="1" t="n">
+        <v>21500000000</v>
+      </c>
+      <c r="D63" s="1" t="n">
+        <v>53900000</v>
+      </c>
+      <c r="E63" s="1" t="n">
+        <v>4610000000</v>
+      </c>
+      <c r="F63" s="1" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="G63" s="1" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H63" s="1" t="n">
+        <v>11.44</v>
+      </c>
+      <c r="I63" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K63" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L63" s="1" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="M63" s="1" t="n">
+        <v>431000000</v>
+      </c>
+      <c r="N63" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="O63" s="1" t="n">
+        <v>1010000000</v>
+      </c>
+      <c r="P63" s="1" t="inlineStr">
+        <is>
+          <t>보스 층 · 허들</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>61</v>
+      </c>
+      <c r="B64" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C64" s="1" t="n">
+        <v>24100000000</v>
+      </c>
+      <c r="D64" s="1" t="n">
+        <v>60300000</v>
+      </c>
+      <c r="E64" s="1" t="n">
+        <v>5320000000</v>
+      </c>
+      <c r="F64" s="1" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="G64" s="1" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H64" s="1" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="I64" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K64" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L64" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" s="1" t="n">
+        <v>483000000</v>
+      </c>
+      <c r="N64" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="O64" s="1" t="n">
+        <v>1130000000</v>
+      </c>
+      <c r="P64" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>62</v>
+      </c>
+      <c r="B65" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C65" s="1" t="n">
+        <v>26100000000</v>
+      </c>
+      <c r="D65" s="1" t="n">
+        <v>65200000</v>
+      </c>
+      <c r="E65" s="1" t="n">
+        <v>5850000000</v>
+      </c>
+      <c r="F65" s="1" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="G65" s="1" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="H65" s="1" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="I65" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="K65" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="L65" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" s="1" t="n">
+        <v>521000000</v>
+      </c>
+      <c r="N65" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="O65" s="1" t="n">
+        <v>1220000000</v>
+      </c>
+      <c r="P65" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>63</v>
+      </c>
+      <c r="B66" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C66" s="1" t="n">
+        <v>29700000000</v>
+      </c>
+      <c r="D66" s="1" t="n">
+        <v>74300000</v>
+      </c>
+      <c r="E66" s="1" t="n">
+        <v>6900000000</v>
+      </c>
+      <c r="F66" s="1" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="G66" s="1" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H66" s="1" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="I66" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K66" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L66" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" s="1" t="n">
+        <v>594000000</v>
+      </c>
+      <c r="N66" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="O66" s="1" t="n">
+        <v>1390000000</v>
+      </c>
+      <c r="P66" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="B67" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C67" s="1" t="n">
+        <v>32100000000</v>
+      </c>
+      <c r="D67" s="1" t="n">
+        <v>80200000</v>
+      </c>
+      <c r="E67" s="1" t="n">
+        <v>7590000000</v>
+      </c>
+      <c r="F67" s="1" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="G67" s="1" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="H67" s="1" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="I67" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="K67" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="L67" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" s="1" t="n">
+        <v>642000000</v>
+      </c>
+      <c r="N67" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="O67" s="1" t="n">
+        <v>1510000000</v>
+      </c>
+      <c r="P67" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="B68" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C68" s="1" t="n">
+        <v>37200000000</v>
+      </c>
+      <c r="D68" s="1" t="n">
+        <v>93100000</v>
+      </c>
+      <c r="E68" s="1" t="n">
+        <v>9140000000</v>
+      </c>
+      <c r="F68" s="1" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="G68" s="1" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H68" s="1" t="n">
+        <v>11.44</v>
+      </c>
+      <c r="I68" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K68" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L68" s="1" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="M68" s="1" t="n">
+        <v>744000000</v>
+      </c>
+      <c r="N68" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="O68" s="1" t="n">
+        <v>1750000000</v>
+      </c>
+      <c r="P68" s="1" t="inlineStr">
+        <is>
+          <t>보스 층 · 허들</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>66</v>
+      </c>
+      <c r="B69" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C69" s="1" t="n">
+        <v>41700000000</v>
+      </c>
+      <c r="D69" s="1" t="n">
+        <v>104000000</v>
+      </c>
+      <c r="E69" s="1" t="n">
+        <v>10500000000</v>
+      </c>
+      <c r="F69" s="1" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="G69" s="1" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="H69" s="1" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="I69" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K69" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L69" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" s="1" t="n">
+        <v>834000000</v>
+      </c>
+      <c r="N69" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="O69" s="1" t="n">
+        <v>1960000000</v>
+      </c>
+      <c r="P69" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>67</v>
+      </c>
+      <c r="B70" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C70" s="1" t="n">
+        <v>45000000000</v>
+      </c>
+      <c r="D70" s="1" t="n">
+        <v>113000000</v>
+      </c>
+      <c r="E70" s="1" t="n">
+        <v>11600000000</v>
+      </c>
+      <c r="F70" s="1" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="G70" s="1" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="H70" s="1" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="I70" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="K70" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="L70" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" s="1" t="n">
+        <v>901000000</v>
+      </c>
+      <c r="N70" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="O70" s="1" t="n">
+        <v>2110000000</v>
+      </c>
+      <c r="P70" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>68</v>
+      </c>
+      <c r="B71" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C71" s="1" t="n">
+        <v>51300000000</v>
+      </c>
+      <c r="D71" s="1" t="n">
+        <v>128000000</v>
+      </c>
+      <c r="E71" s="1" t="n">
+        <v>13700000000</v>
+      </c>
+      <c r="F71" s="1" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="G71" s="1" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="H71" s="1" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="I71" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K71" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L71" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="1" t="n">
+        <v>1030000000</v>
+      </c>
+      <c r="N71" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="O71" s="1" t="n">
+        <v>2410000000</v>
+      </c>
+      <c r="P71" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="B72" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C72" s="1" t="n">
+        <v>55400000000</v>
+      </c>
+      <c r="D72" s="1" t="n">
+        <v>139000000</v>
+      </c>
+      <c r="E72" s="1" t="n">
+        <v>15000000000</v>
+      </c>
+      <c r="F72" s="1" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="G72" s="1" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="H72" s="1" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="I72" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="K72" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="L72" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" s="1" t="n">
+        <v>1110000000</v>
+      </c>
+      <c r="N72" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="O72" s="1" t="n">
+        <v>2600000000</v>
+      </c>
+      <c r="P72" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="B73" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C73" s="1" t="n">
+        <v>64300000000</v>
+      </c>
+      <c r="D73" s="1" t="n">
+        <v>161000000</v>
+      </c>
+      <c r="E73" s="1" t="n">
+        <v>18100000000</v>
+      </c>
+      <c r="F73" s="1" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="G73" s="1" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="H73" s="1" t="n">
+        <v>11.44</v>
+      </c>
+      <c r="I73" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K73" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L73" s="1" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="M73" s="1" t="n">
+        <v>1290000000</v>
+      </c>
+      <c r="N73" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="O73" s="1" t="n">
+        <v>3020000000</v>
+      </c>
+      <c r="P73" s="1" t="inlineStr">
+        <is>
+          <t>보스 층 · 허들</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>71</v>
+      </c>
+      <c r="B74" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C74" s="1" t="n">
+        <v>72000000000</v>
+      </c>
+      <c r="D74" s="1" t="n">
+        <v>180000000</v>
+      </c>
+      <c r="E74" s="1" t="n">
+        <v>20900000000</v>
+      </c>
+      <c r="F74" s="1" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="G74" s="1" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H74" s="1" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="I74" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K74" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L74" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" s="1" t="n">
+        <v>1440000000</v>
+      </c>
+      <c r="N74" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="O74" s="1" t="n">
+        <v>3380000000</v>
+      </c>
+      <c r="P74" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>72</v>
+      </c>
+      <c r="B75" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C75" s="1" t="n">
+        <v>77800000000</v>
+      </c>
+      <c r="D75" s="1" t="n">
+        <v>194000000</v>
+      </c>
+      <c r="E75" s="1" t="n">
+        <v>23000000000</v>
+      </c>
+      <c r="F75" s="1" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="G75" s="1" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="H75" s="1" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="I75" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="K75" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="L75" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" s="1" t="n">
+        <v>1560000000</v>
+      </c>
+      <c r="N75" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="O75" s="1" t="n">
+        <v>3650000000</v>
+      </c>
+      <c r="P75" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>73</v>
+      </c>
+      <c r="B76" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C76" s="1" t="n">
+        <v>88700000000</v>
+      </c>
+      <c r="D76" s="1" t="n">
+        <v>222000000</v>
+      </c>
+      <c r="E76" s="1" t="n">
+        <v>27100000000</v>
+      </c>
+      <c r="F76" s="1" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="G76" s="1" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H76" s="1" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="I76" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K76" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L76" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" s="1" t="n">
+        <v>1770000000</v>
+      </c>
+      <c r="N76" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="O76" s="1" t="n">
+        <v>4160000000</v>
+      </c>
+      <c r="P76" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>74</v>
+      </c>
+      <c r="B77" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C77" s="1" t="n">
+        <v>95800000000</v>
+      </c>
+      <c r="D77" s="1" t="n">
+        <v>239000000</v>
+      </c>
+      <c r="E77" s="1" t="n">
+        <v>29800000000</v>
+      </c>
+      <c r="F77" s="1" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="G77" s="1" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="H77" s="1" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="I77" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="K77" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="L77" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" s="1" t="n">
+        <v>1920000000</v>
+      </c>
+      <c r="N77" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="O77" s="1" t="n">
+        <v>4500000000</v>
+      </c>
+      <c r="P77" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="B78" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C78" s="1" t="n">
+        <v>111000000000</v>
+      </c>
+      <c r="D78" s="1" t="n">
+        <v>278000000</v>
+      </c>
+      <c r="E78" s="1" t="n">
+        <v>35900000000</v>
+      </c>
+      <c r="F78" s="1" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="G78" s="1" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H78" s="1" t="n">
+        <v>11.44</v>
+      </c>
+      <c r="I78" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K78" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L78" s="1" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="M78" s="1" t="n">
+        <v>2220000000</v>
+      </c>
+      <c r="N78" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="O78" s="1" t="n">
+        <v>5210000000</v>
+      </c>
+      <c r="P78" s="1" t="inlineStr">
+        <is>
+          <t>보스 층 · 허들</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>76</v>
+      </c>
+      <c r="B79" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C79" s="1" t="n">
+        <v>124000000000</v>
+      </c>
+      <c r="D79" s="1" t="n">
+        <v>311000000</v>
+      </c>
+      <c r="E79" s="1" t="n">
+        <v>41300000000</v>
+      </c>
+      <c r="F79" s="1" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="G79" s="1" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H79" s="1" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="I79" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K79" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L79" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="1" t="n">
+        <v>2490000000</v>
+      </c>
+      <c r="N79" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="O79" s="1" t="n">
+        <v>5840000000</v>
+      </c>
+      <c r="P79" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>77</v>
+      </c>
+      <c r="B80" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C80" s="1" t="n">
+        <v>134000000000</v>
+      </c>
+      <c r="D80" s="1" t="n">
+        <v>336000000</v>
+      </c>
+      <c r="E80" s="1" t="n">
+        <v>45500000000</v>
+      </c>
+      <c r="F80" s="1" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="G80" s="1" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="H80" s="1" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="I80" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="K80" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="L80" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="1" t="n">
+        <v>2690000000</v>
+      </c>
+      <c r="N80" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="O80" s="1" t="n">
+        <v>6310000000</v>
+      </c>
+      <c r="P80" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>78</v>
+      </c>
+      <c r="B81" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C81" s="1" t="n">
+        <v>153000000000</v>
+      </c>
+      <c r="D81" s="1" t="n">
+        <v>383000000</v>
+      </c>
+      <c r="E81" s="1" t="n">
+        <v>53600000000</v>
+      </c>
+      <c r="F81" s="1" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="G81" s="1" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H81" s="1" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="I81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K81" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="1" t="n">
+        <v>3060000000</v>
+      </c>
+      <c r="N81" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="O81" s="1" t="n">
+        <v>7190000000</v>
+      </c>
+      <c r="P81" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>79</v>
+      </c>
+      <c r="B82" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C82" s="1" t="n">
+        <v>165000000000</v>
+      </c>
+      <c r="D82" s="1" t="n">
+        <v>414000000</v>
+      </c>
+      <c r="E82" s="1" t="n">
+        <v>59000000000</v>
+      </c>
+      <c r="F82" s="1" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="G82" s="1" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="H82" s="1" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="I82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="K82" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="L82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="1" t="n">
+        <v>3310000000</v>
+      </c>
+      <c r="N82" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="O82" s="1" t="n">
+        <v>7770000000</v>
+      </c>
+      <c r="P82" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="B83" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C83" s="1" t="n">
+        <v>192000000000</v>
+      </c>
+      <c r="D83" s="1" t="n">
+        <v>480000000</v>
+      </c>
+      <c r="E83" s="1" t="n">
+        <v>71000000000</v>
+      </c>
+      <c r="F83" s="1" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="G83" s="1" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="H83" s="1" t="n">
+        <v>11.44</v>
+      </c>
+      <c r="I83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K83" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L83" s="1" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="M83" s="1" t="n">
+        <v>3840000000</v>
+      </c>
+      <c r="N83" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="O83" s="1" t="n">
+        <v>9010000000</v>
+      </c>
+      <c r="P83" s="1" t="inlineStr">
+        <is>
+          <t>보스 층 · 허들</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>81</v>
+      </c>
+      <c r="B84" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C84" s="1" t="n">
+        <v>215000000000</v>
+      </c>
+      <c r="D84" s="1" t="n">
+        <v>537000000</v>
+      </c>
+      <c r="E84" s="1" t="n">
+        <v>81800000000</v>
+      </c>
+      <c r="F84" s="1" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="G84" s="1" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H84" s="1" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="I84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K84" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="1" t="n">
+        <v>4300000000</v>
+      </c>
+      <c r="N84" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="O84" s="1" t="n">
+        <v>10100000000</v>
+      </c>
+      <c r="P84" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>82</v>
+      </c>
+      <c r="B85" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C85" s="1" t="n">
+        <v>232000000000</v>
+      </c>
+      <c r="D85" s="1" t="n">
+        <v>580000000</v>
+      </c>
+      <c r="E85" s="1" t="n">
+        <v>90100000000</v>
+      </c>
+      <c r="F85" s="1" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="G85" s="1" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="H85" s="1" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="I85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="K85" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="L85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="1" t="n">
+        <v>4640000000</v>
+      </c>
+      <c r="N85" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="O85" s="1" t="n">
+        <v>10900000000</v>
+      </c>
+      <c r="P85" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>83</v>
+      </c>
+      <c r="B86" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C86" s="1" t="n">
+        <v>265000000000</v>
+      </c>
+      <c r="D86" s="1" t="n">
+        <v>662000000</v>
+      </c>
+      <c r="E86" s="1" t="n">
+        <v>106000000000</v>
+      </c>
+      <c r="F86" s="1" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="G86" s="1" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H86" s="1" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="I86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K86" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="1" t="n">
+        <v>5290000000</v>
+      </c>
+      <c r="N86" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="O86" s="1" t="n">
+        <v>12400000000</v>
+      </c>
+      <c r="P86" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>84</v>
+      </c>
+      <c r="B87" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C87" s="1" t="n">
+        <v>286000000000</v>
+      </c>
+      <c r="D87" s="1" t="n">
+        <v>715000000</v>
+      </c>
+      <c r="E87" s="1" t="n">
+        <v>117000000000</v>
+      </c>
+      <c r="F87" s="1" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="G87" s="1" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="H87" s="1" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="I87" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="K87" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="L87" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="1" t="n">
+        <v>5720000000</v>
+      </c>
+      <c r="N87" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="O87" s="1" t="n">
+        <v>13400000000</v>
+      </c>
+      <c r="P87" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>85</v>
+      </c>
+      <c r="B88" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C88" s="1" t="n">
+        <v>332000000000</v>
+      </c>
+      <c r="D88" s="1" t="n">
+        <v>829000000</v>
+      </c>
+      <c r="E88" s="1" t="n">
+        <v>141000000000</v>
+      </c>
+      <c r="F88" s="1" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="G88" s="1" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H88" s="1" t="n">
+        <v>11.44</v>
+      </c>
+      <c r="I88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K88" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L88" s="1" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="M88" s="1" t="n">
+        <v>6630000000</v>
+      </c>
+      <c r="N88" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="O88" s="1" t="n">
+        <v>15600000000</v>
+      </c>
+      <c r="P88" s="1" t="inlineStr">
+        <is>
+          <t>보스 층 · 허들</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>86</v>
+      </c>
+      <c r="B89" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C89" s="1" t="n">
+        <v>371000000000</v>
+      </c>
+      <c r="D89" s="1" t="n">
+        <v>928000000</v>
+      </c>
+      <c r="E89" s="1" t="n">
+        <v>162000000000</v>
+      </c>
+      <c r="F89" s="1" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="G89" s="1" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="H89" s="1" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="I89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K89" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="1" t="n">
+        <v>7430000000</v>
+      </c>
+      <c r="N89" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="O89" s="1" t="n">
+        <v>17400000000</v>
+      </c>
+      <c r="P89" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>87</v>
+      </c>
+      <c r="B90" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C90" s="1" t="n">
+        <v>401000000000</v>
+      </c>
+      <c r="D90" s="1" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="E90" s="1" t="n">
+        <v>178000000000</v>
+      </c>
+      <c r="F90" s="1" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="G90" s="1" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="H90" s="1" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="I90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="K90" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="L90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="1" t="n">
+        <v>8020000000</v>
+      </c>
+      <c r="N90" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="O90" s="1" t="n">
+        <v>18800000000</v>
+      </c>
+      <c r="P90" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="B91" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C91" s="1" t="n">
+        <v>457000000000</v>
+      </c>
+      <c r="D91" s="1" t="n">
+        <v>1140000000</v>
+      </c>
+      <c r="E91" s="1" t="n">
+        <v>210000000000</v>
+      </c>
+      <c r="F91" s="1" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="G91" s="1" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H91" s="1" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="I91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K91" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="1" t="n">
+        <v>9140000000</v>
+      </c>
+      <c r="N91" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="O91" s="1" t="n">
+        <v>21500000000</v>
+      </c>
+      <c r="P91" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>89</v>
+      </c>
+      <c r="B92" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C92" s="1" t="n">
+        <v>494000000000</v>
+      </c>
+      <c r="D92" s="1" t="n">
+        <v>1230000000</v>
+      </c>
+      <c r="E92" s="1" t="n">
+        <v>231000000000</v>
+      </c>
+      <c r="F92" s="1" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="G92" s="1" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="H92" s="1" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="I92" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="K92" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="L92" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="1" t="n">
+        <v>9870000000</v>
+      </c>
+      <c r="N92" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="O92" s="1" t="n">
+        <v>23200000000</v>
+      </c>
+      <c r="P92" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="B93" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C93" s="1" t="n">
+        <v>573000000000</v>
+      </c>
+      <c r="D93" s="1" t="n">
+        <v>1430000000</v>
+      </c>
+      <c r="E93" s="1" t="n">
+        <v>279000000000</v>
+      </c>
+      <c r="F93" s="1" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="G93" s="1" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H93" s="1" t="n">
+        <v>11.44</v>
+      </c>
+      <c r="I93" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K93" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L93" s="1" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="M93" s="1" t="n">
+        <v>11500000000</v>
+      </c>
+      <c r="N93" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="O93" s="1" t="n">
+        <v>26900000000</v>
+      </c>
+      <c r="P93" s="1" t="inlineStr">
+        <is>
+          <t>보스 층 · 허들</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>91</v>
+      </c>
+      <c r="B94" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C94" s="1" t="n">
+        <v>641000000000</v>
+      </c>
+      <c r="D94" s="1" t="n">
+        <v>1600000000</v>
+      </c>
+      <c r="E94" s="1" t="n">
+        <v>321000000000</v>
+      </c>
+      <c r="F94" s="1" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="G94" s="1" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H94" s="1" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="I94" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K94" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L94" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="1" t="n">
+        <v>12800000000</v>
+      </c>
+      <c r="N94" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="O94" s="1" t="n">
+        <v>30100000000</v>
+      </c>
+      <c r="P94" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>92</v>
+      </c>
+      <c r="B95" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C95" s="1" t="n">
+        <v>693000000000</v>
+      </c>
+      <c r="D95" s="1" t="n">
+        <v>1730000000</v>
+      </c>
+      <c r="E95" s="1" t="n">
+        <v>353000000000</v>
+      </c>
+      <c r="F95" s="1" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="G95" s="1" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="H95" s="1" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="I95" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="K95" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="L95" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="1" t="n">
+        <v>13900000000</v>
+      </c>
+      <c r="N95" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="O95" s="1" t="n">
+        <v>32500000000</v>
+      </c>
+      <c r="P95" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>93</v>
+      </c>
+      <c r="B96" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C96" s="1" t="n">
+        <v>790000000000</v>
+      </c>
+      <c r="D96" s="1" t="n">
+        <v>1970000000</v>
+      </c>
+      <c r="E96" s="1" t="n">
+        <v>416000000000</v>
+      </c>
+      <c r="F96" s="1" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="G96" s="1" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H96" s="1" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="I96" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K96" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L96" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="1" t="n">
+        <v>15800000000</v>
+      </c>
+      <c r="N96" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="O96" s="1" t="n">
+        <v>37100000000</v>
+      </c>
+      <c r="P96" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="B97" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C97" s="1" t="n">
+        <v>853000000000</v>
+      </c>
+      <c r="D97" s="1" t="n">
+        <v>2130000000</v>
+      </c>
+      <c r="E97" s="1" t="n">
+        <v>458000000000</v>
+      </c>
+      <c r="F97" s="1" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="G97" s="1" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H97" s="1" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="I97" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="K97" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="L97" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="M97" s="1" t="n">
+        <v>17100000000</v>
+      </c>
+      <c r="N97" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="O97" s="1" t="n">
+        <v>40000000000</v>
+      </c>
+      <c r="P97" s="1" t="inlineStr">
+        <is>
+          <t>보스 층 · 어려움</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="B98" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C98" s="1" t="n">
+        <v>989000000000</v>
+      </c>
+      <c r="D98" s="1" t="n">
+        <v>2470000000</v>
+      </c>
+      <c r="E98" s="1" t="n">
+        <v>552000000000</v>
+      </c>
+      <c r="F98" s="1" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="G98" s="1" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="H98" s="1" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="I98" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K98" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L98" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="1" t="n">
+        <v>19800000000</v>
+      </c>
+      <c r="N98" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="O98" s="1" t="n">
+        <v>46400000000</v>
+      </c>
+      <c r="P98" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>96</v>
+      </c>
+      <c r="B99" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C99" s="1" t="n">
+        <v>1110000000000</v>
+      </c>
+      <c r="D99" s="1" t="n">
+        <v>2770000000</v>
+      </c>
+      <c r="E99" s="1" t="n">
+        <v>636000000000</v>
+      </c>
+      <c r="F99" s="1" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="G99" s="1" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H99" s="1" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="I99" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K99" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L99" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="1" t="n">
+        <v>22200000000</v>
+      </c>
+      <c r="N99" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="O99" s="1" t="n">
+        <v>52000000000</v>
+      </c>
+      <c r="P99" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>97</v>
+      </c>
+      <c r="B100" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C100" s="1" t="n">
+        <v>1200000000000</v>
+      </c>
+      <c r="D100" s="1" t="n">
+        <v>2990000000</v>
+      </c>
+      <c r="E100" s="1" t="n">
+        <v>700000000000</v>
+      </c>
+      <c r="F100" s="1" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="G100" s="1" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H100" s="1" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="I100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="K100" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="L100" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="M100" s="1" t="n">
+        <v>23900000000</v>
+      </c>
+      <c r="N100" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="O100" s="1" t="n">
+        <v>56200000000</v>
+      </c>
+      <c r="P100" s="1" t="inlineStr">
+        <is>
+          <t>보스 층 · 어려움</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="B101" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C101" s="1" t="n">
+        <v>1360000000000</v>
+      </c>
+      <c r="D101" s="1" t="n">
+        <v>3410000000</v>
+      </c>
+      <c r="E101" s="1" t="n">
+        <v>824000000000</v>
+      </c>
+      <c r="F101" s="1" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="G101" s="1" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H101" s="1" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="I101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K101" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="1" t="n">
+        <v>27300000000</v>
+      </c>
+      <c r="N101" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="O101" s="1" t="n">
+        <v>64000000000</v>
+      </c>
+      <c r="P101" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>99</v>
+      </c>
+      <c r="B102" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C102" s="1" t="n">
+        <v>1470000000000</v>
+      </c>
+      <c r="D102" s="1" t="n">
+        <v>3680000000</v>
+      </c>
+      <c r="E102" s="1" t="n">
+        <v>908000000000</v>
+      </c>
+      <c r="F102" s="1" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="G102" s="1" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="H102" s="1" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="I102" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="K102" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="L102" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="1" t="n">
+        <v>29500000000</v>
+      </c>
+      <c r="N102" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="O102" s="1" t="n">
+        <v>69200000000</v>
+      </c>
+      <c r="P102" s="1" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="B103" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C103" s="1" t="n">
+        <v>1710000000000</v>
+      </c>
+      <c r="D103" s="1" t="n">
+        <v>4270000000</v>
+      </c>
+      <c r="E103" s="1" t="n">
+        <v>1090000000000</v>
+      </c>
+      <c r="F103" s="1" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="G103" s="1" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H103" s="1" t="n">
+        <v>11.44</v>
+      </c>
+      <c r="I103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="1" t="inlineStr">
+        <is>
+          <t>허들</t>
+        </is>
+      </c>
+      <c r="K103" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="L103" s="1" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="M103" s="1" t="n">
+        <v>34200000000</v>
+      </c>
+      <c r="N103" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="O103" s="1" t="n">
+        <v>80200000000</v>
+      </c>
+      <c r="P103" s="1" t="inlineStr">
         <is>
           <t>보스 층 · 허들</t>
         </is>

--- a/Data_Table/스테이지 테이블.xlsx
+++ b/Data_Table/스테이지 테이블.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Stage" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Column_Desc" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stage" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column_Desc" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -706,13 +706,13 @@
         <v>1</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>83.72</v>
+        <v>55.81</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>1.2</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>68.34999999999999</v>
+        <v>45.57</v>
       </c>
       <c r="I4" s="1" t="n">
         <v>0</v>
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="K4" s="1" t="n">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="L4" s="1" t="n">
         <v>0</v>
@@ -760,13 +760,13 @@
         <v>1.32</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>31.81</v>
+        <v>21.21</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>31.81</v>
+        <v>21.21</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>63.62</v>
+        <v>42.42</v>
       </c>
       <c r="I5" s="1" t="n">
         <v>0</v>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="K5" s="1" t="n">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="L5" s="1" t="n">
         <v>0</v>
@@ -814,13 +814,13 @@
         <v>1.75</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>71.95</v>
+        <v>47.97</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>1.2</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>64.95999999999999</v>
+        <v>43.31</v>
       </c>
       <c r="I6" s="1" t="n">
         <v>0</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="K6" s="1" t="n">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="L6" s="1" t="n">
         <v>0</v>
@@ -868,13 +868,13 @@
         <v>2.31</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>20.59</v>
+        <v>13.73</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>10.3</v>
+        <v>6.86</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>41.19</v>
+        <v>27.46</v>
       </c>
       <c r="I7" s="1" t="n">
         <v>0</v>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="K7" s="1" t="n">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="L7" s="1" t="n">
         <v>0</v>
@@ -922,13 +922,13 @@
         <v>4.81</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>2.55</v>
+        <v>1.7</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>1.27</v>
+        <v>0.85</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>15.17</v>
+        <v>10.11</v>
       </c>
       <c r="I8" s="1" t="n">
         <v>0</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="K8" s="1" t="n">
-        <v>162</v>
+        <v>108</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>64.8</v>
+        <v>43.2</v>
       </c>
       <c r="M8" s="1" t="n">
         <v>28.12</v>
@@ -976,13 +976,13 @@
         <v>6.81</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>6.97</v>
+        <v>4.65</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>2.32</v>
+        <v>1.55</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>13.94</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="I9" s="1" t="n">
         <v>0</v>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="K9" s="1" t="n">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="L9" s="1" t="n">
         <v>0</v>
@@ -1030,13 +1030,13 @@
         <v>9.640000000000001</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>8.720000000000001</v>
+        <v>5.81</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>2.91</v>
+        <v>1.94</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>12.41</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="I10" s="1" t="n">
         <v>0</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="K10" s="1" t="n">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="L10" s="1" t="n">
         <v>0</v>
@@ -1084,13 +1084,13 @@
         <v>13.64</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>6.35</v>
+        <v>4.24</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>2.12</v>
+        <v>1.41</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>14.65</v>
+        <v>9.77</v>
       </c>
       <c r="I11" s="1" t="n">
         <v>0</v>
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="K11" s="1" t="n">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="L11" s="1" t="n">
         <v>0</v>
@@ -1138,13 +1138,13 @@
         <v>19.29</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>3.88</v>
+        <v>2.59</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>1.94</v>
+        <v>1.29</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>12.71</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I12" s="1" t="n">
         <v>0</v>
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="K12" s="1" t="n">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="L12" s="1" t="n">
         <v>0</v>
@@ -1192,13 +1192,13 @@
         <v>27.3</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>4.4</v>
+        <v>2.93</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>1.47</v>
+        <v>0.98</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>5.86</v>
+        <v>3.91</v>
       </c>
       <c r="I13" s="1" t="n">
         <v>0</v>
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="K13" s="1" t="n">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>43.2</v>
+        <v>28.8</v>
       </c>
       <c r="M13" s="1" t="n">
         <v>113</v>
@@ -1252,7 +1252,7 @@
         <v>0.8</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>9.77</v>
+        <v>6.52</v>
       </c>
       <c r="I14" s="1" t="n">
         <v>0</v>
@@ -1263,7 +1263,7 @@
         </is>
       </c>
       <c r="K14" s="1" t="n">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="L14" s="1" t="n">
         <v>0</v>
@@ -1300,13 +1300,13 @@
         <v>54.64</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>4.89</v>
+        <v>3.26</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>2.44</v>
+        <v>1.63</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>14.65</v>
+        <v>9.77</v>
       </c>
       <c r="I15" s="1" t="n">
         <v>0</v>
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="K15" s="1" t="n">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="L15" s="1" t="n">
         <v>0</v>
@@ -1354,13 +1354,13 @@
         <v>77.31</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>13.35</v>
+        <v>8.9</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>4.45</v>
+        <v>2.97</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>9.77</v>
+        <v>6.52</v>
       </c>
       <c r="I16" s="1" t="n">
         <v>0</v>
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="K16" s="1" t="n">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="L16" s="1" t="n">
         <v>0</v>
@@ -1408,13 +1408,13 @@
         <v>109</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>7.64</v>
+        <v>5.09</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>2.55</v>
+        <v>1.7</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>15.27</v>
+        <v>10.18</v>
       </c>
       <c r="I17" s="1" t="n">
         <v>0</v>
@@ -1425,7 +1425,7 @@
         </is>
       </c>
       <c r="K17" s="1" t="n">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="L17" s="1" t="n">
         <v>0</v>
@@ -1468,7 +1468,7 @@
         <v>0.8</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>9.16</v>
+        <v>6.11</v>
       </c>
       <c r="I18" s="1" t="n">
         <v>0</v>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="K18" s="1" t="n">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>43.2</v>
+        <v>28.8</v>
       </c>
       <c r="M18" s="1" t="n">
         <v>452</v>
@@ -1516,13 +1516,13 @@
         <v>312</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>91.63</v>
+        <v>61.09</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>91.63</v>
+        <v>61.09</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>22.91</v>
+        <v>15.27</v>
       </c>
       <c r="I19" s="1" t="n">
         <v>0</v>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="K19" s="1" t="n">
-        <v>162</v>
+        <v>108</v>
       </c>
       <c r="L19" s="1" t="n">
         <v>0</v>
@@ -1570,13 +1570,13 @@
         <v>605</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>4.86</v>
+        <v>3.24</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>1.62</v>
+        <v>1.08</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>23.67</v>
+        <v>15.78</v>
       </c>
       <c r="I20" s="1" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="K20" s="1" t="n">
-        <v>135</v>
+        <v>90</v>
       </c>
       <c r="L20" s="1" t="n">
         <v>0</v>
@@ -1624,13 +1624,13 @@
         <v>1530</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>14.2</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>4.73</v>
+        <v>3.16</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>33.85</v>
+        <v>22.57</v>
       </c>
       <c r="I21" s="1" t="n">
         <v>0</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="K21" s="1" t="n">
-        <v>162</v>
+        <v>108</v>
       </c>
       <c r="L21" s="1" t="n">
         <v>0</v>
@@ -1678,13 +1678,13 @@
         <v>4100</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>14.11</v>
+        <v>9.4</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>4.7</v>
+        <v>3.13</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>28.21</v>
+        <v>18.81</v>
       </c>
       <c r="I22" s="1" t="n">
         <v>0</v>
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="K22" s="1" t="n">
-        <v>135</v>
+        <v>90</v>
       </c>
       <c r="L22" s="1" t="n">
         <v>0</v>
@@ -1723,39 +1723,39 @@
         <v>9</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>745000</v>
+        <v>228000</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>1860</v>
+        <v>571</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>12200</v>
+        <v>2790</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>13.49</v>
+        <v>7.49</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>26.78</v>
+        <v>14.88</v>
       </c>
       <c r="I23" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="K23" s="1" t="n">
-        <v>162</v>
+        <v>90</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>64.8</v>
+        <v>36</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>14900</v>
+        <v>4570</v>
       </c>
       <c r="N23" s="1" t="n">
         <v>15</v>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="P23" s="1" t="inlineStr">
         <is>
-          <t>보스 층 · 허들</t>
+          <t>보스 층 · 어려움</t>
         </is>
       </c>
     </row>
@@ -1777,39 +1777,39 @@
         <v>9</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>1300000</v>
+        <v>203000</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>3260</v>
+        <v>508</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>24600</v>
+        <v>2410</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>22.32</v>
+        <v>9.92</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>7.44</v>
+        <v>3.31</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>44.63</v>
+        <v>19.84</v>
       </c>
       <c r="I24" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K24" s="1" t="n">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="L24" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>26100</v>
+        <v>4060</v>
       </c>
       <c r="N24" s="1" t="n">
         <v>16</v>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="P24" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -1831,39 +1831,39 @@
         <v>9</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>2220000</v>
+        <v>208000</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>5540</v>
+        <v>520</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>47800</v>
+        <v>2480</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>43.63</v>
+        <v>23.27</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>14.54</v>
+        <v>7.76</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>37.46</v>
+        <v>19.98</v>
       </c>
       <c r="I25" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J25" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K25" s="1" t="n">
-        <v>135</v>
+        <v>72</v>
       </c>
       <c r="L25" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>44300</v>
+        <v>4160</v>
       </c>
       <c r="N25" s="1" t="n">
         <v>17</v>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="P25" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -1885,39 +1885,39 @@
         <v>9</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>4650000</v>
+        <v>213000</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>11600</v>
+        <v>532</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>121000</v>
+        <v>2550</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>22.16</v>
+        <v>9.85</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>7.39</v>
+        <v>3.28</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>61.88</v>
+        <v>27.5</v>
       </c>
       <c r="I26" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K26" s="1" t="n">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="L26" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>93100</v>
+        <v>4250</v>
       </c>
       <c r="N26" s="1" t="n">
         <v>18</v>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="P26" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -1939,39 +1939,39 @@
         <v>9</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>10200000</v>
+        <v>218000</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>25600</v>
+        <v>544</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>324000</v>
+        <v>2630</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>31.02</v>
+        <v>16.54</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>10.34</v>
+        <v>5.51</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>51.57</v>
+        <v>27.5</v>
       </c>
       <c r="I27" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K27" s="1" t="n">
-        <v>135</v>
+        <v>72</v>
       </c>
       <c r="L27" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>205000</v>
+        <v>4350</v>
       </c>
       <c r="N27" s="1" t="n">
         <v>19</v>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="P27" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -1993,39 +1993,39 @@
         <v>9</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>24600000</v>
+        <v>256000</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>61400</v>
+        <v>640</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>967000</v>
+        <v>3220</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>18.56</v>
+        <v>10.31</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>6.19</v>
+        <v>3.44</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>37.13</v>
+        <v>20.63</v>
       </c>
       <c r="I28" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="K28" s="1" t="n">
-        <v>162</v>
+        <v>90</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>64.8</v>
+        <v>36</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>491000</v>
+        <v>5120</v>
       </c>
       <c r="N28" s="1" t="n">
         <v>20</v>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="P28" s="1" t="inlineStr">
         <is>
-          <t>보스 층 · 허들</t>
+          <t>보스 층 · 어려움</t>
         </is>
       </c>
     </row>
@@ -2047,39 +2047,39 @@
         <v>9</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>43000000</v>
+        <v>228000</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>108000</v>
+        <v>570</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>1950000</v>
+        <v>2780</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>9.529999999999999</v>
+        <v>4.24</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>3.18</v>
+        <v>1.41</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>61.88</v>
+        <v>27.5</v>
       </c>
       <c r="I29" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K29" s="1" t="n">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="L29" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>860000</v>
+        <v>4560</v>
       </c>
       <c r="N29" s="1" t="n">
         <v>20</v>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="P29" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -2101,39 +2101,39 @@
         <v>9</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>73100000</v>
+        <v>233000</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>183000</v>
+        <v>583</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>3780000</v>
+        <v>2870</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>7.94</v>
+        <v>4.24</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>2.65</v>
+        <v>1.41</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>51.57</v>
+        <v>27.5</v>
       </c>
       <c r="I30" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K30" s="1" t="n">
-        <v>135</v>
+        <v>72</v>
       </c>
       <c r="L30" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>1460000</v>
+        <v>4670</v>
       </c>
       <c r="N30" s="1" t="n">
         <v>20</v>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="P30" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -2155,39 +2155,39 @@
         <v>9</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>154000000</v>
+        <v>239000</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>384000</v>
+        <v>597</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>9550000</v>
+        <v>2950</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>9.529999999999999</v>
+        <v>4.24</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>3.18</v>
+        <v>1.41</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>19.06</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I31" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K31" s="1" t="n">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="L31" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>3070000</v>
+        <v>4770</v>
       </c>
       <c r="N31" s="1" t="n">
         <v>20</v>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="P31" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -2209,22 +2209,22 @@
         <v>9</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>338000000</v>
+        <v>244000</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>844000</v>
+        <v>611</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>25600000</v>
+        <v>3040</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>7.94</v>
+        <v>5.29</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>2.65</v>
+        <v>1.76</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>15.88</v>
+        <v>10.59</v>
       </c>
       <c r="I32" s="1" t="n">
         <v>0</v>
@@ -2235,13 +2235,13 @@
         </is>
       </c>
       <c r="K32" s="1" t="n">
-        <v>135</v>
+        <v>90</v>
       </c>
       <c r="L32" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>6760000</v>
+        <v>4890</v>
       </c>
       <c r="N32" s="1" t="n">
         <v>20</v>
@@ -2263,22 +2263,22 @@
         <v>9</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>811000000</v>
+        <v>400000</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>2030000</v>
+        <v>1000</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>76500000</v>
+        <v>5620</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>5.72</v>
+        <v>5.19</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>11.44</v>
+        <v>10.38</v>
       </c>
       <c r="I33" s="1" t="n">
         <v>0</v>
@@ -2289,16 +2289,16 @@
         </is>
       </c>
       <c r="K33" s="1" t="n">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>64.8</v>
+        <v>58.8</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>16200000</v>
+        <v>8000</v>
       </c>
       <c r="N33" s="1" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="O33" s="1" t="n">
         <v>38100000</v>
@@ -2317,49 +2317,49 @@
         <v>9</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>908000000</v>
+        <v>267000</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>2270000</v>
+        <v>669</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>88100000</v>
+        <v>3400</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>9.529999999999999</v>
+        <v>4.24</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>4.76</v>
+        <v>2.12</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>19.06</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I34" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J34" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="K34" s="1" t="n">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="L34" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>18200000</v>
+        <v>5350</v>
       </c>
       <c r="N34" s="1" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="O34" s="1" t="n">
-        <v>42600000</v>
+        <v>25400000</v>
       </c>
       <c r="P34" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>쉬움</t>
         </is>
       </c>
     </row>
@@ -2371,49 +2371,49 @@
         <v>9</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>981000000</v>
+        <v>286000</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>2450000</v>
+        <v>715</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>97000000</v>
+        <v>3700</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>7.94</v>
+        <v>4.24</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>2.65</v>
+        <v>1.41</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>15.88</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I35" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="K35" s="1" t="n">
-        <v>135</v>
+        <v>72</v>
       </c>
       <c r="L35" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>19600000</v>
+        <v>5720</v>
       </c>
       <c r="N35" s="1" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="O35" s="1" t="n">
-        <v>46000000</v>
+        <v>27200000</v>
       </c>
       <c r="P35" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>쉬움</t>
         </is>
       </c>
     </row>
@@ -2425,49 +2425,49 @@
         <v>9</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>1120000000</v>
+        <v>306000</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>2790000</v>
+        <v>765</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>114000000</v>
+        <v>4020</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>9.529999999999999</v>
+        <v>4.24</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>3.18</v>
+        <v>1.41</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>19.06</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I36" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J36" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K36" s="1" t="n">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="L36" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>22400000</v>
+        <v>6120</v>
       </c>
       <c r="N36" s="1" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="O36" s="1" t="n">
-        <v>52500000</v>
+        <v>29100000</v>
       </c>
       <c r="P36" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -2479,49 +2479,49 @@
         <v>9</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>1210000000</v>
+        <v>327000</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>3020000</v>
+        <v>818</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>126000000</v>
+        <v>4370</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>7.94</v>
+        <v>4.24</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>3.97</v>
+        <v>2.12</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>15.88</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I37" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K37" s="1" t="n">
-        <v>135</v>
+        <v>72</v>
       </c>
       <c r="L37" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>24100000</v>
+        <v>6540</v>
       </c>
       <c r="N37" s="1" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="O37" s="1" t="n">
-        <v>56700000</v>
+        <v>31100000</v>
       </c>
       <c r="P37" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -2533,49 +2533,49 @@
         <v>9</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>1400000000</v>
+        <v>402000</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>3500000</v>
+        <v>1010</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>151000000</v>
+        <v>5670</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>5.72</v>
+        <v>3.18</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>1.91</v>
+        <v>1.06</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>11.44</v>
+        <v>6.35</v>
       </c>
       <c r="I38" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J38" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="K38" s="1" t="n">
-        <v>162</v>
+        <v>90</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>64.8</v>
+        <v>36</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>28000000</v>
+        <v>8050</v>
       </c>
       <c r="N38" s="1" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="O38" s="1" t="n">
-        <v>65700000</v>
+        <v>38300000</v>
       </c>
       <c r="P38" s="1" t="inlineStr">
         <is>
-          <t>보스 층 · 허들</t>
+          <t>보스 층 · 어려움</t>
         </is>
       </c>
     </row>
@@ -2587,49 +2587,49 @@
         <v>9</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>1570000000</v>
+        <v>374000</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>3920000</v>
+        <v>936</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>174000000</v>
+        <v>5180</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>9.529999999999999</v>
+        <v>4.24</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>3.18</v>
+        <v>1.41</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>19.06</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I39" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K39" s="1" t="n">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="L39" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>31400000</v>
+        <v>7490</v>
       </c>
       <c r="N39" s="1" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="O39" s="1" t="n">
-        <v>73600000</v>
+        <v>35600000</v>
       </c>
       <c r="P39" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -2641,49 +2641,49 @@
         <v>9</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>1690000000</v>
+        <v>400000</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>4230000</v>
+        <v>1000</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>192000000</v>
+        <v>5630</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>7.94</v>
+        <v>4.24</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>2.65</v>
+        <v>1.41</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>15.88</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I40" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J40" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K40" s="1" t="n">
-        <v>135</v>
+        <v>72</v>
       </c>
       <c r="L40" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>33900000</v>
+        <v>8010</v>
       </c>
       <c r="N40" s="1" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="O40" s="1" t="n">
-        <v>79500000</v>
+        <v>38100000</v>
       </c>
       <c r="P40" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -2695,49 +2695,49 @@
         <v>9</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>1930000000</v>
+        <v>428000</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>4830000</v>
+        <v>1070</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>226000000</v>
+        <v>6120</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>9.529999999999999</v>
+        <v>4.24</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>3.18</v>
+        <v>1.41</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>19.06</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I41" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J41" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K41" s="1" t="n">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="L41" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>38600000</v>
+        <v>8570</v>
       </c>
       <c r="N41" s="1" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="O41" s="1" t="n">
-        <v>90600000</v>
+        <v>40700000</v>
       </c>
       <c r="P41" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -2749,22 +2749,22 @@
         <v>9</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>2090000000</v>
+        <v>458000</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>5210000</v>
+        <v>1150</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>249000000</v>
+        <v>6660</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>7.94</v>
+        <v>5.29</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>3.97</v>
+        <v>2.65</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>15.88</v>
+        <v>10.59</v>
       </c>
       <c r="I42" s="1" t="n">
         <v>0</v>
@@ -2775,19 +2775,19 @@
         </is>
       </c>
       <c r="K42" s="1" t="n">
-        <v>135</v>
+        <v>90</v>
       </c>
       <c r="L42" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>41700000</v>
+        <v>9160</v>
       </c>
       <c r="N42" s="1" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="O42" s="1" t="n">
-        <v>97900000</v>
+        <v>43600000</v>
       </c>
       <c r="P42" s="1" t="inlineStr">
         <is>
@@ -2803,22 +2803,22 @@
         <v>9</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>2420000000</v>
+        <v>784000</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>6050000</v>
+        <v>1960</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>300000000</v>
+        <v>13000</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>5.72</v>
+        <v>5.26</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>2.86</v>
+        <v>2.63</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>11.44</v>
+        <v>10.52</v>
       </c>
       <c r="I43" s="1" t="n">
         <v>0</v>
@@ -2829,19 +2829,19 @@
         </is>
       </c>
       <c r="K43" s="1" t="n">
-        <v>162</v>
+        <v>149.1</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>64.8</v>
+        <v>59.6</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>48400000</v>
+        <v>15700</v>
       </c>
       <c r="N43" s="1" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="O43" s="1" t="n">
-        <v>114000000</v>
+        <v>74600000</v>
       </c>
       <c r="P43" s="1" t="inlineStr">
         <is>
@@ -2857,49 +2857,49 @@
         <v>9</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>2710000000</v>
+        <v>562000</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>6770000</v>
+        <v>1410</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>346000000</v>
+        <v>8610</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>9.529999999999999</v>
+        <v>4.24</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>3.18</v>
+        <v>1.41</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>19.06</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I44" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J44" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="K44" s="1" t="n">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="L44" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>54200000</v>
+        <v>11200</v>
       </c>
       <c r="N44" s="1" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="O44" s="1" t="n">
-        <v>127000000</v>
+        <v>53500000</v>
       </c>
       <c r="P44" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>쉬움</t>
         </is>
       </c>
     </row>
@@ -2911,49 +2911,49 @@
         <v>9</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>2930000000</v>
+        <v>645000</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>7320000</v>
+        <v>1610</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>380000000</v>
+        <v>10200</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>7.94</v>
+        <v>4.24</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>2.65</v>
+        <v>1.41</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>15.88</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I45" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J45" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="K45" s="1" t="n">
-        <v>135</v>
+        <v>72</v>
       </c>
       <c r="L45" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>58500000</v>
+        <v>12900</v>
       </c>
       <c r="N45" s="1" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="O45" s="1" t="n">
-        <v>137000000</v>
+        <v>61400000</v>
       </c>
       <c r="P45" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>쉬움</t>
         </is>
       </c>
     </row>
@@ -2965,49 +2965,49 @@
         <v>9</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>3340000000</v>
+        <v>741000</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>8340000</v>
+        <v>1850</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>448000000</v>
+        <v>12100</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>9.529999999999999</v>
+        <v>4.24</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>4.76</v>
+        <v>2.12</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>19.06</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I46" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J46" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K46" s="1" t="n">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="L46" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M46" s="1" t="n">
-        <v>66700000</v>
+        <v>14800</v>
       </c>
       <c r="N46" s="1" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="O46" s="1" t="n">
-        <v>157000000</v>
+        <v>70500000</v>
       </c>
       <c r="P46" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -3019,49 +3019,49 @@
         <v>9</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>3600000000</v>
+        <v>850000</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>9010000</v>
+        <v>2130</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>493000000</v>
+        <v>14400</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>7.94</v>
+        <v>4.24</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>2.65</v>
+        <v>1.41</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>15.88</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I47" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J47" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K47" s="1" t="n">
-        <v>135</v>
+        <v>72</v>
       </c>
       <c r="L47" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>72100000</v>
+        <v>17000</v>
       </c>
       <c r="N47" s="1" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="O47" s="1" t="n">
-        <v>169000000</v>
+        <v>80900000</v>
       </c>
       <c r="P47" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -3073,49 +3073,49 @@
         <v>9</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>4180000000</v>
+        <v>1120000</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>10400000</v>
+        <v>2800</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>594000000</v>
+        <v>20400</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>5.72</v>
+        <v>3.18</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>1.91</v>
+        <v>1.06</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>11.44</v>
+        <v>6.35</v>
       </c>
       <c r="I48" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="K48" s="1" t="n">
-        <v>162</v>
+        <v>90</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>64.8</v>
+        <v>36</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>83600000</v>
+        <v>22400</v>
       </c>
       <c r="N48" s="1" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="O48" s="1" t="n">
-        <v>196000000</v>
+        <v>107000000</v>
       </c>
       <c r="P48" s="1" t="inlineStr">
         <is>
-          <t>보스 층 · 허들</t>
+          <t>보스 층 · 어려움</t>
         </is>
       </c>
     </row>
@@ -3127,49 +3127,49 @@
         <v>9</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>4680000000</v>
+        <v>1120000</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>11700000</v>
+        <v>2800</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>684000000</v>
+        <v>20400</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>9.529999999999999</v>
+        <v>4.24</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>3.18</v>
+        <v>1.41</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>19.06</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I49" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J49" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K49" s="1" t="n">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="L49" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>93600000</v>
+        <v>22400</v>
       </c>
       <c r="N49" s="1" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="O49" s="1" t="n">
-        <v>220000000</v>
+        <v>107000000</v>
       </c>
       <c r="P49" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -3181,49 +3181,49 @@
         <v>9</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>5060000000</v>
+        <v>1290000</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>12600000</v>
+        <v>3210</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>754000000</v>
+        <v>24200</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>7.94</v>
+        <v>4.24</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>2.65</v>
+        <v>1.41</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>15.88</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I50" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J50" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K50" s="1" t="n">
-        <v>135</v>
+        <v>72</v>
       </c>
       <c r="L50" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M50" s="1" t="n">
-        <v>101000000</v>
+        <v>25700</v>
       </c>
       <c r="N50" s="1" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="O50" s="1" t="n">
-        <v>237000000</v>
+        <v>122000000</v>
       </c>
       <c r="P50" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -3235,49 +3235,49 @@
         <v>9</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>5760000000</v>
+        <v>1470000</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>14400000</v>
+        <v>3690</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>888000000</v>
+        <v>28700</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>9.529999999999999</v>
+        <v>4.24</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>4.76</v>
+        <v>2.12</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>19.06</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I51" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J51" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K51" s="1" t="n">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="L51" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M51" s="1" t="n">
-        <v>115000000</v>
+        <v>29500</v>
       </c>
       <c r="N51" s="1" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O51" s="1" t="n">
-        <v>271000000</v>
+        <v>140000000</v>
       </c>
       <c r="P51" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -3289,22 +3289,22 @@
         <v>9</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>6220000000</v>
+        <v>1690000</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>15600000</v>
+        <v>4230</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>977000000</v>
+        <v>34100</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>7.94</v>
+        <v>5.29</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>3.97</v>
+        <v>2.65</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>15.88</v>
+        <v>10.59</v>
       </c>
       <c r="I52" s="1" t="n">
         <v>0</v>
@@ -3315,19 +3315,19 @@
         </is>
       </c>
       <c r="K52" s="1" t="n">
-        <v>135</v>
+        <v>90</v>
       </c>
       <c r="L52" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M52" s="1" t="n">
-        <v>124000000</v>
+        <v>33900</v>
       </c>
       <c r="N52" s="1" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="O52" s="1" t="n">
-        <v>292000000</v>
+        <v>161000000</v>
       </c>
       <c r="P52" s="1" t="inlineStr">
         <is>
@@ -3343,22 +3343,22 @@
         <v>9</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>7220000000</v>
+        <v>3110000</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>18000000</v>
+        <v>7770</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>1180000000</v>
+        <v>73000</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>5.72</v>
+        <v>5.34</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>2.86</v>
+        <v>2.67</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>11.44</v>
+        <v>10.67</v>
       </c>
       <c r="I53" s="1" t="n">
         <v>0</v>
@@ -3369,19 +3369,19 @@
         </is>
       </c>
       <c r="K53" s="1" t="n">
-        <v>162</v>
+        <v>151.2</v>
       </c>
       <c r="L53" s="1" t="n">
-        <v>64.8</v>
+        <v>60.5</v>
       </c>
       <c r="M53" s="1" t="n">
-        <v>144000000</v>
+        <v>62200</v>
       </c>
       <c r="N53" s="1" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="O53" s="1" t="n">
-        <v>339000000</v>
+        <v>296000000</v>
       </c>
       <c r="P53" s="1" t="inlineStr">
         <is>
@@ -3397,49 +3397,49 @@
         <v>9</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>8090000000</v>
+        <v>2100000</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>20200000</v>
+        <v>5260</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>1360000000</v>
+        <v>44800</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>9.529999999999999</v>
+        <v>4.24</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>3.18</v>
+        <v>1.41</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>19.06</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I54" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J54" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="K54" s="1" t="n">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="L54" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>162000000</v>
+        <v>42100</v>
       </c>
       <c r="N54" s="1" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="O54" s="1" t="n">
-        <v>380000000</v>
+        <v>200000000</v>
       </c>
       <c r="P54" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>쉬움</t>
         </is>
       </c>
     </row>
@@ -3451,49 +3451,49 @@
         <v>9</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>8730000000</v>
+        <v>2280000</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>21800000</v>
+        <v>5700</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>1490000000</v>
+        <v>49500</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>7.94</v>
+        <v>4.24</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>3.97</v>
+        <v>2.12</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>15.88</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I55" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J55" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="K55" s="1" t="n">
-        <v>135</v>
+        <v>72</v>
       </c>
       <c r="L55" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M55" s="1" t="n">
-        <v>175000000</v>
+        <v>45600</v>
       </c>
       <c r="N55" s="1" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="O55" s="1" t="n">
-        <v>410000000</v>
+        <v>217000000</v>
       </c>
       <c r="P55" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>쉬움</t>
         </is>
       </c>
     </row>
@@ -3505,49 +3505,49 @@
         <v>9</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>9960000000</v>
+        <v>2470000</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>24900000</v>
+        <v>6170</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>1760000000</v>
+        <v>54700</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>9.529999999999999</v>
+        <v>4.24</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>3.18</v>
+        <v>1.41</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>19.06</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I56" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J56" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K56" s="1" t="n">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="L56" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M56" s="1" t="n">
-        <v>199000000</v>
+        <v>49400</v>
       </c>
       <c r="N56" s="1" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="O56" s="1" t="n">
-        <v>467000000</v>
+        <v>235000000</v>
       </c>
       <c r="P56" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -3559,49 +3559,49 @@
         <v>9</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>10800000000</v>
+        <v>2670000</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>26900000</v>
+        <v>6690</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>1940000000</v>
+        <v>60500</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>7.94</v>
+        <v>4.24</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>2.65</v>
+        <v>1.41</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>15.88</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I57" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J57" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K57" s="1" t="n">
-        <v>135</v>
+        <v>72</v>
       </c>
       <c r="L57" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M57" s="1" t="n">
-        <v>215000000</v>
+        <v>53500</v>
       </c>
       <c r="N57" s="1" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="O57" s="1" t="n">
-        <v>505000000</v>
+        <v>254000000</v>
       </c>
       <c r="P57" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -3613,49 +3613,49 @@
         <v>9</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>12500000000</v>
+        <v>3330000</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>31200000</v>
+        <v>8330</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>2330000000</v>
+        <v>79600</v>
       </c>
       <c r="F58" s="1" t="n">
-        <v>5.72</v>
+        <v>3.18</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>1.91</v>
+        <v>1.06</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>11.44</v>
+        <v>6.35</v>
       </c>
       <c r="I58" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J58" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="K58" s="1" t="n">
-        <v>162</v>
+        <v>90</v>
       </c>
       <c r="L58" s="1" t="n">
-        <v>64.8</v>
+        <v>36</v>
       </c>
       <c r="M58" s="1" t="n">
-        <v>249000000</v>
+        <v>66600</v>
       </c>
       <c r="N58" s="1" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="O58" s="1" t="n">
-        <v>585000000</v>
+        <v>317000000</v>
       </c>
       <c r="P58" s="1" t="inlineStr">
         <is>
-          <t>보스 층 · 허들</t>
+          <t>보스 층 · 어려움</t>
         </is>
       </c>
     </row>
@@ -3667,49 +3667,49 @@
         <v>9</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>14000000000</v>
+        <v>3140000</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>34900000</v>
+        <v>7840</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>2680000000</v>
+        <v>73800</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>9.529999999999999</v>
+        <v>4.24</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>4.76</v>
+        <v>2.12</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>19.06</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I59" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J59" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K59" s="1" t="n">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="L59" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M59" s="1" t="n">
-        <v>279000000</v>
+        <v>62800</v>
       </c>
       <c r="N59" s="1" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="O59" s="1" t="n">
-        <v>656000000</v>
+        <v>298000000</v>
       </c>
       <c r="P59" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -3721,49 +3721,49 @@
         <v>9</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>15100000000</v>
+        <v>3400000</v>
       </c>
       <c r="D60" s="1" t="n">
-        <v>37700000</v>
+        <v>8500</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>2960000000</v>
+        <v>81600</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>7.94</v>
+        <v>4.24</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>2.65</v>
+        <v>1.41</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>15.88</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I60" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J60" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K60" s="1" t="n">
-        <v>135</v>
+        <v>72</v>
       </c>
       <c r="L60" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M60" s="1" t="n">
-        <v>302000000</v>
+        <v>68000</v>
       </c>
       <c r="N60" s="1" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="O60" s="1" t="n">
-        <v>708000000</v>
+        <v>323000000</v>
       </c>
       <c r="P60" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -3775,49 +3775,49 @@
         <v>9</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>17200000000</v>
+        <v>3680000</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>43000000</v>
+        <v>9200</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>3480000000</v>
+        <v>90200</v>
       </c>
       <c r="F61" s="1" t="n">
-        <v>9.529999999999999</v>
+        <v>4.24</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>4.76</v>
+        <v>2.12</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>19.06</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I61" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J61" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K61" s="1" t="n">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="L61" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M61" s="1" t="n">
-        <v>344000000</v>
+        <v>73600</v>
       </c>
       <c r="N61" s="1" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="O61" s="1" t="n">
-        <v>807000000</v>
+        <v>350000000</v>
       </c>
       <c r="P61" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -3829,22 +3829,22 @@
         <v>9</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>18600000000</v>
+        <v>3990000</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46400000</v>
+        <v>9970</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>3830000000</v>
+        <v>99600</v>
       </c>
       <c r="F62" s="1" t="n">
-        <v>7.94</v>
+        <v>5.29</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>3.97</v>
+        <v>2.65</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>15.88</v>
+        <v>10.59</v>
       </c>
       <c r="I62" s="1" t="n">
         <v>0</v>
@@ -3855,19 +3855,19 @@
         </is>
       </c>
       <c r="K62" s="1" t="n">
-        <v>135</v>
+        <v>90</v>
       </c>
       <c r="L62" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M62" s="1" t="n">
-        <v>372000000</v>
+        <v>79800</v>
       </c>
       <c r="N62" s="1" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="O62" s="1" t="n">
-        <v>872000000</v>
+        <v>379000000</v>
       </c>
       <c r="P62" s="1" t="inlineStr">
         <is>
@@ -3883,22 +3883,22 @@
         <v>9</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>21500000000</v>
+        <v>6910000</v>
       </c>
       <c r="D63" s="1" t="n">
-        <v>53900000</v>
+        <v>17300</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>4610000000</v>
+        <v>198000</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>5.72</v>
+        <v>5.41</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>11.44</v>
+        <v>10.82</v>
       </c>
       <c r="I63" s="1" t="n">
         <v>0</v>
@@ -3909,19 +3909,19 @@
         </is>
       </c>
       <c r="K63" s="1" t="n">
-        <v>162</v>
+        <v>153.3</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>64.8</v>
+        <v>61.3</v>
       </c>
       <c r="M63" s="1" t="n">
-        <v>431000000</v>
+        <v>138000</v>
       </c>
       <c r="N63" s="1" t="n">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="O63" s="1" t="n">
-        <v>1010000000</v>
+        <v>658000000</v>
       </c>
       <c r="P63" s="1" t="inlineStr">
         <is>
@@ -3937,49 +3937,49 @@
         <v>9</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>24100000000</v>
+        <v>4760000</v>
       </c>
       <c r="D64" s="1" t="n">
-        <v>60300000</v>
+        <v>11900</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>5320000000</v>
+        <v>124000</v>
       </c>
       <c r="F64" s="1" t="n">
-        <v>9.529999999999999</v>
+        <v>4.24</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>3.18</v>
+        <v>1.41</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>19.06</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I64" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J64" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="K64" s="1" t="n">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="L64" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M64" s="1" t="n">
-        <v>483000000</v>
+        <v>95100</v>
       </c>
       <c r="N64" s="1" t="n">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="O64" s="1" t="n">
-        <v>1130000000</v>
+        <v>452000000</v>
       </c>
       <c r="P64" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>쉬움</t>
         </is>
       </c>
     </row>
@@ -3991,49 +3991,49 @@
         <v>9</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>26100000000</v>
+        <v>5240000</v>
       </c>
       <c r="D65" s="1" t="n">
-        <v>65200000</v>
+        <v>13100</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>5850000000</v>
+        <v>140000</v>
       </c>
       <c r="F65" s="1" t="n">
-        <v>7.94</v>
+        <v>4.24</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>2.65</v>
+        <v>1.41</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>15.88</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I65" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J65" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="K65" s="1" t="n">
-        <v>135</v>
+        <v>72</v>
       </c>
       <c r="L65" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M65" s="1" t="n">
-        <v>521000000</v>
+        <v>105000</v>
       </c>
       <c r="N65" s="1" t="n">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="O65" s="1" t="n">
-        <v>1220000000</v>
+        <v>498000000</v>
       </c>
       <c r="P65" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>쉬움</t>
         </is>
       </c>
     </row>
@@ -4045,49 +4045,49 @@
         <v>9</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>29700000000</v>
+        <v>5770000</v>
       </c>
       <c r="D66" s="1" t="n">
-        <v>74300000</v>
+        <v>14400</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>6900000000</v>
+        <v>158000</v>
       </c>
       <c r="F66" s="1" t="n">
-        <v>9.529999999999999</v>
+        <v>4.24</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>3.18</v>
+        <v>1.41</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>19.06</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I66" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J66" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K66" s="1" t="n">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="L66" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M66" s="1" t="n">
-        <v>594000000</v>
+        <v>115000</v>
       </c>
       <c r="N66" s="1" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="O66" s="1" t="n">
-        <v>1390000000</v>
+        <v>549000000</v>
       </c>
       <c r="P66" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -4099,49 +4099,49 @@
         <v>9</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>32100000000</v>
+        <v>6350000</v>
       </c>
       <c r="D67" s="1" t="n">
-        <v>80200000</v>
+        <v>15900</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>7590000000</v>
+        <v>178000</v>
       </c>
       <c r="F67" s="1" t="n">
-        <v>7.94</v>
+        <v>4.24</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>2.65</v>
+        <v>1.41</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>15.88</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I67" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J67" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K67" s="1" t="n">
-        <v>135</v>
+        <v>72</v>
       </c>
       <c r="L67" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M67" s="1" t="n">
-        <v>642000000</v>
+        <v>127000</v>
       </c>
       <c r="N67" s="1" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="O67" s="1" t="n">
-        <v>1510000000</v>
+        <v>604000000</v>
       </c>
       <c r="P67" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -4153,49 +4153,49 @@
         <v>9</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>37200000000</v>
+        <v>8040000</v>
       </c>
       <c r="D68" s="1" t="n">
-        <v>93100000</v>
+        <v>20100</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>9140000000</v>
+        <v>239000</v>
       </c>
       <c r="F68" s="1" t="n">
-        <v>5.72</v>
+        <v>3.18</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>1.91</v>
+        <v>1.06</v>
       </c>
       <c r="H68" s="1" t="n">
-        <v>11.44</v>
+        <v>6.35</v>
       </c>
       <c r="I68" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J68" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="K68" s="1" t="n">
-        <v>162</v>
+        <v>90</v>
       </c>
       <c r="L68" s="1" t="n">
-        <v>64.8</v>
+        <v>36</v>
       </c>
       <c r="M68" s="1" t="n">
-        <v>744000000</v>
+        <v>161000</v>
       </c>
       <c r="N68" s="1" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="O68" s="1" t="n">
-        <v>1750000000</v>
+        <v>765000000</v>
       </c>
       <c r="P68" s="1" t="inlineStr">
         <is>
-          <t>보스 층 · 허들</t>
+          <t>보스 층 · 어려움</t>
         </is>
       </c>
     </row>
@@ -4207,49 +4207,49 @@
         <v>9</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>41700000000</v>
+        <v>7700000</v>
       </c>
       <c r="D69" s="1" t="n">
-        <v>104000000</v>
+        <v>19200</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>10500000000</v>
+        <v>227000</v>
       </c>
       <c r="F69" s="1" t="n">
-        <v>9.529999999999999</v>
+        <v>4.24</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>4.76</v>
+        <v>2.12</v>
       </c>
       <c r="H69" s="1" t="n">
-        <v>19.06</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I69" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J69" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K69" s="1" t="n">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="L69" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M69" s="1" t="n">
-        <v>834000000</v>
+        <v>154000</v>
       </c>
       <c r="N69" s="1" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="O69" s="1" t="n">
-        <v>1960000000</v>
+        <v>732000000</v>
       </c>
       <c r="P69" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -4261,49 +4261,49 @@
         <v>9</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45000000000</v>
+        <v>8470000</v>
       </c>
       <c r="D70" s="1" t="n">
-        <v>113000000</v>
+        <v>21200</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>11600000000</v>
+        <v>256000</v>
       </c>
       <c r="F70" s="1" t="n">
-        <v>7.94</v>
+        <v>4.24</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>2.65</v>
+        <v>1.41</v>
       </c>
       <c r="H70" s="1" t="n">
-        <v>15.88</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I70" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J70" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K70" s="1" t="n">
-        <v>135</v>
+        <v>72</v>
       </c>
       <c r="L70" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M70" s="1" t="n">
-        <v>901000000</v>
+        <v>169000</v>
       </c>
       <c r="N70" s="1" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="O70" s="1" t="n">
-        <v>2110000000</v>
+        <v>806000000</v>
       </c>
       <c r="P70" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -4315,49 +4315,49 @@
         <v>9</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>51300000000</v>
+        <v>9330000</v>
       </c>
       <c r="D71" s="1" t="n">
-        <v>128000000</v>
+        <v>23300</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>13700000000</v>
+        <v>288000</v>
       </c>
       <c r="F71" s="1" t="n">
-        <v>9.529999999999999</v>
+        <v>4.24</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>4.76</v>
+        <v>2.12</v>
       </c>
       <c r="H71" s="1" t="n">
-        <v>19.06</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I71" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J71" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K71" s="1" t="n">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="L71" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M71" s="1" t="n">
-        <v>1030000000</v>
+        <v>187000</v>
       </c>
       <c r="N71" s="1" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="O71" s="1" t="n">
-        <v>2410000000</v>
+        <v>888000000</v>
       </c>
       <c r="P71" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -4369,22 +4369,22 @@
         <v>9</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>55400000000</v>
+        <v>10300000</v>
       </c>
       <c r="D72" s="1" t="n">
-        <v>139000000</v>
+        <v>25700</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>15000000000</v>
+        <v>325000</v>
       </c>
       <c r="F72" s="1" t="n">
-        <v>7.94</v>
+        <v>5.29</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>3.97</v>
+        <v>2.65</v>
       </c>
       <c r="H72" s="1" t="n">
-        <v>15.88</v>
+        <v>10.59</v>
       </c>
       <c r="I72" s="1" t="n">
         <v>0</v>
@@ -4395,19 +4395,19 @@
         </is>
       </c>
       <c r="K72" s="1" t="n">
-        <v>135</v>
+        <v>90</v>
       </c>
       <c r="L72" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M72" s="1" t="n">
-        <v>1110000000</v>
+        <v>205000</v>
       </c>
       <c r="N72" s="1" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="O72" s="1" t="n">
-        <v>2600000000</v>
+        <v>977000000</v>
       </c>
       <c r="P72" s="1" t="inlineStr">
         <is>
@@ -4423,22 +4423,22 @@
         <v>9</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>64300000000</v>
+        <v>18100000</v>
       </c>
       <c r="D73" s="1" t="n">
-        <v>161000000</v>
+        <v>45200</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>18100000000</v>
+        <v>660000</v>
       </c>
       <c r="F73" s="1" t="n">
-        <v>5.72</v>
+        <v>5.48</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>2.86</v>
+        <v>2.74</v>
       </c>
       <c r="H73" s="1" t="n">
-        <v>11.44</v>
+        <v>10.97</v>
       </c>
       <c r="I73" s="1" t="n">
         <v>0</v>
@@ -4449,19 +4449,19 @@
         </is>
       </c>
       <c r="K73" s="1" t="n">
-        <v>162</v>
+        <v>155.4</v>
       </c>
       <c r="L73" s="1" t="n">
-        <v>64.8</v>
+        <v>62.2</v>
       </c>
       <c r="M73" s="1" t="n">
-        <v>1290000000</v>
+        <v>362000</v>
       </c>
       <c r="N73" s="1" t="n">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="O73" s="1" t="n">
-        <v>3020000000</v>
+        <v>1720000000</v>
       </c>
       <c r="P73" s="1" t="inlineStr">
         <is>
@@ -4477,49 +4477,49 @@
         <v>9</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>72000000000</v>
+        <v>12000000</v>
       </c>
       <c r="D74" s="1" t="n">
-        <v>180000000</v>
+        <v>30000</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>20900000000</v>
+        <v>394000</v>
       </c>
       <c r="F74" s="1" t="n">
-        <v>9.529999999999999</v>
+        <v>4.24</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>3.18</v>
+        <v>1.41</v>
       </c>
       <c r="H74" s="1" t="n">
-        <v>19.06</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I74" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J74" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="K74" s="1" t="n">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="L74" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M74" s="1" t="n">
-        <v>1440000000</v>
+        <v>240000</v>
       </c>
       <c r="N74" s="1" t="n">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="O74" s="1" t="n">
-        <v>3380000000</v>
+        <v>1140000000</v>
       </c>
       <c r="P74" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>쉬움</t>
         </is>
       </c>
     </row>
@@ -4531,49 +4531,49 @@
         <v>9</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>77800000000</v>
+        <v>12700000</v>
       </c>
       <c r="D75" s="1" t="n">
-        <v>194000000</v>
+        <v>31800</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>23000000000</v>
+        <v>424000</v>
       </c>
       <c r="F75" s="1" t="n">
-        <v>7.94</v>
+        <v>4.24</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>2.65</v>
+        <v>1.41</v>
       </c>
       <c r="H75" s="1" t="n">
-        <v>15.88</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I75" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J75" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="K75" s="1" t="n">
-        <v>135</v>
+        <v>72</v>
       </c>
       <c r="L75" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M75" s="1" t="n">
-        <v>1560000000</v>
+        <v>254000</v>
       </c>
       <c r="N75" s="1" t="n">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="O75" s="1" t="n">
-        <v>3650000000</v>
+        <v>1210000000</v>
       </c>
       <c r="P75" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>쉬움</t>
         </is>
       </c>
     </row>
@@ -4585,49 +4585,49 @@
         <v>9</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>88700000000</v>
+        <v>13500000</v>
       </c>
       <c r="D76" s="1" t="n">
-        <v>222000000</v>
+        <v>33700</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>27100000000</v>
+        <v>456000</v>
       </c>
       <c r="F76" s="1" t="n">
-        <v>9.529999999999999</v>
+        <v>4.24</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>3.18</v>
+        <v>1.41</v>
       </c>
       <c r="H76" s="1" t="n">
-        <v>19.06</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I76" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J76" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K76" s="1" t="n">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="L76" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M76" s="1" t="n">
-        <v>1770000000</v>
+        <v>270000</v>
       </c>
       <c r="N76" s="1" t="n">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="O76" s="1" t="n">
-        <v>4160000000</v>
+        <v>1280000000</v>
       </c>
       <c r="P76" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -4639,49 +4639,49 @@
         <v>9</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>95800000000</v>
+        <v>14300000</v>
       </c>
       <c r="D77" s="1" t="n">
-        <v>239000000</v>
+        <v>35700</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>29800000000</v>
+        <v>491000</v>
       </c>
       <c r="F77" s="1" t="n">
-        <v>7.94</v>
+        <v>4.24</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>2.65</v>
+        <v>1.41</v>
       </c>
       <c r="H77" s="1" t="n">
-        <v>15.88</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I77" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J77" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K77" s="1" t="n">
-        <v>135</v>
+        <v>72</v>
       </c>
       <c r="L77" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M77" s="1" t="n">
-        <v>1920000000</v>
+        <v>286000</v>
       </c>
       <c r="N77" s="1" t="n">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="O77" s="1" t="n">
-        <v>4500000000</v>
+        <v>1360000000</v>
       </c>
       <c r="P77" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -4693,49 +4693,49 @@
         <v>9</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>111000000000</v>
+        <v>17400000</v>
       </c>
       <c r="D78" s="1" t="n">
-        <v>278000000</v>
+        <v>43500</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>35900000000</v>
+        <v>629000</v>
       </c>
       <c r="F78" s="1" t="n">
-        <v>5.72</v>
+        <v>3.18</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>1.91</v>
+        <v>1.06</v>
       </c>
       <c r="H78" s="1" t="n">
-        <v>11.44</v>
+        <v>6.35</v>
       </c>
       <c r="I78" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J78" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="K78" s="1" t="n">
-        <v>162</v>
+        <v>90</v>
       </c>
       <c r="L78" s="1" t="n">
-        <v>64.8</v>
+        <v>36</v>
       </c>
       <c r="M78" s="1" t="n">
-        <v>2220000000</v>
+        <v>348000</v>
       </c>
       <c r="N78" s="1" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="O78" s="1" t="n">
-        <v>5210000000</v>
+        <v>1660000000</v>
       </c>
       <c r="P78" s="1" t="inlineStr">
         <is>
-          <t>보스 층 · 허들</t>
+          <t>보스 층 · 어려움</t>
         </is>
       </c>
     </row>
@@ -4747,49 +4747,49 @@
         <v>9</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>124000000000</v>
+        <v>16100000</v>
       </c>
       <c r="D79" s="1" t="n">
-        <v>311000000</v>
+        <v>40100</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>41300000000</v>
+        <v>568000</v>
       </c>
       <c r="F79" s="1" t="n">
-        <v>9.529999999999999</v>
+        <v>4.24</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>3.18</v>
+        <v>1.41</v>
       </c>
       <c r="H79" s="1" t="n">
-        <v>19.06</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I79" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J79" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K79" s="1" t="n">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="L79" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M79" s="1" t="n">
-        <v>2490000000</v>
+        <v>321000</v>
       </c>
       <c r="N79" s="1" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="O79" s="1" t="n">
-        <v>5840000000</v>
+        <v>1530000000</v>
       </c>
       <c r="P79" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -4801,49 +4801,49 @@
         <v>9</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>134000000000</v>
+        <v>17000000</v>
       </c>
       <c r="D80" s="1" t="n">
-        <v>336000000</v>
+        <v>42600</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>45500000000</v>
+        <v>611000</v>
       </c>
       <c r="F80" s="1" t="n">
-        <v>7.94</v>
+        <v>4.24</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>2.65</v>
+        <v>1.41</v>
       </c>
       <c r="H80" s="1" t="n">
-        <v>15.88</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I80" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J80" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K80" s="1" t="n">
-        <v>135</v>
+        <v>72</v>
       </c>
       <c r="L80" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M80" s="1" t="n">
-        <v>2690000000</v>
+        <v>340000</v>
       </c>
       <c r="N80" s="1" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="O80" s="1" t="n">
-        <v>6310000000</v>
+        <v>1620000000</v>
       </c>
       <c r="P80" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -4855,49 +4855,49 @@
         <v>9</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>153000000000</v>
+        <v>18000000</v>
       </c>
       <c r="D81" s="1" t="n">
-        <v>383000000</v>
+        <v>45100</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>53600000000</v>
+        <v>657000</v>
       </c>
       <c r="F81" s="1" t="n">
-        <v>9.529999999999999</v>
+        <v>4.24</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>3.18</v>
+        <v>1.41</v>
       </c>
       <c r="H81" s="1" t="n">
-        <v>19.06</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I81" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J81" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K81" s="1" t="n">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="L81" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M81" s="1" t="n">
-        <v>3060000000</v>
+        <v>361000</v>
       </c>
       <c r="N81" s="1" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="O81" s="1" t="n">
-        <v>7190000000</v>
+        <v>1720000000</v>
       </c>
       <c r="P81" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -4909,22 +4909,22 @@
         <v>9</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>165000000000</v>
+        <v>19100000</v>
       </c>
       <c r="D82" s="1" t="n">
-        <v>414000000</v>
+        <v>47800</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>59000000000</v>
+        <v>707000</v>
       </c>
       <c r="F82" s="1" t="n">
-        <v>7.94</v>
+        <v>5.29</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>2.65</v>
+        <v>1.76</v>
       </c>
       <c r="H82" s="1" t="n">
-        <v>15.88</v>
+        <v>10.59</v>
       </c>
       <c r="I82" s="1" t="n">
         <v>0</v>
@@ -4935,19 +4935,19 @@
         </is>
       </c>
       <c r="K82" s="1" t="n">
-        <v>135</v>
+        <v>90</v>
       </c>
       <c r="L82" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M82" s="1" t="n">
-        <v>3310000000</v>
+        <v>383000</v>
       </c>
       <c r="N82" s="1" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="O82" s="1" t="n">
-        <v>7770000000</v>
+        <v>1820000000</v>
       </c>
       <c r="P82" s="1" t="inlineStr">
         <is>
@@ -4963,22 +4963,22 @@
         <v>9</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>192000000000</v>
+        <v>32400000</v>
       </c>
       <c r="D83" s="1" t="n">
-        <v>480000000</v>
+        <v>81100</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>71000000000</v>
+        <v>1370000</v>
       </c>
       <c r="F83" s="1" t="n">
-        <v>5.72</v>
+        <v>5.56</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="H83" s="1" t="n">
-        <v>11.44</v>
+        <v>11.12</v>
       </c>
       <c r="I83" s="1" t="n">
         <v>0</v>
@@ -4989,19 +4989,19 @@
         </is>
       </c>
       <c r="K83" s="1" t="n">
-        <v>162</v>
+        <v>157.5</v>
       </c>
       <c r="L83" s="1" t="n">
-        <v>64.8</v>
+        <v>63</v>
       </c>
       <c r="M83" s="1" t="n">
-        <v>3840000000</v>
+        <v>649000</v>
       </c>
       <c r="N83" s="1" t="n">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="O83" s="1" t="n">
-        <v>9010000000</v>
+        <v>3090000000</v>
       </c>
       <c r="P83" s="1" t="inlineStr">
         <is>
@@ -5017,49 +5017,49 @@
         <v>9</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>215000000000</v>
+        <v>21100000</v>
       </c>
       <c r="D84" s="1" t="n">
-        <v>537000000</v>
+        <v>52800</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>81800000000</v>
+        <v>801000</v>
       </c>
       <c r="F84" s="1" t="n">
-        <v>9.529999999999999</v>
+        <v>4.24</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>3.18</v>
+        <v>1.41</v>
       </c>
       <c r="H84" s="1" t="n">
-        <v>19.06</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I84" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J84" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="K84" s="1" t="n">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="L84" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M84" s="1" t="n">
-        <v>4300000000</v>
+        <v>423000</v>
       </c>
       <c r="N84" s="1" t="n">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="O84" s="1" t="n">
-        <v>10100000000</v>
+        <v>2010000000</v>
       </c>
       <c r="P84" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>쉬움</t>
         </is>
       </c>
     </row>
@@ -5071,49 +5071,49 @@
         <v>9</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>232000000000</v>
+        <v>22000000</v>
       </c>
       <c r="D85" s="1" t="n">
-        <v>580000000</v>
+        <v>55000</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>90100000000</v>
+        <v>843000</v>
       </c>
       <c r="F85" s="1" t="n">
-        <v>7.94</v>
+        <v>4.24</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>2.65</v>
+        <v>1.41</v>
       </c>
       <c r="H85" s="1" t="n">
-        <v>15.88</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I85" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J85" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="K85" s="1" t="n">
-        <v>135</v>
+        <v>72</v>
       </c>
       <c r="L85" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M85" s="1" t="n">
-        <v>4640000000</v>
+        <v>440000</v>
       </c>
       <c r="N85" s="1" t="n">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="O85" s="1" t="n">
-        <v>10900000000</v>
+        <v>2090000000</v>
       </c>
       <c r="P85" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>쉬움</t>
         </is>
       </c>
     </row>
@@ -5125,49 +5125,49 @@
         <v>9</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>265000000000</v>
+        <v>22900000</v>
       </c>
       <c r="D86" s="1" t="n">
-        <v>662000000</v>
+        <v>57300</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>106000000000</v>
+        <v>887000</v>
       </c>
       <c r="F86" s="1" t="n">
-        <v>9.529999999999999</v>
+        <v>4.24</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>3.18</v>
+        <v>1.41</v>
       </c>
       <c r="H86" s="1" t="n">
-        <v>19.06</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I86" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J86" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K86" s="1" t="n">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="L86" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M86" s="1" t="n">
-        <v>5290000000</v>
+        <v>459000</v>
       </c>
       <c r="N86" s="1" t="n">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="O86" s="1" t="n">
-        <v>12400000000</v>
+        <v>2180000000</v>
       </c>
       <c r="P86" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -5179,49 +5179,49 @@
         <v>9</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>286000000000</v>
+        <v>23900000</v>
       </c>
       <c r="D87" s="1" t="n">
-        <v>715000000</v>
+        <v>59700</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>117000000000</v>
+        <v>933000</v>
       </c>
       <c r="F87" s="1" t="n">
-        <v>7.94</v>
+        <v>4.24</v>
       </c>
       <c r="G87" s="1" t="n">
-        <v>2.65</v>
+        <v>1.41</v>
       </c>
       <c r="H87" s="1" t="n">
-        <v>15.88</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I87" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J87" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K87" s="1" t="n">
-        <v>135</v>
+        <v>72</v>
       </c>
       <c r="L87" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M87" s="1" t="n">
-        <v>5720000000</v>
+        <v>478000</v>
       </c>
       <c r="N87" s="1" t="n">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="O87" s="1" t="n">
-        <v>13400000000</v>
+        <v>2270000000</v>
       </c>
       <c r="P87" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -5233,49 +5233,49 @@
         <v>9</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>332000000000</v>
+        <v>28600000</v>
       </c>
       <c r="D88" s="1" t="n">
-        <v>829000000</v>
+        <v>71500</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>141000000000</v>
+        <v>1170000</v>
       </c>
       <c r="F88" s="1" t="n">
-        <v>5.72</v>
+        <v>3.18</v>
       </c>
       <c r="G88" s="1" t="n">
-        <v>1.91</v>
+        <v>1.06</v>
       </c>
       <c r="H88" s="1" t="n">
-        <v>11.44</v>
+        <v>6.35</v>
       </c>
       <c r="I88" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J88" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="K88" s="1" t="n">
-        <v>162</v>
+        <v>90</v>
       </c>
       <c r="L88" s="1" t="n">
-        <v>64.8</v>
+        <v>36</v>
       </c>
       <c r="M88" s="1" t="n">
-        <v>6630000000</v>
+        <v>572000</v>
       </c>
       <c r="N88" s="1" t="n">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="O88" s="1" t="n">
-        <v>15600000000</v>
+        <v>2720000000</v>
       </c>
       <c r="P88" s="1" t="inlineStr">
         <is>
-          <t>보스 층 · 허들</t>
+          <t>보스 층 · 어려움</t>
         </is>
       </c>
     </row>
@@ -5287,49 +5287,49 @@
         <v>9</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>371000000000</v>
+        <v>25900000</v>
       </c>
       <c r="D89" s="1" t="n">
-        <v>928000000</v>
+        <v>64800</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>162000000000</v>
+        <v>1030000</v>
       </c>
       <c r="F89" s="1" t="n">
-        <v>9.529999999999999</v>
+        <v>4.24</v>
       </c>
       <c r="G89" s="1" t="n">
-        <v>4.76</v>
+        <v>2.12</v>
       </c>
       <c r="H89" s="1" t="n">
-        <v>19.06</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I89" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J89" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K89" s="1" t="n">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="L89" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M89" s="1" t="n">
-        <v>7430000000</v>
+        <v>518000</v>
       </c>
       <c r="N89" s="1" t="n">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="O89" s="1" t="n">
-        <v>17400000000</v>
+        <v>2470000000</v>
       </c>
       <c r="P89" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -5341,49 +5341,49 @@
         <v>9</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>401000000000</v>
+        <v>27000000</v>
       </c>
       <c r="D90" s="1" t="n">
-        <v>1000000000</v>
+        <v>67500</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>178000000000</v>
+        <v>1090000</v>
       </c>
       <c r="F90" s="1" t="n">
-        <v>7.94</v>
+        <v>4.24</v>
       </c>
       <c r="G90" s="1" t="n">
-        <v>2.65</v>
+        <v>1.41</v>
       </c>
       <c r="H90" s="1" t="n">
-        <v>15.88</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I90" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J90" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K90" s="1" t="n">
-        <v>135</v>
+        <v>72</v>
       </c>
       <c r="L90" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M90" s="1" t="n">
-        <v>8020000000</v>
+        <v>540000</v>
       </c>
       <c r="N90" s="1" t="n">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="O90" s="1" t="n">
-        <v>18800000000</v>
+        <v>2570000000</v>
       </c>
       <c r="P90" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -5395,49 +5395,49 @@
         <v>9</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>457000000000</v>
+        <v>28100000</v>
       </c>
       <c r="D91" s="1" t="n">
-        <v>1140000000</v>
+        <v>70300</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>210000000000</v>
+        <v>1140000</v>
       </c>
       <c r="F91" s="1" t="n">
-        <v>9.529999999999999</v>
+        <v>4.24</v>
       </c>
       <c r="G91" s="1" t="n">
-        <v>3.18</v>
+        <v>1.41</v>
       </c>
       <c r="H91" s="1" t="n">
-        <v>19.06</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I91" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J91" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K91" s="1" t="n">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="L91" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M91" s="1" t="n">
-        <v>9140000000</v>
+        <v>562000</v>
       </c>
       <c r="N91" s="1" t="n">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="O91" s="1" t="n">
-        <v>21500000000</v>
+        <v>2680000000</v>
       </c>
       <c r="P91" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -5449,22 +5449,22 @@
         <v>9</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>494000000000</v>
+        <v>29300000</v>
       </c>
       <c r="D92" s="1" t="n">
-        <v>1230000000</v>
+        <v>73200</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>231000000000</v>
+        <v>1200000</v>
       </c>
       <c r="F92" s="1" t="n">
-        <v>7.94</v>
+        <v>5.29</v>
       </c>
       <c r="G92" s="1" t="n">
-        <v>2.65</v>
+        <v>1.76</v>
       </c>
       <c r="H92" s="1" t="n">
-        <v>15.88</v>
+        <v>10.59</v>
       </c>
       <c r="I92" s="1" t="n">
         <v>0</v>
@@ -5475,19 +5475,19 @@
         </is>
       </c>
       <c r="K92" s="1" t="n">
-        <v>135</v>
+        <v>90</v>
       </c>
       <c r="L92" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M92" s="1" t="n">
-        <v>9870000000</v>
+        <v>586000</v>
       </c>
       <c r="N92" s="1" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="O92" s="1" t="n">
-        <v>23200000000</v>
+        <v>2790000000</v>
       </c>
       <c r="P92" s="1" t="inlineStr">
         <is>
@@ -5503,22 +5503,22 @@
         <v>9</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>573000000000</v>
+        <v>48800000</v>
       </c>
       <c r="D93" s="1" t="n">
-        <v>1430000000</v>
+        <v>122000</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>279000000000</v>
+        <v>2280000</v>
       </c>
       <c r="F93" s="1" t="n">
-        <v>5.72</v>
+        <v>5.63</v>
       </c>
       <c r="G93" s="1" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="H93" s="1" t="n">
-        <v>11.44</v>
+        <v>11.27</v>
       </c>
       <c r="I93" s="1" t="n">
         <v>0</v>
@@ -5529,19 +5529,19 @@
         </is>
       </c>
       <c r="K93" s="1" t="n">
-        <v>162</v>
+        <v>159.6</v>
       </c>
       <c r="L93" s="1" t="n">
-        <v>64.8</v>
+        <v>63.8</v>
       </c>
       <c r="M93" s="1" t="n">
-        <v>11500000000</v>
+        <v>977000</v>
       </c>
       <c r="N93" s="1" t="n">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="O93" s="1" t="n">
-        <v>26900000000</v>
+        <v>4650000000</v>
       </c>
       <c r="P93" s="1" t="inlineStr">
         <is>
@@ -5557,49 +5557,49 @@
         <v>9</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>641000000000</v>
+        <v>31700000</v>
       </c>
       <c r="D94" s="1" t="n">
-        <v>1600000000</v>
+        <v>79300</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>321000000000</v>
+        <v>1330000</v>
       </c>
       <c r="F94" s="1" t="n">
-        <v>9.529999999999999</v>
+        <v>4.24</v>
       </c>
       <c r="G94" s="1" t="n">
-        <v>3.18</v>
+        <v>1.41</v>
       </c>
       <c r="H94" s="1" t="n">
-        <v>19.06</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I94" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J94" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="K94" s="1" t="n">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="L94" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M94" s="1" t="n">
-        <v>12800000000</v>
+        <v>634000</v>
       </c>
       <c r="N94" s="1" t="n">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="O94" s="1" t="n">
-        <v>30100000000</v>
+        <v>3020000000</v>
       </c>
       <c r="P94" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>쉬움</t>
         </is>
       </c>
     </row>
@@ -5611,49 +5611,49 @@
         <v>9</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>693000000000</v>
+        <v>32900000</v>
       </c>
       <c r="D95" s="1" t="n">
-        <v>1730000000</v>
+        <v>82300</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>353000000000</v>
+        <v>1390000</v>
       </c>
       <c r="F95" s="1" t="n">
-        <v>7.94</v>
+        <v>4.24</v>
       </c>
       <c r="G95" s="1" t="n">
-        <v>2.65</v>
+        <v>1.41</v>
       </c>
       <c r="H95" s="1" t="n">
-        <v>15.88</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I95" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J95" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="K95" s="1" t="n">
-        <v>135</v>
+        <v>72</v>
       </c>
       <c r="L95" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M95" s="1" t="n">
-        <v>13900000000</v>
+        <v>659000</v>
       </c>
       <c r="N95" s="1" t="n">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="O95" s="1" t="n">
-        <v>32500000000</v>
+        <v>3130000000</v>
       </c>
       <c r="P95" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>쉬움</t>
         </is>
       </c>
     </row>
@@ -5665,49 +5665,49 @@
         <v>9</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>790000000000</v>
+        <v>34200000</v>
       </c>
       <c r="D96" s="1" t="n">
-        <v>1970000000</v>
+        <v>85500</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>416000000000</v>
+        <v>1460000</v>
       </c>
       <c r="F96" s="1" t="n">
-        <v>9.529999999999999</v>
+        <v>4.24</v>
       </c>
       <c r="G96" s="1" t="n">
-        <v>3.18</v>
+        <v>1.41</v>
       </c>
       <c r="H96" s="1" t="n">
-        <v>19.06</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I96" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J96" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K96" s="1" t="n">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="L96" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M96" s="1" t="n">
-        <v>15800000000</v>
+        <v>684000</v>
       </c>
       <c r="N96" s="1" t="n">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="O96" s="1" t="n">
-        <v>37100000000</v>
+        <v>3250000000</v>
       </c>
       <c r="P96" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -5719,22 +5719,22 @@
         <v>9</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>853000000000</v>
+        <v>40900000</v>
       </c>
       <c r="D97" s="1" t="n">
-        <v>2130000000</v>
+        <v>102000</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>458000000000</v>
+        <v>1830000</v>
       </c>
       <c r="F97" s="1" t="n">
-        <v>4.76</v>
+        <v>3.18</v>
       </c>
       <c r="G97" s="1" t="n">
-        <v>2.38</v>
+        <v>1.59</v>
       </c>
       <c r="H97" s="1" t="n">
-        <v>9.529999999999999</v>
+        <v>6.35</v>
       </c>
       <c r="I97" s="1" t="n">
         <v>0</v>
@@ -5745,19 +5745,19 @@
         </is>
       </c>
       <c r="K97" s="1" t="n">
-        <v>135</v>
+        <v>90</v>
       </c>
       <c r="L97" s="1" t="n">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="M97" s="1" t="n">
-        <v>17100000000</v>
+        <v>817000</v>
       </c>
       <c r="N97" s="1" t="n">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="O97" s="1" t="n">
-        <v>40000000000</v>
+        <v>3890000000</v>
       </c>
       <c r="P97" s="1" t="inlineStr">
         <is>
@@ -5773,49 +5773,49 @@
         <v>9</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>989000000000</v>
+        <v>36900000</v>
       </c>
       <c r="D98" s="1" t="n">
-        <v>2470000000</v>
+        <v>92300</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>552000000000</v>
+        <v>1610000</v>
       </c>
       <c r="F98" s="1" t="n">
-        <v>9.529999999999999</v>
+        <v>4.24</v>
       </c>
       <c r="G98" s="1" t="n">
-        <v>4.76</v>
+        <v>2.12</v>
       </c>
       <c r="H98" s="1" t="n">
-        <v>19.06</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I98" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J98" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K98" s="1" t="n">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="L98" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M98" s="1" t="n">
-        <v>19800000000</v>
+        <v>738000</v>
       </c>
       <c r="N98" s="1" t="n">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="O98" s="1" t="n">
-        <v>46400000000</v>
+        <v>3510000000</v>
       </c>
       <c r="P98" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -5827,49 +5827,49 @@
         <v>9</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>1110000000000</v>
+        <v>38300000</v>
       </c>
       <c r="D99" s="1" t="n">
-        <v>2770000000</v>
+        <v>95900</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>636000000000</v>
+        <v>1690000</v>
       </c>
       <c r="F99" s="1" t="n">
-        <v>9.529999999999999</v>
+        <v>4.24</v>
       </c>
       <c r="G99" s="1" t="n">
-        <v>3.18</v>
+        <v>1.41</v>
       </c>
       <c r="H99" s="1" t="n">
-        <v>19.06</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I99" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J99" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K99" s="1" t="n">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="L99" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M99" s="1" t="n">
-        <v>22200000000</v>
+        <v>767000</v>
       </c>
       <c r="N99" s="1" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="O99" s="1" t="n">
-        <v>52000000000</v>
+        <v>3650000000</v>
       </c>
       <c r="P99" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -5881,22 +5881,22 @@
         <v>9</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>1200000000000</v>
+        <v>45800000</v>
       </c>
       <c r="D100" s="1" t="n">
-        <v>2990000000</v>
+        <v>115000</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>700000000000</v>
+        <v>2110000</v>
       </c>
       <c r="F100" s="1" t="n">
-        <v>4.76</v>
+        <v>3.18</v>
       </c>
       <c r="G100" s="1" t="n">
-        <v>1.59</v>
+        <v>1.06</v>
       </c>
       <c r="H100" s="1" t="n">
-        <v>9.529999999999999</v>
+        <v>6.35</v>
       </c>
       <c r="I100" s="1" t="n">
         <v>0</v>
@@ -5907,19 +5907,19 @@
         </is>
       </c>
       <c r="K100" s="1" t="n">
-        <v>135</v>
+        <v>90</v>
       </c>
       <c r="L100" s="1" t="n">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="M100" s="1" t="n">
-        <v>23900000000</v>
+        <v>916000</v>
       </c>
       <c r="N100" s="1" t="n">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="O100" s="1" t="n">
-        <v>56200000000</v>
+        <v>4360000000</v>
       </c>
       <c r="P100" s="1" t="inlineStr">
         <is>
@@ -5935,49 +5935,49 @@
         <v>9</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>1360000000000</v>
+        <v>41400000</v>
       </c>
       <c r="D101" s="1" t="n">
-        <v>3410000000</v>
+        <v>103000</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>824000000000</v>
+        <v>1860000</v>
       </c>
       <c r="F101" s="1" t="n">
-        <v>9.529999999999999</v>
+        <v>4.24</v>
       </c>
       <c r="G101" s="1" t="n">
-        <v>3.18</v>
+        <v>1.41</v>
       </c>
       <c r="H101" s="1" t="n">
-        <v>19.06</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I101" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J101" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K101" s="1" t="n">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="L101" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M101" s="1" t="n">
-        <v>27300000000</v>
+        <v>828000</v>
       </c>
       <c r="N101" s="1" t="n">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="O101" s="1" t="n">
-        <v>64000000000</v>
+        <v>3940000000</v>
       </c>
       <c r="P101" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -5989,22 +5989,22 @@
         <v>9</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>1470000000000</v>
+        <v>43000000</v>
       </c>
       <c r="D102" s="1" t="n">
-        <v>3680000000</v>
+        <v>107000</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>908000000000</v>
+        <v>1950000</v>
       </c>
       <c r="F102" s="1" t="n">
-        <v>7.94</v>
+        <v>5.29</v>
       </c>
       <c r="G102" s="1" t="n">
-        <v>2.65</v>
+        <v>1.76</v>
       </c>
       <c r="H102" s="1" t="n">
-        <v>15.88</v>
+        <v>10.59</v>
       </c>
       <c r="I102" s="1" t="n">
         <v>0</v>
@@ -6015,19 +6015,19 @@
         </is>
       </c>
       <c r="K102" s="1" t="n">
-        <v>135</v>
+        <v>90</v>
       </c>
       <c r="L102" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M102" s="1" t="n">
-        <v>29500000000</v>
+        <v>860000</v>
       </c>
       <c r="N102" s="1" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="O102" s="1" t="n">
-        <v>69200000000</v>
+        <v>4090000000</v>
       </c>
       <c r="P102" s="1" t="inlineStr">
         <is>
@@ -6043,22 +6043,22 @@
         <v>9</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>1710000000000</v>
+        <v>71400000</v>
       </c>
       <c r="D103" s="1" t="n">
-        <v>4270000000</v>
+        <v>179000</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>1090000000000</v>
+        <v>3670000</v>
       </c>
       <c r="F103" s="1" t="n">
-        <v>5.72</v>
+        <v>5.71</v>
       </c>
       <c r="G103" s="1" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="H103" s="1" t="n">
-        <v>11.44</v>
+        <v>11.41</v>
       </c>
       <c r="I103" s="1" t="n">
         <v>0</v>
@@ -6069,19 +6069,19 @@
         </is>
       </c>
       <c r="K103" s="1" t="n">
-        <v>162</v>
+        <v>161.7</v>
       </c>
       <c r="L103" s="1" t="n">
-        <v>64.8</v>
+        <v>64.7</v>
       </c>
       <c r="M103" s="1" t="n">
-        <v>34200000000</v>
+        <v>1430000</v>
       </c>
       <c r="N103" s="1" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="O103" s="1" t="n">
-        <v>80200000000</v>
+        <v>6800000000</v>
       </c>
       <c r="P103" s="1" t="inlineStr">
         <is>

--- a/Data_Table/스테이지 테이블.xlsx
+++ b/Data_Table/스테이지 테이블.xlsx
@@ -967,13 +967,13 @@
         <v>5</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>1860</v>
+        <v>984</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>4.64</v>
+        <v>2.46</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>6.81</v>
+        <v>3.08</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>4.65</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="K9" s="1" t="n">
@@ -999,7 +999,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>37.12</v>
+        <v>19.69</v>
       </c>
       <c r="N9" s="1" t="n">
         <v>4</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="P9" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
     </row>
@@ -1021,13 +1021,13 @@
         <v>5</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>2450</v>
+        <v>1240</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>6.13</v>
+        <v>3.1</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>9.640000000000001</v>
+        <v>4.11</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>5.81</v>
@@ -1053,7 +1053,7 @@
         <v>0</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>49.01</v>
+        <v>24.81</v>
       </c>
       <c r="N10" s="1" t="n">
         <v>4</v>
@@ -1075,13 +1075,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>3230</v>
+        <v>1560</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>8.09</v>
+        <v>3.91</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>13.64</v>
+        <v>5.49</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>4.24</v>
@@ -1107,7 +1107,7 @@
         <v>0</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>64.69</v>
+        <v>31.26</v>
       </c>
       <c r="N11" s="1" t="n">
         <v>5</v>
@@ -1129,13 +1129,13 @@
         <v>6</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>4270</v>
+        <v>1970</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>10.67</v>
+        <v>4.92</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>19.29</v>
+        <v>7.33</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>2.59</v>
@@ -1161,7 +1161,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>85.39</v>
+        <v>39.38</v>
       </c>
       <c r="N12" s="1" t="n">
         <v>6</v>
@@ -1183,39 +1183,39 @@
         <v>7</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>5640</v>
+        <v>4470</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>14.09</v>
+        <v>11.16</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>27.3</v>
+        <v>20.41</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>2.93</v>
+        <v>4.4</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>0.98</v>
+        <v>1.47</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>3.91</v>
+        <v>5.86</v>
       </c>
       <c r="I13" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="K13" s="1" t="n">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>28.8</v>
+        <v>43.2</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>113</v>
+        <v>89.31999999999999</v>
       </c>
       <c r="N13" s="1" t="n">
         <v>6</v>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="P13" s="1" t="inlineStr">
         <is>
-          <t>보스 층 · 보통</t>
+          <t>보스 층 · 허들</t>
         </is>
       </c>
     </row>
@@ -1237,13 +1237,13 @@
         <v>7</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>7440</v>
+        <v>3130</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>18.6</v>
+        <v>7.82</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>38.62</v>
+        <v>13.07</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>0.8</v>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="J14" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="K14" s="1" t="n">
@@ -1269,7 +1269,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>149</v>
+        <v>62.52</v>
       </c>
       <c r="N14" s="1" t="n">
         <v>7</v>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="P14" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
     </row>
@@ -1291,13 +1291,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>9820</v>
+        <v>3940</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>24.55</v>
+        <v>9.85</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>54.64</v>
+        <v>17.44</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>3.26</v>
@@ -1323,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>196</v>
+        <v>78.78</v>
       </c>
       <c r="N15" s="1" t="n">
         <v>8</v>
@@ -1345,13 +1345,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>13000</v>
+        <v>4960</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>32.4</v>
+        <v>12.41</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>77.31</v>
+        <v>23.29</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>8.9</v>
@@ -1377,7 +1377,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>259</v>
+        <v>99.26000000000001</v>
       </c>
       <c r="N16" s="1" t="n">
         <v>9</v>
@@ -1399,13 +1399,13 @@
         <v>9</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>17100</v>
+        <v>6250</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>42.77</v>
+        <v>15.63</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>109</v>
+        <v>31.09</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>5.09</v>
@@ -1431,7 +1431,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>342</v>
+        <v>125</v>
       </c>
       <c r="N17" s="1" t="n">
         <v>9</v>
@@ -1453,13 +1453,13 @@
         <v>9</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>22600</v>
+        <v>23600</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>56.46</v>
+        <v>59.1</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>0.8</v>
@@ -1468,24 +1468,24 @@
         <v>0.8</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>6.11</v>
+        <v>9.16</v>
       </c>
       <c r="I18" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="K18" s="1" t="n">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>28.8</v>
+        <v>43.2</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>452</v>
+        <v>473</v>
       </c>
       <c r="N18" s="1" t="n">
         <v>10</v>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="P18" s="1" t="inlineStr">
         <is>
-          <t>보스 층 · 보통</t>
+          <t>보스 층 · 허들</t>
         </is>
       </c>
     </row>
@@ -1507,39 +1507,39 @@
         <v>9</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>39500</v>
+        <v>9930</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>98.81</v>
+        <v>24.82</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>312</v>
+        <v>55.4</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>61.09</v>
+        <v>40.72</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>61.09</v>
+        <v>40.72</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>15.27</v>
+        <v>10.18</v>
       </c>
       <c r="I19" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="K19" s="1" t="n">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="L19" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>790</v>
+        <v>199</v>
       </c>
       <c r="N19" s="1" t="n">
         <v>10</v>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="P19" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>쉬움</t>
         </is>
       </c>
     </row>
@@ -1561,39 +1561,39 @@
         <v>9</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>67200</v>
+        <v>12500</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>168</v>
+        <v>31.25</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>605</v>
+        <v>73.89</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>3.24</v>
+        <v>2.59</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>1.08</v>
+        <v>0.86</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>15.78</v>
+        <v>12.62</v>
       </c>
       <c r="I20" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K20" s="1" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="L20" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>1340</v>
+        <v>250</v>
       </c>
       <c r="N20" s="1" t="n">
         <v>10</v>
@@ -1603,7 +1603,7 @@
       </c>
       <c r="P20" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -1615,39 +1615,39 @@
         <v>9</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>141000</v>
+        <v>15700</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>353</v>
+        <v>39.35</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>1530</v>
+        <v>98.56</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>9.470000000000001</v>
+        <v>6.31</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>3.16</v>
+        <v>2.1</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>22.57</v>
+        <v>15.05</v>
       </c>
       <c r="I21" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K21" s="1" t="n">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="L21" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>2820</v>
+        <v>315</v>
       </c>
       <c r="N21" s="1" t="n">
         <v>10</v>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="P21" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -1669,39 +1669,39 @@
         <v>9</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>310000</v>
+        <v>69400</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>776</v>
+        <v>173</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>4100</v>
+        <v>629</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>9.4</v>
+        <v>11.28</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>3.13</v>
+        <v>3.76</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>18.81</v>
+        <v>22.57</v>
       </c>
       <c r="I22" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="K22" s="1" t="n">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="L22" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>6210</v>
+        <v>1390</v>
       </c>
       <c r="N22" s="1" t="n">
         <v>10</v>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="P22" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>허들</t>
         </is>
       </c>
     </row>
@@ -1723,39 +1723,39 @@
         <v>9</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>228000</v>
+        <v>28700</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>571</v>
+        <v>71.75</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>2790</v>
+        <v>209</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>7.49</v>
+        <v>5.99</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>14.88</v>
+        <v>11.9</v>
       </c>
       <c r="I23" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="K23" s="1" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>36</v>
+        <v>28.8</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>4570</v>
+        <v>574</v>
       </c>
       <c r="N23" s="1" t="n">
         <v>15</v>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="P23" s="1" t="inlineStr">
         <is>
-          <t>보스 층 · 어려움</t>
+          <t>보스 층 · 쉬움</t>
         </is>
       </c>
     </row>
@@ -1777,13 +1777,13 @@
         <v>9</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>203000</v>
+        <v>31400</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>508</v>
+        <v>78.56</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>2410</v>
+        <v>234</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>9.92</v>
@@ -1809,7 +1809,7 @@
         <v>0</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>4060</v>
+        <v>628</v>
       </c>
       <c r="N24" s="1" t="n">
         <v>16</v>
@@ -1831,13 +1831,13 @@
         <v>9</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>208000</v>
+        <v>39600</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>520</v>
+        <v>98.92</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>2480</v>
+        <v>312</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>23.27</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>4160</v>
+        <v>791</v>
       </c>
       <c r="N25" s="1" t="n">
         <v>17</v>
@@ -1885,13 +1885,13 @@
         <v>9</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>213000</v>
+        <v>49800</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>532</v>
+        <v>125</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>2550</v>
+        <v>416</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>9.85</v>
@@ -1917,7 +1917,7 @@
         <v>0</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>4250</v>
+        <v>996</v>
       </c>
       <c r="N26" s="1" t="n">
         <v>18</v>
@@ -1939,13 +1939,13 @@
         <v>9</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>218000</v>
+        <v>62700</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>544</v>
+        <v>157</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>2630</v>
+        <v>555</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>16.54</v>
@@ -1971,7 +1971,7 @@
         <v>0</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>4350</v>
+        <v>1250</v>
       </c>
       <c r="N27" s="1" t="n">
         <v>19</v>
@@ -1993,13 +1993,13 @@
         <v>9</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>256000</v>
+        <v>90800</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>640</v>
+        <v>227</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>3220</v>
+        <v>882</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>10.31</v>
@@ -2025,7 +2025,7 @@
         <v>36</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>5120</v>
+        <v>1820</v>
       </c>
       <c r="N28" s="1" t="n">
         <v>20</v>
@@ -2047,13 +2047,13 @@
         <v>9</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>228000</v>
+        <v>99500</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>570</v>
+        <v>249</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>2780</v>
+        <v>987</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>4.24</v>
@@ -2079,7 +2079,7 @@
         <v>0</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>4560</v>
+        <v>1990</v>
       </c>
       <c r="N29" s="1" t="n">
         <v>20</v>
@@ -2101,13 +2101,13 @@
         <v>9</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>233000</v>
+        <v>125000</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>583</v>
+        <v>313</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>2870</v>
+        <v>1320</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>4.24</v>
@@ -2133,7 +2133,7 @@
         <v>0</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>4670</v>
+        <v>2500</v>
       </c>
       <c r="N30" s="1" t="n">
         <v>20</v>
@@ -2155,13 +2155,13 @@
         <v>9</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>239000</v>
+        <v>158000</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>597</v>
+        <v>394</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>2950</v>
+        <v>1760</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>4.24</v>
@@ -2187,7 +2187,7 @@
         <v>0</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>4770</v>
+        <v>3150</v>
       </c>
       <c r="N31" s="1" t="n">
         <v>20</v>
@@ -2209,13 +2209,13 @@
         <v>9</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>244000</v>
+        <v>199000</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>611</v>
+        <v>496</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>3040</v>
+        <v>2340</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>5.29</v>
@@ -2241,7 +2241,7 @@
         <v>0</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>4890</v>
+        <v>3970</v>
       </c>
       <c r="N32" s="1" t="n">
         <v>20</v>

--- a/Data_Table/스테이지 테이블.xlsx
+++ b/Data_Table/스테이지 테이블.xlsx
@@ -1453,13 +1453,13 @@
         <v>9</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>23600</v>
+        <v>15800</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>59.1</v>
+        <v>39.4</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>164</v>
+        <v>98.7</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>0.8</v>
@@ -1485,7 +1485,7 @@
         <v>43.2</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>473</v>
+        <v>315</v>
       </c>
       <c r="N18" s="1" t="n">
         <v>10</v>
@@ -1669,39 +1669,39 @@
         <v>9</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>69400</v>
+        <v>19800</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>173</v>
+        <v>49.55</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>629</v>
+        <v>131</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>11.28</v>
+        <v>7.52</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>3.76</v>
+        <v>2.51</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>22.57</v>
+        <v>15.05</v>
       </c>
       <c r="I22" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K22" s="1" t="n">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="L22" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>1390</v>
+        <v>396</v>
       </c>
       <c r="N22" s="1" t="n">
         <v>10</v>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="P22" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -1723,39 +1723,39 @@
         <v>9</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>28700</v>
+        <v>49900</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>71.75</v>
+        <v>125</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>209</v>
+        <v>417</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>5.99</v>
+        <v>8.99</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>11.9</v>
+        <v>17.85</v>
       </c>
       <c r="I23" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="K23" s="1" t="n">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>28.8</v>
+        <v>43.2</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>574</v>
+        <v>998</v>
       </c>
       <c r="N23" s="1" t="n">
         <v>15</v>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="P23" s="1" t="inlineStr">
         <is>
-          <t>보스 층 · 쉬움</t>
+          <t>보스 층 · 허들</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="J24" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="K24" s="1" t="n">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="P24" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
     </row>

--- a/Data_Table/스테이지 테이블.xlsx
+++ b/Data_Table/스테이지 테이블.xlsx
@@ -773,7 +773,7 @@
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K5" s="1" t="n">
@@ -793,7 +793,7 @@
       </c>
       <c r="P5" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -805,13 +805,13 @@
         <v>3</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>625</v>
+        <v>661</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>47.97</v>
@@ -827,7 +827,7 @@
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K6" s="1" t="n">
@@ -837,7 +837,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>12.5</v>
+        <v>13.21</v>
       </c>
       <c r="N6" s="1" t="n">
         <v>1</v>
@@ -847,7 +847,7 @@
       </c>
       <c r="P6" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -859,13 +859,13 @@
         <v>4</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>781</v>
+        <v>873</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>2.31</v>
+        <v>2.65</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>13.73</v>
@@ -881,7 +881,7 @@
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K7" s="1" t="n">
@@ -891,7 +891,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>15.62</v>
+        <v>17.46</v>
       </c>
       <c r="N7" s="1" t="n">
         <v>1</v>
@@ -901,7 +901,7 @@
       </c>
       <c r="P7" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -913,22 +913,22 @@
         <v>4</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>1410</v>
+        <v>1500</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>3.52</v>
+        <v>3.75</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>4.81</v>
+        <v>5.22</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>1.7</v>
+        <v>1.22</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>10.11</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="I8" s="1" t="n">
         <v>0</v>
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="K8" s="1" t="n">
-        <v>108</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>43.2</v>
+        <v>35.8</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>28.12</v>
+        <v>30</v>
       </c>
       <c r="N8" s="1" t="n">
         <v>3</v>
@@ -967,13 +967,13 @@
         <v>5</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>984</v>
+        <v>1360</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>2.46</v>
+        <v>3.4</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>3.08</v>
+        <v>4.62</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>4.65</v>
@@ -999,7 +999,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>19.69</v>
+        <v>27.21</v>
       </c>
       <c r="N9" s="1" t="n">
         <v>4</v>
@@ -1021,13 +1021,13 @@
         <v>5</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>1240</v>
+        <v>1600</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>3.1</v>
+        <v>4.01</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>4.11</v>
+        <v>5.68</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>5.81</v>
@@ -1053,7 +1053,7 @@
         <v>0</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>24.81</v>
+        <v>32.09</v>
       </c>
       <c r="N10" s="1" t="n">
         <v>4</v>
@@ -1075,13 +1075,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>1560</v>
+        <v>1890</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>3.91</v>
+        <v>4.73</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>5.49</v>
+        <v>6.97</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>4.24</v>
@@ -1107,7 +1107,7 @@
         <v>0</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>31.26</v>
+        <v>37.84</v>
       </c>
       <c r="N11" s="1" t="n">
         <v>5</v>
@@ -1129,39 +1129,39 @@
         <v>6</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>1970</v>
+        <v>2900</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>4.92</v>
+        <v>7.25</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>7.33</v>
+        <v>11.9</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>2.59</v>
+        <v>3.22</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>1.29</v>
+        <v>1.61</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>10.54</v>
       </c>
       <c r="I12" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="K12" s="1" t="n">
-        <v>72</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="L12" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>39.38</v>
+        <v>58</v>
       </c>
       <c r="N12" s="1" t="n">
         <v>6</v>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="P12" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
     </row>
@@ -1183,39 +1183,39 @@
         <v>7</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>4470</v>
+        <v>3010</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>11.16</v>
+        <v>7.53</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>20.41</v>
+        <v>12.47</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>4.4</v>
+        <v>3.66</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>5.86</v>
+        <v>4.89</v>
       </c>
       <c r="I13" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="K13" s="1" t="n">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>43.2</v>
+        <v>36</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>89.31999999999999</v>
+        <v>60.21</v>
       </c>
       <c r="N13" s="1" t="n">
         <v>6</v>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="P13" s="1" t="inlineStr">
         <is>
-          <t>보스 층 · 허들</t>
+          <t>보스 층 · 어려움</t>
         </is>
       </c>
     </row>
@@ -1237,13 +1237,13 @@
         <v>7</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>3130</v>
+        <v>3070</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>7.82</v>
+        <v>7.68</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>13.07</v>
+        <v>12.79</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>0.8</v>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="J14" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K14" s="1" t="n">
@@ -1269,7 +1269,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>62.52</v>
+        <v>61.44</v>
       </c>
       <c r="N14" s="1" t="n">
         <v>7</v>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="P14" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -1291,13 +1291,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>3940</v>
+        <v>3610</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>9.85</v>
+        <v>9.01</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>17.44</v>
+        <v>15.62</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>3.26</v>
@@ -1323,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>78.78</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="N15" s="1" t="n">
         <v>8</v>
@@ -1345,39 +1345,39 @@
         <v>8</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>4960</v>
+        <v>5500</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>12.41</v>
+        <v>13.75</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>23.29</v>
+        <v>26.48</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>8.9</v>
+        <v>11.59</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>2.97</v>
+        <v>3.86</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>6.52</v>
+        <v>8.49</v>
       </c>
       <c r="I16" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="K16" s="1" t="n">
-        <v>72</v>
+        <v>93.8</v>
       </c>
       <c r="L16" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>99.26000000000001</v>
+        <v>110</v>
       </c>
       <c r="N16" s="1" t="n">
         <v>9</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="P16" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
     </row>
@@ -1399,13 +1399,13 @@
         <v>9</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>6250</v>
+        <v>4850</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>15.63</v>
+        <v>12.13</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>31.09</v>
+        <v>22.63</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>5.09</v>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="J17" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="K17" s="1" t="n">
@@ -1431,7 +1431,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>125</v>
+        <v>97.02</v>
       </c>
       <c r="N17" s="1" t="n">
         <v>9</v>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="P17" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
     </row>
@@ -1453,13 +1453,13 @@
         <v>9</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>15800</v>
+        <v>6400</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>39.4</v>
+        <v>15.99</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>98.7</v>
+        <v>31.98</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>0.8</v>
@@ -1468,24 +1468,24 @@
         <v>0.8</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>9.16</v>
+        <v>7.64</v>
       </c>
       <c r="I18" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="K18" s="1" t="n">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>43.2</v>
+        <v>36</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>315</v>
+        <v>128</v>
       </c>
       <c r="N18" s="1" t="n">
         <v>10</v>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="P18" s="1" t="inlineStr">
         <is>
-          <t>보스 층 · 허들</t>
+          <t>보스 층 · 어려움</t>
         </is>
       </c>
     </row>
@@ -1507,13 +1507,13 @@
         <v>9</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>9930</v>
+        <v>6380</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>24.82</v>
+        <v>15.94</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>55.4</v>
+        <v>31.86</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>40.72</v>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="J19" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K19" s="1" t="n">
@@ -1539,7 +1539,7 @@
         <v>0</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>199</v>
+        <v>128</v>
       </c>
       <c r="N19" s="1" t="n">
         <v>10</v>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="P19" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -1561,13 +1561,13 @@
         <v>9</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>12500</v>
+        <v>7310</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>31.25</v>
+        <v>18.28</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>73.89</v>
+        <v>37.8</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>2.59</v>
@@ -1593,7 +1593,7 @@
         <v>0</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>250</v>
+        <v>146</v>
       </c>
       <c r="N20" s="1" t="n">
         <v>10</v>
@@ -1615,39 +1615,39 @@
         <v>9</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>15700</v>
+        <v>10900</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>39.35</v>
+        <v>27.25</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>98.56</v>
+        <v>62.26</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>6.31</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>15.05</v>
+        <v>20.77</v>
       </c>
       <c r="I21" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="K21" s="1" t="n">
-        <v>72</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="L21" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>315</v>
+        <v>218</v>
       </c>
       <c r="N21" s="1" t="n">
         <v>10</v>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="P21" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
     </row>
@@ -1669,13 +1669,13 @@
         <v>9</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>19800</v>
+        <v>9990</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>49.55</v>
+        <v>24.98</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>131</v>
+        <v>55.85</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>7.52</v>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="J22" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="K22" s="1" t="n">
@@ -1701,7 +1701,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>396</v>
+        <v>200</v>
       </c>
       <c r="N22" s="1" t="n">
         <v>10</v>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="P22" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
     </row>
@@ -1723,39 +1723,39 @@
         <v>9</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>49900</v>
+        <v>13700</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>125</v>
+        <v>34.24</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>417</v>
+        <v>82.81</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>8.99</v>
+        <v>7.49</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>17.85</v>
+        <v>14.88</v>
       </c>
       <c r="I23" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="K23" s="1" t="n">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>43.2</v>
+        <v>36</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>998</v>
+        <v>274</v>
       </c>
       <c r="N23" s="1" t="n">
         <v>15</v>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="P23" s="1" t="inlineStr">
         <is>
-          <t>보스 층 · 허들</t>
+          <t>보스 층 · 어려움</t>
         </is>
       </c>
     </row>
@@ -1777,13 +1777,13 @@
         <v>9</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>31400</v>
+        <v>14200</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>78.56</v>
+        <v>35.48</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>234</v>
+        <v>86.58</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>9.92</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="J24" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K24" s="1" t="n">
@@ -1809,7 +1809,7 @@
         <v>0</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>628</v>
+        <v>284</v>
       </c>
       <c r="N24" s="1" t="n">
         <v>16</v>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="P24" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -1831,13 +1831,13 @@
         <v>9</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>39600</v>
+        <v>16900</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>98.92</v>
+        <v>42.28</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>312</v>
+        <v>108</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>23.27</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>791</v>
+        <v>338</v>
       </c>
       <c r="N25" s="1" t="n">
         <v>17</v>
@@ -1885,39 +1885,39 @@
         <v>9</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>49800</v>
+        <v>26200</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>125</v>
+        <v>65.5</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>416</v>
+        <v>186</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>9.85</v>
+        <v>14.36</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>3.28</v>
+        <v>4.79</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>27.5</v>
+        <v>40.11</v>
       </c>
       <c r="I26" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="K26" s="1" t="n">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="L26" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>996</v>
+        <v>524</v>
       </c>
       <c r="N26" s="1" t="n">
         <v>18</v>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="P26" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
     </row>
@@ -1939,13 +1939,13 @@
         <v>9</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>62700</v>
+        <v>23600</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>157</v>
+        <v>59</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>555</v>
+        <v>164</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>16.54</v>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="J27" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="K27" s="1" t="n">
@@ -1971,7 +1971,7 @@
         <v>0</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>1250</v>
+        <v>472</v>
       </c>
       <c r="N27" s="1" t="n">
         <v>19</v>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="P27" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
     </row>
@@ -1993,13 +1993,13 @@
         <v>9</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>90800</v>
+        <v>31800</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>227</v>
+        <v>79.45999999999999</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>882</v>
+        <v>237</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>10.31</v>
@@ -2025,7 +2025,7 @@
         <v>36</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>1820</v>
+        <v>636</v>
       </c>
       <c r="N28" s="1" t="n">
         <v>20</v>
@@ -2047,13 +2047,13 @@
         <v>9</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>99500</v>
+        <v>32400</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>249</v>
+        <v>80.91</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>987</v>
+        <v>243</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>4.24</v>
@@ -2079,7 +2079,7 @@
         <v>0</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>1990</v>
+        <v>647</v>
       </c>
       <c r="N29" s="1" t="n">
         <v>20</v>
@@ -2101,13 +2101,13 @@
         <v>9</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>125000</v>
+        <v>37900</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>313</v>
+        <v>94.75</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>1320</v>
+        <v>296</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>4.24</v>
@@ -2133,7 +2133,7 @@
         <v>0</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>2500</v>
+        <v>758</v>
       </c>
       <c r="N30" s="1" t="n">
         <v>20</v>
@@ -2155,39 +2155,39 @@
         <v>9</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>158000</v>
+        <v>57700</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>394</v>
+        <v>144</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>1760</v>
+        <v>500</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>4.24</v>
+        <v>6.51</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>1.41</v>
+        <v>2.17</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>13.01</v>
       </c>
       <c r="I31" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="K31" s="1" t="n">
-        <v>72</v>
+        <v>110.6</v>
       </c>
       <c r="L31" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>3150</v>
+        <v>1150</v>
       </c>
       <c r="N31" s="1" t="n">
         <v>20</v>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="P31" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
     </row>
@@ -2209,39 +2209,39 @@
         <v>9</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>199000</v>
+        <v>58500</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>496</v>
+        <v>146</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>2340</v>
+        <v>509</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>5.29</v>
+        <v>4.24</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>1.76</v>
+        <v>1.41</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>10.59</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I32" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J32" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="K32" s="1" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="L32" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>3970</v>
+        <v>1170</v>
       </c>
       <c r="N32" s="1" t="n">
         <v>20</v>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="P32" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>쉬움</t>
         </is>
       </c>
     </row>
@@ -2263,49 +2263,49 @@
         <v>9</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>400000</v>
+        <v>88800</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>1000</v>
+        <v>222</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>5620</v>
+        <v>857</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>5.19</v>
+        <v>3.18</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>1.73</v>
+        <v>1.06</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>10.38</v>
+        <v>6.35</v>
       </c>
       <c r="I33" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="K33" s="1" t="n">
-        <v>147</v>
+        <v>90</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>58.8</v>
+        <v>36</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>8000</v>
+        <v>1780</v>
       </c>
       <c r="N33" s="1" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O33" s="1" t="n">
         <v>38100000</v>
       </c>
       <c r="P33" s="1" t="inlineStr">
         <is>
-          <t>보스 층 · 허들</t>
+          <t>보스 층 · 어려움</t>
         </is>
       </c>
     </row>
@@ -2317,13 +2317,13 @@
         <v>9</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>267000</v>
+        <v>102000</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>669</v>
+        <v>255</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>3400</v>
+        <v>1020</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>4.24</v>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="J34" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K34" s="1" t="n">
@@ -2349,17 +2349,17 @@
         <v>0</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>5350</v>
+        <v>2040</v>
       </c>
       <c r="N34" s="1" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O34" s="1" t="n">
-        <v>25400000</v>
+        <v>43600000</v>
       </c>
       <c r="P34" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -2371,13 +2371,13 @@
         <v>9</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>286000</v>
+        <v>134000</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>715</v>
+        <v>336</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>3700</v>
+        <v>1440</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>4.24</v>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="J35" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K35" s="1" t="n">
@@ -2403,17 +2403,17 @@
         <v>0</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>5720</v>
+        <v>2690</v>
       </c>
       <c r="N35" s="1" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O35" s="1" t="n">
-        <v>27200000</v>
+        <v>57600000</v>
       </c>
       <c r="P35" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -2425,13 +2425,13 @@
         <v>9</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>306000</v>
+        <v>177000</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>765</v>
+        <v>443</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>4020</v>
+        <v>2030</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>4.24</v>
@@ -2457,13 +2457,13 @@
         <v>0</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>6120</v>
+        <v>3540</v>
       </c>
       <c r="N36" s="1" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O36" s="1" t="n">
-        <v>29100000</v>
+        <v>75900000</v>
       </c>
       <c r="P36" s="1" t="inlineStr">
         <is>
@@ -2479,49 +2479,49 @@
         <v>9</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>327000</v>
+        <v>304000</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>818</v>
+        <v>760</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>4370</v>
+        <v>3990</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>4.24</v>
+        <v>6.92</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>2.12</v>
+        <v>3.46</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>13.84</v>
       </c>
       <c r="I37" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="K37" s="1" t="n">
-        <v>72</v>
+        <v>117.6</v>
       </c>
       <c r="L37" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>6540</v>
+        <v>6080</v>
       </c>
       <c r="N37" s="1" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="O37" s="1" t="n">
-        <v>31100000</v>
+        <v>130000000</v>
       </c>
       <c r="P37" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
     </row>
@@ -2533,13 +2533,13 @@
         <v>9</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>402000</v>
+        <v>298000</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>1010</v>
+        <v>744</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>5670</v>
+        <v>3890</v>
       </c>
       <c r="F38" s="1" t="n">
         <v>3.18</v>
@@ -2565,13 +2565,13 @@
         <v>36</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>8050</v>
+        <v>5950</v>
       </c>
       <c r="N38" s="1" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="O38" s="1" t="n">
-        <v>38300000</v>
+        <v>128000000</v>
       </c>
       <c r="P38" s="1" t="inlineStr">
         <is>
@@ -2587,13 +2587,13 @@
         <v>9</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>374000</v>
+        <v>287000</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>936</v>
+        <v>716</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>5180</v>
+        <v>3710</v>
       </c>
       <c r="F39" s="1" t="n">
         <v>4.24</v>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>7490</v>
+        <v>5730</v>
       </c>
       <c r="N39" s="1" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="O39" s="1" t="n">
-        <v>35600000</v>
+        <v>123000000</v>
       </c>
       <c r="P39" s="1" t="inlineStr">
         <is>
@@ -2641,13 +2641,13 @@
         <v>9</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>400000</v>
+        <v>317000</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>1000</v>
+        <v>793</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>5630</v>
+        <v>4210</v>
       </c>
       <c r="F40" s="1" t="n">
         <v>4.24</v>
@@ -2673,13 +2673,13 @@
         <v>0</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>8010</v>
+        <v>6350</v>
       </c>
       <c r="N40" s="1" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="O40" s="1" t="n">
-        <v>38100000</v>
+        <v>136000000</v>
       </c>
       <c r="P40" s="1" t="inlineStr">
         <is>
@@ -2695,13 +2695,13 @@
         <v>9</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>428000</v>
+        <v>351000</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>1070</v>
+        <v>878</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>6120</v>
+        <v>4780</v>
       </c>
       <c r="F41" s="1" t="n">
         <v>4.24</v>
@@ -2727,13 +2727,13 @@
         <v>0</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>8570</v>
+        <v>7030</v>
       </c>
       <c r="N41" s="1" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O41" s="1" t="n">
-        <v>40700000</v>
+        <v>151000000</v>
       </c>
       <c r="P41" s="1" t="inlineStr">
         <is>
@@ -2749,49 +2749,49 @@
         <v>9</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>458000</v>
+        <v>389000</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>1150</v>
+        <v>973</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>6660</v>
+        <v>5430</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>5.29</v>
+        <v>4.24</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>2.65</v>
+        <v>2.12</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>10.59</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I42" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J42" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K42" s="1" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="L42" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>9160</v>
+        <v>7780</v>
       </c>
       <c r="N42" s="1" t="n">
         <v>35</v>
       </c>
       <c r="O42" s="1" t="n">
-        <v>43600000</v>
+        <v>167000000</v>
       </c>
       <c r="P42" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -2803,22 +2803,22 @@
         <v>9</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>784000</v>
+        <v>560000</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>1960</v>
+        <v>1400</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>13000</v>
+        <v>8560</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>5.26</v>
+        <v>5.19</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>10.52</v>
+        <v>10.38</v>
       </c>
       <c r="I43" s="1" t="n">
         <v>0</v>
@@ -2829,19 +2829,19 @@
         </is>
       </c>
       <c r="K43" s="1" t="n">
-        <v>149.1</v>
+        <v>147</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>59.6</v>
+        <v>58.8</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>15700</v>
+        <v>11200</v>
       </c>
       <c r="N43" s="1" t="n">
         <v>41</v>
       </c>
       <c r="O43" s="1" t="n">
-        <v>74600000</v>
+        <v>240000000</v>
       </c>
       <c r="P43" s="1" t="inlineStr">
         <is>
@@ -2857,13 +2857,13 @@
         <v>9</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>562000</v>
+        <v>456000</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>1410</v>
+        <v>1140</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>8610</v>
+        <v>6620</v>
       </c>
       <c r="F44" s="1" t="n">
         <v>4.24</v>
@@ -2889,13 +2889,13 @@
         <v>0</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>11200</v>
+        <v>9110</v>
       </c>
       <c r="N44" s="1" t="n">
         <v>41</v>
       </c>
       <c r="O44" s="1" t="n">
-        <v>53500000</v>
+        <v>195000000</v>
       </c>
       <c r="P44" s="1" t="inlineStr">
         <is>
@@ -2911,13 +2911,13 @@
         <v>9</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>645000</v>
+        <v>482000</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>1610</v>
+        <v>1200</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>10200</v>
+        <v>7100</v>
       </c>
       <c r="F45" s="1" t="n">
         <v>4.24</v>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="J45" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K45" s="1" t="n">
@@ -2943,17 +2943,17 @@
         <v>0</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>12900</v>
+        <v>9640</v>
       </c>
       <c r="N45" s="1" t="n">
         <v>41</v>
       </c>
       <c r="O45" s="1" t="n">
-        <v>61400000</v>
+        <v>207000000</v>
       </c>
       <c r="P45" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -2965,13 +2965,13 @@
         <v>9</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>741000</v>
+        <v>510000</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>1850</v>
+        <v>1270</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>12100</v>
+        <v>7610</v>
       </c>
       <c r="F46" s="1" t="n">
         <v>4.24</v>
@@ -2997,13 +2997,13 @@
         <v>0</v>
       </c>
       <c r="M46" s="1" t="n">
-        <v>14800</v>
+        <v>10200</v>
       </c>
       <c r="N46" s="1" t="n">
         <v>41</v>
       </c>
       <c r="O46" s="1" t="n">
-        <v>70500000</v>
+        <v>218000000</v>
       </c>
       <c r="P46" s="1" t="inlineStr">
         <is>
@@ -3019,13 +3019,13 @@
         <v>9</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>850000</v>
+        <v>539000</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>2130</v>
+        <v>1350</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>14400</v>
+        <v>8170</v>
       </c>
       <c r="F47" s="1" t="n">
         <v>4.24</v>
@@ -3051,13 +3051,13 @@
         <v>0</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>17000</v>
+        <v>10800</v>
       </c>
       <c r="N47" s="1" t="n">
         <v>41</v>
       </c>
       <c r="O47" s="1" t="n">
-        <v>80900000</v>
+        <v>231000000</v>
       </c>
       <c r="P47" s="1" t="inlineStr">
         <is>
@@ -3073,13 +3073,13 @@
         <v>9</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>1120000</v>
+        <v>656000</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>2800</v>
+        <v>1640</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>20400</v>
+        <v>10400</v>
       </c>
       <c r="F48" s="1" t="n">
         <v>3.18</v>
@@ -3105,13 +3105,13 @@
         <v>36</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>22400</v>
+        <v>13100</v>
       </c>
       <c r="N48" s="1" t="n">
         <v>41</v>
       </c>
       <c r="O48" s="1" t="n">
-        <v>107000000</v>
+        <v>281000000</v>
       </c>
       <c r="P48" s="1" t="inlineStr">
         <is>
@@ -3127,49 +3127,49 @@
         <v>9</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>1120000</v>
+        <v>784000</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>2800</v>
+        <v>1960</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>20400</v>
+        <v>13000</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>4.24</v>
+        <v>7.41</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>1.41</v>
+        <v>2.47</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>14.82</v>
       </c>
       <c r="I49" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J49" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="K49" s="1" t="n">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="L49" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>22400</v>
+        <v>15700</v>
       </c>
       <c r="N49" s="1" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="O49" s="1" t="n">
-        <v>107000000</v>
+        <v>336000000</v>
       </c>
       <c r="P49" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
     </row>
@@ -3181,13 +3181,13 @@
         <v>9</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>1290000</v>
+        <v>759000</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>3210</v>
+        <v>1900</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>24200</v>
+        <v>12500</v>
       </c>
       <c r="F50" s="1" t="n">
         <v>4.24</v>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="J50" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="K50" s="1" t="n">
@@ -3213,17 +3213,17 @@
         <v>0</v>
       </c>
       <c r="M50" s="1" t="n">
-        <v>25700</v>
+        <v>15200</v>
       </c>
       <c r="N50" s="1" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="O50" s="1" t="n">
-        <v>122000000</v>
+        <v>325000000</v>
       </c>
       <c r="P50" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
     </row>
@@ -3235,13 +3235,13 @@
         <v>9</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>1470000</v>
+        <v>954000</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>3690</v>
+        <v>2390</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>28700</v>
+        <v>16700</v>
       </c>
       <c r="F51" s="1" t="n">
         <v>4.24</v>
@@ -3267,13 +3267,13 @@
         <v>0</v>
       </c>
       <c r="M51" s="1" t="n">
-        <v>29500</v>
+        <v>19100</v>
       </c>
       <c r="N51" s="1" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O51" s="1" t="n">
-        <v>140000000</v>
+        <v>409000000</v>
       </c>
       <c r="P51" s="1" t="inlineStr">
         <is>
@@ -3289,49 +3289,49 @@
         <v>9</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>1690000</v>
+        <v>1200000</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>4230</v>
+        <v>3000</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>34100</v>
+        <v>22200</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>5.29</v>
+        <v>4.24</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>2.65</v>
+        <v>2.12</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>10.59</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I52" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J52" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K52" s="1" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="L52" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M52" s="1" t="n">
-        <v>33900</v>
+        <v>24000</v>
       </c>
       <c r="N52" s="1" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O52" s="1" t="n">
-        <v>161000000</v>
+        <v>515000000</v>
       </c>
       <c r="P52" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -3343,49 +3343,49 @@
         <v>9</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>3110000</v>
+        <v>1740000</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>7770</v>
+        <v>4340</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>73000</v>
+        <v>35300</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>5.34</v>
+        <v>3.18</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>2.67</v>
+        <v>1.59</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>10.67</v>
+        <v>6.35</v>
       </c>
       <c r="I53" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J53" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="K53" s="1" t="n">
-        <v>151.2</v>
+        <v>90</v>
       </c>
       <c r="L53" s="1" t="n">
-        <v>60.5</v>
+        <v>36</v>
       </c>
       <c r="M53" s="1" t="n">
-        <v>62200</v>
+        <v>34700</v>
       </c>
       <c r="N53" s="1" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="O53" s="1" t="n">
-        <v>296000000</v>
+        <v>744000000</v>
       </c>
       <c r="P53" s="1" t="inlineStr">
         <is>
-          <t>보스 층 · 허들</t>
+          <t>보스 층 · 어려움</t>
         </is>
       </c>
     </row>
@@ -3397,13 +3397,13 @@
         <v>9</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>2100000</v>
+        <v>1900000</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>5260</v>
+        <v>4750</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>44800</v>
+        <v>39400</v>
       </c>
       <c r="F54" s="1" t="n">
         <v>4.24</v>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="J54" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K54" s="1" t="n">
@@ -3429,17 +3429,17 @@
         <v>0</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>42100</v>
+        <v>38000</v>
       </c>
       <c r="N54" s="1" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="O54" s="1" t="n">
-        <v>200000000</v>
+        <v>814000000</v>
       </c>
       <c r="P54" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -3451,49 +3451,49 @@
         <v>9</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>2280000</v>
+        <v>3110000</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>5700</v>
+        <v>7770</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>49500</v>
+        <v>73000</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>4.24</v>
+        <v>7.41</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>2.12</v>
+        <v>3.71</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>14.82</v>
       </c>
       <c r="I55" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J55" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="K55" s="1" t="n">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="L55" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M55" s="1" t="n">
-        <v>45600</v>
+        <v>62200</v>
       </c>
       <c r="N55" s="1" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O55" s="1" t="n">
-        <v>217000000</v>
+        <v>1330000000</v>
       </c>
       <c r="P55" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>허들</t>
         </is>
       </c>
     </row>
@@ -3505,13 +3505,13 @@
         <v>9</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>2470000</v>
+        <v>2730000</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>6170</v>
+        <v>6830</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>54700</v>
+        <v>62100</v>
       </c>
       <c r="F56" s="1" t="n">
         <v>4.24</v>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="J56" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="K56" s="1" t="n">
@@ -3537,17 +3537,17 @@
         <v>0</v>
       </c>
       <c r="M56" s="1" t="n">
-        <v>49400</v>
+        <v>54600</v>
       </c>
       <c r="N56" s="1" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O56" s="1" t="n">
-        <v>235000000</v>
+        <v>1170000000</v>
       </c>
       <c r="P56" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
     </row>
@@ -3559,13 +3559,13 @@
         <v>9</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>2670000</v>
+        <v>3120000</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>6690</v>
+        <v>7800</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>60500</v>
+        <v>73300</v>
       </c>
       <c r="F57" s="1" t="n">
         <v>4.24</v>
@@ -3591,13 +3591,13 @@
         <v>0</v>
       </c>
       <c r="M57" s="1" t="n">
-        <v>53500</v>
+        <v>62400</v>
       </c>
       <c r="N57" s="1" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O57" s="1" t="n">
-        <v>254000000</v>
+        <v>1340000000</v>
       </c>
       <c r="P57" s="1" t="inlineStr">
         <is>
@@ -3613,13 +3613,13 @@
         <v>9</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>3330000</v>
+        <v>4100000</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>8330</v>
+        <v>10300</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>79600</v>
+        <v>103000</v>
       </c>
       <c r="F58" s="1" t="n">
         <v>3.18</v>
@@ -3645,13 +3645,13 @@
         <v>36</v>
       </c>
       <c r="M58" s="1" t="n">
-        <v>66600</v>
+        <v>82000</v>
       </c>
       <c r="N58" s="1" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O58" s="1" t="n">
-        <v>317000000</v>
+        <v>1760000000</v>
       </c>
       <c r="P58" s="1" t="inlineStr">
         <is>
@@ -3667,13 +3667,13 @@
         <v>9</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>3140000</v>
+        <v>4070000</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>7840</v>
+        <v>10200</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>73800</v>
+        <v>102000</v>
       </c>
       <c r="F59" s="1" t="n">
         <v>4.24</v>
@@ -3699,13 +3699,13 @@
         <v>0</v>
       </c>
       <c r="M59" s="1" t="n">
-        <v>62800</v>
+        <v>81500</v>
       </c>
       <c r="N59" s="1" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O59" s="1" t="n">
-        <v>298000000</v>
+        <v>1750000000</v>
       </c>
       <c r="P59" s="1" t="inlineStr">
         <is>
@@ -3721,13 +3721,13 @@
         <v>9</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>3400000</v>
+        <v>4650000</v>
       </c>
       <c r="D60" s="1" t="n">
-        <v>8500</v>
+        <v>11600</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>81600</v>
+        <v>121000</v>
       </c>
       <c r="F60" s="1" t="n">
         <v>4.24</v>
@@ -3753,13 +3753,13 @@
         <v>0</v>
       </c>
       <c r="M60" s="1" t="n">
-        <v>68000</v>
+        <v>93100</v>
       </c>
       <c r="N60" s="1" t="n">
         <v>53</v>
       </c>
       <c r="O60" s="1" t="n">
-        <v>323000000</v>
+        <v>1990000000</v>
       </c>
       <c r="P60" s="1" t="inlineStr">
         <is>
@@ -3775,49 +3775,49 @@
         <v>9</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>3680000</v>
+        <v>6910000</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>9200</v>
+        <v>17300</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>90200</v>
+        <v>198000</v>
       </c>
       <c r="F61" s="1" t="n">
-        <v>4.24</v>
+        <v>7.41</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>2.12</v>
+        <v>3.71</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>14.82</v>
       </c>
       <c r="I61" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J61" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="K61" s="1" t="n">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="L61" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M61" s="1" t="n">
-        <v>73600</v>
+        <v>138000</v>
       </c>
       <c r="N61" s="1" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="O61" s="1" t="n">
-        <v>350000000</v>
+        <v>2960000000</v>
       </c>
       <c r="P61" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
     </row>
@@ -3829,49 +3829,49 @@
         <v>9</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>3990000</v>
+        <v>6240000</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>9970</v>
+        <v>15600</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>99600</v>
+        <v>174000</v>
       </c>
       <c r="F62" s="1" t="n">
-        <v>5.29</v>
+        <v>4.24</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>2.65</v>
+        <v>2.12</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>10.59</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I62" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J62" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="K62" s="1" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="L62" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M62" s="1" t="n">
-        <v>79800</v>
+        <v>125000</v>
       </c>
       <c r="N62" s="1" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="O62" s="1" t="n">
-        <v>379000000</v>
+        <v>2670000000</v>
       </c>
       <c r="P62" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>쉬움</t>
         </is>
       </c>
     </row>
@@ -3883,49 +3883,49 @@
         <v>9</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>6910000</v>
+        <v>8430000</v>
       </c>
       <c r="D63" s="1" t="n">
-        <v>17300</v>
+        <v>21100</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>198000</v>
+        <v>254000</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>5.41</v>
+        <v>3.18</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>1.8</v>
+        <v>1.06</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>10.82</v>
+        <v>6.35</v>
       </c>
       <c r="I63" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J63" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="K63" s="1" t="n">
-        <v>153.3</v>
+        <v>90</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>61.3</v>
+        <v>36</v>
       </c>
       <c r="M63" s="1" t="n">
-        <v>138000</v>
+        <v>169000</v>
       </c>
       <c r="N63" s="1" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="O63" s="1" t="n">
-        <v>658000000</v>
+        <v>3610000000</v>
       </c>
       <c r="P63" s="1" t="inlineStr">
         <is>
-          <t>보스 층 · 허들</t>
+          <t>보스 층 · 어려움</t>
         </is>
       </c>
     </row>
@@ -3937,13 +3937,13 @@
         <v>9</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>4760000</v>
+        <v>8600000</v>
       </c>
       <c r="D64" s="1" t="n">
-        <v>11900</v>
+        <v>21500</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>124000</v>
+        <v>260000</v>
       </c>
       <c r="F64" s="1" t="n">
         <v>4.24</v>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="J64" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K64" s="1" t="n">
@@ -3969,17 +3969,17 @@
         <v>0</v>
       </c>
       <c r="M64" s="1" t="n">
-        <v>95100</v>
+        <v>172000</v>
       </c>
       <c r="N64" s="1" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="O64" s="1" t="n">
-        <v>452000000</v>
+        <v>3690000000</v>
       </c>
       <c r="P64" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -3991,13 +3991,13 @@
         <v>9</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>5240000</v>
+        <v>10100000</v>
       </c>
       <c r="D65" s="1" t="n">
-        <v>13100</v>
+        <v>25200</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>140000</v>
+        <v>318000</v>
       </c>
       <c r="F65" s="1" t="n">
         <v>4.24</v>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="J65" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K65" s="1" t="n">
@@ -4023,17 +4023,17 @@
         <v>0</v>
       </c>
       <c r="M65" s="1" t="n">
-        <v>105000</v>
+        <v>202000</v>
       </c>
       <c r="N65" s="1" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="O65" s="1" t="n">
-        <v>498000000</v>
+        <v>4330000000</v>
       </c>
       <c r="P65" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -4045,13 +4045,13 @@
         <v>9</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>5770000</v>
+        <v>11900000</v>
       </c>
       <c r="D66" s="1" t="n">
-        <v>14400</v>
+        <v>29600</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>158000</v>
+        <v>389000</v>
       </c>
       <c r="F66" s="1" t="n">
         <v>4.24</v>
@@ -4077,13 +4077,13 @@
         <v>0</v>
       </c>
       <c r="M66" s="1" t="n">
-        <v>115000</v>
+        <v>237000</v>
       </c>
       <c r="N66" s="1" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="O66" s="1" t="n">
-        <v>549000000</v>
+        <v>5080000000</v>
       </c>
       <c r="P66" s="1" t="inlineStr">
         <is>
@@ -4099,49 +4099,49 @@
         <v>9</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>6350000</v>
+        <v>18100000</v>
       </c>
       <c r="D67" s="1" t="n">
-        <v>15900</v>
+        <v>45200</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>178000</v>
+        <v>660000</v>
       </c>
       <c r="F67" s="1" t="n">
-        <v>4.24</v>
+        <v>7.41</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>1.41</v>
+        <v>2.47</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>14.82</v>
       </c>
       <c r="I67" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J67" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="K67" s="1" t="n">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="L67" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M67" s="1" t="n">
-        <v>127000</v>
+        <v>362000</v>
       </c>
       <c r="N67" s="1" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="O67" s="1" t="n">
-        <v>604000000</v>
+        <v>7750000000</v>
       </c>
       <c r="P67" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
     </row>
@@ -4153,13 +4153,13 @@
         <v>9</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>8040000</v>
+        <v>17600000</v>
       </c>
       <c r="D68" s="1" t="n">
-        <v>20100</v>
+        <v>44100</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>239000</v>
+        <v>639000</v>
       </c>
       <c r="F68" s="1" t="n">
         <v>3.18</v>
@@ -4185,13 +4185,13 @@
         <v>36</v>
       </c>
       <c r="M68" s="1" t="n">
-        <v>161000</v>
+        <v>353000</v>
       </c>
       <c r="N68" s="1" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="O68" s="1" t="n">
-        <v>765000000</v>
+        <v>7560000000</v>
       </c>
       <c r="P68" s="1" t="inlineStr">
         <is>
@@ -4207,13 +4207,13 @@
         <v>9</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>7700000</v>
+        <v>16900000</v>
       </c>
       <c r="D69" s="1" t="n">
-        <v>19200</v>
+        <v>42300</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>227000</v>
+        <v>606000</v>
       </c>
       <c r="F69" s="1" t="n">
         <v>4.24</v>
@@ -4239,13 +4239,13 @@
         <v>0</v>
       </c>
       <c r="M69" s="1" t="n">
-        <v>154000</v>
+        <v>338000</v>
       </c>
       <c r="N69" s="1" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="O69" s="1" t="n">
-        <v>732000000</v>
+        <v>7250000000</v>
       </c>
       <c r="P69" s="1" t="inlineStr">
         <is>
@@ -4261,13 +4261,13 @@
         <v>9</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>8470000</v>
+        <v>18600000</v>
       </c>
       <c r="D70" s="1" t="n">
-        <v>21200</v>
+        <v>46600</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>256000</v>
+        <v>685000</v>
       </c>
       <c r="F70" s="1" t="n">
         <v>4.24</v>
@@ -4293,13 +4293,13 @@
         <v>0</v>
       </c>
       <c r="M70" s="1" t="n">
-        <v>169000</v>
+        <v>373000</v>
       </c>
       <c r="N70" s="1" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="O70" s="1" t="n">
-        <v>806000000</v>
+        <v>7990000000</v>
       </c>
       <c r="P70" s="1" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>9</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>9330000</v>
+        <v>20500000</v>
       </c>
       <c r="D71" s="1" t="n">
-        <v>23300</v>
+        <v>51400</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>288000</v>
+        <v>773000</v>
       </c>
       <c r="F71" s="1" t="n">
         <v>4.24</v>
@@ -4347,13 +4347,13 @@
         <v>0</v>
       </c>
       <c r="M71" s="1" t="n">
-        <v>187000</v>
+        <v>411000</v>
       </c>
       <c r="N71" s="1" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O71" s="1" t="n">
-        <v>888000000</v>
+        <v>8800000000</v>
       </c>
       <c r="P71" s="1" t="inlineStr">
         <is>
@@ -4369,49 +4369,49 @@
         <v>9</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>10300000</v>
+        <v>22600000</v>
       </c>
       <c r="D72" s="1" t="n">
-        <v>25700</v>
+        <v>56600</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>325000</v>
+        <v>873000</v>
       </c>
       <c r="F72" s="1" t="n">
-        <v>5.29</v>
+        <v>4.24</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>2.65</v>
+        <v>2.12</v>
       </c>
       <c r="H72" s="1" t="n">
-        <v>10.59</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I72" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J72" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K72" s="1" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="L72" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M72" s="1" t="n">
-        <v>205000</v>
+        <v>453000</v>
       </c>
       <c r="N72" s="1" t="n">
         <v>65</v>
       </c>
       <c r="O72" s="1" t="n">
-        <v>977000000</v>
+        <v>9700000000</v>
       </c>
       <c r="P72" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -4423,22 +4423,22 @@
         <v>9</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>18100000</v>
+        <v>32400000</v>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45200</v>
+        <v>81100</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>660000</v>
+        <v>1370000</v>
       </c>
       <c r="F73" s="1" t="n">
-        <v>5.48</v>
+        <v>5.56</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="H73" s="1" t="n">
-        <v>10.97</v>
+        <v>11.12</v>
       </c>
       <c r="I73" s="1" t="n">
         <v>0</v>
@@ -4449,19 +4449,19 @@
         </is>
       </c>
       <c r="K73" s="1" t="n">
-        <v>155.4</v>
+        <v>157.5</v>
       </c>
       <c r="L73" s="1" t="n">
-        <v>62.2</v>
+        <v>63</v>
       </c>
       <c r="M73" s="1" t="n">
-        <v>362000</v>
+        <v>649000</v>
       </c>
       <c r="N73" s="1" t="n">
         <v>71</v>
       </c>
       <c r="O73" s="1" t="n">
-        <v>1720000000</v>
+        <v>13900000000</v>
       </c>
       <c r="P73" s="1" t="inlineStr">
         <is>
@@ -4477,13 +4477,13 @@
         <v>9</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>12000000</v>
+        <v>26500000</v>
       </c>
       <c r="D74" s="1" t="n">
-        <v>30000</v>
+        <v>66200</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>394000</v>
+        <v>1060000</v>
       </c>
       <c r="F74" s="1" t="n">
         <v>4.24</v>
@@ -4509,13 +4509,13 @@
         <v>0</v>
       </c>
       <c r="M74" s="1" t="n">
-        <v>240000</v>
+        <v>529000</v>
       </c>
       <c r="N74" s="1" t="n">
         <v>71</v>
       </c>
       <c r="O74" s="1" t="n">
-        <v>1140000000</v>
+        <v>11300000000</v>
       </c>
       <c r="P74" s="1" t="inlineStr">
         <is>
@@ -4531,13 +4531,13 @@
         <v>9</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>12700000</v>
+        <v>28100000</v>
       </c>
       <c r="D75" s="1" t="n">
-        <v>31800</v>
+        <v>70100</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>424000</v>
+        <v>1140000</v>
       </c>
       <c r="F75" s="1" t="n">
         <v>4.24</v>
@@ -4553,7 +4553,7 @@
       </c>
       <c r="J75" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K75" s="1" t="n">
@@ -4563,17 +4563,17 @@
         <v>0</v>
       </c>
       <c r="M75" s="1" t="n">
-        <v>254000</v>
+        <v>561000</v>
       </c>
       <c r="N75" s="1" t="n">
         <v>71</v>
       </c>
       <c r="O75" s="1" t="n">
-        <v>1210000000</v>
+        <v>12000000000</v>
       </c>
       <c r="P75" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -4585,13 +4585,13 @@
         <v>9</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>13500000</v>
+        <v>29700000</v>
       </c>
       <c r="D76" s="1" t="n">
-        <v>33700</v>
+        <v>74300</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>456000</v>
+        <v>1230000</v>
       </c>
       <c r="F76" s="1" t="n">
         <v>4.24</v>
@@ -4617,13 +4617,13 @@
         <v>0</v>
       </c>
       <c r="M76" s="1" t="n">
-        <v>270000</v>
+        <v>595000</v>
       </c>
       <c r="N76" s="1" t="n">
         <v>71</v>
       </c>
       <c r="O76" s="1" t="n">
-        <v>1280000000</v>
+        <v>12700000000</v>
       </c>
       <c r="P76" s="1" t="inlineStr">
         <is>
@@ -4639,13 +4639,13 @@
         <v>9</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>14300000</v>
+        <v>31500000</v>
       </c>
       <c r="D77" s="1" t="n">
-        <v>35700</v>
+        <v>78800</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>491000</v>
+        <v>1320000</v>
       </c>
       <c r="F77" s="1" t="n">
         <v>4.24</v>
@@ -4671,13 +4671,13 @@
         <v>0</v>
       </c>
       <c r="M77" s="1" t="n">
-        <v>286000</v>
+        <v>631000</v>
       </c>
       <c r="N77" s="1" t="n">
         <v>71</v>
       </c>
       <c r="O77" s="1" t="n">
-        <v>1360000000</v>
+        <v>13500000000</v>
       </c>
       <c r="P77" s="1" t="inlineStr">
         <is>
@@ -4693,13 +4693,13 @@
         <v>9</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>17400000</v>
+        <v>38400000</v>
       </c>
       <c r="D78" s="1" t="n">
-        <v>43500</v>
+        <v>96100</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>629000</v>
+        <v>1690000</v>
       </c>
       <c r="F78" s="1" t="n">
         <v>3.18</v>
@@ -4725,13 +4725,13 @@
         <v>36</v>
       </c>
       <c r="M78" s="1" t="n">
-        <v>348000</v>
+        <v>769000</v>
       </c>
       <c r="N78" s="1" t="n">
         <v>71</v>
       </c>
       <c r="O78" s="1" t="n">
-        <v>1660000000</v>
+        <v>16500000000</v>
       </c>
       <c r="P78" s="1" t="inlineStr">
         <is>
@@ -4747,13 +4747,13 @@
         <v>9</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>16100000</v>
+        <v>35400000</v>
       </c>
       <c r="D79" s="1" t="n">
-        <v>40100</v>
+        <v>88600</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>568000</v>
+        <v>1530000</v>
       </c>
       <c r="F79" s="1" t="n">
         <v>4.24</v>
@@ -4779,13 +4779,13 @@
         <v>0</v>
       </c>
       <c r="M79" s="1" t="n">
-        <v>321000</v>
+        <v>709000</v>
       </c>
       <c r="N79" s="1" t="n">
         <v>72</v>
       </c>
       <c r="O79" s="1" t="n">
-        <v>1530000000</v>
+        <v>15200000000</v>
       </c>
       <c r="P79" s="1" t="inlineStr">
         <is>
@@ -4801,49 +4801,49 @@
         <v>9</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>17000000</v>
+        <v>48800000</v>
       </c>
       <c r="D80" s="1" t="n">
-        <v>42600</v>
+        <v>122000</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>611000</v>
+        <v>2280000</v>
       </c>
       <c r="F80" s="1" t="n">
-        <v>4.24</v>
+        <v>7.41</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>1.41</v>
+        <v>2.47</v>
       </c>
       <c r="H80" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>14.82</v>
       </c>
       <c r="I80" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J80" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="K80" s="1" t="n">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="L80" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M80" s="1" t="n">
-        <v>340000</v>
+        <v>977000</v>
       </c>
       <c r="N80" s="1" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="O80" s="1" t="n">
-        <v>1620000000</v>
+        <v>20900000000</v>
       </c>
       <c r="P80" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
     </row>
@@ -4855,13 +4855,13 @@
         <v>9</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>18000000</v>
+        <v>39700000</v>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45100</v>
+        <v>99100</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>657000</v>
+        <v>1760000</v>
       </c>
       <c r="F81" s="1" t="n">
         <v>4.24</v>
@@ -4877,7 +4877,7 @@
       </c>
       <c r="J81" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="K81" s="1" t="n">
@@ -4887,17 +4887,17 @@
         <v>0</v>
       </c>
       <c r="M81" s="1" t="n">
-        <v>361000</v>
+        <v>793000</v>
       </c>
       <c r="N81" s="1" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="O81" s="1" t="n">
-        <v>1720000000</v>
+        <v>17000000000</v>
       </c>
       <c r="P81" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
     </row>
@@ -4909,49 +4909,49 @@
         <v>9</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>19100000</v>
+        <v>41900000</v>
       </c>
       <c r="D82" s="1" t="n">
-        <v>47800</v>
+        <v>105000</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>707000</v>
+        <v>1880000</v>
       </c>
       <c r="F82" s="1" t="n">
-        <v>5.29</v>
+        <v>4.24</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>1.76</v>
+        <v>1.41</v>
       </c>
       <c r="H82" s="1" t="n">
-        <v>10.59</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I82" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J82" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K82" s="1" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="L82" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M82" s="1" t="n">
-        <v>383000</v>
+        <v>838000</v>
       </c>
       <c r="N82" s="1" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="O82" s="1" t="n">
-        <v>1820000000</v>
+        <v>17900000000</v>
       </c>
       <c r="P82" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -4963,49 +4963,49 @@
         <v>9</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>32400000</v>
+        <v>50800000</v>
       </c>
       <c r="D83" s="1" t="n">
-        <v>81100</v>
+        <v>127000</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>1370000</v>
+        <v>2400000</v>
       </c>
       <c r="F83" s="1" t="n">
-        <v>5.56</v>
+        <v>3.18</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>2.78</v>
+        <v>1.59</v>
       </c>
       <c r="H83" s="1" t="n">
-        <v>11.12</v>
+        <v>6.35</v>
       </c>
       <c r="I83" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J83" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="K83" s="1" t="n">
-        <v>157.5</v>
+        <v>90</v>
       </c>
       <c r="L83" s="1" t="n">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="M83" s="1" t="n">
-        <v>649000</v>
+        <v>1020000</v>
       </c>
       <c r="N83" s="1" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="O83" s="1" t="n">
-        <v>3090000000</v>
+        <v>21800000000</v>
       </c>
       <c r="P83" s="1" t="inlineStr">
         <is>
-          <t>보스 층 · 허들</t>
+          <t>보스 층 · 어려움</t>
         </is>
       </c>
     </row>
@@ -5017,13 +5017,13 @@
         <v>9</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>21100000</v>
+        <v>46700000</v>
       </c>
       <c r="D84" s="1" t="n">
-        <v>52800</v>
+        <v>117000</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>801000</v>
+        <v>2160000</v>
       </c>
       <c r="F84" s="1" t="n">
         <v>4.24</v>
@@ -5039,7 +5039,7 @@
       </c>
       <c r="J84" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K84" s="1" t="n">
@@ -5049,17 +5049,17 @@
         <v>0</v>
       </c>
       <c r="M84" s="1" t="n">
-        <v>423000</v>
+        <v>934000</v>
       </c>
       <c r="N84" s="1" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="O84" s="1" t="n">
-        <v>2010000000</v>
+        <v>20000000000</v>
       </c>
       <c r="P84" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -5071,13 +5071,13 @@
         <v>9</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>22000000</v>
+        <v>49300000</v>
       </c>
       <c r="D85" s="1" t="n">
-        <v>55000</v>
+        <v>123000</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>843000</v>
+        <v>2310000</v>
       </c>
       <c r="F85" s="1" t="n">
         <v>4.24</v>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="J85" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K85" s="1" t="n">
@@ -5103,17 +5103,17 @@
         <v>0</v>
       </c>
       <c r="M85" s="1" t="n">
-        <v>440000</v>
+        <v>986000</v>
       </c>
       <c r="N85" s="1" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="O85" s="1" t="n">
-        <v>2090000000</v>
+        <v>21100000000</v>
       </c>
       <c r="P85" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -5125,13 +5125,13 @@
         <v>9</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>22900000</v>
+        <v>52100000</v>
       </c>
       <c r="D86" s="1" t="n">
-        <v>57300</v>
+        <v>130000</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>887000</v>
+        <v>2470000</v>
       </c>
       <c r="F86" s="1" t="n">
         <v>4.24</v>
@@ -5157,13 +5157,13 @@
         <v>0</v>
       </c>
       <c r="M86" s="1" t="n">
-        <v>459000</v>
+        <v>1040000</v>
       </c>
       <c r="N86" s="1" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="O86" s="1" t="n">
-        <v>2180000000</v>
+        <v>22300000000</v>
       </c>
       <c r="P86" s="1" t="inlineStr">
         <is>
@@ -5179,49 +5179,49 @@
         <v>9</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>23900000</v>
+        <v>71400000</v>
       </c>
       <c r="D87" s="1" t="n">
-        <v>59700</v>
+        <v>179000</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>933000</v>
+        <v>3670000</v>
       </c>
       <c r="F87" s="1" t="n">
-        <v>4.24</v>
+        <v>7.41</v>
       </c>
       <c r="G87" s="1" t="n">
-        <v>1.41</v>
+        <v>2.47</v>
       </c>
       <c r="H87" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>14.82</v>
       </c>
       <c r="I87" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J87" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="K87" s="1" t="n">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="L87" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M87" s="1" t="n">
-        <v>478000</v>
+        <v>1430000</v>
       </c>
       <c r="N87" s="1" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="O87" s="1" t="n">
-        <v>2270000000</v>
+        <v>30600000000</v>
       </c>
       <c r="P87" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
     </row>
@@ -5233,13 +5233,13 @@
         <v>9</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>28600000</v>
+        <v>66300000</v>
       </c>
       <c r="D88" s="1" t="n">
-        <v>71500</v>
+        <v>166000</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>1170000</v>
+        <v>3350000</v>
       </c>
       <c r="F88" s="1" t="n">
         <v>3.18</v>
@@ -5265,13 +5265,13 @@
         <v>36</v>
       </c>
       <c r="M88" s="1" t="n">
-        <v>572000</v>
+        <v>1330000</v>
       </c>
       <c r="N88" s="1" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="O88" s="1" t="n">
-        <v>2720000000</v>
+        <v>28400000000</v>
       </c>
       <c r="P88" s="1" t="inlineStr">
         <is>
@@ -5287,13 +5287,13 @@
         <v>9</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>25900000</v>
+        <v>60500000</v>
       </c>
       <c r="D89" s="1" t="n">
-        <v>64800</v>
+        <v>151000</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>1030000</v>
+        <v>2980000</v>
       </c>
       <c r="F89" s="1" t="n">
         <v>4.24</v>
@@ -5319,13 +5319,13 @@
         <v>0</v>
       </c>
       <c r="M89" s="1" t="n">
-        <v>518000</v>
+        <v>1210000</v>
       </c>
       <c r="N89" s="1" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="O89" s="1" t="n">
-        <v>2470000000</v>
+        <v>25900000000</v>
       </c>
       <c r="P89" s="1" t="inlineStr">
         <is>
@@ -5341,13 +5341,13 @@
         <v>9</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>27000000</v>
+        <v>63500000</v>
       </c>
       <c r="D90" s="1" t="n">
-        <v>67500</v>
+        <v>159000</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>1090000</v>
+        <v>3170000</v>
       </c>
       <c r="F90" s="1" t="n">
         <v>4.24</v>
@@ -5373,13 +5373,13 @@
         <v>0</v>
       </c>
       <c r="M90" s="1" t="n">
-        <v>540000</v>
+        <v>1270000</v>
       </c>
       <c r="N90" s="1" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="O90" s="1" t="n">
-        <v>2570000000</v>
+        <v>27200000000</v>
       </c>
       <c r="P90" s="1" t="inlineStr">
         <is>
@@ -5395,13 +5395,13 @@
         <v>9</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>28100000</v>
+        <v>66600000</v>
       </c>
       <c r="D91" s="1" t="n">
-        <v>70300</v>
+        <v>167000</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>1140000</v>
+        <v>3360000</v>
       </c>
       <c r="F91" s="1" t="n">
         <v>4.24</v>
@@ -5427,13 +5427,13 @@
         <v>0</v>
       </c>
       <c r="M91" s="1" t="n">
-        <v>562000</v>
+        <v>1330000</v>
       </c>
       <c r="N91" s="1" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O91" s="1" t="n">
-        <v>2680000000</v>
+        <v>28500000000</v>
       </c>
       <c r="P91" s="1" t="inlineStr">
         <is>
@@ -5449,49 +5449,49 @@
         <v>9</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>29300000</v>
+        <v>69900000</v>
       </c>
       <c r="D92" s="1" t="n">
-        <v>73200</v>
+        <v>175000</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>1200000</v>
+        <v>3570000</v>
       </c>
       <c r="F92" s="1" t="n">
-        <v>5.29</v>
+        <v>4.24</v>
       </c>
       <c r="G92" s="1" t="n">
-        <v>1.76</v>
+        <v>1.41</v>
       </c>
       <c r="H92" s="1" t="n">
-        <v>10.59</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I92" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J92" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K92" s="1" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="L92" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M92" s="1" t="n">
-        <v>586000</v>
+        <v>1400000</v>
       </c>
       <c r="N92" s="1" t="n">
         <v>85</v>
       </c>
       <c r="O92" s="1" t="n">
-        <v>2790000000</v>
+        <v>30000000000</v>
       </c>
       <c r="P92" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -5503,49 +5503,49 @@
         <v>9</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>48800000</v>
+        <v>84300000</v>
       </c>
       <c r="D93" s="1" t="n">
-        <v>122000</v>
+        <v>211000</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>2280000</v>
+        <v>4520000</v>
       </c>
       <c r="F93" s="1" t="n">
-        <v>5.63</v>
+        <v>3.18</v>
       </c>
       <c r="G93" s="1" t="n">
-        <v>1.88</v>
+        <v>1.06</v>
       </c>
       <c r="H93" s="1" t="n">
-        <v>11.27</v>
+        <v>6.35</v>
       </c>
       <c r="I93" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J93" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="K93" s="1" t="n">
-        <v>159.6</v>
+        <v>90</v>
       </c>
       <c r="L93" s="1" t="n">
-        <v>63.8</v>
+        <v>36</v>
       </c>
       <c r="M93" s="1" t="n">
-        <v>977000</v>
+        <v>1690000</v>
       </c>
       <c r="N93" s="1" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="O93" s="1" t="n">
-        <v>4650000000</v>
+        <v>36100000000</v>
       </c>
       <c r="P93" s="1" t="inlineStr">
         <is>
-          <t>보스 층 · 허들</t>
+          <t>보스 층 · 어려움</t>
         </is>
       </c>
     </row>
@@ -5557,13 +5557,13 @@
         <v>9</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>31700000</v>
+        <v>76900000</v>
       </c>
       <c r="D94" s="1" t="n">
-        <v>79300</v>
+        <v>192000</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>1330000</v>
+        <v>4030000</v>
       </c>
       <c r="F94" s="1" t="n">
         <v>4.24</v>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="J94" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K94" s="1" t="n">
@@ -5589,17 +5589,17 @@
         <v>0</v>
       </c>
       <c r="M94" s="1" t="n">
-        <v>634000</v>
+        <v>1540000</v>
       </c>
       <c r="N94" s="1" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="O94" s="1" t="n">
-        <v>3020000000</v>
+        <v>33000000000</v>
       </c>
       <c r="P94" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -5611,49 +5611,49 @@
         <v>9</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>32900000</v>
+        <v>105000000</v>
       </c>
       <c r="D95" s="1" t="n">
-        <v>82300</v>
+        <v>262000</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>1390000</v>
+        <v>5940000</v>
       </c>
       <c r="F95" s="1" t="n">
-        <v>4.24</v>
+        <v>7.41</v>
       </c>
       <c r="G95" s="1" t="n">
-        <v>1.41</v>
+        <v>2.47</v>
       </c>
       <c r="H95" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>14.82</v>
       </c>
       <c r="I95" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J95" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="K95" s="1" t="n">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="L95" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M95" s="1" t="n">
-        <v>659000</v>
+        <v>2100000</v>
       </c>
       <c r="N95" s="1" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="O95" s="1" t="n">
-        <v>3130000000</v>
+        <v>45000000000</v>
       </c>
       <c r="P95" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>허들</t>
         </is>
       </c>
     </row>
@@ -5665,13 +5665,13 @@
         <v>9</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>34200000</v>
+        <v>83200000</v>
       </c>
       <c r="D96" s="1" t="n">
-        <v>85500</v>
+        <v>208000</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>1460000</v>
+        <v>4440000</v>
       </c>
       <c r="F96" s="1" t="n">
         <v>4.24</v>
@@ -5687,7 +5687,7 @@
       </c>
       <c r="J96" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="K96" s="1" t="n">
@@ -5697,17 +5697,17 @@
         <v>0</v>
       </c>
       <c r="M96" s="1" t="n">
-        <v>684000</v>
+        <v>1660000</v>
       </c>
       <c r="N96" s="1" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="O96" s="1" t="n">
-        <v>3250000000</v>
+        <v>35600000000</v>
       </c>
       <c r="P96" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
     </row>
@@ -5719,13 +5719,13 @@
         <v>9</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>40900000</v>
+        <v>98500000</v>
       </c>
       <c r="D97" s="1" t="n">
-        <v>102000</v>
+        <v>246000</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>1830000</v>
+        <v>5490000</v>
       </c>
       <c r="F97" s="1" t="n">
         <v>3.18</v>
@@ -5751,13 +5751,13 @@
         <v>36</v>
       </c>
       <c r="M97" s="1" t="n">
-        <v>817000</v>
+        <v>1970000</v>
       </c>
       <c r="N97" s="1" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="O97" s="1" t="n">
-        <v>3890000000</v>
+        <v>42200000000</v>
       </c>
       <c r="P97" s="1" t="inlineStr">
         <is>
@@ -5773,13 +5773,13 @@
         <v>9</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>36900000</v>
+        <v>88200000</v>
       </c>
       <c r="D98" s="1" t="n">
-        <v>92300</v>
+        <v>221000</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>1610000</v>
+        <v>4780000</v>
       </c>
       <c r="F98" s="1" t="n">
         <v>4.24</v>
@@ -5805,13 +5805,13 @@
         <v>0</v>
       </c>
       <c r="M98" s="1" t="n">
-        <v>738000</v>
+        <v>1760000</v>
       </c>
       <c r="N98" s="1" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="O98" s="1" t="n">
-        <v>3510000000</v>
+        <v>37800000000</v>
       </c>
       <c r="P98" s="1" t="inlineStr">
         <is>
@@ -5827,13 +5827,13 @@
         <v>9</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>38300000</v>
+        <v>90900000</v>
       </c>
       <c r="D99" s="1" t="n">
-        <v>95900</v>
+        <v>227000</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>1690000</v>
+        <v>4960000</v>
       </c>
       <c r="F99" s="1" t="n">
         <v>4.24</v>
@@ -5859,13 +5859,13 @@
         <v>0</v>
       </c>
       <c r="M99" s="1" t="n">
-        <v>767000</v>
+        <v>1820000</v>
       </c>
       <c r="N99" s="1" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O99" s="1" t="n">
-        <v>3650000000</v>
+        <v>38900000000</v>
       </c>
       <c r="P99" s="1" t="inlineStr">
         <is>
@@ -5881,13 +5881,13 @@
         <v>9</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45800000</v>
+        <v>108000000</v>
       </c>
       <c r="D100" s="1" t="n">
-        <v>115000</v>
+        <v>269000</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>2110000</v>
+        <v>6130000</v>
       </c>
       <c r="F100" s="1" t="n">
         <v>3.18</v>
@@ -5913,13 +5913,13 @@
         <v>36</v>
       </c>
       <c r="M100" s="1" t="n">
-        <v>916000</v>
+        <v>2150000</v>
       </c>
       <c r="N100" s="1" t="n">
         <v>93</v>
       </c>
       <c r="O100" s="1" t="n">
-        <v>4360000000</v>
+        <v>46100000000</v>
       </c>
       <c r="P100" s="1" t="inlineStr">
         <is>
@@ -5935,13 +5935,13 @@
         <v>9</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>41400000</v>
+        <v>96400000</v>
       </c>
       <c r="D101" s="1" t="n">
-        <v>103000</v>
+        <v>241000</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>1860000</v>
+        <v>5340000</v>
       </c>
       <c r="F101" s="1" t="n">
         <v>4.24</v>
@@ -5967,13 +5967,13 @@
         <v>0</v>
       </c>
       <c r="M101" s="1" t="n">
-        <v>828000</v>
+        <v>1930000</v>
       </c>
       <c r="N101" s="1" t="n">
         <v>94</v>
       </c>
       <c r="O101" s="1" t="n">
-        <v>3940000000</v>
+        <v>41300000000</v>
       </c>
       <c r="P101" s="1" t="inlineStr">
         <is>
@@ -5989,49 +5989,49 @@
         <v>9</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>43000000</v>
+        <v>99300000</v>
       </c>
       <c r="D102" s="1" t="n">
-        <v>107000</v>
+        <v>248000</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>1950000</v>
+        <v>5540000</v>
       </c>
       <c r="F102" s="1" t="n">
-        <v>5.29</v>
+        <v>4.24</v>
       </c>
       <c r="G102" s="1" t="n">
-        <v>1.76</v>
+        <v>1.41</v>
       </c>
       <c r="H102" s="1" t="n">
-        <v>10.59</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I102" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J102" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K102" s="1" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="L102" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M102" s="1" t="n">
-        <v>860000</v>
+        <v>1990000</v>
       </c>
       <c r="N102" s="1" t="n">
         <v>95</v>
       </c>
       <c r="O102" s="1" t="n">
-        <v>4090000000</v>
+        <v>42600000000</v>
       </c>
       <c r="P102" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -6043,49 +6043,49 @@
         <v>9</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>71400000</v>
+        <v>143000000</v>
       </c>
       <c r="D103" s="1" t="n">
-        <v>179000</v>
+        <v>358000</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>3670000</v>
+        <v>8760000</v>
       </c>
       <c r="F103" s="1" t="n">
-        <v>5.71</v>
+        <v>3.18</v>
       </c>
       <c r="G103" s="1" t="n">
-        <v>1.9</v>
+        <v>1.06</v>
       </c>
       <c r="H103" s="1" t="n">
-        <v>11.41</v>
+        <v>6.35</v>
       </c>
       <c r="I103" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J103" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="K103" s="1" t="n">
-        <v>161.7</v>
+        <v>90</v>
       </c>
       <c r="L103" s="1" t="n">
-        <v>64.7</v>
+        <v>36</v>
       </c>
       <c r="M103" s="1" t="n">
-        <v>1430000</v>
+        <v>2860000</v>
       </c>
       <c r="N103" s="1" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="O103" s="1" t="n">
-        <v>6800000000</v>
+        <v>61400000000</v>
       </c>
       <c r="P103" s="1" t="inlineStr">
         <is>
-          <t>보스 층 · 허들</t>
+          <t>보스 층 · 어려움</t>
         </is>
       </c>
     </row>

--- a/Data_Table/스테이지 테이블.xlsx
+++ b/Data_Table/스테이지 테이블.xlsx
@@ -948,7 +948,7 @@
         <v>30</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O8" s="1" t="n">
         <v>273</v>
@@ -1002,7 +1002,7 @@
         <v>27.21</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O9" s="1" t="n">
         <v>402</v>
@@ -1056,7 +1056,7 @@
         <v>32.09</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O10" s="1" t="n">
         <v>601</v>
@@ -1110,7 +1110,7 @@
         <v>37.84</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O11" s="1" t="n">
         <v>836</v>
@@ -1164,7 +1164,7 @@
         <v>58</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O12" s="1" t="n">
         <v>1120</v>
@@ -1218,7 +1218,7 @@
         <v>60.21</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O13" s="1" t="n">
         <v>1500</v>
@@ -1272,7 +1272,7 @@
         <v>61.44</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O14" s="1" t="n">
         <v>2010</v>
@@ -1326,7 +1326,7 @@
         <v>72.09999999999999</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O15" s="1" t="n">
         <v>2690</v>
@@ -1380,7 +1380,7 @@
         <v>110</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="O16" s="1" t="n">
         <v>3610</v>
@@ -1434,7 +1434,7 @@
         <v>97.02</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="O17" s="1" t="n">
         <v>4840</v>
@@ -1488,7 +1488,7 @@
         <v>128</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O18" s="1" t="n">
         <v>6480</v>
@@ -1542,7 +1542,7 @@
         <v>128</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O19" s="1" t="n">
         <v>9340</v>
@@ -1596,7 +1596,7 @@
         <v>146</v>
       </c>
       <c r="N20" s="1" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O20" s="1" t="n">
         <v>14900</v>
@@ -1650,7 +1650,7 @@
         <v>218</v>
       </c>
       <c r="N21" s="1" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="O21" s="1" t="n">
         <v>24900</v>
@@ -1704,7 +1704,7 @@
         <v>200</v>
       </c>
       <c r="N22" s="1" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="O22" s="1" t="n">
         <v>43700</v>
@@ -1758,7 +1758,7 @@
         <v>274</v>
       </c>
       <c r="N23" s="1" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="O23" s="1" t="n">
         <v>81000</v>
@@ -1812,7 +1812,7 @@
         <v>284</v>
       </c>
       <c r="N24" s="1" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="O24" s="1" t="n">
         <v>150000</v>
@@ -1866,7 +1866,7 @@
         <v>338</v>
       </c>
       <c r="N25" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O25" s="1" t="n">
         <v>277000</v>
@@ -1920,7 +1920,7 @@
         <v>524</v>
       </c>
       <c r="N26" s="1" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="O26" s="1" t="n">
         <v>513000</v>
@@ -1974,7 +1974,7 @@
         <v>472</v>
       </c>
       <c r="N27" s="1" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="O27" s="1" t="n">
         <v>949000</v>
@@ -2028,7 +2028,7 @@
         <v>636</v>
       </c>
       <c r="N28" s="1" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="O28" s="1" t="n">
         <v>1760000</v>
@@ -2082,7 +2082,7 @@
         <v>647</v>
       </c>
       <c r="N29" s="1" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="O29" s="1" t="n">
         <v>3250000</v>
@@ -2136,7 +2136,7 @@
         <v>758</v>
       </c>
       <c r="N30" s="1" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="O30" s="1" t="n">
         <v>6010000</v>
@@ -2190,7 +2190,7 @@
         <v>1150</v>
       </c>
       <c r="N31" s="1" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="O31" s="1" t="n">
         <v>11100000</v>
@@ -2209,13 +2209,13 @@
         <v>9</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>58500</v>
+        <v>56700</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>509</v>
+        <v>489</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>4.24</v>
@@ -2241,10 +2241,10 @@
         <v>0</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>1170</v>
+        <v>1130</v>
       </c>
       <c r="N32" s="1" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="O32" s="1" t="n">
         <v>20600000</v>
@@ -2263,13 +2263,13 @@
         <v>9</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>88800</v>
+        <v>83400</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>857</v>
+        <v>792</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>3.18</v>
@@ -2295,7 +2295,7 @@
         <v>36</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>1780</v>
+        <v>1670</v>
       </c>
       <c r="N33" s="1" t="n">
         <v>29</v>
@@ -2317,13 +2317,13 @@
         <v>9</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>102000</v>
+        <v>92700</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>255</v>
+        <v>232</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>1020</v>
+        <v>904</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>4.24</v>
@@ -2349,13 +2349,13 @@
         <v>0</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>2040</v>
+        <v>1850</v>
       </c>
       <c r="N34" s="1" t="n">
         <v>29</v>
       </c>
       <c r="O34" s="1" t="n">
-        <v>43600000</v>
+        <v>42300000</v>
       </c>
       <c r="P34" s="1" t="inlineStr">
         <is>
@@ -2371,13 +2371,13 @@
         <v>9</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>134000</v>
+        <v>119000</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>336</v>
+        <v>296</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>1440</v>
+        <v>1230</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>4.24</v>
@@ -2403,13 +2403,13 @@
         <v>0</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>2690</v>
+        <v>2370</v>
       </c>
       <c r="N35" s="1" t="n">
         <v>29</v>
       </c>
       <c r="O35" s="1" t="n">
-        <v>57600000</v>
+        <v>54100000</v>
       </c>
       <c r="P35" s="1" t="inlineStr">
         <is>
@@ -2425,13 +2425,13 @@
         <v>9</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>177000</v>
+        <v>151000</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>443</v>
+        <v>379</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>2030</v>
+        <v>1670</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>4.24</v>
@@ -2457,13 +2457,13 @@
         <v>0</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>3540</v>
+        <v>3030</v>
       </c>
       <c r="N36" s="1" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O36" s="1" t="n">
-        <v>75900000</v>
+        <v>69100000</v>
       </c>
       <c r="P36" s="1" t="inlineStr">
         <is>
@@ -2479,13 +2479,13 @@
         <v>9</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>304000</v>
+        <v>252000</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>760</v>
+        <v>629</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>3990</v>
+        <v>3150</v>
       </c>
       <c r="F37" s="1" t="n">
         <v>6.92</v>
@@ -2511,13 +2511,13 @@
         <v>0</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>6080</v>
+        <v>5030</v>
       </c>
       <c r="N37" s="1" t="n">
         <v>35</v>
       </c>
       <c r="O37" s="1" t="n">
-        <v>130000000</v>
+        <v>115000000</v>
       </c>
       <c r="P37" s="1" t="inlineStr">
         <is>
@@ -2533,13 +2533,13 @@
         <v>9</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>298000</v>
+        <v>247000</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>744</v>
+        <v>616</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>3890</v>
+        <v>3070</v>
       </c>
       <c r="F38" s="1" t="n">
         <v>3.18</v>
@@ -2565,13 +2565,13 @@
         <v>36</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>5950</v>
+        <v>4930</v>
       </c>
       <c r="N38" s="1" t="n">
         <v>35</v>
       </c>
       <c r="O38" s="1" t="n">
-        <v>128000000</v>
+        <v>112000000</v>
       </c>
       <c r="P38" s="1" t="inlineStr">
         <is>
@@ -2587,13 +2587,13 @@
         <v>9</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>287000</v>
+        <v>237000</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>716</v>
+        <v>594</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>3710</v>
+        <v>2930</v>
       </c>
       <c r="F39" s="1" t="n">
         <v>4.24</v>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>5730</v>
+        <v>4750</v>
       </c>
       <c r="N39" s="1" t="n">
         <v>35</v>
       </c>
       <c r="O39" s="1" t="n">
-        <v>123000000</v>
+        <v>108000000</v>
       </c>
       <c r="P39" s="1" t="inlineStr">
         <is>
@@ -2641,13 +2641,13 @@
         <v>9</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>317000</v>
+        <v>263000</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>793</v>
+        <v>657</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>4210</v>
+        <v>3330</v>
       </c>
       <c r="F40" s="1" t="n">
         <v>4.24</v>
@@ -2673,13 +2673,13 @@
         <v>0</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>6350</v>
+        <v>5260</v>
       </c>
       <c r="N40" s="1" t="n">
         <v>35</v>
       </c>
       <c r="O40" s="1" t="n">
-        <v>136000000</v>
+        <v>120000000</v>
       </c>
       <c r="P40" s="1" t="inlineStr">
         <is>
@@ -2695,13 +2695,13 @@
         <v>9</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>351000</v>
+        <v>291000</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>878</v>
+        <v>728</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>4780</v>
+        <v>3780</v>
       </c>
       <c r="F41" s="1" t="n">
         <v>4.24</v>
@@ -2727,13 +2727,13 @@
         <v>0</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>7030</v>
+        <v>5820</v>
       </c>
       <c r="N41" s="1" t="n">
         <v>35</v>
       </c>
       <c r="O41" s="1" t="n">
-        <v>151000000</v>
+        <v>133000000</v>
       </c>
       <c r="P41" s="1" t="inlineStr">
         <is>
@@ -2749,13 +2749,13 @@
         <v>9</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>389000</v>
+        <v>322000</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>973</v>
+        <v>806</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>5430</v>
+        <v>4290</v>
       </c>
       <c r="F42" s="1" t="n">
         <v>4.24</v>
@@ -2781,13 +2781,13 @@
         <v>0</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>7780</v>
+        <v>6450</v>
       </c>
       <c r="N42" s="1" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O42" s="1" t="n">
-        <v>167000000</v>
+        <v>147000000</v>
       </c>
       <c r="P42" s="1" t="inlineStr">
         <is>
@@ -2803,13 +2803,13 @@
         <v>9</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>560000</v>
+        <v>464000</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>1400</v>
+        <v>1160</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>8560</v>
+        <v>6770</v>
       </c>
       <c r="F43" s="1" t="n">
         <v>5.19</v>
@@ -2835,13 +2835,13 @@
         <v>58.8</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>11200</v>
+        <v>9280</v>
       </c>
       <c r="N43" s="1" t="n">
         <v>41</v>
       </c>
       <c r="O43" s="1" t="n">
-        <v>240000000</v>
+        <v>212000000</v>
       </c>
       <c r="P43" s="1" t="inlineStr">
         <is>
@@ -2857,13 +2857,13 @@
         <v>9</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>456000</v>
+        <v>378000</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>1140</v>
+        <v>944</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>6620</v>
+        <v>5230</v>
       </c>
       <c r="F44" s="1" t="n">
         <v>4.24</v>
@@ -2889,13 +2889,13 @@
         <v>0</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>9110</v>
+        <v>7550</v>
       </c>
       <c r="N44" s="1" t="n">
         <v>41</v>
       </c>
       <c r="O44" s="1" t="n">
-        <v>195000000</v>
+        <v>172000000</v>
       </c>
       <c r="P44" s="1" t="inlineStr">
         <is>
@@ -2911,13 +2911,13 @@
         <v>9</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>482000</v>
+        <v>399000</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>1200</v>
+        <v>998</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>7100</v>
+        <v>5610</v>
       </c>
       <c r="F45" s="1" t="n">
         <v>4.24</v>
@@ -2943,13 +2943,13 @@
         <v>0</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>9640</v>
+        <v>7990</v>
       </c>
       <c r="N45" s="1" t="n">
         <v>41</v>
       </c>
       <c r="O45" s="1" t="n">
-        <v>207000000</v>
+        <v>182000000</v>
       </c>
       <c r="P45" s="1" t="inlineStr">
         <is>
@@ -2965,13 +2965,13 @@
         <v>9</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>510000</v>
+        <v>422000</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>1270</v>
+        <v>1060</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>7610</v>
+        <v>6020</v>
       </c>
       <c r="F46" s="1" t="n">
         <v>4.24</v>
@@ -2997,13 +2997,13 @@
         <v>0</v>
       </c>
       <c r="M46" s="1" t="n">
-        <v>10200</v>
+        <v>8450</v>
       </c>
       <c r="N46" s="1" t="n">
         <v>41</v>
       </c>
       <c r="O46" s="1" t="n">
-        <v>218000000</v>
+        <v>193000000</v>
       </c>
       <c r="P46" s="1" t="inlineStr">
         <is>
@@ -3019,13 +3019,13 @@
         <v>9</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>539000</v>
+        <v>447000</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>1350</v>
+        <v>1120</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>8170</v>
+        <v>6460</v>
       </c>
       <c r="F47" s="1" t="n">
         <v>4.24</v>
@@ -3051,13 +3051,13 @@
         <v>0</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>10800</v>
+        <v>8930</v>
       </c>
       <c r="N47" s="1" t="n">
         <v>41</v>
       </c>
       <c r="O47" s="1" t="n">
-        <v>231000000</v>
+        <v>204000000</v>
       </c>
       <c r="P47" s="1" t="inlineStr">
         <is>
@@ -3073,13 +3073,13 @@
         <v>9</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>656000</v>
+        <v>543000</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>1640</v>
+        <v>1360</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>10400</v>
+        <v>8250</v>
       </c>
       <c r="F48" s="1" t="n">
         <v>3.18</v>
@@ -3105,13 +3105,13 @@
         <v>36</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>13100</v>
+        <v>10900</v>
       </c>
       <c r="N48" s="1" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O48" s="1" t="n">
-        <v>281000000</v>
+        <v>248000000</v>
       </c>
       <c r="P48" s="1" t="inlineStr">
         <is>
@@ -3127,13 +3127,13 @@
         <v>9</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>784000</v>
+        <v>650000</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>1960</v>
+        <v>1620</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>13000</v>
+        <v>10300</v>
       </c>
       <c r="F49" s="1" t="n">
         <v>7.41</v>
@@ -3159,13 +3159,13 @@
         <v>0</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>15700</v>
+        <v>13000</v>
       </c>
       <c r="N49" s="1" t="n">
         <v>47</v>
       </c>
       <c r="O49" s="1" t="n">
-        <v>336000000</v>
+        <v>296000000</v>
       </c>
       <c r="P49" s="1" t="inlineStr">
         <is>
@@ -3181,13 +3181,13 @@
         <v>9</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>759000</v>
+        <v>630000</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>1900</v>
+        <v>1570</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>12500</v>
+        <v>9920</v>
       </c>
       <c r="F50" s="1" t="n">
         <v>4.24</v>
@@ -3213,13 +3213,13 @@
         <v>0</v>
       </c>
       <c r="M50" s="1" t="n">
-        <v>15200</v>
+        <v>12600</v>
       </c>
       <c r="N50" s="1" t="n">
         <v>47</v>
       </c>
       <c r="O50" s="1" t="n">
-        <v>325000000</v>
+        <v>287000000</v>
       </c>
       <c r="P50" s="1" t="inlineStr">
         <is>
@@ -3235,13 +3235,13 @@
         <v>9</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>954000</v>
+        <v>794000</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>2390</v>
+        <v>1980</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>16700</v>
+        <v>13200</v>
       </c>
       <c r="F51" s="1" t="n">
         <v>4.24</v>
@@ -3267,13 +3267,13 @@
         <v>0</v>
       </c>
       <c r="M51" s="1" t="n">
-        <v>19100</v>
+        <v>15900</v>
       </c>
       <c r="N51" s="1" t="n">
         <v>47</v>
       </c>
       <c r="O51" s="1" t="n">
-        <v>409000000</v>
+        <v>362000000</v>
       </c>
       <c r="P51" s="1" t="inlineStr">
         <is>
@@ -3289,13 +3289,13 @@
         <v>9</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>1200000</v>
+        <v>1000000</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>22200</v>
+        <v>17700</v>
       </c>
       <c r="F52" s="1" t="n">
         <v>4.24</v>
@@ -3321,13 +3321,13 @@
         <v>0</v>
       </c>
       <c r="M52" s="1" t="n">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="N52" s="1" t="n">
         <v>47</v>
       </c>
       <c r="O52" s="1" t="n">
-        <v>515000000</v>
+        <v>456000000</v>
       </c>
       <c r="P52" s="1" t="inlineStr">
         <is>
@@ -3343,13 +3343,13 @@
         <v>9</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>1740000</v>
+        <v>1450000</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>4340</v>
+        <v>3630</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>35300</v>
+        <v>28100</v>
       </c>
       <c r="F53" s="1" t="n">
         <v>3.18</v>
@@ -3375,13 +3375,13 @@
         <v>36</v>
       </c>
       <c r="M53" s="1" t="n">
-        <v>34700</v>
+        <v>29000</v>
       </c>
       <c r="N53" s="1" t="n">
         <v>47</v>
       </c>
       <c r="O53" s="1" t="n">
-        <v>744000000</v>
+        <v>662000000</v>
       </c>
       <c r="P53" s="1" t="inlineStr">
         <is>
@@ -3397,13 +3397,13 @@
         <v>9</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>1900000</v>
+        <v>1590000</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>4750</v>
+        <v>3970</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>39400</v>
+        <v>31500</v>
       </c>
       <c r="F54" s="1" t="n">
         <v>4.24</v>
@@ -3429,13 +3429,13 @@
         <v>0</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>38000</v>
+        <v>31800</v>
       </c>
       <c r="N54" s="1" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O54" s="1" t="n">
-        <v>814000000</v>
+        <v>725000000</v>
       </c>
       <c r="P54" s="1" t="inlineStr">
         <is>
@@ -3451,13 +3451,13 @@
         <v>9</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>3110000</v>
+        <v>2600000</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>7770</v>
+        <v>6510</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>73000</v>
+        <v>58500</v>
       </c>
       <c r="F55" s="1" t="n">
         <v>7.41</v>
@@ -3483,13 +3483,13 @@
         <v>0</v>
       </c>
       <c r="M55" s="1" t="n">
-        <v>62200</v>
+        <v>52100</v>
       </c>
       <c r="N55" s="1" t="n">
         <v>53</v>
       </c>
       <c r="O55" s="1" t="n">
-        <v>1330000000</v>
+        <v>1190000000</v>
       </c>
       <c r="P55" s="1" t="inlineStr">
         <is>
@@ -3505,13 +3505,13 @@
         <v>9</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>2730000</v>
+        <v>2290000</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>6830</v>
+        <v>5720</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>62100</v>
+        <v>49800</v>
       </c>
       <c r="F56" s="1" t="n">
         <v>4.24</v>
@@ -3537,13 +3537,13 @@
         <v>0</v>
       </c>
       <c r="M56" s="1" t="n">
-        <v>54600</v>
+        <v>45800</v>
       </c>
       <c r="N56" s="1" t="n">
         <v>53</v>
       </c>
       <c r="O56" s="1" t="n">
-        <v>1170000000</v>
+        <v>1040000000</v>
       </c>
       <c r="P56" s="1" t="inlineStr">
         <is>
@@ -3559,13 +3559,13 @@
         <v>9</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>3120000</v>
+        <v>2610000</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>7800</v>
+        <v>6540</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>73300</v>
+        <v>58800</v>
       </c>
       <c r="F57" s="1" t="n">
         <v>4.24</v>
@@ -3591,13 +3591,13 @@
         <v>0</v>
       </c>
       <c r="M57" s="1" t="n">
-        <v>62400</v>
+        <v>52300</v>
       </c>
       <c r="N57" s="1" t="n">
         <v>53</v>
       </c>
       <c r="O57" s="1" t="n">
-        <v>1340000000</v>
+        <v>1190000000</v>
       </c>
       <c r="P57" s="1" t="inlineStr">
         <is>
@@ -3613,13 +3613,13 @@
         <v>9</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>4100000</v>
+        <v>3440000</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>10300</v>
+        <v>8590</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>103000</v>
+        <v>82700</v>
       </c>
       <c r="F58" s="1" t="n">
         <v>3.18</v>
@@ -3645,13 +3645,13 @@
         <v>36</v>
       </c>
       <c r="M58" s="1" t="n">
-        <v>82000</v>
+        <v>68700</v>
       </c>
       <c r="N58" s="1" t="n">
         <v>53</v>
       </c>
       <c r="O58" s="1" t="n">
-        <v>1760000000</v>
+        <v>1570000000</v>
       </c>
       <c r="P58" s="1" t="inlineStr">
         <is>
@@ -3667,13 +3667,13 @@
         <v>9</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>4070000</v>
+        <v>3410000</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>10200</v>
+        <v>8530</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>102000</v>
+        <v>82000</v>
       </c>
       <c r="F59" s="1" t="n">
         <v>4.24</v>
@@ -3699,13 +3699,13 @@
         <v>0</v>
       </c>
       <c r="M59" s="1" t="n">
-        <v>81500</v>
+        <v>68300</v>
       </c>
       <c r="N59" s="1" t="n">
         <v>53</v>
       </c>
       <c r="O59" s="1" t="n">
-        <v>1750000000</v>
+        <v>1560000000</v>
       </c>
       <c r="P59" s="1" t="inlineStr">
         <is>
@@ -3721,13 +3721,13 @@
         <v>9</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>4650000</v>
+        <v>3900000</v>
       </c>
       <c r="D60" s="1" t="n">
-        <v>11600</v>
+        <v>9750</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>121000</v>
+        <v>96900</v>
       </c>
       <c r="F60" s="1" t="n">
         <v>4.24</v>
@@ -3753,13 +3753,13 @@
         <v>0</v>
       </c>
       <c r="M60" s="1" t="n">
-        <v>93100</v>
+        <v>78000</v>
       </c>
       <c r="N60" s="1" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O60" s="1" t="n">
-        <v>1990000000</v>
+        <v>1780000000</v>
       </c>
       <c r="P60" s="1" t="inlineStr">
         <is>
@@ -3775,13 +3775,13 @@
         <v>9</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>6910000</v>
+        <v>5790000</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>17300</v>
+        <v>14500</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>198000</v>
+        <v>159000</v>
       </c>
       <c r="F61" s="1" t="n">
         <v>7.41</v>
@@ -3807,13 +3807,13 @@
         <v>0</v>
       </c>
       <c r="M61" s="1" t="n">
-        <v>138000</v>
+        <v>116000</v>
       </c>
       <c r="N61" s="1" t="n">
         <v>59</v>
       </c>
       <c r="O61" s="1" t="n">
-        <v>2960000000</v>
+        <v>2640000000</v>
       </c>
       <c r="P61" s="1" t="inlineStr">
         <is>
@@ -3829,13 +3829,13 @@
         <v>9</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>6240000</v>
+        <v>5240000</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>15600</v>
+        <v>13100</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>174000</v>
+        <v>140000</v>
       </c>
       <c r="F62" s="1" t="n">
         <v>4.24</v>
@@ -3861,13 +3861,13 @@
         <v>0</v>
       </c>
       <c r="M62" s="1" t="n">
-        <v>125000</v>
+        <v>105000</v>
       </c>
       <c r="N62" s="1" t="n">
         <v>59</v>
       </c>
       <c r="O62" s="1" t="n">
-        <v>2670000000</v>
+        <v>2390000000</v>
       </c>
       <c r="P62" s="1" t="inlineStr">
         <is>
@@ -3883,13 +3883,13 @@
         <v>9</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>8430000</v>
+        <v>7080000</v>
       </c>
       <c r="D63" s="1" t="n">
-        <v>21100</v>
+        <v>17700</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>254000</v>
+        <v>204000</v>
       </c>
       <c r="F63" s="1" t="n">
         <v>3.18</v>
@@ -3915,13 +3915,13 @@
         <v>36</v>
       </c>
       <c r="M63" s="1" t="n">
-        <v>169000</v>
+        <v>142000</v>
       </c>
       <c r="N63" s="1" t="n">
         <v>59</v>
       </c>
       <c r="O63" s="1" t="n">
-        <v>3610000000</v>
+        <v>3230000000</v>
       </c>
       <c r="P63" s="1" t="inlineStr">
         <is>
@@ -3937,13 +3937,13 @@
         <v>9</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>8600000</v>
+        <v>7240000</v>
       </c>
       <c r="D64" s="1" t="n">
-        <v>21500</v>
+        <v>18100</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>260000</v>
+        <v>210000</v>
       </c>
       <c r="F64" s="1" t="n">
         <v>4.24</v>
@@ -3969,13 +3969,13 @@
         <v>0</v>
       </c>
       <c r="M64" s="1" t="n">
-        <v>172000</v>
+        <v>145000</v>
       </c>
       <c r="N64" s="1" t="n">
         <v>59</v>
       </c>
       <c r="O64" s="1" t="n">
-        <v>3690000000</v>
+        <v>3300000000</v>
       </c>
       <c r="P64" s="1" t="inlineStr">
         <is>
@@ -3991,13 +3991,13 @@
         <v>9</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>10100000</v>
+        <v>8520000</v>
       </c>
       <c r="D65" s="1" t="n">
-        <v>25200</v>
+        <v>21300</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>318000</v>
+        <v>257000</v>
       </c>
       <c r="F65" s="1" t="n">
         <v>4.24</v>
@@ -4023,13 +4023,13 @@
         <v>0</v>
       </c>
       <c r="M65" s="1" t="n">
-        <v>202000</v>
+        <v>170000</v>
       </c>
       <c r="N65" s="1" t="n">
         <v>59</v>
       </c>
       <c r="O65" s="1" t="n">
-        <v>4330000000</v>
+        <v>3890000000</v>
       </c>
       <c r="P65" s="1" t="inlineStr">
         <is>
@@ -4045,13 +4045,13 @@
         <v>9</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>11900000</v>
+        <v>10000000</v>
       </c>
       <c r="D66" s="1" t="n">
-        <v>29600</v>
+        <v>25000</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>389000</v>
+        <v>315000</v>
       </c>
       <c r="F66" s="1" t="n">
         <v>4.24</v>
@@ -4077,13 +4077,13 @@
         <v>0</v>
       </c>
       <c r="M66" s="1" t="n">
-        <v>237000</v>
+        <v>200000</v>
       </c>
       <c r="N66" s="1" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O66" s="1" t="n">
-        <v>5080000000</v>
+        <v>4570000000</v>
       </c>
       <c r="P66" s="1" t="inlineStr">
         <is>
@@ -4099,13 +4099,13 @@
         <v>9</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>18100000</v>
+        <v>15300000</v>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45200</v>
+        <v>38300</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>660000</v>
+        <v>535000</v>
       </c>
       <c r="F67" s="1" t="n">
         <v>7.41</v>
@@ -4131,13 +4131,13 @@
         <v>0</v>
       </c>
       <c r="M67" s="1" t="n">
-        <v>362000</v>
+        <v>306000</v>
       </c>
       <c r="N67" s="1" t="n">
         <v>65</v>
       </c>
       <c r="O67" s="1" t="n">
-        <v>7750000000</v>
+        <v>6990000000</v>
       </c>
       <c r="P67" s="1" t="inlineStr">
         <is>
@@ -4153,13 +4153,13 @@
         <v>9</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>17600000</v>
+        <v>14900000</v>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44100</v>
+        <v>37300</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>639000</v>
+        <v>519000</v>
       </c>
       <c r="F68" s="1" t="n">
         <v>3.18</v>
@@ -4185,13 +4185,13 @@
         <v>36</v>
       </c>
       <c r="M68" s="1" t="n">
-        <v>353000</v>
+        <v>299000</v>
       </c>
       <c r="N68" s="1" t="n">
         <v>65</v>
       </c>
       <c r="O68" s="1" t="n">
-        <v>7560000000</v>
+        <v>6810000000</v>
       </c>
       <c r="P68" s="1" t="inlineStr">
         <is>
@@ -4207,13 +4207,13 @@
         <v>9</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>16900000</v>
+        <v>14300000</v>
       </c>
       <c r="D69" s="1" t="n">
-        <v>42300</v>
+        <v>35800</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>606000</v>
+        <v>492000</v>
       </c>
       <c r="F69" s="1" t="n">
         <v>4.24</v>
@@ -4239,13 +4239,13 @@
         <v>0</v>
       </c>
       <c r="M69" s="1" t="n">
-        <v>338000</v>
+        <v>286000</v>
       </c>
       <c r="N69" s="1" t="n">
         <v>65</v>
       </c>
       <c r="O69" s="1" t="n">
-        <v>7250000000</v>
+        <v>6530000000</v>
       </c>
       <c r="P69" s="1" t="inlineStr">
         <is>
@@ -4261,13 +4261,13 @@
         <v>9</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>18600000</v>
+        <v>15800000</v>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46600</v>
+        <v>39400</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>685000</v>
+        <v>556000</v>
       </c>
       <c r="F70" s="1" t="n">
         <v>4.24</v>
@@ -4293,13 +4293,13 @@
         <v>0</v>
       </c>
       <c r="M70" s="1" t="n">
-        <v>373000</v>
+        <v>315000</v>
       </c>
       <c r="N70" s="1" t="n">
         <v>65</v>
       </c>
       <c r="O70" s="1" t="n">
-        <v>7990000000</v>
+        <v>7200000000</v>
       </c>
       <c r="P70" s="1" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>9</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>20500000</v>
+        <v>17400000</v>
       </c>
       <c r="D71" s="1" t="n">
-        <v>51400</v>
+        <v>43500</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>773000</v>
+        <v>628000</v>
       </c>
       <c r="F71" s="1" t="n">
         <v>4.24</v>
@@ -4347,13 +4347,13 @@
         <v>0</v>
       </c>
       <c r="M71" s="1" t="n">
-        <v>411000</v>
+        <v>348000</v>
       </c>
       <c r="N71" s="1" t="n">
         <v>65</v>
       </c>
       <c r="O71" s="1" t="n">
-        <v>8800000000</v>
+        <v>7930000000</v>
       </c>
       <c r="P71" s="1" t="inlineStr">
         <is>
@@ -4369,13 +4369,13 @@
         <v>9</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>22600000</v>
+        <v>19200000</v>
       </c>
       <c r="D72" s="1" t="n">
-        <v>56600</v>
+        <v>47900</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>873000</v>
+        <v>709000</v>
       </c>
       <c r="F72" s="1" t="n">
         <v>4.24</v>
@@ -4401,13 +4401,13 @@
         <v>0</v>
       </c>
       <c r="M72" s="1" t="n">
-        <v>453000</v>
+        <v>383000</v>
       </c>
       <c r="N72" s="1" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O72" s="1" t="n">
-        <v>9700000000</v>
+        <v>8740000000</v>
       </c>
       <c r="P72" s="1" t="inlineStr">
         <is>
@@ -4423,13 +4423,13 @@
         <v>9</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>32400000</v>
+        <v>27500000</v>
       </c>
       <c r="D73" s="1" t="n">
-        <v>81100</v>
+        <v>68600</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>1370000</v>
+        <v>1110000</v>
       </c>
       <c r="F73" s="1" t="n">
         <v>5.56</v>
@@ -4455,13 +4455,13 @@
         <v>63</v>
       </c>
       <c r="M73" s="1" t="n">
-        <v>649000</v>
+        <v>549000</v>
       </c>
       <c r="N73" s="1" t="n">
         <v>71</v>
       </c>
       <c r="O73" s="1" t="n">
-        <v>13900000000</v>
+        <v>12500000000</v>
       </c>
       <c r="P73" s="1" t="inlineStr">
         <is>
@@ -4477,13 +4477,13 @@
         <v>9</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>26500000</v>
+        <v>22400000</v>
       </c>
       <c r="D74" s="1" t="n">
-        <v>66200</v>
+        <v>56000</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>1060000</v>
+        <v>861000</v>
       </c>
       <c r="F74" s="1" t="n">
         <v>4.24</v>
@@ -4509,13 +4509,13 @@
         <v>0</v>
       </c>
       <c r="M74" s="1" t="n">
-        <v>529000</v>
+        <v>448000</v>
       </c>
       <c r="N74" s="1" t="n">
         <v>71</v>
       </c>
       <c r="O74" s="1" t="n">
-        <v>11300000000</v>
+        <v>10200000000</v>
       </c>
       <c r="P74" s="1" t="inlineStr">
         <is>
@@ -4531,13 +4531,13 @@
         <v>9</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>28100000</v>
+        <v>23700000</v>
       </c>
       <c r="D75" s="1" t="n">
-        <v>70100</v>
+        <v>59300</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>1140000</v>
+        <v>926000</v>
       </c>
       <c r="F75" s="1" t="n">
         <v>4.24</v>
@@ -4563,13 +4563,13 @@
         <v>0</v>
       </c>
       <c r="M75" s="1" t="n">
-        <v>561000</v>
+        <v>475000</v>
       </c>
       <c r="N75" s="1" t="n">
         <v>71</v>
       </c>
       <c r="O75" s="1" t="n">
-        <v>12000000000</v>
+        <v>10800000000</v>
       </c>
       <c r="P75" s="1" t="inlineStr">
         <is>
@@ -4585,13 +4585,13 @@
         <v>9</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>29700000</v>
+        <v>25200000</v>
       </c>
       <c r="D76" s="1" t="n">
-        <v>74300</v>
+        <v>62900</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>1230000</v>
+        <v>996000</v>
       </c>
       <c r="F76" s="1" t="n">
         <v>4.24</v>
@@ -4617,13 +4617,13 @@
         <v>0</v>
       </c>
       <c r="M76" s="1" t="n">
-        <v>595000</v>
+        <v>503000</v>
       </c>
       <c r="N76" s="1" t="n">
         <v>71</v>
       </c>
       <c r="O76" s="1" t="n">
-        <v>12700000000</v>
+        <v>11500000000</v>
       </c>
       <c r="P76" s="1" t="inlineStr">
         <is>
@@ -4639,13 +4639,13 @@
         <v>9</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>31500000</v>
+        <v>26700000</v>
       </c>
       <c r="D77" s="1" t="n">
-        <v>78800</v>
+        <v>66700</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>1320000</v>
+        <v>1070000</v>
       </c>
       <c r="F77" s="1" t="n">
         <v>4.24</v>
@@ -4671,13 +4671,13 @@
         <v>0</v>
       </c>
       <c r="M77" s="1" t="n">
-        <v>631000</v>
+        <v>534000</v>
       </c>
       <c r="N77" s="1" t="n">
         <v>71</v>
       </c>
       <c r="O77" s="1" t="n">
-        <v>13500000000</v>
+        <v>12200000000</v>
       </c>
       <c r="P77" s="1" t="inlineStr">
         <is>
@@ -4693,13 +4693,13 @@
         <v>9</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>38400000</v>
+        <v>32500000</v>
       </c>
       <c r="D78" s="1" t="n">
-        <v>96100</v>
+        <v>81300</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>1690000</v>
+        <v>1370000</v>
       </c>
       <c r="F78" s="1" t="n">
         <v>3.18</v>
@@ -4725,13 +4725,13 @@
         <v>36</v>
       </c>
       <c r="M78" s="1" t="n">
-        <v>769000</v>
+        <v>650000</v>
       </c>
       <c r="N78" s="1" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O78" s="1" t="n">
-        <v>16500000000</v>
+        <v>14800000000</v>
       </c>
       <c r="P78" s="1" t="inlineStr">
         <is>
@@ -4747,13 +4747,13 @@
         <v>9</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>35400000</v>
+        <v>30000000</v>
       </c>
       <c r="D79" s="1" t="n">
-        <v>88600</v>
+        <v>74900</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>1530000</v>
+        <v>1240000</v>
       </c>
       <c r="F79" s="1" t="n">
         <v>4.24</v>
@@ -4779,13 +4779,13 @@
         <v>0</v>
       </c>
       <c r="M79" s="1" t="n">
-        <v>709000</v>
+        <v>600000</v>
       </c>
       <c r="N79" s="1" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O79" s="1" t="n">
-        <v>15200000000</v>
+        <v>13700000000</v>
       </c>
       <c r="P79" s="1" t="inlineStr">
         <is>
@@ -4801,13 +4801,13 @@
         <v>9</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>48800000</v>
+        <v>41300000</v>
       </c>
       <c r="D80" s="1" t="n">
-        <v>122000</v>
+        <v>103000</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>2280000</v>
+        <v>1850000</v>
       </c>
       <c r="F80" s="1" t="n">
         <v>7.41</v>
@@ -4833,13 +4833,13 @@
         <v>0</v>
       </c>
       <c r="M80" s="1" t="n">
-        <v>977000</v>
+        <v>826000</v>
       </c>
       <c r="N80" s="1" t="n">
         <v>78</v>
       </c>
       <c r="O80" s="1" t="n">
-        <v>20900000000</v>
+        <v>18900000000</v>
       </c>
       <c r="P80" s="1" t="inlineStr">
         <is>
@@ -4855,13 +4855,13 @@
         <v>9</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>39700000</v>
+        <v>33600000</v>
       </c>
       <c r="D81" s="1" t="n">
-        <v>99100</v>
+        <v>83900</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>1760000</v>
+        <v>1430000</v>
       </c>
       <c r="F81" s="1" t="n">
         <v>4.24</v>
@@ -4887,13 +4887,13 @@
         <v>0</v>
       </c>
       <c r="M81" s="1" t="n">
-        <v>793000</v>
+        <v>671000</v>
       </c>
       <c r="N81" s="1" t="n">
         <v>78</v>
       </c>
       <c r="O81" s="1" t="n">
-        <v>17000000000</v>
+        <v>15300000000</v>
       </c>
       <c r="P81" s="1" t="inlineStr">
         <is>
@@ -4909,13 +4909,13 @@
         <v>9</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>41900000</v>
+        <v>35400000</v>
       </c>
       <c r="D82" s="1" t="n">
-        <v>105000</v>
+        <v>88600</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>1880000</v>
+        <v>1530000</v>
       </c>
       <c r="F82" s="1" t="n">
         <v>4.24</v>
@@ -4941,13 +4941,13 @@
         <v>0</v>
       </c>
       <c r="M82" s="1" t="n">
-        <v>838000</v>
+        <v>709000</v>
       </c>
       <c r="N82" s="1" t="n">
         <v>78</v>
       </c>
       <c r="O82" s="1" t="n">
-        <v>17900000000</v>
+        <v>16200000000</v>
       </c>
       <c r="P82" s="1" t="inlineStr">
         <is>
@@ -4963,13 +4963,13 @@
         <v>9</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>50800000</v>
+        <v>43000000</v>
       </c>
       <c r="D83" s="1" t="n">
-        <v>127000</v>
+        <v>108000</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>2400000</v>
+        <v>1950000</v>
       </c>
       <c r="F83" s="1" t="n">
         <v>3.18</v>
@@ -4995,13 +4995,13 @@
         <v>36</v>
       </c>
       <c r="M83" s="1" t="n">
-        <v>1020000</v>
+        <v>861000</v>
       </c>
       <c r="N83" s="1" t="n">
         <v>78</v>
       </c>
       <c r="O83" s="1" t="n">
-        <v>21800000000</v>
+        <v>19600000000</v>
       </c>
       <c r="P83" s="1" t="inlineStr">
         <is>
@@ -5017,13 +5017,13 @@
         <v>9</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>46700000</v>
+        <v>39500000</v>
       </c>
       <c r="D84" s="1" t="n">
-        <v>117000</v>
+        <v>98800</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>2160000</v>
+        <v>1750000</v>
       </c>
       <c r="F84" s="1" t="n">
         <v>4.24</v>
@@ -5049,13 +5049,13 @@
         <v>0</v>
       </c>
       <c r="M84" s="1" t="n">
-        <v>934000</v>
+        <v>790000</v>
       </c>
       <c r="N84" s="1" t="n">
         <v>78</v>
       </c>
       <c r="O84" s="1" t="n">
-        <v>20000000000</v>
+        <v>18000000000</v>
       </c>
       <c r="P84" s="1" t="inlineStr">
         <is>
@@ -5071,13 +5071,13 @@
         <v>9</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>49300000</v>
+        <v>41700000</v>
       </c>
       <c r="D85" s="1" t="n">
-        <v>123000</v>
+        <v>104000</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>2310000</v>
+        <v>1870000</v>
       </c>
       <c r="F85" s="1" t="n">
         <v>4.24</v>
@@ -5103,13 +5103,13 @@
         <v>0</v>
       </c>
       <c r="M85" s="1" t="n">
-        <v>986000</v>
+        <v>834000</v>
       </c>
       <c r="N85" s="1" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O85" s="1" t="n">
-        <v>21100000000</v>
+        <v>19000000000</v>
       </c>
       <c r="P85" s="1" t="inlineStr">
         <is>
@@ -5125,13 +5125,13 @@
         <v>9</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>52100000</v>
+        <v>44000000</v>
       </c>
       <c r="D86" s="1" t="n">
-        <v>130000</v>
+        <v>110000</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>2470000</v>
+        <v>2010000</v>
       </c>
       <c r="F86" s="1" t="n">
         <v>4.24</v>
@@ -5157,13 +5157,13 @@
         <v>0</v>
       </c>
       <c r="M86" s="1" t="n">
-        <v>1040000</v>
+        <v>881000</v>
       </c>
       <c r="N86" s="1" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O86" s="1" t="n">
-        <v>22300000000</v>
+        <v>20100000000</v>
       </c>
       <c r="P86" s="1" t="inlineStr">
         <is>
@@ -5179,13 +5179,13 @@
         <v>9</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>71400000</v>
+        <v>60500000</v>
       </c>
       <c r="D87" s="1" t="n">
-        <v>179000</v>
+        <v>151000</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>3670000</v>
+        <v>2980000</v>
       </c>
       <c r="F87" s="1" t="n">
         <v>7.41</v>
@@ -5211,13 +5211,13 @@
         <v>0</v>
       </c>
       <c r="M87" s="1" t="n">
-        <v>1430000</v>
+        <v>1210000</v>
       </c>
       <c r="N87" s="1" t="n">
         <v>85</v>
       </c>
       <c r="O87" s="1" t="n">
-        <v>30600000000</v>
+        <v>27600000000</v>
       </c>
       <c r="P87" s="1" t="inlineStr">
         <is>
@@ -5233,13 +5233,13 @@
         <v>9</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>66300000</v>
+        <v>56200000</v>
       </c>
       <c r="D88" s="1" t="n">
-        <v>166000</v>
+        <v>140000</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>3350000</v>
+        <v>2720000</v>
       </c>
       <c r="F88" s="1" t="n">
         <v>3.18</v>
@@ -5265,13 +5265,13 @@
         <v>36</v>
       </c>
       <c r="M88" s="1" t="n">
-        <v>1330000</v>
+        <v>1120000</v>
       </c>
       <c r="N88" s="1" t="n">
         <v>85</v>
       </c>
       <c r="O88" s="1" t="n">
-        <v>28400000000</v>
+        <v>25600000000</v>
       </c>
       <c r="P88" s="1" t="inlineStr">
         <is>
@@ -5287,13 +5287,13 @@
         <v>9</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>60500000</v>
+        <v>51300000</v>
       </c>
       <c r="D89" s="1" t="n">
-        <v>151000</v>
+        <v>128000</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>2980000</v>
+        <v>2430000</v>
       </c>
       <c r="F89" s="1" t="n">
         <v>4.24</v>
@@ -5319,13 +5319,13 @@
         <v>0</v>
       </c>
       <c r="M89" s="1" t="n">
-        <v>1210000</v>
+        <v>1030000</v>
       </c>
       <c r="N89" s="1" t="n">
         <v>85</v>
       </c>
       <c r="O89" s="1" t="n">
-        <v>25900000000</v>
+        <v>23400000000</v>
       </c>
       <c r="P89" s="1" t="inlineStr">
         <is>
@@ -5341,13 +5341,13 @@
         <v>9</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>63500000</v>
+        <v>53900000</v>
       </c>
       <c r="D90" s="1" t="n">
-        <v>159000</v>
+        <v>135000</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>3170000</v>
+        <v>2580000</v>
       </c>
       <c r="F90" s="1" t="n">
         <v>4.24</v>
@@ -5373,13 +5373,13 @@
         <v>0</v>
       </c>
       <c r="M90" s="1" t="n">
-        <v>1270000</v>
+        <v>1080000</v>
       </c>
       <c r="N90" s="1" t="n">
         <v>85</v>
       </c>
       <c r="O90" s="1" t="n">
-        <v>27200000000</v>
+        <v>24600000000</v>
       </c>
       <c r="P90" s="1" t="inlineStr">
         <is>
@@ -5395,13 +5395,13 @@
         <v>9</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>66600000</v>
+        <v>56600000</v>
       </c>
       <c r="D91" s="1" t="n">
-        <v>167000</v>
+        <v>142000</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>3360000</v>
+        <v>2750000</v>
       </c>
       <c r="F91" s="1" t="n">
         <v>4.24</v>
@@ -5427,13 +5427,13 @@
         <v>0</v>
       </c>
       <c r="M91" s="1" t="n">
-        <v>1330000</v>
+        <v>1130000</v>
       </c>
       <c r="N91" s="1" t="n">
         <v>85</v>
       </c>
       <c r="O91" s="1" t="n">
-        <v>28500000000</v>
+        <v>25800000000</v>
       </c>
       <c r="P91" s="1" t="inlineStr">
         <is>
@@ -5449,13 +5449,13 @@
         <v>9</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>69900000</v>
+        <v>59500000</v>
       </c>
       <c r="D92" s="1" t="n">
-        <v>175000</v>
+        <v>149000</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>3570000</v>
+        <v>2920000</v>
       </c>
       <c r="F92" s="1" t="n">
         <v>4.24</v>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="M92" s="1" t="n">
-        <v>1400000</v>
+        <v>1190000</v>
       </c>
       <c r="N92" s="1" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O92" s="1" t="n">
-        <v>30000000000</v>
+        <v>27100000000</v>
       </c>
       <c r="P92" s="1" t="inlineStr">
         <is>
@@ -5503,13 +5503,13 @@
         <v>9</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>84300000</v>
+        <v>71800000</v>
       </c>
       <c r="D93" s="1" t="n">
-        <v>211000</v>
+        <v>180000</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>4520000</v>
+        <v>3700000</v>
       </c>
       <c r="F93" s="1" t="n">
         <v>3.18</v>
@@ -5535,13 +5535,13 @@
         <v>36</v>
       </c>
       <c r="M93" s="1" t="n">
-        <v>1690000</v>
+        <v>1440000</v>
       </c>
       <c r="N93" s="1" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O93" s="1" t="n">
-        <v>36100000000</v>
+        <v>32800000000</v>
       </c>
       <c r="P93" s="1" t="inlineStr">
         <is>
@@ -5557,13 +5557,13 @@
         <v>9</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>76900000</v>
+        <v>65600000</v>
       </c>
       <c r="D94" s="1" t="n">
-        <v>192000</v>
+        <v>164000</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>4030000</v>
+        <v>3300000</v>
       </c>
       <c r="F94" s="1" t="n">
         <v>4.24</v>
@@ -5589,13 +5589,13 @@
         <v>0</v>
       </c>
       <c r="M94" s="1" t="n">
-        <v>1540000</v>
+        <v>1310000</v>
       </c>
       <c r="N94" s="1" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O94" s="1" t="n">
-        <v>33000000000</v>
+        <v>29900000000</v>
       </c>
       <c r="P94" s="1" t="inlineStr">
         <is>
@@ -5611,13 +5611,13 @@
         <v>9</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>105000000</v>
+        <v>89600000</v>
       </c>
       <c r="D95" s="1" t="n">
-        <v>262000</v>
+        <v>224000</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>5940000</v>
+        <v>4870000</v>
       </c>
       <c r="F95" s="1" t="n">
         <v>7.41</v>
@@ -5643,13 +5643,13 @@
         <v>0</v>
       </c>
       <c r="M95" s="1" t="n">
-        <v>2100000</v>
+        <v>1790000</v>
       </c>
       <c r="N95" s="1" t="n">
         <v>93</v>
       </c>
       <c r="O95" s="1" t="n">
-        <v>45000000000</v>
+        <v>40900000000</v>
       </c>
       <c r="P95" s="1" t="inlineStr">
         <is>
@@ -5665,13 +5665,13 @@
         <v>9</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>83200000</v>
+        <v>71000000</v>
       </c>
       <c r="D96" s="1" t="n">
-        <v>208000</v>
+        <v>177000</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>4440000</v>
+        <v>3640000</v>
       </c>
       <c r="F96" s="1" t="n">
         <v>4.24</v>
@@ -5697,13 +5697,13 @@
         <v>0</v>
       </c>
       <c r="M96" s="1" t="n">
-        <v>1660000</v>
+        <v>1420000</v>
       </c>
       <c r="N96" s="1" t="n">
         <v>93</v>
       </c>
       <c r="O96" s="1" t="n">
-        <v>35600000000</v>
+        <v>32400000000</v>
       </c>
       <c r="P96" s="1" t="inlineStr">
         <is>
@@ -5719,13 +5719,13 @@
         <v>9</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>98500000</v>
+        <v>84100000</v>
       </c>
       <c r="D97" s="1" t="n">
-        <v>246000</v>
+        <v>210000</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>5490000</v>
+        <v>4500000</v>
       </c>
       <c r="F97" s="1" t="n">
         <v>3.18</v>
@@ -5751,13 +5751,13 @@
         <v>36</v>
       </c>
       <c r="M97" s="1" t="n">
-        <v>1970000</v>
+        <v>1680000</v>
       </c>
       <c r="N97" s="1" t="n">
         <v>93</v>
       </c>
       <c r="O97" s="1" t="n">
-        <v>42200000000</v>
+        <v>38400000000</v>
       </c>
       <c r="P97" s="1" t="inlineStr">
         <is>
@@ -5773,13 +5773,13 @@
         <v>9</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>88200000</v>
+        <v>75300000</v>
       </c>
       <c r="D98" s="1" t="n">
-        <v>221000</v>
+        <v>188000</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>4780000</v>
+        <v>3920000</v>
       </c>
       <c r="F98" s="1" t="n">
         <v>4.24</v>
@@ -5805,13 +5805,13 @@
         <v>0</v>
       </c>
       <c r="M98" s="1" t="n">
-        <v>1760000</v>
+        <v>1510000</v>
       </c>
       <c r="N98" s="1" t="n">
         <v>93</v>
       </c>
       <c r="O98" s="1" t="n">
-        <v>37800000000</v>
+        <v>34400000000</v>
       </c>
       <c r="P98" s="1" t="inlineStr">
         <is>
@@ -5827,13 +5827,13 @@
         <v>9</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>90900000</v>
+        <v>77600000</v>
       </c>
       <c r="D99" s="1" t="n">
-        <v>227000</v>
+        <v>194000</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>4960000</v>
+        <v>4070000</v>
       </c>
       <c r="F99" s="1" t="n">
         <v>4.24</v>
@@ -5859,13 +5859,13 @@
         <v>0</v>
       </c>
       <c r="M99" s="1" t="n">
-        <v>1820000</v>
+        <v>1550000</v>
       </c>
       <c r="N99" s="1" t="n">
         <v>93</v>
       </c>
       <c r="O99" s="1" t="n">
-        <v>38900000000</v>
+        <v>35400000000</v>
       </c>
       <c r="P99" s="1" t="inlineStr">
         <is>
@@ -5881,13 +5881,13 @@
         <v>9</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>108000000</v>
+        <v>91900000</v>
       </c>
       <c r="D100" s="1" t="n">
-        <v>269000</v>
+        <v>230000</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>6130000</v>
+        <v>5030000</v>
       </c>
       <c r="F100" s="1" t="n">
         <v>3.18</v>
@@ -5913,13 +5913,13 @@
         <v>36</v>
       </c>
       <c r="M100" s="1" t="n">
-        <v>2150000</v>
+        <v>1840000</v>
       </c>
       <c r="N100" s="1" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O100" s="1" t="n">
-        <v>46100000000</v>
+        <v>41900000000</v>
       </c>
       <c r="P100" s="1" t="inlineStr">
         <is>
@@ -5935,13 +5935,13 @@
         <v>9</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>96400000</v>
+        <v>82300000</v>
       </c>
       <c r="D101" s="1" t="n">
-        <v>241000</v>
+        <v>206000</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>5340000</v>
+        <v>4380000</v>
       </c>
       <c r="F101" s="1" t="n">
         <v>4.24</v>
@@ -5967,13 +5967,13 @@
         <v>0</v>
       </c>
       <c r="M101" s="1" t="n">
-        <v>1930000</v>
+        <v>1650000</v>
       </c>
       <c r="N101" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O101" s="1" t="n">
-        <v>41300000000</v>
+        <v>37500000000</v>
       </c>
       <c r="P101" s="1" t="inlineStr">
         <is>
@@ -5989,13 +5989,13 @@
         <v>9</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>99300000</v>
+        <v>84800000</v>
       </c>
       <c r="D102" s="1" t="n">
-        <v>248000</v>
+        <v>212000</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>5540000</v>
+        <v>4550000</v>
       </c>
       <c r="F102" s="1" t="n">
         <v>4.24</v>
@@ -6021,13 +6021,13 @@
         <v>0</v>
       </c>
       <c r="M102" s="1" t="n">
-        <v>1990000</v>
+        <v>1700000</v>
       </c>
       <c r="N102" s="1" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O102" s="1" t="n">
-        <v>42600000000</v>
+        <v>38700000000</v>
       </c>
       <c r="P102" s="1" t="inlineStr">
         <is>
@@ -6043,13 +6043,13 @@
         <v>9</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>143000000</v>
+        <v>122000000</v>
       </c>
       <c r="D103" s="1" t="n">
-        <v>358000</v>
+        <v>306000</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>8760000</v>
+        <v>7180000</v>
       </c>
       <c r="F103" s="1" t="n">
         <v>3.18</v>
@@ -6075,13 +6075,13 @@
         <v>36</v>
       </c>
       <c r="M103" s="1" t="n">
-        <v>2860000</v>
+        <v>2440000</v>
       </c>
       <c r="N103" s="1" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O103" s="1" t="n">
-        <v>61400000000</v>
+        <v>55800000000</v>
       </c>
       <c r="P103" s="1" t="inlineStr">
         <is>

--- a/Data_Table/스테이지 테이블.xlsx
+++ b/Data_Table/스테이지 테이블.xlsx
@@ -706,7 +706,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>55.81</v>
+        <v>27.91</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>1.2</v>
@@ -814,7 +814,7 @@
         <v>1.87</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>47.97</v>
+        <v>23.98</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>1.2</v>

--- a/Data_Table/스테이지 테이블.xlsx
+++ b/Data_Table/스테이지 테이블.xlsx
@@ -697,7 +697,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>300</v>
+        <v>95.87</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>1</v>
@@ -706,13 +706,13 @@
         <v>1</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>27.91</v>
+        <v>22.33</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>1.2</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>45.57</v>
+        <v>36.46</v>
       </c>
       <c r="I4" s="1" t="n">
         <v>0</v>
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="K4" s="1" t="n">
-        <v>72</v>
+        <v>57.6</v>
       </c>
       <c r="L4" s="1" t="n">
         <v>0</v>
@@ -751,22 +751,22 @@
         <v>3</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>500</v>
+        <v>125</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>21.21</v>
+        <v>17.11</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>21.21</v>
+        <v>17.11</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>42.42</v>
+        <v>34.23</v>
       </c>
       <c r="I5" s="1" t="n">
         <v>0</v>
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="K5" s="1" t="n">
-        <v>72</v>
+        <v>58.1</v>
       </c>
       <c r="L5" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="N5" s="1" t="n">
         <v>1</v>
@@ -805,22 +805,22 @@
         <v>3</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>661</v>
+        <v>192</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>1.87</v>
+        <v>2.38</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>23.98</v>
+        <v>19.55</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>1.2</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>43.31</v>
+        <v>35.31</v>
       </c>
       <c r="I6" s="1" t="n">
         <v>0</v>
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="K6" s="1" t="n">
-        <v>72</v>
+        <v>58.7</v>
       </c>
       <c r="L6" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>13.21</v>
+        <v>16.01</v>
       </c>
       <c r="N6" s="1" t="n">
         <v>1</v>
@@ -859,22 +859,22 @@
         <v>4</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>873</v>
+        <v>347</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>2.18</v>
+        <v>3.62</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>2.65</v>
+        <v>4.99</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>13.73</v>
+        <v>11.29</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>6.86</v>
+        <v>5.64</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>27.46</v>
+        <v>22.58</v>
       </c>
       <c r="I7" s="1" t="n">
         <v>0</v>
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="K7" s="1" t="n">
-        <v>72</v>
+        <v>59.2</v>
       </c>
       <c r="L7" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>17.46</v>
+        <v>28.96</v>
       </c>
       <c r="N7" s="1" t="n">
         <v>1</v>
@@ -913,13 +913,13 @@
         <v>4</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>1500</v>
+        <v>789</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>3.75</v>
+        <v>8.23</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>5.22</v>
+        <v>13.94</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>1.22</v>
@@ -945,7 +945,7 @@
         <v>35.8</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>30</v>
+        <v>65.83</v>
       </c>
       <c r="N8" s="1" t="n">
         <v>6</v>
@@ -967,22 +967,22 @@
         <v>5</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>1360</v>
+        <v>440</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>3.4</v>
+        <v>4.59</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>4.62</v>
+        <v>6.71</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>4.65</v>
+        <v>3.89</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>9.289999999999999</v>
+        <v>7.78</v>
       </c>
       <c r="I9" s="1" t="n">
         <v>0</v>
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="K9" s="1" t="n">
-        <v>72</v>
+        <v>60.3</v>
       </c>
       <c r="L9" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>27.21</v>
+        <v>36.69</v>
       </c>
       <c r="N9" s="1" t="n">
         <v>6</v>
@@ -1021,22 +1021,22 @@
         <v>5</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>1600</v>
+        <v>611</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>4.01</v>
+        <v>6.38</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>5.68</v>
+        <v>10.13</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>5.81</v>
+        <v>4.91</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>1.94</v>
+        <v>1.64</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>8.279999999999999</v>
+        <v>6.99</v>
       </c>
       <c r="I10" s="1" t="n">
         <v>0</v>
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="K10" s="1" t="n">
-        <v>72</v>
+        <v>60.8</v>
       </c>
       <c r="L10" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>32.09</v>
+        <v>51.01</v>
       </c>
       <c r="N10" s="1" t="n">
         <v>6</v>
@@ -1075,22 +1075,22 @@
         <v>6</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>1890</v>
+        <v>758</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>4.73</v>
+        <v>7.9</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>6.97</v>
+        <v>13.25</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>4.24</v>
+        <v>3.61</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>9.77</v>
+        <v>8.32</v>
       </c>
       <c r="I11" s="1" t="n">
         <v>0</v>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="K11" s="1" t="n">
-        <v>72</v>
+        <v>61.3</v>
       </c>
       <c r="L11" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>37.84</v>
+        <v>63.23</v>
       </c>
       <c r="N11" s="1" t="n">
         <v>6</v>
@@ -1129,49 +1129,49 @@
         <v>6</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>2900</v>
+        <v>1040</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>7.25</v>
+        <v>10.84</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>11.9</v>
+        <v>19.67</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>3.22</v>
+        <v>2.22</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>1.61</v>
+        <v>1.11</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>10.54</v>
+        <v>7.28</v>
       </c>
       <c r="I12" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K12" s="1" t="n">
-        <v>89.59999999999999</v>
+        <v>61.9</v>
       </c>
       <c r="L12" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>58</v>
+        <v>86.73</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O12" s="1" t="n">
         <v>1120</v>
       </c>
       <c r="P12" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -1183,22 +1183,22 @@
         <v>7</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>3010</v>
+        <v>1680</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>7.53</v>
+        <v>17.56</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>12.47</v>
+        <v>35.96</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>3.66</v>
+        <v>3.18</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>4.89</v>
+        <v>4.24</v>
       </c>
       <c r="I13" s="1" t="n">
         <v>0</v>
@@ -1209,16 +1209,16 @@
         </is>
       </c>
       <c r="K13" s="1" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>36</v>
+        <v>31.2</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>60.21</v>
+        <v>141</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O13" s="1" t="n">
         <v>1500</v>
@@ -1237,13 +1237,13 @@
         <v>7</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>3070</v>
+        <v>2110</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>7.68</v>
+        <v>21.99</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>12.79</v>
+        <v>47.62</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>0.8</v>
@@ -1252,34 +1252,34 @@
         <v>0.8</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>6.52</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="I14" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="K14" s="1" t="n">
-        <v>72</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="L14" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>61.44</v>
+        <v>176</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O14" s="1" t="n">
         <v>2010</v>
       </c>
       <c r="P14" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
     </row>
@@ -1291,49 +1291,49 @@
         <v>8</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>3610</v>
+        <v>834</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>9.01</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>15.62</v>
+        <v>14.95</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>3.26</v>
+        <v>2.87</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>9.77</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="I15" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="K15" s="1" t="n">
-        <v>72</v>
+        <v>63.5</v>
       </c>
       <c r="L15" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>72.09999999999999</v>
+        <v>69.62</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O15" s="1" t="n">
         <v>2690</v>
       </c>
       <c r="P15" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
     </row>
@@ -1345,49 +1345,49 @@
         <v>8</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>5500</v>
+        <v>1280</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>13.75</v>
+        <v>13.37</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>26.48</v>
+        <v>25.56</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>11.59</v>
+        <v>7.91</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>3.86</v>
+        <v>2.64</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>8.49</v>
+        <v>5.79</v>
       </c>
       <c r="I16" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K16" s="1" t="n">
-        <v>93.8</v>
+        <v>64</v>
       </c>
       <c r="L16" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O16" s="1" t="n">
         <v>3610</v>
       </c>
       <c r="P16" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -1399,49 +1399,49 @@
         <v>9</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>4850</v>
+        <v>1430</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>12.13</v>
+        <v>14.88</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>22.63</v>
+        <v>29.23</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>5.09</v>
+        <v>4.56</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>10.18</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="I17" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K17" s="1" t="n">
-        <v>72</v>
+        <v>64.5</v>
       </c>
       <c r="L17" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>97.02</v>
+        <v>119</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O17" s="1" t="n">
         <v>4840</v>
       </c>
       <c r="P17" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -1453,13 +1453,13 @@
         <v>9</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>6400</v>
+        <v>2110</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>15.99</v>
+        <v>21.99</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>31.98</v>
+        <v>47.62</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>0.8</v>
@@ -1468,7 +1468,7 @@
         <v>0.8</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>7.64</v>
+        <v>6.9</v>
       </c>
       <c r="I18" s="1" t="n">
         <v>0</v>
@@ -1479,16 +1479,16 @@
         </is>
       </c>
       <c r="K18" s="1" t="n">
-        <v>90</v>
+        <v>81.3</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>36</v>
+        <v>32.5</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>128</v>
+        <v>176</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O18" s="1" t="n">
         <v>6480</v>
@@ -1507,22 +1507,22 @@
         <v>9</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>6380</v>
+        <v>2370</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>15.94</v>
+        <v>24.77</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>31.86</v>
+        <v>55.26</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>40.72</v>
+        <v>37.1</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>40.72</v>
+        <v>37.1</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>10.18</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="I19" s="1" t="n">
         <v>0</v>
@@ -1533,16 +1533,16 @@
         </is>
       </c>
       <c r="K19" s="1" t="n">
-        <v>72</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="L19" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>128</v>
+        <v>198</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O19" s="1" t="n">
         <v>9340</v>
@@ -1561,49 +1561,49 @@
         <v>9</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>7310</v>
+        <v>3120</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>18.28</v>
+        <v>32.51</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>37.8</v>
+        <v>77.64</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>2.59</v>
+        <v>3.37</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>0.86</v>
+        <v>1.12</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>12.62</v>
+        <v>16.45</v>
       </c>
       <c r="I20" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="K20" s="1" t="n">
-        <v>72</v>
+        <v>93.8</v>
       </c>
       <c r="L20" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>146</v>
+        <v>260</v>
       </c>
       <c r="N20" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="O20" s="1" t="n">
         <v>14900</v>
       </c>
       <c r="P20" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
     </row>
@@ -1615,49 +1615,49 @@
         <v>9</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>10900</v>
+        <v>1450</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>27.25</v>
+        <v>15.11</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>62.26</v>
+        <v>29.79</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>8.710000000000001</v>
+        <v>5.85</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>2.9</v>
+        <v>1.95</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>20.77</v>
+        <v>13.94</v>
       </c>
       <c r="I21" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="K21" s="1" t="n">
-        <v>99.40000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="L21" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>218</v>
+        <v>121</v>
       </c>
       <c r="N21" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O21" s="1" t="n">
         <v>24900</v>
       </c>
       <c r="P21" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>쉬움</t>
         </is>
       </c>
     </row>
@@ -1669,49 +1669,49 @@
         <v>9</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>9990</v>
+        <v>1890</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>24.98</v>
+        <v>19.68</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>55.85</v>
+        <v>41.46</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>7.52</v>
+        <v>7.02</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>2.51</v>
+        <v>2.34</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>15.05</v>
+        <v>14.04</v>
       </c>
       <c r="I22" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K22" s="1" t="n">
-        <v>72</v>
+        <v>67.2</v>
       </c>
       <c r="L22" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>200</v>
+        <v>157</v>
       </c>
       <c r="N22" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O22" s="1" t="n">
         <v>43700</v>
       </c>
       <c r="P22" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -1723,22 +1723,22 @@
         <v>9</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>13700</v>
+        <v>2500</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>34.24</v>
+        <v>26.11</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>82.81</v>
+        <v>59.03</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>7.49</v>
+        <v>7.05</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>14.88</v>
+        <v>14</v>
       </c>
       <c r="I23" s="1" t="n">
         <v>0</v>
@@ -1749,16 +1749,16 @@
         </is>
       </c>
       <c r="K23" s="1" t="n">
-        <v>90</v>
+        <v>84.7</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>36</v>
+        <v>33.9</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>274</v>
+        <v>209</v>
       </c>
       <c r="N23" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O23" s="1" t="n">
         <v>81000</v>
@@ -1777,22 +1777,22 @@
         <v>9</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>14200</v>
+        <v>2790</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>35.48</v>
+        <v>29.15</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>86.58</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>9.92</v>
+        <v>9.41</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>3.31</v>
+        <v>3.14</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>19.84</v>
+        <v>18.82</v>
       </c>
       <c r="I24" s="1" t="n">
         <v>0</v>
@@ -1803,16 +1803,16 @@
         </is>
       </c>
       <c r="K24" s="1" t="n">
-        <v>72</v>
+        <v>68.3</v>
       </c>
       <c r="L24" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>284</v>
+        <v>233</v>
       </c>
       <c r="N24" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O24" s="1" t="n">
         <v>150000</v>
@@ -1831,22 +1831,22 @@
         <v>9</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>16900</v>
+        <v>3520</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>42.28</v>
+        <v>36.73</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>108</v>
+        <v>90.42</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>23.27</v>
+        <v>22.24</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>7.76</v>
+        <v>7.41</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>19.98</v>
+        <v>19.09</v>
       </c>
       <c r="I25" s="1" t="n">
         <v>0</v>
@@ -1857,13 +1857,13 @@
         </is>
       </c>
       <c r="K25" s="1" t="n">
-        <v>72</v>
+        <v>68.8</v>
       </c>
       <c r="L25" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>338</v>
+        <v>294</v>
       </c>
       <c r="N25" s="1" t="n">
         <v>19</v>
@@ -1885,49 +1885,49 @@
         <v>9</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>26200</v>
+        <v>3630</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>65.5</v>
+        <v>37.88</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>186</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>14.36</v>
+        <v>9.48</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>4.79</v>
+        <v>3.16</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>40.11</v>
+        <v>26.47</v>
       </c>
       <c r="I26" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K26" s="1" t="n">
-        <v>105</v>
+        <v>69.3</v>
       </c>
       <c r="L26" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>524</v>
+        <v>303</v>
       </c>
       <c r="N26" s="1" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="O26" s="1" t="n">
         <v>513000</v>
       </c>
       <c r="P26" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -1939,49 +1939,49 @@
         <v>9</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>23600</v>
+        <v>5100</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>59</v>
+        <v>53.18</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>16.54</v>
+        <v>22.84</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>5.51</v>
+        <v>7.61</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>27.5</v>
+        <v>37.97</v>
       </c>
       <c r="I27" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="K27" s="1" t="n">
-        <v>72</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="L27" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>472</v>
+        <v>425</v>
       </c>
       <c r="N27" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O27" s="1" t="n">
         <v>949000</v>
       </c>
       <c r="P27" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>허들</t>
         </is>
       </c>
     </row>
@@ -1993,22 +1993,22 @@
         <v>9</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>31800</v>
+        <v>3000</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>79.45999999999999</v>
+        <v>31.27</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>237</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>10.31</v>
+        <v>10.08</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>3.44</v>
+        <v>3.36</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>20.63</v>
+        <v>20.17</v>
       </c>
       <c r="I28" s="1" t="n">
         <v>0</v>
@@ -2019,16 +2019,16 @@
         </is>
       </c>
       <c r="K28" s="1" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>36</v>
+        <v>35.2</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>636</v>
+        <v>250</v>
       </c>
       <c r="N28" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O28" s="1" t="n">
         <v>1760000</v>
@@ -2047,22 +2047,22 @@
         <v>9</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>32400</v>
+        <v>3650</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>80.91</v>
+        <v>38.05</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>243</v>
+        <v>94.51000000000001</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>4.24</v>
+        <v>4.17</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>27.5</v>
+        <v>27.08</v>
       </c>
       <c r="I29" s="1" t="n">
         <v>0</v>
@@ -2073,16 +2073,16 @@
         </is>
       </c>
       <c r="K29" s="1" t="n">
-        <v>72</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="L29" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>647</v>
+        <v>304</v>
       </c>
       <c r="N29" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O29" s="1" t="n">
         <v>3250000</v>
@@ -2101,22 +2101,22 @@
         <v>9</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>37900</v>
+        <v>5000</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>94.75</v>
+        <v>52.14</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>296</v>
+        <v>140</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>4.24</v>
+        <v>4.21</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>27.5</v>
+        <v>27.31</v>
       </c>
       <c r="I30" s="1" t="n">
         <v>0</v>
@@ -2127,16 +2127,16 @@
         </is>
       </c>
       <c r="K30" s="1" t="n">
-        <v>72</v>
+        <v>71.5</v>
       </c>
       <c r="L30" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>758</v>
+        <v>417</v>
       </c>
       <c r="N30" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O30" s="1" t="n">
         <v>6010000</v>
@@ -2155,49 +2155,49 @@
         <v>9</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>57700</v>
+        <v>10400</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>144</v>
+        <v>109</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>6.51</v>
+        <v>4.24</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>2.17</v>
+        <v>1.41</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>13.01</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I31" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K31" s="1" t="n">
-        <v>110.6</v>
+        <v>72</v>
       </c>
       <c r="L31" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>1150</v>
+        <v>868</v>
       </c>
       <c r="N31" s="1" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="O31" s="1" t="n">
         <v>11100000</v>
       </c>
       <c r="P31" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -2209,49 +2209,49 @@
         <v>9</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>56700</v>
+        <v>14000</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>489</v>
+        <v>508</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>4.24</v>
+        <v>4.26</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="I32" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J32" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K32" s="1" t="n">
-        <v>72</v>
+        <v>72.5</v>
       </c>
       <c r="L32" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>1130</v>
+        <v>1170</v>
       </c>
       <c r="N32" s="1" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="O32" s="1" t="n">
         <v>20600000</v>
       </c>
       <c r="P32" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -2263,49 +2263,49 @@
         <v>9</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>83400</v>
+        <v>19500</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>792</v>
+        <v>767</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>3.18</v>
+        <v>4.2</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>1.06</v>
+        <v>1.4</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>6.35</v>
+        <v>8.4</v>
       </c>
       <c r="I33" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="K33" s="1" t="n">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>36</v>
+        <v>47.6</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>1670</v>
+        <v>1630</v>
       </c>
       <c r="N33" s="1" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="O33" s="1" t="n">
         <v>38100000</v>
       </c>
       <c r="P33" s="1" t="inlineStr">
         <is>
-          <t>보스 층 · 어려움</t>
+          <t>보스 층 · 허들</t>
         </is>
       </c>
     </row>
@@ -2317,49 +2317,49 @@
         <v>9</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>92700</v>
+        <v>12500</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>232</v>
+        <v>130</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>904</v>
+        <v>439</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>4.24</v>
+        <v>4.33</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>8.66</v>
       </c>
       <c r="I34" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J34" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="K34" s="1" t="n">
-        <v>72</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="L34" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>1850</v>
+        <v>1040</v>
       </c>
       <c r="N34" s="1" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="O34" s="1" t="n">
-        <v>42300000</v>
+        <v>24300000</v>
       </c>
       <c r="P34" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
     </row>
@@ -2371,22 +2371,22 @@
         <v>9</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>119000</v>
+        <v>17000</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>296</v>
+        <v>177</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>1230</v>
+        <v>646</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>4.24</v>
+        <v>4.36</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="I35" s="1" t="n">
         <v>0</v>
@@ -2397,19 +2397,19 @@
         </is>
       </c>
       <c r="K35" s="1" t="n">
-        <v>72</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L35" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>2370</v>
+        <v>1420</v>
       </c>
       <c r="N35" s="1" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="O35" s="1" t="n">
-        <v>54100000</v>
+        <v>33200000</v>
       </c>
       <c r="P35" s="1" t="inlineStr">
         <is>
@@ -2425,22 +2425,22 @@
         <v>9</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>151000</v>
+        <v>22900</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>379</v>
+        <v>238</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>1670</v>
+        <v>937</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>4.24</v>
+        <v>4.39</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="I36" s="1" t="n">
         <v>0</v>
@@ -2451,19 +2451,19 @@
         </is>
       </c>
       <c r="K36" s="1" t="n">
-        <v>72</v>
+        <v>74.7</v>
       </c>
       <c r="L36" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>3030</v>
+        <v>1910</v>
       </c>
       <c r="N36" s="1" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O36" s="1" t="n">
-        <v>69100000</v>
+        <v>44600000</v>
       </c>
       <c r="P36" s="1" t="inlineStr">
         <is>
@@ -2479,49 +2479,49 @@
         <v>9</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>252000</v>
+        <v>30500</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>629</v>
+        <v>318</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>3150</v>
+        <v>1340</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>6.92</v>
+        <v>4.42</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>3.46</v>
+        <v>2.21</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>13.84</v>
+        <v>8.85</v>
       </c>
       <c r="I37" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K37" s="1" t="n">
-        <v>117.6</v>
+        <v>75.2</v>
       </c>
       <c r="L37" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>5030</v>
+        <v>2540</v>
       </c>
       <c r="N37" s="1" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="O37" s="1" t="n">
-        <v>115000000</v>
+        <v>59500000</v>
       </c>
       <c r="P37" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -2533,22 +2533,22 @@
         <v>9</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>247000</v>
+        <v>46000</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>616</v>
+        <v>479</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>3070</v>
+        <v>2240</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>3.18</v>
+        <v>3.34</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>6.35</v>
+        <v>6.68</v>
       </c>
       <c r="I38" s="1" t="n">
         <v>0</v>
@@ -2559,19 +2559,19 @@
         </is>
       </c>
       <c r="K38" s="1" t="n">
-        <v>90</v>
+        <v>94.7</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>36</v>
+        <v>37.9</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>4930</v>
+        <v>3840</v>
       </c>
       <c r="N38" s="1" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="O38" s="1" t="n">
-        <v>112000000</v>
+        <v>89800000</v>
       </c>
       <c r="P38" s="1" t="inlineStr">
         <is>
@@ -2587,49 +2587,49 @@
         <v>9</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>237000</v>
+        <v>60600</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>594</v>
+        <v>632</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>2930</v>
+        <v>3170</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>4.24</v>
+        <v>6.51</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>1.41</v>
+        <v>2.17</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>13.01</v>
       </c>
       <c r="I39" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="K39" s="1" t="n">
-        <v>72</v>
+        <v>110.6</v>
       </c>
       <c r="L39" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>4750</v>
+        <v>5060</v>
       </c>
       <c r="N39" s="1" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="O39" s="1" t="n">
-        <v>108000000</v>
+        <v>118000000</v>
       </c>
       <c r="P39" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
     </row>
@@ -2641,49 +2641,49 @@
         <v>9</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>263000</v>
+        <v>27600</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>657</v>
+        <v>288</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>3330</v>
+        <v>1190</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>4.24</v>
+        <v>4.52</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="I40" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J40" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="K40" s="1" t="n">
-        <v>72</v>
+        <v>76.8</v>
       </c>
       <c r="L40" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>5260</v>
+        <v>2310</v>
       </c>
       <c r="N40" s="1" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="O40" s="1" t="n">
-        <v>120000000</v>
+        <v>54000000</v>
       </c>
       <c r="P40" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
     </row>
@@ -2695,22 +2695,22 @@
         <v>9</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>291000</v>
+        <v>40000</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>728</v>
+        <v>417</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>3780</v>
+        <v>1890</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>4.24</v>
+        <v>4.55</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="I41" s="1" t="n">
         <v>0</v>
@@ -2721,19 +2721,19 @@
         </is>
       </c>
       <c r="K41" s="1" t="n">
-        <v>72</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="L41" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>5820</v>
+        <v>3340</v>
       </c>
       <c r="N41" s="1" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="O41" s="1" t="n">
-        <v>133000000</v>
+        <v>78100000</v>
       </c>
       <c r="P41" s="1" t="inlineStr">
         <is>
@@ -2749,22 +2749,22 @@
         <v>9</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>322000</v>
+        <v>57200</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>806</v>
+        <v>597</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>4290</v>
+        <v>2950</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>4.24</v>
+        <v>4.58</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>2.12</v>
+        <v>2.29</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>9.16</v>
       </c>
       <c r="I42" s="1" t="n">
         <v>0</v>
@@ -2775,19 +2775,19 @@
         </is>
       </c>
       <c r="K42" s="1" t="n">
-        <v>72</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="L42" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>6450</v>
+        <v>4770</v>
       </c>
       <c r="N42" s="1" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O42" s="1" t="n">
-        <v>147000000</v>
+        <v>112000000</v>
       </c>
       <c r="P42" s="1" t="inlineStr">
         <is>
@@ -2803,49 +2803,49 @@
         <v>9</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>464000</v>
+        <v>92300</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>1160</v>
+        <v>963</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>6770</v>
+        <v>5370</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>5.19</v>
+        <v>3.46</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>2.59</v>
+        <v>1.73</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>10.38</v>
+        <v>6.92</v>
       </c>
       <c r="I43" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J43" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="K43" s="1" t="n">
-        <v>147</v>
+        <v>98</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>58.8</v>
+        <v>39.2</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>9280</v>
+        <v>7710</v>
       </c>
       <c r="N43" s="1" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="O43" s="1" t="n">
-        <v>212000000</v>
+        <v>180000000</v>
       </c>
       <c r="P43" s="1" t="inlineStr">
         <is>
-          <t>보스 층 · 허들</t>
+          <t>보스 층 · 어려움</t>
         </is>
       </c>
     </row>
@@ -2857,49 +2857,49 @@
         <v>9</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>378000</v>
+        <v>114000</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>944</v>
+        <v>1190</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>5230</v>
+        <v>6960</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>4.24</v>
+        <v>4.65</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="I44" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J44" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K44" s="1" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="L44" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>7550</v>
+        <v>9480</v>
       </c>
       <c r="N44" s="1" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="O44" s="1" t="n">
-        <v>172000000</v>
+        <v>222000000</v>
       </c>
       <c r="P44" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -2911,22 +2911,22 @@
         <v>9</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>399000</v>
+        <v>146000</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>998</v>
+        <v>1530</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>5610</v>
+        <v>9540</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>4.24</v>
+        <v>4.68</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>9.35</v>
       </c>
       <c r="I45" s="1" t="n">
         <v>0</v>
@@ -2937,19 +2937,19 @@
         </is>
       </c>
       <c r="K45" s="1" t="n">
-        <v>72</v>
+        <v>79.5</v>
       </c>
       <c r="L45" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>7990</v>
+        <v>12200</v>
       </c>
       <c r="N45" s="1" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="O45" s="1" t="n">
-        <v>182000000</v>
+        <v>286000000</v>
       </c>
       <c r="P45" s="1" t="inlineStr">
         <is>
@@ -2965,49 +2965,49 @@
         <v>9</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>422000</v>
+        <v>238000</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>1060</v>
+        <v>2480</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>6020</v>
+        <v>17500</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>4.24</v>
+        <v>6.92</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>2.12</v>
+        <v>3.46</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>13.84</v>
       </c>
       <c r="I46" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J46" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="K46" s="1" t="n">
-        <v>72</v>
+        <v>117.6</v>
       </c>
       <c r="L46" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M46" s="1" t="n">
-        <v>8450</v>
+        <v>19800</v>
       </c>
       <c r="N46" s="1" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="O46" s="1" t="n">
-        <v>193000000</v>
+        <v>464000000</v>
       </c>
       <c r="P46" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
     </row>
@@ -3019,49 +3019,49 @@
         <v>9</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>447000</v>
+        <v>137000</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>1120</v>
+        <v>1430</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>6460</v>
+        <v>8770</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>4.24</v>
+        <v>4.74</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>9.48</v>
       </c>
       <c r="I47" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J47" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="K47" s="1" t="n">
-        <v>72</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="L47" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>8930</v>
+        <v>11400</v>
       </c>
       <c r="N47" s="1" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="O47" s="1" t="n">
-        <v>204000000</v>
+        <v>267000000</v>
       </c>
       <c r="P47" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
     </row>
@@ -3073,22 +3073,22 @@
         <v>9</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>543000</v>
+        <v>205000</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>1360</v>
+        <v>2140</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>8250</v>
+        <v>14600</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>3.18</v>
+        <v>3.58</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>6.35</v>
+        <v>7.16</v>
       </c>
       <c r="I48" s="1" t="n">
         <v>0</v>
@@ -3099,19 +3099,19 @@
         </is>
       </c>
       <c r="K48" s="1" t="n">
-        <v>90</v>
+        <v>101.4</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>36</v>
+        <v>40.6</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>10900</v>
+        <v>17100</v>
       </c>
       <c r="N48" s="1" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="O48" s="1" t="n">
-        <v>248000000</v>
+        <v>401000000</v>
       </c>
       <c r="P48" s="1" t="inlineStr">
         <is>
@@ -3127,49 +3127,49 @@
         <v>9</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>650000</v>
+        <v>234000</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>1620</v>
+        <v>2440</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>10300</v>
+        <v>17100</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>7.41</v>
+        <v>4.8</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>2.47</v>
+        <v>1.6</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>14.82</v>
+        <v>9.6</v>
       </c>
       <c r="I49" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J49" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K49" s="1" t="n">
-        <v>126</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="L49" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>13000</v>
+        <v>19500</v>
       </c>
       <c r="N49" s="1" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="O49" s="1" t="n">
-        <v>296000000</v>
+        <v>456000000</v>
       </c>
       <c r="P49" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -3181,49 +3181,49 @@
         <v>9</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>630000</v>
+        <v>300000</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>1570</v>
+        <v>3130</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>9920</v>
+        <v>23400</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>4.24</v>
+        <v>4.84</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>1.41</v>
+        <v>1.61</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="I50" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J50" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K50" s="1" t="n">
-        <v>72</v>
+        <v>82.2</v>
       </c>
       <c r="L50" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M50" s="1" t="n">
-        <v>12600</v>
+        <v>25100</v>
       </c>
       <c r="N50" s="1" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="O50" s="1" t="n">
-        <v>287000000</v>
+        <v>587000000</v>
       </c>
       <c r="P50" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -3235,22 +3235,22 @@
         <v>9</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>794000</v>
+        <v>383000</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>1980</v>
+        <v>4000</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>13200</v>
+        <v>31800</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>4.24</v>
+        <v>4.86</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>2.12</v>
+        <v>2.43</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="I51" s="1" t="n">
         <v>0</v>
@@ -3261,19 +3261,19 @@
         </is>
       </c>
       <c r="K51" s="1" t="n">
-        <v>72</v>
+        <v>82.7</v>
       </c>
       <c r="L51" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M51" s="1" t="n">
-        <v>15900</v>
+        <v>32000</v>
       </c>
       <c r="N51" s="1" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="O51" s="1" t="n">
-        <v>362000000</v>
+        <v>748000000</v>
       </c>
       <c r="P51" s="1" t="inlineStr">
         <is>
@@ -3289,49 +3289,49 @@
         <v>9</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>1000000</v>
+        <v>578000</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>2500</v>
+        <v>6030</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>17700</v>
+        <v>53100</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>4.24</v>
+        <v>7.41</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>2.12</v>
+        <v>3.71</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>14.82</v>
       </c>
       <c r="I52" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J52" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="K52" s="1" t="n">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="L52" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M52" s="1" t="n">
-        <v>20000</v>
+        <v>48200</v>
       </c>
       <c r="N52" s="1" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O52" s="1" t="n">
-        <v>456000000</v>
+        <v>1130000000</v>
       </c>
       <c r="P52" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
     </row>
@@ -3343,22 +3343,22 @@
         <v>9</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>1450000</v>
+        <v>359000</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>3630</v>
+        <v>3740</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>28100</v>
+        <v>29300</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>3.18</v>
+        <v>3.7</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>1.59</v>
+        <v>1.85</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>6.35</v>
+        <v>7.39</v>
       </c>
       <c r="I53" s="1" t="n">
         <v>0</v>
@@ -3369,19 +3369,19 @@
         </is>
       </c>
       <c r="K53" s="1" t="n">
-        <v>90</v>
+        <v>104.7</v>
       </c>
       <c r="L53" s="1" t="n">
-        <v>36</v>
+        <v>41.9</v>
       </c>
       <c r="M53" s="1" t="n">
-        <v>29000</v>
+        <v>29900</v>
       </c>
       <c r="N53" s="1" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O53" s="1" t="n">
-        <v>662000000</v>
+        <v>700000000</v>
       </c>
       <c r="P53" s="1" t="inlineStr">
         <is>
@@ -3397,22 +3397,22 @@
         <v>9</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>1590000</v>
+        <v>386000</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>3970</v>
+        <v>4020</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>31500</v>
+        <v>32000</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>4.24</v>
+        <v>4.96</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>1.41</v>
+        <v>1.65</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>9.92</v>
       </c>
       <c r="I54" s="1" t="n">
         <v>0</v>
@@ -3423,19 +3423,19 @@
         </is>
       </c>
       <c r="K54" s="1" t="n">
-        <v>72</v>
+        <v>84.3</v>
       </c>
       <c r="L54" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>31800</v>
+        <v>32200</v>
       </c>
       <c r="N54" s="1" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O54" s="1" t="n">
-        <v>725000000</v>
+        <v>753000000</v>
       </c>
       <c r="P54" s="1" t="inlineStr">
         <is>
@@ -3451,49 +3451,49 @@
         <v>9</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>2600000</v>
+        <v>467000</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>6510</v>
+        <v>4880</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>58500</v>
+        <v>40700</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>7.41</v>
+        <v>4.99</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>3.71</v>
+        <v>2.49</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>14.82</v>
+        <v>9.98</v>
       </c>
       <c r="I55" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J55" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K55" s="1" t="n">
-        <v>126</v>
+        <v>84.8</v>
       </c>
       <c r="L55" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M55" s="1" t="n">
-        <v>52100</v>
+        <v>39000</v>
       </c>
       <c r="N55" s="1" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="O55" s="1" t="n">
-        <v>1190000000</v>
+        <v>913000000</v>
       </c>
       <c r="P55" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -3505,49 +3505,49 @@
         <v>9</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>2290000</v>
+        <v>561000</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>5720</v>
+        <v>5850</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>49800</v>
+        <v>51200</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>4.24</v>
+        <v>5.02</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>10.05</v>
       </c>
       <c r="I56" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J56" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K56" s="1" t="n">
-        <v>72</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="L56" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M56" s="1" t="n">
-        <v>45800</v>
+        <v>46800</v>
       </c>
       <c r="N56" s="1" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="O56" s="1" t="n">
-        <v>1040000000</v>
+        <v>1100000000</v>
       </c>
       <c r="P56" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -3559,22 +3559,22 @@
         <v>9</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>2610000</v>
+        <v>668000</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>6540</v>
+        <v>6960</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>58800</v>
+        <v>63600</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>4.24</v>
+        <v>5.05</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>1.41</v>
+        <v>1.68</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>10.11</v>
       </c>
       <c r="I57" s="1" t="n">
         <v>0</v>
@@ -3585,19 +3585,19 @@
         </is>
       </c>
       <c r="K57" s="1" t="n">
-        <v>72</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="L57" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M57" s="1" t="n">
-        <v>52300</v>
+        <v>55700</v>
       </c>
       <c r="N57" s="1" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="O57" s="1" t="n">
-        <v>1190000000</v>
+        <v>1300000000</v>
       </c>
       <c r="P57" s="1" t="inlineStr">
         <is>
@@ -3613,22 +3613,22 @@
         <v>9</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>3440000</v>
+        <v>832000</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>8590</v>
+        <v>8670</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>82700</v>
+        <v>83700</v>
       </c>
       <c r="F58" s="1" t="n">
-        <v>3.18</v>
+        <v>3.81</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>1.06</v>
+        <v>1.27</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>6.35</v>
+        <v>7.62</v>
       </c>
       <c r="I58" s="1" t="n">
         <v>0</v>
@@ -3639,19 +3639,19 @@
         </is>
       </c>
       <c r="K58" s="1" t="n">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="L58" s="1" t="n">
-        <v>36</v>
+        <v>43.2</v>
       </c>
       <c r="M58" s="1" t="n">
-        <v>68700</v>
+        <v>69400</v>
       </c>
       <c r="N58" s="1" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O58" s="1" t="n">
-        <v>1570000000</v>
+        <v>1620000000</v>
       </c>
       <c r="P58" s="1" t="inlineStr">
         <is>
@@ -3667,49 +3667,49 @@
         <v>9</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>3410000</v>
+        <v>1020000</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>8530</v>
+        <v>10600</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>82000</v>
+        <v>108000</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>4.24</v>
+        <v>7.41</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>2.12</v>
+        <v>3.71</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>14.82</v>
       </c>
       <c r="I59" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J59" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="K59" s="1" t="n">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="L59" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M59" s="1" t="n">
-        <v>68300</v>
+        <v>84900</v>
       </c>
       <c r="N59" s="1" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="O59" s="1" t="n">
-        <v>1560000000</v>
+        <v>1990000000</v>
       </c>
       <c r="P59" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
     </row>
@@ -3721,49 +3721,49 @@
         <v>9</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>3900000</v>
+        <v>567000</v>
       </c>
       <c r="D60" s="1" t="n">
-        <v>9750</v>
+        <v>5910</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>96900</v>
+        <v>51800</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>4.24</v>
+        <v>5.15</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>10.29</v>
       </c>
       <c r="I60" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J60" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="K60" s="1" t="n">
-        <v>72</v>
+        <v>87.5</v>
       </c>
       <c r="L60" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M60" s="1" t="n">
-        <v>78000</v>
+        <v>47300</v>
       </c>
       <c r="N60" s="1" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O60" s="1" t="n">
-        <v>1780000000</v>
+        <v>1110000000</v>
       </c>
       <c r="P60" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
     </row>
@@ -3775,49 +3775,49 @@
         <v>9</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>5790000</v>
+        <v>820000</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>14500</v>
+        <v>8550</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>159000</v>
+        <v>82200</v>
       </c>
       <c r="F61" s="1" t="n">
-        <v>7.41</v>
+        <v>5.18</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>3.71</v>
+        <v>2.59</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>14.82</v>
+        <v>10.35</v>
       </c>
       <c r="I61" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J61" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K61" s="1" t="n">
-        <v>126</v>
+        <v>88</v>
       </c>
       <c r="L61" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M61" s="1" t="n">
-        <v>116000</v>
+        <v>68400</v>
       </c>
       <c r="N61" s="1" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="O61" s="1" t="n">
-        <v>2640000000</v>
+        <v>1600000000</v>
       </c>
       <c r="P61" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -3829,49 +3829,49 @@
         <v>9</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>5240000</v>
+        <v>1170000</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>13100</v>
+        <v>12200</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>140000</v>
+        <v>128000</v>
       </c>
       <c r="F62" s="1" t="n">
-        <v>4.24</v>
+        <v>5.21</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>2.12</v>
+        <v>2.61</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>10.42</v>
       </c>
       <c r="I62" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J62" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K62" s="1" t="n">
-        <v>72</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="L62" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M62" s="1" t="n">
-        <v>105000</v>
+        <v>97600</v>
       </c>
       <c r="N62" s="1" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="O62" s="1" t="n">
-        <v>2390000000</v>
+        <v>2290000000</v>
       </c>
       <c r="P62" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -3883,22 +3883,22 @@
         <v>9</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>7080000</v>
+        <v>1890000</v>
       </c>
       <c r="D63" s="1" t="n">
-        <v>17700</v>
+        <v>19700</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>204000</v>
+        <v>233000</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>3.18</v>
+        <v>3.93</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>1.06</v>
+        <v>1.31</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>6.35</v>
+        <v>7.86</v>
       </c>
       <c r="I63" s="1" t="n">
         <v>0</v>
@@ -3909,19 +3909,19 @@
         </is>
       </c>
       <c r="K63" s="1" t="n">
-        <v>90</v>
+        <v>111.4</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>36</v>
+        <v>44.6</v>
       </c>
       <c r="M63" s="1" t="n">
-        <v>142000</v>
+        <v>157000</v>
       </c>
       <c r="N63" s="1" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="O63" s="1" t="n">
-        <v>3230000000</v>
+        <v>3690000000</v>
       </c>
       <c r="P63" s="1" t="inlineStr">
         <is>
@@ -3937,22 +3937,22 @@
         <v>9</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>7240000</v>
+        <v>2320000</v>
       </c>
       <c r="D64" s="1" t="n">
-        <v>18100</v>
+        <v>24200</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>210000</v>
+        <v>302000</v>
       </c>
       <c r="F64" s="1" t="n">
-        <v>4.24</v>
+        <v>5.27</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>1.41</v>
+        <v>1.76</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>10.54</v>
       </c>
       <c r="I64" s="1" t="n">
         <v>0</v>
@@ -3963,19 +3963,19 @@
         </is>
       </c>
       <c r="K64" s="1" t="n">
-        <v>72</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="L64" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M64" s="1" t="n">
-        <v>145000</v>
+        <v>194000</v>
       </c>
       <c r="N64" s="1" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O64" s="1" t="n">
-        <v>3300000000</v>
+        <v>4530000000</v>
       </c>
       <c r="P64" s="1" t="inlineStr">
         <is>
@@ -3991,22 +3991,22 @@
         <v>9</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>8520000</v>
+        <v>2980000</v>
       </c>
       <c r="D65" s="1" t="n">
-        <v>21300</v>
+        <v>31100</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>257000</v>
+        <v>413000</v>
       </c>
       <c r="F65" s="1" t="n">
-        <v>4.24</v>
+        <v>5.31</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>1.41</v>
+        <v>1.77</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>10.61</v>
       </c>
       <c r="I65" s="1" t="n">
         <v>0</v>
@@ -4017,19 +4017,19 @@
         </is>
       </c>
       <c r="K65" s="1" t="n">
-        <v>72</v>
+        <v>90.2</v>
       </c>
       <c r="L65" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M65" s="1" t="n">
-        <v>170000</v>
+        <v>249000</v>
       </c>
       <c r="N65" s="1" t="n">
         <v>59</v>
       </c>
       <c r="O65" s="1" t="n">
-        <v>3890000000</v>
+        <v>5830000000</v>
       </c>
       <c r="P65" s="1" t="inlineStr">
         <is>
@@ -4045,49 +4045,49 @@
         <v>9</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>10000000</v>
+        <v>4870000</v>
       </c>
       <c r="D66" s="1" t="n">
-        <v>25000</v>
+        <v>50800</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>315000</v>
+        <v>763000</v>
       </c>
       <c r="F66" s="1" t="n">
-        <v>4.24</v>
+        <v>7.41</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>1.41</v>
+        <v>2.47</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>14.82</v>
       </c>
       <c r="I66" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J66" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="K66" s="1" t="n">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="L66" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M66" s="1" t="n">
-        <v>200000</v>
+        <v>407000</v>
       </c>
       <c r="N66" s="1" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="O66" s="1" t="n">
-        <v>4570000000</v>
+        <v>9520000000</v>
       </c>
       <c r="P66" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
     </row>
@@ -4099,49 +4099,49 @@
         <v>9</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>15300000</v>
+        <v>2730000</v>
       </c>
       <c r="D67" s="1" t="n">
-        <v>38300</v>
+        <v>28500</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>535000</v>
+        <v>370000</v>
       </c>
       <c r="F67" s="1" t="n">
-        <v>7.41</v>
+        <v>5.36</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>2.47</v>
+        <v>1.79</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>14.82</v>
+        <v>10.73</v>
       </c>
       <c r="I67" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J67" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="K67" s="1" t="n">
-        <v>126</v>
+        <v>91.2</v>
       </c>
       <c r="L67" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M67" s="1" t="n">
-        <v>306000</v>
+        <v>228000</v>
       </c>
       <c r="N67" s="1" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O67" s="1" t="n">
-        <v>6990000000</v>
+        <v>5340000000</v>
       </c>
       <c r="P67" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>쉬움</t>
         </is>
       </c>
     </row>
@@ -4153,22 +4153,22 @@
         <v>9</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>14900000</v>
+        <v>4250000</v>
       </c>
       <c r="D68" s="1" t="n">
-        <v>37300</v>
+        <v>44300</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>519000</v>
+        <v>644000</v>
       </c>
       <c r="F68" s="1" t="n">
-        <v>3.18</v>
+        <v>4.05</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>1.06</v>
+        <v>1.35</v>
       </c>
       <c r="H68" s="1" t="n">
-        <v>6.35</v>
+        <v>8.1</v>
       </c>
       <c r="I68" s="1" t="n">
         <v>0</v>
@@ -4179,19 +4179,19 @@
         </is>
       </c>
       <c r="K68" s="1" t="n">
-        <v>90</v>
+        <v>114.7</v>
       </c>
       <c r="L68" s="1" t="n">
-        <v>36</v>
+        <v>45.9</v>
       </c>
       <c r="M68" s="1" t="n">
-        <v>299000</v>
+        <v>355000</v>
       </c>
       <c r="N68" s="1" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O68" s="1" t="n">
-        <v>6810000000</v>
+        <v>8300000000</v>
       </c>
       <c r="P68" s="1" t="inlineStr">
         <is>
@@ -4207,22 +4207,22 @@
         <v>9</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>14300000</v>
+        <v>5020000</v>
       </c>
       <c r="D69" s="1" t="n">
-        <v>35800</v>
+        <v>52400</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>492000</v>
+        <v>793000</v>
       </c>
       <c r="F69" s="1" t="n">
-        <v>4.24</v>
+        <v>5.43</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>2.12</v>
+        <v>2.71</v>
       </c>
       <c r="H69" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>10.86</v>
       </c>
       <c r="I69" s="1" t="n">
         <v>0</v>
@@ -4233,19 +4233,19 @@
         </is>
       </c>
       <c r="K69" s="1" t="n">
-        <v>72</v>
+        <v>92.3</v>
       </c>
       <c r="L69" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M69" s="1" t="n">
-        <v>286000</v>
+        <v>419000</v>
       </c>
       <c r="N69" s="1" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O69" s="1" t="n">
-        <v>6530000000</v>
+        <v>9810000000</v>
       </c>
       <c r="P69" s="1" t="inlineStr">
         <is>
@@ -4261,22 +4261,22 @@
         <v>9</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>15800000</v>
+        <v>6710000</v>
       </c>
       <c r="D70" s="1" t="n">
-        <v>39400</v>
+        <v>69900</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>556000</v>
+        <v>1140000</v>
       </c>
       <c r="F70" s="1" t="n">
-        <v>4.24</v>
+        <v>5.46</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>1.41</v>
+        <v>1.82</v>
       </c>
       <c r="H70" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>10.92</v>
       </c>
       <c r="I70" s="1" t="n">
         <v>0</v>
@@ -4287,19 +4287,19 @@
         </is>
       </c>
       <c r="K70" s="1" t="n">
-        <v>72</v>
+        <v>92.8</v>
       </c>
       <c r="L70" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M70" s="1" t="n">
-        <v>315000</v>
+        <v>560000</v>
       </c>
       <c r="N70" s="1" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O70" s="1" t="n">
-        <v>7200000000</v>
+        <v>13100000000</v>
       </c>
       <c r="P70" s="1" t="inlineStr">
         <is>
@@ -4315,22 +4315,22 @@
         <v>9</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>17400000</v>
+        <v>8870000</v>
       </c>
       <c r="D71" s="1" t="n">
-        <v>43500</v>
+        <v>92600</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>628000</v>
+        <v>1610000</v>
       </c>
       <c r="F71" s="1" t="n">
-        <v>4.24</v>
+        <v>5.49</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>2.12</v>
+        <v>2.75</v>
       </c>
       <c r="H71" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>10.99</v>
       </c>
       <c r="I71" s="1" t="n">
         <v>0</v>
@@ -4341,19 +4341,19 @@
         </is>
       </c>
       <c r="K71" s="1" t="n">
-        <v>72</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="L71" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M71" s="1" t="n">
-        <v>348000</v>
+        <v>740000</v>
       </c>
       <c r="N71" s="1" t="n">
         <v>65</v>
       </c>
       <c r="O71" s="1" t="n">
-        <v>7930000000</v>
+        <v>17300000000</v>
       </c>
       <c r="P71" s="1" t="inlineStr">
         <is>
@@ -4369,49 +4369,49 @@
         <v>9</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>19200000</v>
+        <v>13600000</v>
       </c>
       <c r="D72" s="1" t="n">
-        <v>47900</v>
+        <v>142000</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>709000</v>
+        <v>2750000</v>
       </c>
       <c r="F72" s="1" t="n">
-        <v>4.24</v>
+        <v>7.41</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>2.12</v>
+        <v>3.71</v>
       </c>
       <c r="H72" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>14.82</v>
       </c>
       <c r="I72" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J72" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="K72" s="1" t="n">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="L72" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M72" s="1" t="n">
-        <v>383000</v>
+        <v>1130000</v>
       </c>
       <c r="N72" s="1" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="O72" s="1" t="n">
-        <v>8740000000</v>
+        <v>26600000000</v>
       </c>
       <c r="P72" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
     </row>
@@ -4423,49 +4423,49 @@
         <v>9</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>27500000</v>
+        <v>9000000</v>
       </c>
       <c r="D73" s="1" t="n">
-        <v>68600</v>
+        <v>93800</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>1110000</v>
+        <v>1640000</v>
       </c>
       <c r="F73" s="1" t="n">
-        <v>5.56</v>
+        <v>4.16</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>2.78</v>
+        <v>2.08</v>
       </c>
       <c r="H73" s="1" t="n">
-        <v>11.12</v>
+        <v>8.33</v>
       </c>
       <c r="I73" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J73" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="K73" s="1" t="n">
-        <v>157.5</v>
+        <v>118</v>
       </c>
       <c r="L73" s="1" t="n">
-        <v>63</v>
+        <v>47.2</v>
       </c>
       <c r="M73" s="1" t="n">
-        <v>549000</v>
+        <v>751000</v>
       </c>
       <c r="N73" s="1" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O73" s="1" t="n">
-        <v>12500000000</v>
+        <v>17600000000</v>
       </c>
       <c r="P73" s="1" t="inlineStr">
         <is>
-          <t>보스 층 · 허들</t>
+          <t>보스 층 · 어려움</t>
         </is>
       </c>
     </row>
@@ -4477,49 +4477,49 @@
         <v>9</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>22400000</v>
+        <v>11000000</v>
       </c>
       <c r="D74" s="1" t="n">
-        <v>56000</v>
+        <v>115000</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>861000</v>
+        <v>2110000</v>
       </c>
       <c r="F74" s="1" t="n">
-        <v>4.24</v>
+        <v>5.59</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>1.41</v>
+        <v>1.86</v>
       </c>
       <c r="H74" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>11.18</v>
       </c>
       <c r="I74" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J74" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K74" s="1" t="n">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="L74" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M74" s="1" t="n">
-        <v>448000</v>
+        <v>918000</v>
       </c>
       <c r="N74" s="1" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O74" s="1" t="n">
-        <v>10200000000</v>
+        <v>21500000000</v>
       </c>
       <c r="P74" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -4531,22 +4531,22 @@
         <v>9</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>23700000</v>
+        <v>15200000</v>
       </c>
       <c r="D75" s="1" t="n">
-        <v>59300</v>
+        <v>158000</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>926000</v>
+        <v>3150000</v>
       </c>
       <c r="F75" s="1" t="n">
-        <v>4.24</v>
+        <v>5.62</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>1.41</v>
+        <v>1.87</v>
       </c>
       <c r="H75" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>11.24</v>
       </c>
       <c r="I75" s="1" t="n">
         <v>0</v>
@@ -4557,19 +4557,19 @@
         </is>
       </c>
       <c r="K75" s="1" t="n">
-        <v>72</v>
+        <v>95.5</v>
       </c>
       <c r="L75" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M75" s="1" t="n">
-        <v>475000</v>
+        <v>1260000</v>
       </c>
       <c r="N75" s="1" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O75" s="1" t="n">
-        <v>10800000000</v>
+        <v>29600000000</v>
       </c>
       <c r="P75" s="1" t="inlineStr">
         <is>
@@ -4585,22 +4585,22 @@
         <v>9</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>25200000</v>
+        <v>20700000</v>
       </c>
       <c r="D76" s="1" t="n">
-        <v>62900</v>
+        <v>216000</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>996000</v>
+        <v>4650000</v>
       </c>
       <c r="F76" s="1" t="n">
-        <v>4.24</v>
+        <v>5.65</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>1.41</v>
+        <v>1.88</v>
       </c>
       <c r="H76" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>11.29</v>
       </c>
       <c r="I76" s="1" t="n">
         <v>0</v>
@@ -4611,19 +4611,19 @@
         </is>
       </c>
       <c r="K76" s="1" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="L76" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M76" s="1" t="n">
-        <v>503000</v>
+        <v>1730000</v>
       </c>
       <c r="N76" s="1" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O76" s="1" t="n">
-        <v>11500000000</v>
+        <v>40400000000</v>
       </c>
       <c r="P76" s="1" t="inlineStr">
         <is>
@@ -4639,22 +4639,22 @@
         <v>9</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>26700000</v>
+        <v>28000000</v>
       </c>
       <c r="D77" s="1" t="n">
-        <v>66700</v>
+        <v>292000</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>1070000</v>
+        <v>6780000</v>
       </c>
       <c r="F77" s="1" t="n">
-        <v>4.24</v>
+        <v>5.68</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>1.41</v>
+        <v>1.89</v>
       </c>
       <c r="H77" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>11.36</v>
       </c>
       <c r="I77" s="1" t="n">
         <v>0</v>
@@ -4665,19 +4665,19 @@
         </is>
       </c>
       <c r="K77" s="1" t="n">
-        <v>72</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="L77" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M77" s="1" t="n">
-        <v>534000</v>
+        <v>2330000</v>
       </c>
       <c r="N77" s="1" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O77" s="1" t="n">
-        <v>12200000000</v>
+        <v>54600000000</v>
       </c>
       <c r="P77" s="1" t="inlineStr">
         <is>
@@ -4693,49 +4693,49 @@
         <v>9</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>32500000</v>
+        <v>45000000</v>
       </c>
       <c r="D78" s="1" t="n">
-        <v>81300</v>
+        <v>470000</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>1370000</v>
+        <v>12300000</v>
       </c>
       <c r="F78" s="1" t="n">
-        <v>3.18</v>
+        <v>5.48</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>1.06</v>
+        <v>1.83</v>
       </c>
       <c r="H78" s="1" t="n">
-        <v>6.35</v>
+        <v>10.97</v>
       </c>
       <c r="I78" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J78" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="K78" s="1" t="n">
-        <v>90</v>
+        <v>155.4</v>
       </c>
       <c r="L78" s="1" t="n">
-        <v>36</v>
+        <v>62.2</v>
       </c>
       <c r="M78" s="1" t="n">
-        <v>650000</v>
+        <v>3760000</v>
       </c>
       <c r="N78" s="1" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="O78" s="1" t="n">
-        <v>14800000000</v>
+        <v>87900000000</v>
       </c>
       <c r="P78" s="1" t="inlineStr">
         <is>
-          <t>보스 층 · 어려움</t>
+          <t>보스 층 · 허들</t>
         </is>
       </c>
     </row>
@@ -4747,49 +4747,49 @@
         <v>9</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>30000000</v>
+        <v>38600000</v>
       </c>
       <c r="D79" s="1" t="n">
-        <v>74900</v>
+        <v>403000</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>1240000</v>
+        <v>10100000</v>
       </c>
       <c r="F79" s="1" t="n">
-        <v>4.24</v>
+        <v>5.74</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>1.41</v>
+        <v>1.91</v>
       </c>
       <c r="H79" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>11.48</v>
       </c>
       <c r="I79" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J79" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="K79" s="1" t="n">
-        <v>72</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="L79" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M79" s="1" t="n">
-        <v>600000</v>
+        <v>3220000</v>
       </c>
       <c r="N79" s="1" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="O79" s="1" t="n">
-        <v>13700000000</v>
+        <v>75400000000</v>
       </c>
       <c r="P79" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
     </row>
@@ -4801,49 +4801,49 @@
         <v>9</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>41300000</v>
+        <v>52100000</v>
       </c>
       <c r="D80" s="1" t="n">
-        <v>103000</v>
+        <v>544000</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>1850000</v>
+        <v>14800000</v>
       </c>
       <c r="F80" s="1" t="n">
-        <v>7.41</v>
+        <v>5.78</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>2.47</v>
+        <v>1.93</v>
       </c>
       <c r="H80" s="1" t="n">
-        <v>14.82</v>
+        <v>11.55</v>
       </c>
       <c r="I80" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J80" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K80" s="1" t="n">
-        <v>126</v>
+        <v>98.2</v>
       </c>
       <c r="L80" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M80" s="1" t="n">
-        <v>826000</v>
+        <v>4350000</v>
       </c>
       <c r="N80" s="1" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="O80" s="1" t="n">
-        <v>18900000000</v>
+        <v>102000000000</v>
       </c>
       <c r="P80" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -4855,49 +4855,49 @@
         <v>9</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>33600000</v>
+        <v>69600000</v>
       </c>
       <c r="D81" s="1" t="n">
-        <v>83900</v>
+        <v>726000</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>1430000</v>
+        <v>21200000</v>
       </c>
       <c r="F81" s="1" t="n">
-        <v>4.24</v>
+        <v>5.81</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>1.41</v>
+        <v>1.94</v>
       </c>
       <c r="H81" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>11.61</v>
       </c>
       <c r="I81" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J81" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K81" s="1" t="n">
-        <v>72</v>
+        <v>98.7</v>
       </c>
       <c r="L81" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M81" s="1" t="n">
-        <v>671000</v>
+        <v>5810000</v>
       </c>
       <c r="N81" s="1" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="O81" s="1" t="n">
-        <v>15300000000</v>
+        <v>136000000000</v>
       </c>
       <c r="P81" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -4909,22 +4909,22 @@
         <v>9</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>35400000</v>
+        <v>91900000</v>
       </c>
       <c r="D82" s="1" t="n">
-        <v>88600</v>
+        <v>959000</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>1530000</v>
+        <v>30000000</v>
       </c>
       <c r="F82" s="1" t="n">
-        <v>4.24</v>
+        <v>5.84</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>1.41</v>
+        <v>1.95</v>
       </c>
       <c r="H82" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>11.67</v>
       </c>
       <c r="I82" s="1" t="n">
         <v>0</v>
@@ -4935,19 +4935,19 @@
         </is>
       </c>
       <c r="K82" s="1" t="n">
-        <v>72</v>
+        <v>99.2</v>
       </c>
       <c r="L82" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M82" s="1" t="n">
-        <v>709000</v>
+        <v>7670000</v>
       </c>
       <c r="N82" s="1" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="O82" s="1" t="n">
-        <v>16200000000</v>
+        <v>180000000000</v>
       </c>
       <c r="P82" s="1" t="inlineStr">
         <is>
@@ -4963,49 +4963,49 @@
         <v>9</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>43000000</v>
+        <v>144000000</v>
       </c>
       <c r="D83" s="1" t="n">
-        <v>108000</v>
+        <v>1510000</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>1950000</v>
+        <v>52800000</v>
       </c>
       <c r="F83" s="1" t="n">
-        <v>3.18</v>
+        <v>5.56</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>1.59</v>
+        <v>2.78</v>
       </c>
       <c r="H83" s="1" t="n">
-        <v>6.35</v>
+        <v>11.12</v>
       </c>
       <c r="I83" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J83" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="K83" s="1" t="n">
-        <v>90</v>
+        <v>157.5</v>
       </c>
       <c r="L83" s="1" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="M83" s="1" t="n">
-        <v>861000</v>
+        <v>12100000</v>
       </c>
       <c r="N83" s="1" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="O83" s="1" t="n">
-        <v>19600000000</v>
+        <v>282000000000</v>
       </c>
       <c r="P83" s="1" t="inlineStr">
         <is>
-          <t>보스 층 · 어려움</t>
+          <t>보스 층 · 허들</t>
         </is>
       </c>
     </row>
@@ -5017,49 +5017,49 @@
         <v>9</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>39500000</v>
+        <v>138000000</v>
       </c>
       <c r="D84" s="1" t="n">
-        <v>98800</v>
+        <v>1430000</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>1750000</v>
+        <v>49700000</v>
       </c>
       <c r="F84" s="1" t="n">
-        <v>4.24</v>
+        <v>5.9</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>1.41</v>
+        <v>1.97</v>
       </c>
       <c r="H84" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>11.8</v>
       </c>
       <c r="I84" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J84" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="K84" s="1" t="n">
-        <v>72</v>
+        <v>100.3</v>
       </c>
       <c r="L84" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M84" s="1" t="n">
-        <v>790000</v>
+        <v>11500000</v>
       </c>
       <c r="N84" s="1" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="O84" s="1" t="n">
-        <v>18000000000</v>
+        <v>269000000000</v>
       </c>
       <c r="P84" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
     </row>
@@ -5071,22 +5071,22 @@
         <v>9</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>41700000</v>
+        <v>178000000</v>
       </c>
       <c r="D85" s="1" t="n">
-        <v>104000</v>
+        <v>1860000</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>1870000</v>
+        <v>68500000</v>
       </c>
       <c r="F85" s="1" t="n">
-        <v>4.24</v>
+        <v>5.93</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>1.41</v>
+        <v>1.98</v>
       </c>
       <c r="H85" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>11.86</v>
       </c>
       <c r="I85" s="1" t="n">
         <v>0</v>
@@ -5097,19 +5097,19 @@
         </is>
       </c>
       <c r="K85" s="1" t="n">
-        <v>72</v>
+        <v>100.8</v>
       </c>
       <c r="L85" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M85" s="1" t="n">
-        <v>834000</v>
+        <v>14800000</v>
       </c>
       <c r="N85" s="1" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O85" s="1" t="n">
-        <v>19000000000</v>
+        <v>347000000000</v>
       </c>
       <c r="P85" s="1" t="inlineStr">
         <is>
@@ -5125,22 +5125,22 @@
         <v>9</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>44000000</v>
+        <v>227000000</v>
       </c>
       <c r="D86" s="1" t="n">
-        <v>110000</v>
+        <v>2370000</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>2010000</v>
+        <v>92900000</v>
       </c>
       <c r="F86" s="1" t="n">
-        <v>4.24</v>
+        <v>5.96</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>1.41</v>
+        <v>1.99</v>
       </c>
       <c r="H86" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>11.93</v>
       </c>
       <c r="I86" s="1" t="n">
         <v>0</v>
@@ -5151,19 +5151,19 @@
         </is>
       </c>
       <c r="K86" s="1" t="n">
-        <v>72</v>
+        <v>101.4</v>
       </c>
       <c r="L86" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M86" s="1" t="n">
-        <v>881000</v>
+        <v>19000000</v>
       </c>
       <c r="N86" s="1" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O86" s="1" t="n">
-        <v>20100000000</v>
+        <v>444000000000</v>
       </c>
       <c r="P86" s="1" t="inlineStr">
         <is>
@@ -5179,49 +5179,49 @@
         <v>9</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>60500000</v>
+        <v>287000000</v>
       </c>
       <c r="D87" s="1" t="n">
-        <v>151000</v>
+        <v>3000000</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>2980000</v>
+        <v>125000000</v>
       </c>
       <c r="F87" s="1" t="n">
-        <v>7.41</v>
+        <v>5.99</v>
       </c>
       <c r="G87" s="1" t="n">
-        <v>2.47</v>
+        <v>2</v>
       </c>
       <c r="H87" s="1" t="n">
-        <v>14.82</v>
+        <v>11.99</v>
       </c>
       <c r="I87" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J87" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K87" s="1" t="n">
-        <v>126</v>
+        <v>101.9</v>
       </c>
       <c r="L87" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M87" s="1" t="n">
-        <v>1210000</v>
+        <v>24000000</v>
       </c>
       <c r="N87" s="1" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O87" s="1" t="n">
-        <v>27600000000</v>
+        <v>561000000000</v>
       </c>
       <c r="P87" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -5233,49 +5233,49 @@
         <v>9</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>56200000</v>
+        <v>433000000</v>
       </c>
       <c r="D88" s="1" t="n">
-        <v>140000</v>
+        <v>4520000</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>2720000</v>
+        <v>208000000</v>
       </c>
       <c r="F88" s="1" t="n">
-        <v>3.18</v>
+        <v>5.63</v>
       </c>
       <c r="G88" s="1" t="n">
-        <v>1.06</v>
+        <v>1.88</v>
       </c>
       <c r="H88" s="1" t="n">
-        <v>6.35</v>
+        <v>11.27</v>
       </c>
       <c r="I88" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J88" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="K88" s="1" t="n">
-        <v>90</v>
+        <v>159.6</v>
       </c>
       <c r="L88" s="1" t="n">
-        <v>36</v>
+        <v>63.8</v>
       </c>
       <c r="M88" s="1" t="n">
-        <v>1120000</v>
+        <v>36100000</v>
       </c>
       <c r="N88" s="1" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O88" s="1" t="n">
-        <v>25600000000</v>
+        <v>845000000000</v>
       </c>
       <c r="P88" s="1" t="inlineStr">
         <is>
-          <t>보스 층 · 어려움</t>
+          <t>보스 층 · 허들</t>
         </is>
       </c>
     </row>
@@ -5287,49 +5287,49 @@
         <v>9</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>51300000</v>
+        <v>422000000</v>
       </c>
       <c r="D89" s="1" t="n">
-        <v>128000</v>
+        <v>4400000</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>2430000</v>
+        <v>202000000</v>
       </c>
       <c r="F89" s="1" t="n">
-        <v>4.24</v>
+        <v>6.06</v>
       </c>
       <c r="G89" s="1" t="n">
-        <v>2.12</v>
+        <v>3.03</v>
       </c>
       <c r="H89" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>12.12</v>
       </c>
       <c r="I89" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J89" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="K89" s="1" t="n">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="L89" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M89" s="1" t="n">
-        <v>1030000</v>
+        <v>35200000</v>
       </c>
       <c r="N89" s="1" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O89" s="1" t="n">
-        <v>23400000000</v>
+        <v>825000000000</v>
       </c>
       <c r="P89" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
     </row>
@@ -5341,22 +5341,22 @@
         <v>9</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>53900000</v>
+        <v>542000000</v>
       </c>
       <c r="D90" s="1" t="n">
-        <v>135000</v>
+        <v>5650000</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>2580000</v>
+        <v>276000000</v>
       </c>
       <c r="F90" s="1" t="n">
-        <v>4.24</v>
+        <v>6.09</v>
       </c>
       <c r="G90" s="1" t="n">
-        <v>1.41</v>
+        <v>2.03</v>
       </c>
       <c r="H90" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>12.18</v>
       </c>
       <c r="I90" s="1" t="n">
         <v>0</v>
@@ -5367,19 +5367,19 @@
         </is>
       </c>
       <c r="K90" s="1" t="n">
-        <v>72</v>
+        <v>103.5</v>
       </c>
       <c r="L90" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M90" s="1" t="n">
-        <v>1080000</v>
+        <v>45200000</v>
       </c>
       <c r="N90" s="1" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O90" s="1" t="n">
-        <v>24600000000</v>
+        <v>1060000000000</v>
       </c>
       <c r="P90" s="1" t="inlineStr">
         <is>
@@ -5395,22 +5395,22 @@
         <v>9</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>56600000</v>
+        <v>688000000</v>
       </c>
       <c r="D91" s="1" t="n">
-        <v>142000</v>
+        <v>7170000</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>2750000</v>
+        <v>371000000</v>
       </c>
       <c r="F91" s="1" t="n">
-        <v>4.24</v>
+        <v>6.12</v>
       </c>
       <c r="G91" s="1" t="n">
-        <v>1.41</v>
+        <v>2.04</v>
       </c>
       <c r="H91" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>12.24</v>
       </c>
       <c r="I91" s="1" t="n">
         <v>0</v>
@@ -5421,19 +5421,19 @@
         </is>
       </c>
       <c r="K91" s="1" t="n">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="L91" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M91" s="1" t="n">
-        <v>1130000</v>
+        <v>57400000</v>
       </c>
       <c r="N91" s="1" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O91" s="1" t="n">
-        <v>25800000000</v>
+        <v>1340000000000</v>
       </c>
       <c r="P91" s="1" t="inlineStr">
         <is>
@@ -5449,22 +5449,22 @@
         <v>9</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>59500000</v>
+        <v>863000000</v>
       </c>
       <c r="D92" s="1" t="n">
-        <v>149000</v>
+        <v>9000000</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>2920000</v>
+        <v>493000000</v>
       </c>
       <c r="F92" s="1" t="n">
-        <v>4.24</v>
+        <v>6.15</v>
       </c>
       <c r="G92" s="1" t="n">
-        <v>1.41</v>
+        <v>2.05</v>
       </c>
       <c r="H92" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>12.31</v>
       </c>
       <c r="I92" s="1" t="n">
         <v>0</v>
@@ -5475,19 +5475,19 @@
         </is>
       </c>
       <c r="K92" s="1" t="n">
-        <v>72</v>
+        <v>104.6</v>
       </c>
       <c r="L92" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M92" s="1" t="n">
-        <v>1190000</v>
+        <v>72000000</v>
       </c>
       <c r="N92" s="1" t="n">
         <v>86</v>
       </c>
       <c r="O92" s="1" t="n">
-        <v>27100000000</v>
+        <v>1690000000000</v>
       </c>
       <c r="P92" s="1" t="inlineStr">
         <is>
@@ -5503,49 +5503,49 @@
         <v>9</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>71800000</v>
+        <v>1290000000</v>
       </c>
       <c r="D93" s="1" t="n">
-        <v>180000</v>
+        <v>13500000</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>3700000</v>
+        <v>819000000</v>
       </c>
       <c r="F93" s="1" t="n">
-        <v>3.18</v>
+        <v>5.71</v>
       </c>
       <c r="G93" s="1" t="n">
-        <v>1.06</v>
+        <v>1.9</v>
       </c>
       <c r="H93" s="1" t="n">
-        <v>6.35</v>
+        <v>11.41</v>
       </c>
       <c r="I93" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J93" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="K93" s="1" t="n">
-        <v>90</v>
+        <v>161.7</v>
       </c>
       <c r="L93" s="1" t="n">
-        <v>36</v>
+        <v>64.7</v>
       </c>
       <c r="M93" s="1" t="n">
-        <v>1440000</v>
+        <v>108000000</v>
       </c>
       <c r="N93" s="1" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="O93" s="1" t="n">
-        <v>32800000000</v>
+        <v>2530000000000</v>
       </c>
       <c r="P93" s="1" t="inlineStr">
         <is>
-          <t>보스 층 · 어려움</t>
+          <t>보스 층 · 허들</t>
         </is>
       </c>
     </row>
@@ -5557,49 +5557,49 @@
         <v>9</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>65600000</v>
+        <v>1290000000</v>
       </c>
       <c r="D94" s="1" t="n">
-        <v>164000</v>
+        <v>13500000</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>3300000</v>
+        <v>817000000</v>
       </c>
       <c r="F94" s="1" t="n">
-        <v>4.24</v>
+        <v>6.21</v>
       </c>
       <c r="G94" s="1" t="n">
-        <v>1.41</v>
+        <v>2.07</v>
       </c>
       <c r="H94" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>12.42</v>
       </c>
       <c r="I94" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J94" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="K94" s="1" t="n">
-        <v>72</v>
+        <v>105.6</v>
       </c>
       <c r="L94" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M94" s="1" t="n">
-        <v>1310000</v>
+        <v>108000000</v>
       </c>
       <c r="N94" s="1" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="O94" s="1" t="n">
-        <v>29900000000</v>
+        <v>2530000000000</v>
       </c>
       <c r="P94" s="1" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
     </row>
@@ -5611,49 +5611,49 @@
         <v>9</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>89600000</v>
+        <v>1550000000</v>
       </c>
       <c r="D95" s="1" t="n">
-        <v>224000</v>
+        <v>16200000</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>4870000</v>
+        <v>1020000000</v>
       </c>
       <c r="F95" s="1" t="n">
-        <v>7.41</v>
+        <v>6.25</v>
       </c>
       <c r="G95" s="1" t="n">
-        <v>2.47</v>
+        <v>2.08</v>
       </c>
       <c r="H95" s="1" t="n">
-        <v>14.82</v>
+        <v>12.49</v>
       </c>
       <c r="I95" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J95" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K95" s="1" t="n">
-        <v>126</v>
+        <v>106.2</v>
       </c>
       <c r="L95" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M95" s="1" t="n">
-        <v>1790000</v>
+        <v>129000000</v>
       </c>
       <c r="N95" s="1" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="O95" s="1" t="n">
-        <v>40900000000</v>
+        <v>3020000000000</v>
       </c>
       <c r="P95" s="1" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -5665,49 +5665,49 @@
         <v>9</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>71000000</v>
+        <v>1830000000</v>
       </c>
       <c r="D96" s="1" t="n">
-        <v>177000</v>
+        <v>19100000</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>3640000</v>
+        <v>1260000000</v>
       </c>
       <c r="F96" s="1" t="n">
-        <v>4.24</v>
+        <v>6.28</v>
       </c>
       <c r="G96" s="1" t="n">
-        <v>1.41</v>
+        <v>2.09</v>
       </c>
       <c r="H96" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>12.55</v>
       </c>
       <c r="I96" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J96" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K96" s="1" t="n">
-        <v>72</v>
+        <v>106.7</v>
       </c>
       <c r="L96" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M96" s="1" t="n">
-        <v>1420000</v>
+        <v>153000000</v>
       </c>
       <c r="N96" s="1" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="O96" s="1" t="n">
-        <v>32400000000</v>
+        <v>3580000000000</v>
       </c>
       <c r="P96" s="1" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
     </row>
@@ -5719,22 +5719,22 @@
         <v>9</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>84100000</v>
+        <v>2450000000</v>
       </c>
       <c r="D97" s="1" t="n">
-        <v>210000</v>
+        <v>25500000</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>4500000</v>
+        <v>1820000000</v>
       </c>
       <c r="F97" s="1" t="n">
-        <v>3.18</v>
+        <v>4.73</v>
       </c>
       <c r="G97" s="1" t="n">
-        <v>1.59</v>
+        <v>2.37</v>
       </c>
       <c r="H97" s="1" t="n">
-        <v>6.35</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="I97" s="1" t="n">
         <v>0</v>
@@ -5745,19 +5745,19 @@
         </is>
       </c>
       <c r="K97" s="1" t="n">
-        <v>90</v>
+        <v>134.1</v>
       </c>
       <c r="L97" s="1" t="n">
-        <v>36</v>
+        <v>53.6</v>
       </c>
       <c r="M97" s="1" t="n">
-        <v>1680000</v>
+        <v>204000000</v>
       </c>
       <c r="N97" s="1" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="O97" s="1" t="n">
-        <v>38400000000</v>
+        <v>4780000000000</v>
       </c>
       <c r="P97" s="1" t="inlineStr">
         <is>
@@ -5773,22 +5773,22 @@
         <v>9</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>75300000</v>
+        <v>2500000000</v>
       </c>
       <c r="D98" s="1" t="n">
-        <v>188000</v>
+        <v>26000000</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>3920000</v>
+        <v>1860000000</v>
       </c>
       <c r="F98" s="1" t="n">
-        <v>4.24</v>
+        <v>6.34</v>
       </c>
       <c r="G98" s="1" t="n">
-        <v>2.12</v>
+        <v>3.17</v>
       </c>
       <c r="H98" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>12.68</v>
       </c>
       <c r="I98" s="1" t="n">
         <v>0</v>
@@ -5799,19 +5799,19 @@
         </is>
       </c>
       <c r="K98" s="1" t="n">
-        <v>72</v>
+        <v>107.8</v>
       </c>
       <c r="L98" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M98" s="1" t="n">
-        <v>1510000</v>
+        <v>208000000</v>
       </c>
       <c r="N98" s="1" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="O98" s="1" t="n">
-        <v>34400000000</v>
+        <v>4870000000000</v>
       </c>
       <c r="P98" s="1" t="inlineStr">
         <is>
@@ -5827,22 +5827,22 @@
         <v>9</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>77600000</v>
+        <v>2880000000</v>
       </c>
       <c r="D99" s="1" t="n">
-        <v>194000</v>
+        <v>30000000</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>4070000</v>
+        <v>2220000000</v>
       </c>
       <c r="F99" s="1" t="n">
-        <v>4.24</v>
+        <v>6.37</v>
       </c>
       <c r="G99" s="1" t="n">
-        <v>1.41</v>
+        <v>2.12</v>
       </c>
       <c r="H99" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>12.74</v>
       </c>
       <c r="I99" s="1" t="n">
         <v>0</v>
@@ -5853,19 +5853,19 @@
         </is>
       </c>
       <c r="K99" s="1" t="n">
-        <v>72</v>
+        <v>108.3</v>
       </c>
       <c r="L99" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M99" s="1" t="n">
-        <v>1550000</v>
+        <v>240000000</v>
       </c>
       <c r="N99" s="1" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="O99" s="1" t="n">
-        <v>35400000000</v>
+        <v>5630000000000</v>
       </c>
       <c r="P99" s="1" t="inlineStr">
         <is>
@@ -5881,22 +5881,22 @@
         <v>9</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>91900000</v>
+        <v>3770000000</v>
       </c>
       <c r="D100" s="1" t="n">
-        <v>230000</v>
+        <v>39300000</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>5030000</v>
+        <v>3110000000</v>
       </c>
       <c r="F100" s="1" t="n">
-        <v>3.18</v>
+        <v>4.8</v>
       </c>
       <c r="G100" s="1" t="n">
-        <v>1.06</v>
+        <v>1.6</v>
       </c>
       <c r="H100" s="1" t="n">
-        <v>6.35</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="I100" s="1" t="n">
         <v>0</v>
@@ -5907,19 +5907,19 @@
         </is>
       </c>
       <c r="K100" s="1" t="n">
-        <v>90</v>
+        <v>136.1</v>
       </c>
       <c r="L100" s="1" t="n">
-        <v>36</v>
+        <v>54.4</v>
       </c>
       <c r="M100" s="1" t="n">
-        <v>1840000</v>
+        <v>314000000</v>
       </c>
       <c r="N100" s="1" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="O100" s="1" t="n">
-        <v>41900000000</v>
+        <v>7360000000000</v>
       </c>
       <c r="P100" s="1" t="inlineStr">
         <is>
@@ -5935,22 +5935,22 @@
         <v>9</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>82300000</v>
+        <v>3520000000</v>
       </c>
       <c r="D101" s="1" t="n">
-        <v>206000</v>
+        <v>36700000</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>4380000</v>
+        <v>2860000000</v>
       </c>
       <c r="F101" s="1" t="n">
-        <v>4.24</v>
+        <v>6.44</v>
       </c>
       <c r="G101" s="1" t="n">
-        <v>1.41</v>
+        <v>2.15</v>
       </c>
       <c r="H101" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>12.87</v>
       </c>
       <c r="I101" s="1" t="n">
         <v>0</v>
@@ -5961,19 +5961,19 @@
         </is>
       </c>
       <c r="K101" s="1" t="n">
-        <v>72</v>
+        <v>109.4</v>
       </c>
       <c r="L101" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M101" s="1" t="n">
-        <v>1650000</v>
+        <v>294000000</v>
       </c>
       <c r="N101" s="1" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="O101" s="1" t="n">
-        <v>37500000000</v>
+        <v>6880000000000</v>
       </c>
       <c r="P101" s="1" t="inlineStr">
         <is>
@@ -5989,22 +5989,22 @@
         <v>9</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>84800000</v>
+        <v>3750000000</v>
       </c>
       <c r="D102" s="1" t="n">
-        <v>212000</v>
+        <v>39200000</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>4550000</v>
+        <v>3100000000</v>
       </c>
       <c r="F102" s="1" t="n">
-        <v>4.24</v>
+        <v>6.46</v>
       </c>
       <c r="G102" s="1" t="n">
-        <v>1.41</v>
+        <v>2.15</v>
       </c>
       <c r="H102" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>12.93</v>
       </c>
       <c r="I102" s="1" t="n">
         <v>0</v>
@@ -6015,19 +6015,19 @@
         </is>
       </c>
       <c r="K102" s="1" t="n">
-        <v>72</v>
+        <v>109.9</v>
       </c>
       <c r="L102" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M102" s="1" t="n">
-        <v>1700000</v>
+        <v>313000000</v>
       </c>
       <c r="N102" s="1" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="O102" s="1" t="n">
-        <v>38700000000</v>
+        <v>7330000000000</v>
       </c>
       <c r="P102" s="1" t="inlineStr">
         <is>
@@ -6043,49 +6043,49 @@
         <v>9</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>122000000</v>
+        <v>4810000000</v>
       </c>
       <c r="D103" s="1" t="n">
-        <v>306000</v>
+        <v>50200000</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>7180000</v>
+        <v>4220000000</v>
       </c>
       <c r="F103" s="1" t="n">
-        <v>3.18</v>
+        <v>5.78</v>
       </c>
       <c r="G103" s="1" t="n">
-        <v>1.06</v>
+        <v>1.93</v>
       </c>
       <c r="H103" s="1" t="n">
-        <v>6.35</v>
+        <v>11.56</v>
       </c>
       <c r="I103" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J103" s="1" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="K103" s="1" t="n">
-        <v>90</v>
+        <v>163.8</v>
       </c>
       <c r="L103" s="1" t="n">
-        <v>36</v>
+        <v>65.5</v>
       </c>
       <c r="M103" s="1" t="n">
-        <v>2440000</v>
+        <v>402000000</v>
       </c>
       <c r="N103" s="1" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="O103" s="1" t="n">
-        <v>55800000000</v>
+        <v>9400000000000</v>
       </c>
       <c r="P103" s="1" t="inlineStr">
         <is>
-          <t>보스 층 · 어려움</t>
+          <t>보스 층 · 허들</t>
         </is>
       </c>
     </row>
